--- a/public/ArmyTable.xlsx
+++ b/public/ArmyTable.xlsx
@@ -6,32 +6,6 @@
     <sheet name="ArmyTable" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Admin</author>
-  </authors>
-  <commentList>
-    <comment ref="R4" authorId="0">
-      <text>
-        <t xml:space="preserve">Admin:
-Admin:
-格式为[[类型，类型编号，类型数值]]
-类型分为两种,
-1为全局属性
-11为兵种属性</t>
-      </text>
-    </comment>
-    <comment ref="T4" authorId="0">
-      <text>
-        <t xml:space="preserve">Admin:
-攻击范围最好根据碰撞半径设定，一个单位距离是Raduis * 100;</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
@@ -848,16 +822,16 @@
         <v>10001</v>
       </c>
       <c r="C5" t="str">
-        <v>关平🛡️ T1</v>
+        <v>关兴🛡️ T1</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G5">
         <v>0.4</v>
@@ -872,19 +846,19 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="P5" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -893,13 +867,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S5">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="T5">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U5">
-        <v>200</v>
+        <v>1224</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -961,16 +935,16 @@
         <v>10002</v>
       </c>
       <c r="C6" t="str">
-        <v>华雄🛡️ T1</v>
+        <v>刘封🛡️ T1</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6">
         <v>0.4</v>
@@ -985,19 +959,19 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="P6" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1009,10 +983,10 @@
         <v>76</v>
       </c>
       <c r="T6">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="U6">
-        <v>201</v>
+        <v>1200</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1074,16 +1048,16 @@
         <v>10003</v>
       </c>
       <c r="C7" t="str">
-        <v>周泰🛡️ T2</v>
+        <v>徐晃🛡️ T2</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G7">
         <v>0.4</v>
@@ -1098,19 +1072,19 @@
         <v>1</v>
       </c>
       <c r="K7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="N7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="P7" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1122,10 +1096,10 @@
         <v>77</v>
       </c>
       <c r="T7">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="U7">
-        <v>198</v>
+        <v>1302</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1187,16 +1161,16 @@
         <v>10004</v>
       </c>
       <c r="C8" t="str">
-        <v>丁奉🛡️ T2</v>
+        <v>于禁🛡️ T2</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>0.4</v>
@@ -1211,19 +1185,19 @@
         <v>1</v>
       </c>
       <c r="K8">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="L8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="P8" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1232,13 +1206,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T8">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="U8">
-        <v>184</v>
+        <v>1272</v>
       </c>
       <c r="W8">
         <v>0</v>
@@ -1300,16 +1274,16 @@
         <v>10005</v>
       </c>
       <c r="C9" t="str">
-        <v>甘宁🛡️ T3</v>
+        <v>孙策🛡️ T3</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G9">
         <v>0.4</v>
@@ -1324,19 +1298,19 @@
         <v>1</v>
       </c>
       <c r="K9">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="L9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M9">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="N9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O9">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="P9" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1348,10 +1322,10 @@
         <v>75</v>
       </c>
       <c r="T9">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U9">
-        <v>212</v>
+        <v>1302</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1413,16 +1387,16 @@
         <v>10006</v>
       </c>
       <c r="C10" t="str">
-        <v>关羽🛡️ T4</v>
+        <v>孙权🛡️ T4</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="G10">
         <v>0.4</v>
@@ -1437,19 +1411,19 @@
         <v>1</v>
       </c>
       <c r="K10">
-        <v>449</v>
+        <v>364</v>
       </c>
       <c r="L10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M10">
-        <v>449</v>
+        <v>364</v>
       </c>
       <c r="N10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O10">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="P10" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1458,13 +1432,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S10">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T10">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="U10">
-        <v>183</v>
+        <v>1182</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -1532,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G11">
         <v>0.4</v>
@@ -1550,19 +1524,19 @@
         <v>1</v>
       </c>
       <c r="K11">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="L11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M11">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="N11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O11">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="P11" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1571,13 +1545,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S11">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T11">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="U11">
-        <v>220</v>
+        <v>1086</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -1639,16 +1613,16 @@
         <v>20001</v>
       </c>
       <c r="C12" t="str">
-        <v>蒋钦⚔️ T1</v>
+        <v>王基⚔️ T1</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G12">
         <v>0.4</v>
@@ -1663,19 +1637,19 @@
         <v>1</v>
       </c>
       <c r="K12">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="L12">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M12">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="N12">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O12">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="P12" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1684,13 +1658,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S12">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T12">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="U12">
-        <v>217</v>
+        <v>1116</v>
       </c>
       <c r="W12">
         <v>4</v>
@@ -1752,16 +1726,16 @@
         <v>20002</v>
       </c>
       <c r="C13" t="str">
-        <v>朱然⚔️ T1</v>
+        <v>全琮⚔️ T1</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G13">
         <v>0.4</v>
@@ -1776,19 +1750,19 @@
         <v>1</v>
       </c>
       <c r="K13">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L13">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M13">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N13">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O13">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1797,13 +1771,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S13">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T13">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="U13">
-        <v>186</v>
+        <v>1248</v>
       </c>
       <c r="W13">
         <v>4</v>
@@ -1865,16 +1839,16 @@
         <v>20003</v>
       </c>
       <c r="C14" t="str">
-        <v>徐盛⚔️ T2</v>
+        <v>陈泰⚔️ T2</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G14">
         <v>0.4</v>
@@ -1889,19 +1863,19 @@
         <v>1</v>
       </c>
       <c r="K14">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="L14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M14">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="N14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O14">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1910,13 +1884,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S14">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="U14">
-        <v>185</v>
+        <v>1296</v>
       </c>
       <c r="W14">
         <v>4</v>
@@ -1978,16 +1952,16 @@
         <v>20004</v>
       </c>
       <c r="C15" t="str">
-        <v>陈泰⚔️ T2</v>
+        <v>郝昭⚔️ T2</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G15">
         <v>0.4</v>
@@ -2002,19 +1976,19 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="L15">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M15">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="N15">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O15">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="P15" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2026,10 +2000,10 @@
         <v>75</v>
       </c>
       <c r="T15">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="U15">
-        <v>209</v>
+        <v>1116</v>
       </c>
       <c r="W15">
         <v>4</v>
@@ -2091,16 +2065,16 @@
         <v>20005</v>
       </c>
       <c r="C16" t="str">
-        <v>魏延⚔️ T3</v>
+        <v>太史慈⚔️ T3</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="G16">
         <v>0.4</v>
@@ -2115,19 +2089,19 @@
         <v>1</v>
       </c>
       <c r="K16">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="L16">
         <v>27</v>
       </c>
       <c r="M16">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="N16">
         <v>27</v>
       </c>
       <c r="O16">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="P16" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2142,7 +2116,7 @@
         <v>91</v>
       </c>
       <c r="U16">
-        <v>215</v>
+        <v>1236</v>
       </c>
       <c r="W16">
         <v>4</v>
@@ -2210,10 +2184,10 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="G17">
         <v>0.4</v>
@@ -2228,19 +2202,19 @@
         <v>1</v>
       </c>
       <c r="K17">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="L17">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M17">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="N17">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O17">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2249,13 +2223,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S17">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T17">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="U17">
-        <v>190</v>
+        <v>1194</v>
       </c>
       <c r="W17">
         <v>4</v>
@@ -2323,10 +2297,10 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G18">
         <v>0.4</v>
@@ -2341,19 +2315,19 @@
         <v>1</v>
       </c>
       <c r="K18">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="L18">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M18">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="N18">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O18">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="P18" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2362,13 +2336,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S18">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T18">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="U18">
-        <v>194</v>
+        <v>1140</v>
       </c>
       <c r="W18">
         <v>4</v>
@@ -2436,10 +2410,10 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="G19">
         <v>0.4</v>
@@ -2454,19 +2428,19 @@
         <v>1</v>
       </c>
       <c r="K19">
-        <v>219</v>
+        <v>281</v>
       </c>
       <c r="L19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M19">
-        <v>219</v>
+        <v>281</v>
       </c>
       <c r="N19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O19">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P19" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2478,10 +2452,10 @@
         <v>76</v>
       </c>
       <c r="T19">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="U19">
-        <v>186</v>
+        <v>1146</v>
       </c>
       <c r="W19">
         <v>4</v>
@@ -2543,16 +2517,16 @@
         <v>30001</v>
       </c>
       <c r="C20" t="str">
-        <v>王异🎯 T1</v>
+        <v>辛宪英🎯 T1</v>
       </c>
       <c r="D20">
         <v>2</v>
       </c>
       <c r="E20">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G20">
         <v>0.4</v>
@@ -2567,19 +2541,19 @@
         <v>1</v>
       </c>
       <c r="K20">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M20">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O20">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="P20" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2588,13 +2562,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S20">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="T20">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="U20">
-        <v>717</v>
+        <v>4176</v>
       </c>
       <c r="W20">
         <v>1</v>
@@ -2656,16 +2630,16 @@
         <v>30002</v>
       </c>
       <c r="C21" t="str">
-        <v>小乔🎯 T1</v>
+        <v>张春华🎯 T1</v>
       </c>
       <c r="D21">
         <v>2</v>
       </c>
       <c r="E21">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="G21">
         <v>0.4</v>
@@ -2680,19 +2654,19 @@
         <v>1</v>
       </c>
       <c r="K21">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M21">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O21">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="P21" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2701,13 +2675,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S21">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T21">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="U21">
-        <v>745</v>
+        <v>4500</v>
       </c>
       <c r="W21">
         <v>1</v>
@@ -2769,16 +2743,16 @@
         <v>30003</v>
       </c>
       <c r="C22" t="str">
-        <v>蔡文姬🎯 T1</v>
+        <v>庞德公🎯 T1</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G22">
         <v>0.4</v>
@@ -2793,19 +2767,19 @@
         <v>1</v>
       </c>
       <c r="K22">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M22">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O22">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="P22" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2814,13 +2788,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S22">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="T22">
-        <v>593</v>
+        <v>638</v>
       </c>
       <c r="U22">
-        <v>643</v>
+        <v>4236</v>
       </c>
       <c r="W22">
         <v>1</v>
@@ -2882,13 +2856,13 @@
         <v>30004</v>
       </c>
       <c r="C23" t="str">
-        <v>张春华🎯 T1</v>
+        <v>杨修🎯 T1</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <v>101</v>
@@ -2909,16 +2883,16 @@
         <v>46</v>
       </c>
       <c r="L23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M23">
         <v>46</v>
       </c>
       <c r="N23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O23">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2927,13 +2901,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S23">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T23">
-        <v>546</v>
+        <v>652</v>
       </c>
       <c r="U23">
-        <v>694</v>
+        <v>3822</v>
       </c>
       <c r="W23">
         <v>1</v>
@@ -2995,16 +2969,16 @@
         <v>30005</v>
       </c>
       <c r="C24" t="str">
-        <v>田丰🎯 T2</v>
+        <v>鲁肃🎯 T2</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="G24">
         <v>0.4</v>
@@ -3019,19 +2993,19 @@
         <v>1</v>
       </c>
       <c r="K24">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L24">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="M24">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N24">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="O24">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="P24" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3043,10 +3017,10 @@
         <v>76</v>
       </c>
       <c r="T24">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="U24">
-        <v>648</v>
+        <v>4614</v>
       </c>
       <c r="W24">
         <v>1</v>
@@ -3108,16 +3082,16 @@
         <v>30006</v>
       </c>
       <c r="C25" t="str">
-        <v>沮授🎯 T2</v>
+        <v>徐庶🎯 T2</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="G25">
         <v>0.4</v>
@@ -3132,19 +3106,19 @@
         <v>1</v>
       </c>
       <c r="K25">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="L25">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M25">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="N25">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="O25">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="P25" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3153,13 +3127,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S25">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="T25">
-        <v>606</v>
+        <v>548</v>
       </c>
       <c r="U25">
-        <v>731</v>
+        <v>3894</v>
       </c>
       <c r="W25">
         <v>1</v>
@@ -3227,10 +3201,10 @@
         <v>2</v>
       </c>
       <c r="E26">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="G26">
         <v>0.4</v>
@@ -3245,19 +3219,19 @@
         <v>1</v>
       </c>
       <c r="K26">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="L26">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M26">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="N26">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O26">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="P26" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3266,13 +3240,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S26">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="T26">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="U26">
-        <v>687</v>
+        <v>4368</v>
       </c>
       <c r="W26">
         <v>1</v>
@@ -3334,16 +3308,16 @@
         <v>30008</v>
       </c>
       <c r="C27" t="str">
-        <v>太史慈🎯 T3</v>
+        <v>陆逊🎯 T3</v>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
       <c r="E27">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>337</v>
+        <v>268</v>
       </c>
       <c r="G27">
         <v>0.4</v>
@@ -3358,19 +3332,19 @@
         <v>1</v>
       </c>
       <c r="K27">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="L27">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M27">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="N27">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O27">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="P27" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3379,13 +3353,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S27">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T27">
-        <v>588</v>
+        <v>657</v>
       </c>
       <c r="U27">
-        <v>669</v>
+        <v>4068</v>
       </c>
       <c r="W27">
         <v>1</v>
@@ -3447,16 +3421,16 @@
         <v>30009</v>
       </c>
       <c r="C28" t="str">
-        <v>贾诩🎯 T3</v>
+        <v>荀彧🎯 T3</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
       <c r="E28">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="G28">
         <v>0.4</v>
@@ -3471,19 +3445,19 @@
         <v>1</v>
       </c>
       <c r="K28">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="L28">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M28">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="N28">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O28">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="P28" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3495,10 +3469,10 @@
         <v>76</v>
       </c>
       <c r="T28">
-        <v>630</v>
+        <v>605</v>
       </c>
       <c r="U28">
-        <v>658</v>
+        <v>3954</v>
       </c>
       <c r="W28">
         <v>1</v>
@@ -3560,16 +3534,16 @@
         <v>30010</v>
       </c>
       <c r="C29" t="str">
-        <v>荀彧🎯 T3</v>
+        <v>庞统🎯 T3</v>
       </c>
       <c r="D29">
         <v>2</v>
       </c>
       <c r="E29">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="G29">
         <v>0.4</v>
@@ -3584,19 +3558,19 @@
         <v>1</v>
       </c>
       <c r="K29">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="L29">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M29">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="N29">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O29">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="P29" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3605,13 +3579,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S29">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="T29">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="U29">
-        <v>632</v>
+        <v>4536</v>
       </c>
       <c r="W29">
         <v>1</v>
@@ -3679,10 +3653,10 @@
         <v>2</v>
       </c>
       <c r="E30">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="G30">
         <v>0.4</v>
@@ -3697,19 +3671,19 @@
         <v>1</v>
       </c>
       <c r="K30">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="L30">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="M30">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="N30">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="O30">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="P30" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3718,13 +3692,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S30">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T30">
-        <v>545</v>
+        <v>591</v>
       </c>
       <c r="U30">
-        <v>684</v>
+        <v>3786</v>
       </c>
       <c r="W30">
         <v>1</v>
@@ -3792,10 +3766,10 @@
         <v>2</v>
       </c>
       <c r="E31">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>375</v>
+        <v>457</v>
       </c>
       <c r="G31">
         <v>0.4</v>
@@ -3810,19 +3784,19 @@
         <v>1</v>
       </c>
       <c r="K31">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="L31">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M31">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="N31">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="O31">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="P31" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3831,13 +3805,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S31">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T31">
-        <v>579</v>
+        <v>641</v>
       </c>
       <c r="U31">
-        <v>767</v>
+        <v>4254</v>
       </c>
       <c r="W31">
         <v>1</v>
@@ -3905,10 +3879,10 @@
         <v>2</v>
       </c>
       <c r="E32">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>344</v>
+        <v>447</v>
       </c>
       <c r="G32">
         <v>0.4</v>
@@ -3923,19 +3897,19 @@
         <v>1</v>
       </c>
       <c r="K32">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="L32">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M32">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="N32">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="O32">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="P32" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3947,10 +3921,10 @@
         <v>77</v>
       </c>
       <c r="T32">
-        <v>632</v>
+        <v>562</v>
       </c>
       <c r="U32">
-        <v>705</v>
+        <v>4026</v>
       </c>
       <c r="W32">
         <v>1</v>
@@ -4012,16 +3986,16 @@
         <v>40001</v>
       </c>
       <c r="C33" t="str">
-        <v>成公英🌀 T1</v>
+        <v>马云禄🌀 T1</v>
       </c>
       <c r="D33">
         <v>3</v>
       </c>
       <c r="E33">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G33">
         <v>0.4</v>
@@ -4036,19 +4010,19 @@
         <v>1</v>
       </c>
       <c r="K33">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="L33">
         <v>10</v>
       </c>
       <c r="M33">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="N33">
         <v>10</v>
       </c>
       <c r="O33">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="P33" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4057,13 +4031,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T33">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="U33">
-        <v>542</v>
+        <v>2790</v>
       </c>
       <c r="W33">
         <v>3</v>
@@ -4125,16 +4099,16 @@
         <v>40002</v>
       </c>
       <c r="C34" t="str">
-        <v>孙尚香🌀 T2</v>
+        <v>公孙瓒🌀 T2</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
       <c r="E34">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="G34">
         <v>0.4</v>
@@ -4149,19 +4123,19 @@
         <v>1</v>
       </c>
       <c r="K34">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="L34">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M34">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="N34">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O34">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P34" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4170,13 +4144,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S34">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="T34">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="U34">
-        <v>510</v>
+        <v>3246</v>
       </c>
       <c r="W34">
         <v>3</v>
@@ -4238,16 +4212,16 @@
         <v>40003</v>
       </c>
       <c r="C35" t="str">
-        <v>曹纯🌀 T2</v>
+        <v>庞德🌀 T2</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="G35">
         <v>0.4</v>
@@ -4262,19 +4236,19 @@
         <v>1</v>
       </c>
       <c r="K35">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="L35">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M35">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="N35">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O35">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="P35" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4286,10 +4260,10 @@
         <v>76</v>
       </c>
       <c r="T35">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="U35">
-        <v>513</v>
+        <v>2868</v>
       </c>
       <c r="W35">
         <v>3</v>
@@ -4357,10 +4331,10 @@
         <v>3</v>
       </c>
       <c r="E36">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G36">
         <v>0.4</v>
@@ -4375,19 +4349,19 @@
         <v>1</v>
       </c>
       <c r="K36">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M36">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="N36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O36">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="P36" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4396,13 +4370,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S36">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T36">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="U36">
-        <v>506</v>
+        <v>3210</v>
       </c>
       <c r="W36">
         <v>3</v>
@@ -4464,16 +4438,16 @@
         <v>40005</v>
       </c>
       <c r="C37" t="str">
-        <v>赵云🌀 T4</v>
+        <v>张辽🌀 T4</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="G37">
         <v>0.4</v>
@@ -4488,19 +4462,19 @@
         <v>1</v>
       </c>
       <c r="K37">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="L37">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M37">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="N37">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="O37">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="P37" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4509,13 +4483,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S37">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T37">
-        <v>426</v>
+        <v>376</v>
       </c>
       <c r="U37">
-        <v>531</v>
+        <v>2760</v>
       </c>
       <c r="W37">
         <v>3</v>
@@ -4577,7 +4551,7 @@
         <v>90001</v>
       </c>
       <c r="C38" t="str">
-        <v>【变异主宰】曹仁🛡️ T3</v>
+        <v>【末日先兆】曹仁🛡️ T3</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -4586,7 +4560,7 @@
         <v>20</v>
       </c>
       <c r="F38">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G38">
         <v>0.4</v>
@@ -4601,19 +4575,19 @@
         <v>1</v>
       </c>
       <c r="K38">
-        <v>1214</v>
+        <v>1242</v>
       </c>
       <c r="L38">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M38">
-        <v>1214</v>
+        <v>1242</v>
       </c>
       <c r="N38">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O38">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="P38" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4622,13 +4596,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S38">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T38">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="U38">
-        <v>187</v>
+        <v>1290</v>
       </c>
       <c r="W38">
         <v>0</v>
@@ -4690,7 +4664,7 @@
         <v>90002</v>
       </c>
       <c r="C39" t="str">
-        <v>【末日先兆】陈泰⚔️ T2</v>
+        <v>【零号病毒】陈泰⚔️ T2</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -4699,7 +4673,7 @@
         <v>20</v>
       </c>
       <c r="F39">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="G39">
         <v>0.4</v>
@@ -4714,19 +4688,19 @@
         <v>1</v>
       </c>
       <c r="K39">
-        <v>576</v>
+        <v>480</v>
       </c>
       <c r="L39">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M39">
-        <v>576</v>
+        <v>480</v>
       </c>
       <c r="N39">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="O39">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="P39" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4735,13 +4709,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S39">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T39">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="U39">
-        <v>215</v>
+        <v>1266</v>
       </c>
       <c r="W39">
         <v>4</v>
@@ -4803,7 +4777,7 @@
         <v>90003</v>
       </c>
       <c r="C40" t="str">
-        <v>【极秘项目】张飞⚔️ T4</v>
+        <v>【变异主宰】张飞⚔️ T4</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -4812,7 +4786,7 @@
         <v>20</v>
       </c>
       <c r="F40">
-        <v>655</v>
+        <v>701</v>
       </c>
       <c r="G40">
         <v>0.4</v>
@@ -4827,19 +4801,19 @@
         <v>1</v>
       </c>
       <c r="K40">
-        <v>1068</v>
+        <v>1140</v>
       </c>
       <c r="L40">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M40">
-        <v>1068</v>
+        <v>1140</v>
       </c>
       <c r="N40">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O40">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P40" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4848,13 +4822,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S40">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T40">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="U40">
-        <v>211</v>
+        <v>1128</v>
       </c>
       <c r="W40">
         <v>4</v>
@@ -4916,7 +4890,7 @@
         <v>90004</v>
       </c>
       <c r="C41" t="str">
-        <v>【末日先兆】诸葛瑾🎯 T2</v>
+        <v>【虚空母体】满宠🎯 T2</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -4925,7 +4899,7 @@
         <v>20</v>
       </c>
       <c r="F41">
-        <v>425</v>
+        <v>467</v>
       </c>
       <c r="G41">
         <v>0.4</v>
@@ -4940,19 +4914,19 @@
         <v>1</v>
       </c>
       <c r="K41">
-        <v>251</v>
+        <v>333</v>
       </c>
       <c r="L41">
         <v>51</v>
       </c>
       <c r="M41">
-        <v>251</v>
+        <v>333</v>
       </c>
       <c r="N41">
         <v>51</v>
       </c>
       <c r="O41">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="P41" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4961,13 +4935,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S41">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T41">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="U41">
-        <v>763</v>
+        <v>4056</v>
       </c>
       <c r="W41">
         <v>1</v>
@@ -5029,7 +5003,7 @@
         <v>90005</v>
       </c>
       <c r="C42" t="str">
-        <v>【零号病毒】太史慈🎯 T3</v>
+        <v>【虚空母体】贾诩🎯 T3</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -5038,7 +5012,7 @@
         <v>20</v>
       </c>
       <c r="F42">
-        <v>666</v>
+        <v>601</v>
       </c>
       <c r="G42">
         <v>0.4</v>
@@ -5053,19 +5027,19 @@
         <v>1</v>
       </c>
       <c r="K42">
-        <v>474</v>
+        <v>373</v>
       </c>
       <c r="L42">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M42">
-        <v>474</v>
+        <v>373</v>
       </c>
       <c r="N42">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O42">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="P42" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5077,10 +5051,10 @@
         <v>75</v>
       </c>
       <c r="T42">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="U42">
-        <v>650</v>
+        <v>3840</v>
       </c>
       <c r="W42">
         <v>1</v>
@@ -5142,7 +5116,7 @@
         <v>90006</v>
       </c>
       <c r="C43" t="str">
-        <v>【钢铁暴君】司马懿🎯 T4</v>
+        <v>【零号病毒】周瑜🎯 T4</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -5151,7 +5125,7 @@
         <v>20</v>
       </c>
       <c r="F43">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="G43">
         <v>0.4</v>
@@ -5166,19 +5140,19 @@
         <v>1</v>
       </c>
       <c r="K43">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="L43">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M43">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="N43">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O43">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="P43" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5187,13 +5161,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S43">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T43">
-        <v>557</v>
+        <v>659</v>
       </c>
       <c r="U43">
-        <v>727</v>
+        <v>4242</v>
       </c>
       <c r="W43">
         <v>1</v>
@@ -5255,7 +5229,7 @@
         <v>90007</v>
       </c>
       <c r="C44" t="str">
-        <v>【虚空母体】赵云🌀 T4</v>
+        <v>【虚空母体】张辽🌀 T4</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -5264,7 +5238,7 @@
         <v>20</v>
       </c>
       <c r="F44">
-        <v>872</v>
+        <v>1023</v>
       </c>
       <c r="G44">
         <v>0.4</v>
@@ -5279,19 +5253,19 @@
         <v>1</v>
       </c>
       <c r="K44">
-        <v>739</v>
+        <v>786</v>
       </c>
       <c r="L44">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M44">
-        <v>739</v>
+        <v>786</v>
       </c>
       <c r="N44">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O44">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P44" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5300,13 +5274,13 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="S44">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T44">
-        <v>369</v>
+        <v>413</v>
       </c>
       <c r="U44">
-        <v>520</v>
+        <v>2916</v>
       </c>
       <c r="W44">
         <v>3</v>
@@ -5419,7 +5393,7 @@
         <v>84</v>
       </c>
       <c r="U45">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W45">
         <v>0</v>
@@ -5532,7 +5506,7 @@
         <v>84</v>
       </c>
       <c r="U46">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W46">
         <v>1</v>
@@ -5645,7 +5619,7 @@
         <v>84</v>
       </c>
       <c r="U47">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W47">
         <v>2</v>
@@ -5758,7 +5732,7 @@
         <v>84</v>
       </c>
       <c r="U48">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W48">
         <v>3</v>
@@ -5871,7 +5845,7 @@
         <v>490</v>
       </c>
       <c r="U49">
-        <v>2100</v>
+        <v>8400</v>
       </c>
       <c r="W49">
         <v>1</v>
@@ -5984,7 +5958,7 @@
         <v>560</v>
       </c>
       <c r="U50">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W50">
         <v>1</v>
@@ -6100,7 +6074,7 @@
         <v>560</v>
       </c>
       <c r="U51">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W51">
         <v>1</v>
@@ -6216,7 +6190,7 @@
         <v>100</v>
       </c>
       <c r="U52">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W52">
         <v>0</v>
@@ -6332,7 +6306,7 @@
         <v>150</v>
       </c>
       <c r="U53">
-        <v>1320</v>
+        <v>5280</v>
       </c>
       <c r="W53">
         <v>1</v>
@@ -6445,7 +6419,7 @@
         <v>112</v>
       </c>
       <c r="U54">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -6561,7 +6535,7 @@
         <v>840</v>
       </c>
       <c r="U55">
-        <v>3600</v>
+        <v>14400</v>
       </c>
       <c r="W55">
         <v>1</v>
@@ -6674,7 +6648,7 @@
         <v>490</v>
       </c>
       <c r="U56">
-        <v>2100</v>
+        <v>8400</v>
       </c>
       <c r="W56">
         <v>1</v>
@@ -6787,7 +6761,7 @@
         <v>80</v>
       </c>
       <c r="U57">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="V57" t="str">
         <v>[1,500]</v>
@@ -6903,7 +6877,7 @@
         <v>420</v>
       </c>
       <c r="U58">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="W58">
         <v>1</v>
@@ -7019,7 +6993,7 @@
         <v>100</v>
       </c>
       <c r="U59">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -7135,7 +7109,7 @@
         <v>84</v>
       </c>
       <c r="U60">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W60">
         <v>0</v>
@@ -7248,7 +7222,7 @@
         <v>560</v>
       </c>
       <c r="U61">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W61">
         <v>1</v>
@@ -7364,7 +7338,7 @@
         <v>130</v>
       </c>
       <c r="U62">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W62">
         <v>0</v>
@@ -7480,7 +7454,7 @@
         <v>90</v>
       </c>
       <c r="U63">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="V63" t="str">
         <v>[1,800]</v>
@@ -7599,7 +7573,7 @@
         <v>560</v>
       </c>
       <c r="U64">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W64">
         <v>1</v>
@@ -7712,7 +7686,7 @@
         <v>320</v>
       </c>
       <c r="U65">
-        <v>1280</v>
+        <v>5120</v>
       </c>
       <c r="W65">
         <v>1</v>
@@ -7822,7 +7796,7 @@
         <v>320</v>
       </c>
       <c r="U66">
-        <v>1280</v>
+        <v>5120</v>
       </c>
       <c r="W66">
         <v>0</v>
@@ -7932,7 +7906,7 @@
         <v>630</v>
       </c>
       <c r="U67">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="W67">
         <v>2</v>
@@ -8045,7 +8019,7 @@
         <v>630</v>
       </c>
       <c r="U68">
-        <v>2700</v>
+        <v>10800</v>
       </c>
       <c r="W68">
         <v>1</v>
@@ -8158,7 +8132,7 @@
         <v>105</v>
       </c>
       <c r="U69">
-        <v>780</v>
+        <v>3120</v>
       </c>
       <c r="W69">
         <v>0</v>
@@ -8271,7 +8245,7 @@
         <v>350</v>
       </c>
       <c r="U70">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="W70">
         <v>1</v>
@@ -8384,7 +8358,7 @@
         <v>320</v>
       </c>
       <c r="U71">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W71">
         <v>1</v>
@@ -8497,7 +8471,7 @@
         <v>130</v>
       </c>
       <c r="U72">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W72">
         <v>0</v>
@@ -8610,7 +8584,7 @@
         <v>600</v>
       </c>
       <c r="U73">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W73">
         <v>1</v>
@@ -8723,7 +8697,7 @@
         <v>600</v>
       </c>
       <c r="U74">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W74">
         <v>1</v>
@@ -8836,7 +8810,7 @@
         <v>130</v>
       </c>
       <c r="U75">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W75">
         <v>0</v>
@@ -8949,7 +8923,7 @@
         <v>130</v>
       </c>
       <c r="U76">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W76">
         <v>0</v>
@@ -9062,7 +9036,7 @@
         <v>200</v>
       </c>
       <c r="U77">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="W77">
         <v>0</v>
@@ -9175,7 +9149,7 @@
         <v>130</v>
       </c>
       <c r="U78">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W78">
         <v>0</v>
@@ -9288,7 +9262,7 @@
         <v>750</v>
       </c>
       <c r="U79">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="W79">
         <v>1</v>
@@ -9401,7 +9375,7 @@
         <v>320</v>
       </c>
       <c r="U80">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W80">
         <v>1</v>
@@ -9514,7 +9488,7 @@
         <v>130</v>
       </c>
       <c r="U81">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W81">
         <v>0</v>
@@ -9627,7 +9601,7 @@
         <v>84</v>
       </c>
       <c r="U82">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W82">
         <v>0</v>
@@ -9740,7 +9714,7 @@
         <v>130</v>
       </c>
       <c r="U83">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W83">
         <v>0</v>
@@ -9853,7 +9827,7 @@
         <v>130</v>
       </c>
       <c r="U84">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="V84" t="str">
         <v>[1,800]</v>
@@ -9969,7 +9943,7 @@
         <v>130</v>
       </c>
       <c r="U85">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W85">
         <v>0</v>
@@ -10082,7 +10056,7 @@
         <v>850</v>
       </c>
       <c r="U86">
-        <v>3400</v>
+        <v>13600</v>
       </c>
       <c r="W86">
         <v>1</v>
@@ -10195,7 +10169,7 @@
         <v>130</v>
       </c>
       <c r="U87">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="W87">
         <v>0</v>
@@ -10308,7 +10282,7 @@
         <v>550</v>
       </c>
       <c r="U88">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="W88">
         <v>1</v>
@@ -10421,7 +10395,7 @@
         <v>850</v>
       </c>
       <c r="U89">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W89">
         <v>1</v>
@@ -10534,7 +10508,7 @@
         <v>630</v>
       </c>
       <c r="U90">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="W90">
         <v>2</v>
@@ -10645,7 +10619,7 @@
         <v>56</v>
       </c>
       <c r="U91">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W91">
         <v>0</v>
@@ -10759,7 +10733,7 @@
         <v>150</v>
       </c>
       <c r="U92">
-        <v>1320</v>
+        <v>5280</v>
       </c>
       <c r="W92">
         <v>1</v>
@@ -10876,7 +10850,7 @@
         <v>56</v>
       </c>
       <c r="U93">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W93">
         <v>0</v>
@@ -10993,7 +10967,7 @@
         <v>840</v>
       </c>
       <c r="U94">
-        <v>3600</v>
+        <v>14400</v>
       </c>
       <c r="W94">
         <v>1</v>
@@ -11110,7 +11084,7 @@
         <v>490</v>
       </c>
       <c r="U95">
-        <v>2100</v>
+        <v>8400</v>
       </c>
       <c r="W95">
         <v>1</v>
@@ -11224,7 +11198,7 @@
         <v>84</v>
       </c>
       <c r="U96">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="V96" t="str">
         <v>[100,3000]</v>
@@ -11344,7 +11318,7 @@
         <v>420</v>
       </c>
       <c r="U97">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="W97">
         <v>1</v>
@@ -11461,7 +11435,7 @@
         <v>100</v>
       </c>
       <c r="U98">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W98">
         <v>0</v>
@@ -11578,7 +11552,7 @@
         <v>560</v>
       </c>
       <c r="U99">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W99">
         <v>1</v>
@@ -11695,7 +11669,7 @@
         <v>130</v>
       </c>
       <c r="U100">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W100">
         <v>0</v>
@@ -11812,7 +11786,7 @@
         <v>90</v>
       </c>
       <c r="U101">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="V101" t="str">
         <v>[1,1100]</v>
@@ -11929,7 +11903,7 @@
         <v>560</v>
       </c>
       <c r="U102">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W102">
         <v>1</v>
@@ -12046,7 +12020,7 @@
         <v>150</v>
       </c>
       <c r="U103">
-        <v>1320</v>
+        <v>5280</v>
       </c>
       <c r="W103">
         <v>1</v>
@@ -12163,7 +12137,7 @@
         <v>130</v>
       </c>
       <c r="U104">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W104">
         <v>0</v>
@@ -12280,7 +12254,7 @@
         <v>250</v>
       </c>
       <c r="U105">
-        <v>2700</v>
+        <v>10800</v>
       </c>
       <c r="W105">
         <v>1</v>
@@ -12397,7 +12371,7 @@
         <v>130</v>
       </c>
       <c r="U106">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W106">
         <v>0</v>
@@ -12511,7 +12485,7 @@
         <v>130</v>
       </c>
       <c r="U107">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W107">
         <v>0</v>
@@ -12628,7 +12602,7 @@
         <v>130</v>
       </c>
       <c r="U108">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W108">
         <v>0</v>
@@ -12745,7 +12719,7 @@
         <v>130</v>
       </c>
       <c r="U109">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W109">
         <v>0</v>
@@ -12862,7 +12836,7 @@
         <v>130</v>
       </c>
       <c r="U110">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W110">
         <v>0</v>
@@ -12979,7 +12953,7 @@
         <v>130</v>
       </c>
       <c r="U111">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W111">
         <v>0</v>
@@ -13096,7 +13070,7 @@
         <v>130</v>
       </c>
       <c r="U112">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W112">
         <v>0</v>
@@ -13213,7 +13187,7 @@
         <v>250</v>
       </c>
       <c r="U113">
-        <v>2100</v>
+        <v>8400</v>
       </c>
       <c r="W113">
         <v>1</v>
@@ -13327,7 +13301,7 @@
         <v>130</v>
       </c>
       <c r="U114">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="V114" t="str">
         <v>[1,500]</v>
@@ -13447,7 +13421,7 @@
         <v>200</v>
       </c>
       <c r="U115">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="W115">
         <v>1</v>
@@ -13564,7 +13538,7 @@
         <v>200</v>
       </c>
       <c r="U116">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="W116">
         <v>0</v>
@@ -13681,7 +13655,7 @@
         <v>300</v>
       </c>
       <c r="U117">
-        <v>2800</v>
+        <v>11200</v>
       </c>
       <c r="W117">
         <v>1</v>
@@ -13798,7 +13772,7 @@
         <v>250</v>
       </c>
       <c r="U118">
-        <v>2800</v>
+        <v>11200</v>
       </c>
       <c r="W118">
         <v>1</v>
@@ -13915,7 +13889,7 @@
         <v>130</v>
       </c>
       <c r="U119">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="W119">
         <v>0</v>
@@ -14032,7 +14006,7 @@
         <v>250</v>
       </c>
       <c r="U120">
-        <v>2800</v>
+        <v>11200</v>
       </c>
       <c r="W120">
         <v>1</v>
@@ -14149,7 +14123,7 @@
         <v>200</v>
       </c>
       <c r="U121">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W121">
         <v>0</v>
@@ -14266,7 +14240,7 @@
         <v>250</v>
       </c>
       <c r="U122">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W122">
         <v>1</v>
@@ -14383,7 +14357,7 @@
         <v>120</v>
       </c>
       <c r="U123">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W123">
         <v>0</v>
@@ -14500,7 +14474,7 @@
         <v>250</v>
       </c>
       <c r="U124">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="W124">
         <v>1</v>
@@ -14617,7 +14591,7 @@
         <v>130</v>
       </c>
       <c r="U125">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="W125">
         <v>0</v>
@@ -14734,7 +14708,7 @@
         <v>400</v>
       </c>
       <c r="U126">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="W126">
         <v>1</v>
@@ -14851,7 +14825,7 @@
         <v>100</v>
       </c>
       <c r="U127">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="V127" t="str">
         <v>[1,1100]</v>
@@ -14968,7 +14942,7 @@
         <v>260</v>
       </c>
       <c r="U128">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W128">
         <v>1</v>
@@ -15085,7 +15059,7 @@
         <v>140</v>
       </c>
       <c r="U129">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W129">
         <v>0</v>
@@ -15199,7 +15173,7 @@
         <v>220</v>
       </c>
       <c r="U130">
-        <v>1960</v>
+        <v>7840</v>
       </c>
       <c r="W130">
         <v>1</v>
@@ -15316,7 +15290,7 @@
         <v>400</v>
       </c>
       <c r="U131">
-        <v>3560</v>
+        <v>14240</v>
       </c>
       <c r="W131">
         <v>1</v>
@@ -15433,7 +15407,7 @@
         <v>250</v>
       </c>
       <c r="U132">
-        <v>1800</v>
+        <v>7200</v>
       </c>
       <c r="W132">
         <v>1</v>
@@ -15550,7 +15524,7 @@
         <v>630</v>
       </c>
       <c r="U133">
-        <v>2700</v>
+        <v>10800</v>
       </c>
       <c r="W133">
         <v>1</v>
@@ -15667,7 +15641,7 @@
         <v>350</v>
       </c>
       <c r="U134">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="W134">
         <v>1</v>
@@ -15784,7 +15758,7 @@
         <v>320</v>
       </c>
       <c r="U135">
-        <v>2400</v>
+        <v>9600</v>
       </c>
       <c r="W135">
         <v>0</v>
@@ -15843,6 +15817,5 @@
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:AN135"/>
   </ignoredErrors>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/ArmyTable.xlsx
+++ b/public/ArmyTable.xlsx
@@ -3054,7 +3054,7 @@
         <v>10001</v>
       </c>
       <c r="C28" t="str">
-        <v>廖化-步兵 T1</v>
+        <v>乐进-步兵 T1</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3063,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G28">
         <v>3</v>
@@ -3075,13 +3075,13 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="K28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="M28" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3090,10 +3090,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P28">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q28">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -3152,7 +3152,7 @@
         <v>10002</v>
       </c>
       <c r="C29" t="str">
-        <v>牵招-步兵 T1</v>
+        <v>颜良-步兵 T1</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -3161,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G29">
         <v>3</v>
@@ -3173,13 +3173,13 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="K29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="M29" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3188,10 +3188,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P29">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q29">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -3250,7 +3250,7 @@
         <v>10003</v>
       </c>
       <c r="C30" t="str">
-        <v>曹真-步兵 T1</v>
+        <v>管亥-步兵 T1</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -3259,7 +3259,7 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -3271,13 +3271,13 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="K30">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="M30" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3286,10 +3286,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P30">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q30">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -3348,7 +3348,7 @@
         <v>10004</v>
       </c>
       <c r="C31" t="str">
-        <v>孙权-步兵 T1</v>
+        <v>李典-步兵 T1</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -3357,7 +3357,7 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -3369,13 +3369,13 @@
         <v>1</v>
       </c>
       <c r="J31">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="K31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="M31" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3384,10 +3384,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P31">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q31">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -3446,7 +3446,7 @@
         <v>10005</v>
       </c>
       <c r="C32" t="str">
-        <v>韩猛-步兵 T1</v>
+        <v>张苞-步兵 T1</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -3455,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -3467,13 +3467,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K32">
         <v>10</v>
       </c>
       <c r="L32">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="M32" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3482,10 +3482,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P32">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q32">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -3544,7 +3544,7 @@
         <v>10006</v>
       </c>
       <c r="C33" t="str">
-        <v>祖茂-步兵 T1</v>
+        <v>傅佥-步兵 T1</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -3553,7 +3553,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -3565,13 +3565,13 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="K33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="M33" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3580,10 +3580,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P33">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q33">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -3642,7 +3642,7 @@
         <v>10007</v>
       </c>
       <c r="C34" t="str">
-        <v>苏由-步兵 T1</v>
+        <v>臧霸-步兵 T1</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -3663,13 +3663,13 @@
         <v>1</v>
       </c>
       <c r="J34">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="K34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="M34" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3678,10 +3678,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P34">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q34">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>10008</v>
       </c>
       <c r="C35" t="str">
-        <v>管亥-步兵 T1</v>
+        <v>淳于琼-步兵 T1</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -3761,13 +3761,13 @@
         <v>1</v>
       </c>
       <c r="J35">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="K35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="M35" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3779,7 +3779,7 @@
         <v>77</v>
       </c>
       <c r="Q35">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -3838,7 +3838,7 @@
         <v>10009</v>
       </c>
       <c r="C36" t="str">
-        <v>李典-步兵 T1</v>
+        <v>廖化-步兵 T1</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -3859,13 +3859,13 @@
         <v>1</v>
       </c>
       <c r="J36">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="K36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="M36" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3874,10 +3874,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P36">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q36">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>10010</v>
       </c>
       <c r="C37" t="str">
-        <v>丁奉-步兵 T1</v>
+        <v>裴元绍-步兵 T1</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -3957,13 +3957,13 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="K37">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="M37" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3975,7 +3975,7 @@
         <v>79</v>
       </c>
       <c r="Q37">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -4034,7 +4034,7 @@
         <v>10011</v>
       </c>
       <c r="C38" t="str">
-        <v>曹仁-步兵 T1</v>
+        <v>孙权-步兵 T1</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G38">
         <v>3</v>
@@ -4055,13 +4055,13 @@
         <v>1</v>
       </c>
       <c r="J38">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="K38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L38">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="M38" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4070,10 +4070,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P38">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q38">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -4132,7 +4132,7 @@
         <v>10012</v>
       </c>
       <c r="C39" t="str">
-        <v>张苞-步兵 T1</v>
+        <v>王威-步兵 T1</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -4141,7 +4141,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -4153,13 +4153,13 @@
         <v>1</v>
       </c>
       <c r="J39">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="K39">
         <v>8</v>
       </c>
       <c r="L39">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="M39" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4168,10 +4168,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P39">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q39">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>10013</v>
       </c>
       <c r="C40" t="str">
-        <v>吕公-步兵 T2</v>
+        <v>曹洪-步兵 T2</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -4251,10 +4251,10 @@
         <v>1</v>
       </c>
       <c r="J40">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="K40">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L40">
         <v>1.07</v>
@@ -4266,10 +4266,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P40">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q40">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -4328,7 +4328,7 @@
         <v>10014</v>
       </c>
       <c r="C41" t="str">
-        <v>刘封-步兵 T2</v>
+        <v>吕凯-步兵 T2</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -4337,7 +4337,7 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -4349,13 +4349,13 @@
         <v>1</v>
       </c>
       <c r="J41">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="K41">
         <v>11</v>
       </c>
       <c r="L41">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="M41" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4364,10 +4364,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P41">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q41">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         <v>10015</v>
       </c>
       <c r="C42" t="str">
-        <v>王颀-步兵 T2</v>
+        <v>吕公-步兵 T2</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -4435,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -4447,13 +4447,13 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L42">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="M42" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4462,10 +4462,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P42">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q42">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -4524,7 +4524,7 @@
         <v>10016</v>
       </c>
       <c r="C43" t="str">
-        <v>吕凯-步兵 T2</v>
+        <v>王颀-步兵 T2</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -4533,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -4551,7 +4551,7 @@
         <v>12</v>
       </c>
       <c r="L43">
-        <v>1.05</v>
+        <v>0.94</v>
       </c>
       <c r="M43" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4560,10 +4560,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P43">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q43">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>10017</v>
       </c>
       <c r="C44" t="str">
-        <v>向宠-步兵 T2</v>
+        <v>吕旷-步兵 T2</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -4631,7 +4631,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -4643,13 +4643,13 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>182</v>
+        <v>268</v>
       </c>
       <c r="K44">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L44">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="M44" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4658,10 +4658,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P44">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q44">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>10018</v>
       </c>
       <c r="C45" t="str">
-        <v>徐盛-步兵 T2</v>
+        <v>潘凤-步兵 T2</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -4729,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -4741,13 +4741,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="K45">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L45">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4756,10 +4756,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P45">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q45">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -4818,7 +4818,7 @@
         <v>10019</v>
       </c>
       <c r="C46" t="str">
-        <v>王威-步兵 T2</v>
+        <v>曹休-步兵 T2</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -4839,13 +4839,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K46">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L46">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="M46" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4854,10 +4854,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P46">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q46">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>10020</v>
       </c>
       <c r="C47" t="str">
-        <v>颜良-步兵 T2</v>
+        <v>田豫-步兵 T2</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -4925,7 +4925,7 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -4937,13 +4937,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="K47">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="M47" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4952,10 +4952,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P47">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q47">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -5014,7 +5014,7 @@
         <v>10021</v>
       </c>
       <c r="C48" t="str">
-        <v>孙坚-步兵 T2</v>
+        <v>周仓-步兵 T2</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -5023,7 +5023,7 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G48">
         <v>4</v>
@@ -5035,13 +5035,13 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="K48">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L48">
-        <v>0.94</v>
+        <v>1.07</v>
       </c>
       <c r="M48" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5053,7 +5053,7 @@
         <v>75</v>
       </c>
       <c r="Q48">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         <v>10022</v>
       </c>
       <c r="C49" t="str">
-        <v>吴班-步兵 T2</v>
+        <v>于禁-步兵 T2</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -5121,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -5133,13 +5133,13 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="K49">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M49" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5151,7 +5151,7 @@
         <v>76</v>
       </c>
       <c r="Q49">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -5210,7 +5210,7 @@
         <v>10023</v>
       </c>
       <c r="C50" t="str">
-        <v>曹操-步兵 T2</v>
+        <v>文丑-步兵 T2</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -5231,13 +5231,13 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="K50">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L50">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="M50" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5249,7 +5249,7 @@
         <v>76</v>
       </c>
       <c r="Q50">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -5308,7 +5308,7 @@
         <v>10024</v>
       </c>
       <c r="C51" t="str">
-        <v>马忠-步兵 T2</v>
+        <v>关樾-步兵 T2</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -5317,7 +5317,7 @@
         <v>1</v>
       </c>
       <c r="F51">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G51">
         <v>4</v>
@@ -5329,13 +5329,13 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="K51">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L51">
-        <v>0.93</v>
+        <v>1.02</v>
       </c>
       <c r="M51" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5344,10 +5344,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P51">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q51">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -5406,7 +5406,7 @@
         <v>10025</v>
       </c>
       <c r="C52" t="str">
-        <v>曹洪-步兵 T3</v>
+        <v>胡车儿-步兵 T3</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="F52">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -5427,13 +5427,13 @@
         <v>1</v>
       </c>
       <c r="J52">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="K52">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L52">
-        <v>0.91</v>
+        <v>1.07</v>
       </c>
       <c r="M52" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5442,10 +5442,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P52">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q52">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -5504,7 +5504,7 @@
         <v>10026</v>
       </c>
       <c r="C53" t="str">
-        <v>程普-步兵 T3</v>
+        <v>焦触-步兵 T3</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -5513,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="F53">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -5525,13 +5525,13 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="K53">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L53">
-        <v>0.94</v>
+        <v>1.08</v>
       </c>
       <c r="M53" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5540,10 +5540,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P53">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q53">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -5602,7 +5602,7 @@
         <v>10027</v>
       </c>
       <c r="C54" t="str">
-        <v>黄盖-步兵 T3</v>
+        <v>韩当-步兵 T3</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -5611,7 +5611,7 @@
         <v>1</v>
       </c>
       <c r="F54">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G54">
         <v>5</v>
@@ -5623,13 +5623,13 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="K54">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L54">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="M54" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5638,10 +5638,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P54">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q54">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -5700,7 +5700,7 @@
         <v>10028</v>
       </c>
       <c r="C55" t="str">
-        <v>华雄-步兵 T3</v>
+        <v>韩猛-步兵 T3</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -5709,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="F55">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="G55">
         <v>5</v>
@@ -5721,13 +5721,13 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>293</v>
+        <v>255</v>
       </c>
       <c r="K55">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L55">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="M55" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5736,10 +5736,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P55">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q55">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -5798,7 +5798,7 @@
         <v>10029</v>
       </c>
       <c r="C56" t="str">
-        <v>裴元绍-步兵 T3</v>
+        <v>高览-步兵 T3</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -5807,7 +5807,7 @@
         <v>1</v>
       </c>
       <c r="F56">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G56">
         <v>5</v>
@@ -5819,13 +5819,13 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="K56">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L56">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="M56" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5834,10 +5834,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P56">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q56">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>10030</v>
       </c>
       <c r="C57" t="str">
-        <v>淳于琼-步兵 T3</v>
+        <v>曹仁-步兵 T3</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -5905,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="F57">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G57">
         <v>5</v>
@@ -5917,13 +5917,13 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="K57">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L57">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="M57" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5932,10 +5932,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P57">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q57">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -5994,7 +5994,7 @@
         <v>10031</v>
       </c>
       <c r="C58" t="str">
-        <v>田豫-步兵 T3</v>
+        <v>霍峻-步兵 T3</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>1</v>
       </c>
       <c r="F58">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G58">
         <v>5</v>
@@ -6015,13 +6015,13 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="K58">
         <v>16</v>
       </c>
       <c r="L58">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="M58" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6030,10 +6030,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P58">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q58">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -6092,7 +6092,7 @@
         <v>10032</v>
       </c>
       <c r="C59" t="str">
-        <v>傅佥-步兵 T3</v>
+        <v>周泰-步兵 T3</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -6101,7 +6101,7 @@
         <v>1</v>
       </c>
       <c r="F59">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="G59">
         <v>5</v>
@@ -6113,13 +6113,13 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="K59">
         <v>15</v>
       </c>
       <c r="L59">
-        <v>0.94</v>
+        <v>1.09</v>
       </c>
       <c r="M59" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6131,7 +6131,7 @@
         <v>75</v>
       </c>
       <c r="Q59">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -6190,7 +6190,7 @@
         <v>10033</v>
       </c>
       <c r="C60" t="str">
-        <v>张允-步兵 T3</v>
+        <v>华雄-步兵 T3</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -6199,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="F60">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G60">
         <v>5</v>
@@ -6211,13 +6211,13 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="K60">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L60">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="M60" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6229,7 +6229,7 @@
         <v>79</v>
       </c>
       <c r="Q60">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -6288,7 +6288,7 @@
         <v>10034</v>
       </c>
       <c r="C61" t="str">
-        <v>马延-步兵 T3</v>
+        <v>孙策-步兵 T3</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -6297,7 +6297,7 @@
         <v>1</v>
       </c>
       <c r="F61">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="G61">
         <v>5</v>
@@ -6309,13 +6309,13 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <v>355</v>
+        <v>280</v>
       </c>
       <c r="K61">
         <v>19</v>
       </c>
       <c r="L61">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="M61" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6324,10 +6324,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P61">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q61">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -6386,7 +6386,7 @@
         <v>10035</v>
       </c>
       <c r="C62" t="str">
-        <v>甘宁-步兵 T3</v>
+        <v>刘封-步兵 T3</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -6395,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="F62">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="G62">
         <v>5</v>
@@ -6407,13 +6407,13 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="K62">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L62">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="M62" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6422,10 +6422,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P62">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q62">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -6484,7 +6484,7 @@
         <v>10036</v>
       </c>
       <c r="C63" t="str">
-        <v>关兴-步兵 T3</v>
+        <v>关平-步兵 T3</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -6493,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="F63">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="G63">
         <v>5</v>
@@ -6505,13 +6505,13 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="K63">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L63">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="M63" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6520,10 +6520,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P63">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q63">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -6582,7 +6582,7 @@
         <v>10037</v>
       </c>
       <c r="C64" t="str">
-        <v>严白虎-步兵 T4</v>
+        <v>关兴-步兵 T4</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -6591,7 +6591,7 @@
         <v>1</v>
       </c>
       <c r="F64">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="G64">
         <v>6</v>
@@ -6603,13 +6603,13 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="K64">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L64">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="M64" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6618,10 +6618,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P64">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q64">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>10038</v>
       </c>
       <c r="C65" t="str">
-        <v>关平-步兵 T4</v>
+        <v>许褚-步兵 T4</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -6689,7 +6689,7 @@
         <v>1</v>
       </c>
       <c r="F65">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G65">
         <v>6</v>
@@ -6701,13 +6701,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>333</v>
+        <v>395</v>
       </c>
       <c r="K65">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L65">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="M65" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6716,7 +6716,7 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P65">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q65">
         <v>99</v>
@@ -6778,7 +6778,7 @@
         <v>10039</v>
       </c>
       <c r="C66" t="str">
-        <v>张南-步兵 T4</v>
+        <v>吴班-步兵 T4</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -6787,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="G66">
         <v>6</v>
@@ -6799,13 +6799,13 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <v>403</v>
+        <v>343</v>
       </c>
       <c r="K66">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L66">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="M66" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6814,10 +6814,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P66">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q66">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -6876,7 +6876,7 @@
         <v>10040</v>
       </c>
       <c r="C67" t="str">
-        <v>周仓-步兵 T4</v>
+        <v>张翼-步兵 T4</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -6885,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="F67">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G67">
         <v>6</v>
@@ -6897,13 +6897,13 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>426</v>
+        <v>360</v>
       </c>
       <c r="K67">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L67">
-        <v>0.94</v>
+        <v>0.98</v>
       </c>
       <c r="M67" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6912,10 +6912,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P67">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q67">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -6974,7 +6974,7 @@
         <v>10041</v>
       </c>
       <c r="C68" t="str">
-        <v>傅彤-步兵 T4</v>
+        <v>朱桓-步兵 T4</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>1</v>
       </c>
       <c r="F68">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -6995,13 +6995,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>404</v>
+        <v>331</v>
       </c>
       <c r="K68">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L68">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="M68" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7010,10 +7010,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P68">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q68">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -7072,7 +7072,7 @@
         <v>10042</v>
       </c>
       <c r="C69" t="str">
-        <v>霍峻-步兵 T4</v>
+        <v>徐晃-步兵 T4</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -7081,7 +7081,7 @@
         <v>1</v>
       </c>
       <c r="F69">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G69">
         <v>6</v>
@@ -7093,13 +7093,13 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="K69">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L69">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="M69" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7108,10 +7108,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P69">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q69">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -7170,7 +7170,7 @@
         <v>10043</v>
       </c>
       <c r="C70" t="str">
-        <v>潘凤-步兵 T4</v>
+        <v>蒋义渠-步兵 T4</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -7179,7 +7179,7 @@
         <v>1</v>
       </c>
       <c r="F70">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="G70">
         <v>6</v>
@@ -7191,13 +7191,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>413</v>
+        <v>302</v>
       </c>
       <c r="K70">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L70">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="M70" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7206,10 +7206,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P70">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q70">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>10044</v>
       </c>
       <c r="C71" t="str">
-        <v>郭援-步兵 T4</v>
+        <v>丁奉-步兵 T4</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="F71">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="G71">
         <v>6</v>
@@ -7289,13 +7289,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>310</v>
+        <v>381</v>
       </c>
       <c r="K71">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L71">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="M71" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7304,10 +7304,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P71">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q71">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -7366,7 +7366,7 @@
         <v>10045</v>
       </c>
       <c r="C72" t="str">
-        <v>吕旷-步兵 T4</v>
+        <v>典韦-步兵 T4</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -7375,7 +7375,7 @@
         <v>1</v>
       </c>
       <c r="F72">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="G72">
         <v>6</v>
@@ -7387,13 +7387,13 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <v>366</v>
+        <v>428</v>
       </c>
       <c r="K72">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L72">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="M72" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7402,10 +7402,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P72">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q72">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -7464,7 +7464,7 @@
         <v>10046</v>
       </c>
       <c r="C73" t="str">
-        <v>张翼-步兵 T4</v>
+        <v>张郃-步兵 T4</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -7473,7 +7473,7 @@
         <v>1</v>
       </c>
       <c r="F73">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="G73">
         <v>6</v>
@@ -7485,13 +7485,13 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="K73">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L73">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="M73" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7500,10 +7500,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P73">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q73">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -7562,7 +7562,7 @@
         <v>10047</v>
       </c>
       <c r="C74" t="str">
-        <v>臧霸-步兵 T4</v>
+        <v>徐盛-步兵 T4</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -7571,7 +7571,7 @@
         <v>1</v>
       </c>
       <c r="F74">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="G74">
         <v>6</v>
@@ -7583,13 +7583,13 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="K74">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L74">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="M74" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7598,10 +7598,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P74">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q74">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -7660,7 +7660,7 @@
         <v>10048</v>
       </c>
       <c r="C75" t="str">
-        <v>蒋舒-步兵 T4</v>
+        <v>孙坚-步兵 T4</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -7669,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="F75">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="G75">
         <v>6</v>
@@ -7681,13 +7681,13 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <v>307</v>
+        <v>427</v>
       </c>
       <c r="K75">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L75">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="M75" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7696,10 +7696,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P75">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q75">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -7853,7 +7853,7 @@
         <v>20001</v>
       </c>
       <c r="C77" t="str">
-        <v>戏志才-弓箭手 T1</v>
+        <v>诸葛亮-弓箭手 T1</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -7862,7 +7862,7 @@
         <v>1</v>
       </c>
       <c r="F77">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G77">
         <v>3</v>
@@ -7874,13 +7874,13 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K77">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L77">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="M77" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7889,10 +7889,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P77">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q77">
-        <v>641</v>
+        <v>602</v>
       </c>
       <c r="S77">
         <v>1</v>
@@ -7951,7 +7951,7 @@
         <v>20002</v>
       </c>
       <c r="C78" t="str">
-        <v>刘晔-弓箭手 T1</v>
+        <v>顾雍-弓箭手 T1</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -7960,7 +7960,7 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G78">
         <v>3</v>
@@ -7972,13 +7972,13 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="K78">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L78">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="M78" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7987,10 +7987,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P78">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q78">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="S78">
         <v>1</v>
@@ -8049,7 +8049,7 @@
         <v>20003</v>
       </c>
       <c r="C79" t="str">
-        <v>蒯良-弓箭手 T1</v>
+        <v>钟繇-弓箭手 T1</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -8058,7 +8058,7 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G79">
         <v>3</v>
@@ -8070,13 +8070,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="K79">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L79">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="M79" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8085,10 +8085,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P79">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q79">
-        <v>659</v>
+        <v>629</v>
       </c>
       <c r="S79">
         <v>1</v>
@@ -8147,7 +8147,7 @@
         <v>20004</v>
       </c>
       <c r="C80" t="str">
-        <v>虞翻-弓箭手 T1</v>
+        <v>逢纪-弓箭手 T1</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -8156,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="F80">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G80">
         <v>3</v>
@@ -8168,13 +8168,13 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K80">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L80">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="M80" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8183,10 +8183,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P80">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q80">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="S80">
         <v>1</v>
@@ -8245,7 +8245,7 @@
         <v>20005</v>
       </c>
       <c r="C81" t="str">
-        <v>陈宫-弓箭手 T1</v>
+        <v>满宠-弓箭手 T1</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -8254,7 +8254,7 @@
         <v>1</v>
       </c>
       <c r="F81">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G81">
         <v>3</v>
@@ -8266,13 +8266,13 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K81">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L81">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="M81" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8281,10 +8281,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P81">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q81">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="S81">
         <v>1</v>
@@ -8343,7 +8343,7 @@
         <v>20006</v>
       </c>
       <c r="C82" t="str">
-        <v>蔡文姬-弓箭手 T1</v>
+        <v>简雍-弓箭手 T1</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -8352,7 +8352,7 @@
         <v>1</v>
       </c>
       <c r="F82">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="G82">
         <v>3</v>
@@ -8364,13 +8364,13 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K82">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L82">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="M82" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8382,7 +8382,7 @@
         <v>75</v>
       </c>
       <c r="Q82">
-        <v>545</v>
+        <v>655</v>
       </c>
       <c r="S82">
         <v>1</v>
@@ -8441,7 +8441,7 @@
         <v>20007</v>
       </c>
       <c r="C83" t="str">
-        <v>庞统-弓箭手 T1</v>
+        <v>薛综-弓箭手 T1</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -8450,7 +8450,7 @@
         <v>1</v>
       </c>
       <c r="F83">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G83">
         <v>3</v>
@@ -8462,13 +8462,13 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K83">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L83">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="M83" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8477,10 +8477,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P83">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q83">
-        <v>659</v>
+        <v>568</v>
       </c>
       <c r="S83">
         <v>1</v>
@@ -8539,7 +8539,7 @@
         <v>20008</v>
       </c>
       <c r="C84" t="str">
-        <v>蒋琬-弓箭手 T1</v>
+        <v>华歆-弓箭手 T1</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -8548,7 +8548,7 @@
         <v>1</v>
       </c>
       <c r="F84">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G84">
         <v>3</v>
@@ -8560,13 +8560,13 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K84">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L84">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="M84" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8575,10 +8575,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P84">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q84">
-        <v>611</v>
+        <v>642</v>
       </c>
       <c r="S84">
         <v>1</v>
@@ -8637,7 +8637,7 @@
         <v>20009</v>
       </c>
       <c r="C85" t="str">
-        <v>邓芝-弓箭手 T1</v>
+        <v>阚泽-弓箭手 T1</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -8646,7 +8646,7 @@
         <v>1</v>
       </c>
       <c r="F85">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G85">
         <v>3</v>
@@ -8658,13 +8658,13 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K85">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L85">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="M85" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8673,10 +8673,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P85">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q85">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="S85">
         <v>1</v>
@@ -8735,7 +8735,7 @@
         <v>20010</v>
       </c>
       <c r="C86" t="str">
-        <v>孙乾-弓箭手 T1</v>
+        <v>蒋琬-弓箭手 T1</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -8744,7 +8744,7 @@
         <v>1</v>
       </c>
       <c r="F86">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="G86">
         <v>3</v>
@@ -8756,13 +8756,13 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="K86">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L86">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="M86" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8771,10 +8771,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P86">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q86">
-        <v>643</v>
+        <v>613</v>
       </c>
       <c r="S86">
         <v>1</v>
@@ -8833,7 +8833,7 @@
         <v>20011</v>
       </c>
       <c r="C87" t="str">
-        <v>鲁肃-弓箭手 T1</v>
+        <v>糜竺-弓箭手 T1</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -8842,7 +8842,7 @@
         <v>1</v>
       </c>
       <c r="F87">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G87">
         <v>3</v>
@@ -8854,13 +8854,13 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K87">
         <v>22</v>
       </c>
       <c r="L87">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="M87" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8869,10 +8869,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P87">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q87">
-        <v>617</v>
+        <v>559</v>
       </c>
       <c r="S87">
         <v>1</v>
@@ -8931,7 +8931,7 @@
         <v>20012</v>
       </c>
       <c r="C88" t="str">
-        <v>郭嘉-弓箭手 T1</v>
+        <v>刘晔-弓箭手 T1</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -8940,7 +8940,7 @@
         <v>1</v>
       </c>
       <c r="F88">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G88">
         <v>3</v>
@@ -8952,13 +8952,13 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K88">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L88">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="M88" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8967,10 +8967,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P88">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q88">
-        <v>576</v>
+        <v>652</v>
       </c>
       <c r="S88">
         <v>1</v>
@@ -9029,7 +9029,7 @@
         <v>20013</v>
       </c>
       <c r="C89" t="str">
-        <v>黄月英-弓箭手 T2</v>
+        <v>步练师-弓箭手 T2</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -9038,7 +9038,7 @@
         <v>1</v>
       </c>
       <c r="F89">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="G89">
         <v>4</v>
@@ -9050,13 +9050,13 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="K89">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L89">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="M89" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9065,10 +9065,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P89">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q89">
-        <v>553</v>
+        <v>651</v>
       </c>
       <c r="S89">
         <v>1</v>
@@ -9127,7 +9127,7 @@
         <v>20014</v>
       </c>
       <c r="C90" t="str">
-        <v>阚泽-弓箭手 T2</v>
+        <v>孙乾-弓箭手 T2</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -9136,7 +9136,7 @@
         <v>1</v>
       </c>
       <c r="F90">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G90">
         <v>4</v>
@@ -9148,10 +9148,10 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K90">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L90">
         <v>1.73</v>
@@ -9163,10 +9163,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P90">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q90">
-        <v>644</v>
+        <v>588</v>
       </c>
       <c r="S90">
         <v>1</v>
@@ -9225,7 +9225,7 @@
         <v>20015</v>
       </c>
       <c r="C91" t="str">
-        <v>薛综-弓箭手 T2</v>
+        <v>审配-弓箭手 T2</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -9234,7 +9234,7 @@
         <v>1</v>
       </c>
       <c r="F91">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="G91">
         <v>4</v>
@@ -9246,13 +9246,13 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="K91">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L91">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="M91" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9261,10 +9261,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P91">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q91">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="S91">
         <v>1</v>
@@ -9323,7 +9323,7 @@
         <v>20016</v>
       </c>
       <c r="C92" t="str">
-        <v>顾雍-弓箭手 T2</v>
+        <v>张春华-弓箭手 T2</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -9332,7 +9332,7 @@
         <v>1</v>
       </c>
       <c r="F92">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="G92">
         <v>4</v>
@@ -9347,10 +9347,10 @@
         <v>86</v>
       </c>
       <c r="K92">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L92">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="M92" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9359,10 +9359,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P92">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q92">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="S92">
         <v>1</v>
@@ -9421,7 +9421,7 @@
         <v>20017</v>
       </c>
       <c r="C93" t="str">
-        <v>满宠-弓箭手 T2</v>
+        <v>庞统-弓箭手 T2</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -9430,7 +9430,7 @@
         <v>1</v>
       </c>
       <c r="F93">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G93">
         <v>4</v>
@@ -9442,13 +9442,13 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K93">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L93">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="M93" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9457,10 +9457,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P93">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q93">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="S93">
         <v>1</v>
@@ -9519,7 +9519,7 @@
         <v>20018</v>
       </c>
       <c r="C94" t="str">
-        <v>费祎-弓箭手 T2</v>
+        <v>庞德公-弓箭手 T2</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -9528,7 +9528,7 @@
         <v>1</v>
       </c>
       <c r="F94">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="G94">
         <v>4</v>
@@ -9540,13 +9540,13 @@
         <v>1</v>
       </c>
       <c r="J94">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K94">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L94">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="M94" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9555,10 +9555,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P94">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q94">
-        <v>560</v>
+        <v>622</v>
       </c>
       <c r="S94">
         <v>1</v>
@@ -9617,7 +9617,7 @@
         <v>20019</v>
       </c>
       <c r="C95" t="str">
-        <v>贾诩-弓箭手 T2</v>
+        <v>小乔-弓箭手 T2</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -9626,7 +9626,7 @@
         <v>1</v>
       </c>
       <c r="F95">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="G95">
         <v>4</v>
@@ -9638,13 +9638,13 @@
         <v>1</v>
       </c>
       <c r="J95">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="K95">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L95">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="M95" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9653,10 +9653,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P95">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q95">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="S95">
         <v>1</v>
@@ -9715,7 +9715,7 @@
         <v>20020</v>
       </c>
       <c r="C96" t="str">
-        <v>司马懿-弓箭手 T2</v>
+        <v>辛宪英-弓箭手 T2</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -9724,7 +9724,7 @@
         <v>1</v>
       </c>
       <c r="F96">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G96">
         <v>4</v>
@@ -9736,13 +9736,13 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="K96">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L96">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="M96" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9751,10 +9751,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P96">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q96">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="S96">
         <v>1</v>
@@ -9813,7 +9813,7 @@
         <v>20021</v>
       </c>
       <c r="C97" t="str">
-        <v>诸葛亮-弓箭手 T2</v>
+        <v>陆逊-弓箭手 T2</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -9822,7 +9822,7 @@
         <v>1</v>
       </c>
       <c r="F97">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="G97">
         <v>4</v>
@@ -9834,13 +9834,13 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="K97">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L97">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="M97" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9849,10 +9849,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P97">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q97">
-        <v>559</v>
+        <v>647</v>
       </c>
       <c r="S97">
         <v>1</v>
@@ -9911,7 +9911,7 @@
         <v>20022</v>
       </c>
       <c r="C98" t="str">
-        <v>沮授-弓箭手 T2</v>
+        <v>管辂-弓箭手 T2</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -9920,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="F98">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G98">
         <v>4</v>
@@ -9932,13 +9932,13 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K98">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L98">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="M98" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9947,10 +9947,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P98">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q98">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="S98">
         <v>1</v>
@@ -10009,7 +10009,7 @@
         <v>20023</v>
       </c>
       <c r="C99" t="str">
-        <v>简雍-弓箭手 T2</v>
+        <v>王异-弓箭手 T2</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -10018,7 +10018,7 @@
         <v>1</v>
       </c>
       <c r="F99">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G99">
         <v>4</v>
@@ -10030,13 +10030,13 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="K99">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L99">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="M99" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10048,7 +10048,7 @@
         <v>75</v>
       </c>
       <c r="Q99">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="S99">
         <v>1</v>
@@ -10107,7 +10107,7 @@
         <v>20024</v>
       </c>
       <c r="C100" t="str">
-        <v>徐庶-弓箭手 T2</v>
+        <v>董昭-弓箭手 T2</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -10116,7 +10116,7 @@
         <v>1</v>
       </c>
       <c r="F100">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="G100">
         <v>4</v>
@@ -10128,13 +10128,13 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="K100">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L100">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="M100" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10146,7 +10146,7 @@
         <v>77</v>
       </c>
       <c r="Q100">
-        <v>643</v>
+        <v>620</v>
       </c>
       <c r="S100">
         <v>1</v>
@@ -10205,7 +10205,7 @@
         <v>20025</v>
       </c>
       <c r="C101" t="str">
-        <v>逢纪-弓箭手 T3</v>
+        <v>陈群-弓箭手 T3</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -10214,7 +10214,7 @@
         <v>1</v>
       </c>
       <c r="F101">
-        <v>228</v>
+        <v>291</v>
       </c>
       <c r="G101">
         <v>5</v>
@@ -10226,13 +10226,13 @@
         <v>1</v>
       </c>
       <c r="J101">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K101">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L101">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="M101" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10241,10 +10241,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P101">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q101">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="S101">
         <v>1</v>
@@ -10303,7 +10303,7 @@
         <v>20026</v>
       </c>
       <c r="C102" t="str">
-        <v>陆逊-弓箭手 T3</v>
+        <v>左慈-弓箭手 T3</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -10312,7 +10312,7 @@
         <v>1</v>
       </c>
       <c r="F102">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G102">
         <v>5</v>
@@ -10324,13 +10324,13 @@
         <v>1</v>
       </c>
       <c r="J102">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="K102">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L102">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="M102" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10339,10 +10339,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P102">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q102">
-        <v>566</v>
+        <v>607</v>
       </c>
       <c r="S102">
         <v>1</v>
@@ -10401,7 +10401,7 @@
         <v>20027</v>
       </c>
       <c r="C103" t="str">
-        <v>杨修-弓箭手 T3</v>
+        <v>糜芳-弓箭手 T3</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -10410,7 +10410,7 @@
         <v>1</v>
       </c>
       <c r="F103">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="G103">
         <v>5</v>
@@ -10422,13 +10422,13 @@
         <v>1</v>
       </c>
       <c r="J103">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="K103">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L103">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="M103" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10437,10 +10437,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P103">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q103">
-        <v>549</v>
+        <v>627</v>
       </c>
       <c r="S103">
         <v>1</v>
@@ -10499,7 +10499,7 @@
         <v>20028</v>
       </c>
       <c r="C104" t="str">
-        <v>华佗-弓箭手 T3</v>
+        <v>邓芝-弓箭手 T3</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -10508,7 +10508,7 @@
         <v>1</v>
       </c>
       <c r="F104">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="G104">
         <v>5</v>
@@ -10520,13 +10520,13 @@
         <v>1</v>
       </c>
       <c r="J104">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="K104">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="L104">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="M104" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10535,10 +10535,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P104">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q104">
-        <v>606</v>
+        <v>543</v>
       </c>
       <c r="S104">
         <v>1</v>
@@ -10597,7 +10597,7 @@
         <v>20029</v>
       </c>
       <c r="C105" t="str">
-        <v>黄忠-弓箭手 T3</v>
+        <v>张昭-弓箭手 T3</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -10606,7 +10606,7 @@
         <v>1</v>
       </c>
       <c r="F105">
-        <v>213</v>
+        <v>261</v>
       </c>
       <c r="G105">
         <v>5</v>
@@ -10618,13 +10618,13 @@
         <v>1</v>
       </c>
       <c r="J105">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="K105">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L105">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="M105" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10633,10 +10633,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P105">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q105">
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="S105">
         <v>1</v>
@@ -10695,7 +10695,7 @@
         <v>20030</v>
       </c>
       <c r="C106" t="str">
-        <v>太史慈-弓箭手 T3</v>
+        <v>陈震-弓箭手 T3</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -10704,7 +10704,7 @@
         <v>1</v>
       </c>
       <c r="F106">
-        <v>273</v>
+        <v>204</v>
       </c>
       <c r="G106">
         <v>5</v>
@@ -10716,13 +10716,13 @@
         <v>1</v>
       </c>
       <c r="J106">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K106">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L106">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M106" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10734,7 +10734,7 @@
         <v>78</v>
       </c>
       <c r="Q106">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="S106">
         <v>1</v>
@@ -10793,7 +10793,7 @@
         <v>20031</v>
       </c>
       <c r="C107" t="str">
-        <v>钟繇-弓箭手 T3</v>
+        <v>虞翻-弓箭手 T3</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -10802,7 +10802,7 @@
         <v>1</v>
       </c>
       <c r="F107">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G107">
         <v>5</v>
@@ -10814,13 +10814,13 @@
         <v>1</v>
       </c>
       <c r="J107">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="K107">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L107">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="M107" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10829,10 +10829,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P107">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q107">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="S107">
         <v>1</v>
@@ -10891,7 +10891,7 @@
         <v>20032</v>
       </c>
       <c r="C108" t="str">
-        <v>糜竺-弓箭手 T3</v>
+        <v>蒯良-弓箭手 T3</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -10900,7 +10900,7 @@
         <v>1</v>
       </c>
       <c r="F108">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="G108">
         <v>5</v>
@@ -10912,13 +10912,13 @@
         <v>1</v>
       </c>
       <c r="J108">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K108">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="L108">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="M108" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10927,10 +10927,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P108">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q108">
-        <v>559</v>
+        <v>635</v>
       </c>
       <c r="S108">
         <v>1</v>
@@ -10989,7 +10989,7 @@
         <v>20033</v>
       </c>
       <c r="C109" t="str">
-        <v>庞德公-弓箭手 T3</v>
+        <v>郑玄-弓箭手 T3</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -10998,7 +10998,7 @@
         <v>1</v>
       </c>
       <c r="F109">
-        <v>255</v>
+        <v>201</v>
       </c>
       <c r="G109">
         <v>5</v>
@@ -11010,13 +11010,13 @@
         <v>1</v>
       </c>
       <c r="J109">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K109">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L109">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="M109" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11025,10 +11025,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P109">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q109">
-        <v>545</v>
+        <v>641</v>
       </c>
       <c r="S109">
         <v>1</v>
@@ -11087,7 +11087,7 @@
         <v>20034</v>
       </c>
       <c r="C110" t="str">
-        <v>步骘-弓箭手 T3</v>
+        <v>廖立-弓箭手 T3</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -11096,7 +11096,7 @@
         <v>1</v>
       </c>
       <c r="F110">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="G110">
         <v>5</v>
@@ -11108,13 +11108,13 @@
         <v>1</v>
       </c>
       <c r="J110">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="K110">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L110">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="M110" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11123,10 +11123,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P110">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q110">
-        <v>560</v>
+        <v>598</v>
       </c>
       <c r="S110">
         <v>1</v>
@@ -11185,7 +11185,7 @@
         <v>20035</v>
       </c>
       <c r="C111" t="str">
-        <v>糜芳-弓箭手 T3</v>
+        <v>诸葛瑾-弓箭手 T3</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>1</v>
       </c>
       <c r="F111">
-        <v>286</v>
+        <v>252</v>
       </c>
       <c r="G111">
         <v>5</v>
@@ -11206,13 +11206,13 @@
         <v>1</v>
       </c>
       <c r="J111">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="K111">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L111">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="M111" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11221,10 +11221,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P111">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q111">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="S111">
         <v>1</v>
@@ -11283,7 +11283,7 @@
         <v>20036</v>
       </c>
       <c r="C112" t="str">
-        <v>蒯越-弓箭手 T3</v>
+        <v>王朗-弓箭手 T3</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -11292,7 +11292,7 @@
         <v>1</v>
       </c>
       <c r="F112">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="G112">
         <v>5</v>
@@ -11304,13 +11304,13 @@
         <v>1</v>
       </c>
       <c r="J112">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K112">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="L112">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="M112" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11322,7 +11322,7 @@
         <v>77</v>
       </c>
       <c r="Q112">
-        <v>575</v>
+        <v>632</v>
       </c>
       <c r="S112">
         <v>1</v>
@@ -11381,7 +11381,7 @@
         <v>20037</v>
       </c>
       <c r="C113" t="str">
-        <v>陈震-弓箭手 T4</v>
+        <v>秦宓-弓箭手 T4</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -11390,7 +11390,7 @@
         <v>1</v>
       </c>
       <c r="F113">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="G113">
         <v>6</v>
@@ -11402,13 +11402,13 @@
         <v>1</v>
       </c>
       <c r="J113">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="K113">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="L113">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="M113" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11417,10 +11417,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P113">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q113">
-        <v>622</v>
+        <v>603</v>
       </c>
       <c r="S113">
         <v>1</v>
@@ -11479,7 +11479,7 @@
         <v>20038</v>
       </c>
       <c r="C114" t="str">
-        <v>王异-弓箭手 T4</v>
+        <v>貂蝉-弓箭手 T4</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -11488,7 +11488,7 @@
         <v>1</v>
       </c>
       <c r="F114">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="G114">
         <v>6</v>
@@ -11500,13 +11500,13 @@
         <v>1</v>
       </c>
       <c r="J114">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="K114">
         <v>55</v>
       </c>
       <c r="L114">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="M114" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11515,10 +11515,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P114">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q114">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="S114">
         <v>1</v>
@@ -11577,7 +11577,7 @@
         <v>20039</v>
       </c>
       <c r="C115" t="str">
-        <v>左慈-弓箭手 T4</v>
+        <v>司马懿-弓箭手 T4</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -11586,7 +11586,7 @@
         <v>1</v>
       </c>
       <c r="F115">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="G115">
         <v>6</v>
@@ -11598,13 +11598,13 @@
         <v>1</v>
       </c>
       <c r="J115">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K115">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L115">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M115" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11613,10 +11613,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P115">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q115">
-        <v>647</v>
+        <v>611</v>
       </c>
       <c r="S115">
         <v>1</v>
@@ -11675,7 +11675,7 @@
         <v>20040</v>
       </c>
       <c r="C116" t="str">
-        <v>张昭-弓箭手 T4</v>
+        <v>郭嘉-弓箭手 T4</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -11684,7 +11684,7 @@
         <v>1</v>
       </c>
       <c r="F116">
-        <v>411</v>
+        <v>322</v>
       </c>
       <c r="G116">
         <v>6</v>
@@ -11696,13 +11696,13 @@
         <v>1</v>
       </c>
       <c r="J116">
-        <v>169</v>
+        <v>124</v>
       </c>
       <c r="K116">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L116">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="M116" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11711,10 +11711,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P116">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q116">
-        <v>630</v>
+        <v>588</v>
       </c>
       <c r="S116">
         <v>1</v>
@@ -11773,7 +11773,7 @@
         <v>20041</v>
       </c>
       <c r="C117" t="str">
-        <v>荀彧-弓箭手 T4</v>
+        <v>徐庶-弓箭手 T4</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -11782,7 +11782,7 @@
         <v>1</v>
       </c>
       <c r="F117">
-        <v>373</v>
+        <v>292</v>
       </c>
       <c r="G117">
         <v>6</v>
@@ -11794,13 +11794,13 @@
         <v>1</v>
       </c>
       <c r="J117">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K117">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="L117">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M117" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11809,10 +11809,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P117">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q117">
-        <v>633</v>
+        <v>589</v>
       </c>
       <c r="S117">
         <v>1</v>
@@ -11871,7 +11871,7 @@
         <v>20042</v>
       </c>
       <c r="C118" t="str">
-        <v>审配-弓箭手 T4</v>
+        <v>鲁肃-弓箭手 T4</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -11880,7 +11880,7 @@
         <v>1</v>
       </c>
       <c r="F118">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="G118">
         <v>6</v>
@@ -11892,13 +11892,13 @@
         <v>1</v>
       </c>
       <c r="J118">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="K118">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L118">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="M118" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11907,10 +11907,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P118">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q118">
-        <v>572</v>
+        <v>619</v>
       </c>
       <c r="S118">
         <v>1</v>
@@ -11969,7 +11969,7 @@
         <v>20043</v>
       </c>
       <c r="C119" t="str">
-        <v>宗预-弓箭手 T4</v>
+        <v>陈宫-弓箭手 T4</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -11978,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="F119">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="G119">
         <v>6</v>
@@ -11990,13 +11990,13 @@
         <v>1</v>
       </c>
       <c r="J119">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="K119">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L119">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="M119" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12005,10 +12005,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P119">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q119">
-        <v>622</v>
+        <v>541</v>
       </c>
       <c r="S119">
         <v>1</v>
@@ -12067,7 +12067,7 @@
         <v>20044</v>
       </c>
       <c r="C120" t="str">
-        <v>姜维-弓箭手 T4</v>
+        <v>沮授-弓箭手 T4</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -12076,7 +12076,7 @@
         <v>1</v>
       </c>
       <c r="F120">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="G120">
         <v>6</v>
@@ -12088,13 +12088,13 @@
         <v>1</v>
       </c>
       <c r="J120">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="K120">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L120">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M120" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12103,10 +12103,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P120">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q120">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="S120">
         <v>1</v>
@@ -12165,7 +12165,7 @@
         <v>20045</v>
       </c>
       <c r="C121" t="str">
-        <v>秦宓-弓箭手 T4</v>
+        <v>蒯越-弓箭手 T4</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -12174,7 +12174,7 @@
         <v>1</v>
       </c>
       <c r="F121">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="G121">
         <v>6</v>
@@ -12186,13 +12186,13 @@
         <v>1</v>
       </c>
       <c r="J121">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="K121">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L121">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="M121" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12204,7 +12204,7 @@
         <v>78</v>
       </c>
       <c r="Q121">
-        <v>620</v>
+        <v>542</v>
       </c>
       <c r="S121">
         <v>1</v>
@@ -12263,7 +12263,7 @@
         <v>20046</v>
       </c>
       <c r="C122" t="str">
-        <v>水镜先生-弓箭手 T4</v>
+        <v>蔡文姬-弓箭手 T4</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -12272,7 +12272,7 @@
         <v>1</v>
       </c>
       <c r="F122">
-        <v>335</v>
+        <v>289</v>
       </c>
       <c r="G122">
         <v>6</v>
@@ -12284,13 +12284,13 @@
         <v>1</v>
       </c>
       <c r="J122">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="K122">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L122">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="M122" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12299,10 +12299,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P122">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q122">
-        <v>628</v>
+        <v>659</v>
       </c>
       <c r="S122">
         <v>1</v>
@@ -12361,7 +12361,7 @@
         <v>20047</v>
       </c>
       <c r="C123" t="str">
-        <v>程昱-弓箭手 T4</v>
+        <v>张温-弓箭手 T4</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -12370,7 +12370,7 @@
         <v>1</v>
       </c>
       <c r="F123">
-        <v>290</v>
+        <v>412</v>
       </c>
       <c r="G123">
         <v>6</v>
@@ -12382,13 +12382,13 @@
         <v>1</v>
       </c>
       <c r="J123">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K123">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="L123">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="M123" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12397,10 +12397,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P123">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q123">
-        <v>627</v>
+        <v>595</v>
       </c>
       <c r="S123">
         <v>1</v>
@@ -12459,7 +12459,7 @@
         <v>20048</v>
       </c>
       <c r="C124" t="str">
-        <v>董昭-弓箭手 T4</v>
+        <v>黄月英-弓箭手 T4</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -12468,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="F124">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G124">
         <v>6</v>
@@ -12480,13 +12480,13 @@
         <v>1</v>
       </c>
       <c r="J124">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="K124">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L124">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="M124" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12495,10 +12495,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P124">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q124">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="S124">
         <v>1</v>
@@ -15611,7 +15611,7 @@
         <v>30001</v>
       </c>
       <c r="C155" t="str">
-        <v>楼班-骑兵 T1</v>
+        <v>公孙瓒-骑兵 T1</v>
       </c>
       <c r="D155">
         <v>2</v>
@@ -15620,7 +15620,7 @@
         <v>1</v>
       </c>
       <c r="F155">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="G155">
         <v>3</v>
@@ -15632,13 +15632,13 @@
         <v>1</v>
       </c>
       <c r="J155">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K155">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L155">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="M155" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15650,7 +15650,7 @@
         <v>77</v>
       </c>
       <c r="Q155">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="S155">
         <v>3</v>
@@ -15709,7 +15709,7 @@
         <v>30002</v>
       </c>
       <c r="C156" t="str">
-        <v>樊稠-骑兵 T1</v>
+        <v>马休-骑兵 T1</v>
       </c>
       <c r="D156">
         <v>2</v>
@@ -15718,7 +15718,7 @@
         <v>1</v>
       </c>
       <c r="F156">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G156">
         <v>3</v>
@@ -15730,13 +15730,13 @@
         <v>1</v>
       </c>
       <c r="J156">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="K156">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L156">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="M156" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15745,10 +15745,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P156">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q156">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="S156">
         <v>3</v>
@@ -15807,7 +15807,7 @@
         <v>30003</v>
       </c>
       <c r="C157" t="str">
-        <v>成公英-骑兵 T1</v>
+        <v>公孙渊-骑兵 T1</v>
       </c>
       <c r="D157">
         <v>2</v>
@@ -15816,7 +15816,7 @@
         <v>1</v>
       </c>
       <c r="F157">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G157">
         <v>3</v>
@@ -15828,13 +15828,13 @@
         <v>1</v>
       </c>
       <c r="J157">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K157">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L157">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="M157" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15843,10 +15843,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P157">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q157">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="S157">
         <v>3</v>
@@ -15905,7 +15905,7 @@
         <v>30004</v>
       </c>
       <c r="C158" t="str">
-        <v>张绣-骑兵 T1</v>
+        <v>张辽-骑兵 T1</v>
       </c>
       <c r="D158">
         <v>2</v>
@@ -15914,7 +15914,7 @@
         <v>1</v>
       </c>
       <c r="F158">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G158">
         <v>3</v>
@@ -15926,13 +15926,13 @@
         <v>1</v>
       </c>
       <c r="J158">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="K158">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L158">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="M158" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15941,10 +15941,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P158">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q158">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S158">
         <v>3</v>
@@ -16003,7 +16003,7 @@
         <v>30005</v>
       </c>
       <c r="C159" t="str">
-        <v>郭汜-骑兵 T1</v>
+        <v>马铁-骑兵 T1</v>
       </c>
       <c r="D159">
         <v>2</v>
@@ -16012,7 +16012,7 @@
         <v>1</v>
       </c>
       <c r="F159">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G159">
         <v>3</v>
@@ -16024,13 +16024,13 @@
         <v>1</v>
       </c>
       <c r="J159">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="K159">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L159">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="M159" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16039,10 +16039,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P159">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q159">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="S159">
         <v>3</v>
@@ -16101,7 +16101,7 @@
         <v>30006</v>
       </c>
       <c r="C160" t="str">
-        <v>杨奉-骑兵 T1</v>
+        <v>赵弘-骑兵 T1</v>
       </c>
       <c r="D160">
         <v>2</v>
@@ -16110,7 +16110,7 @@
         <v>1</v>
       </c>
       <c r="F160">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G160">
         <v>3</v>
@@ -16122,13 +16122,13 @@
         <v>1</v>
       </c>
       <c r="J160">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="K160">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L160">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="M160" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16140,7 +16140,7 @@
         <v>78</v>
       </c>
       <c r="Q160">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="S160">
         <v>3</v>
@@ -16199,7 +16199,7 @@
         <v>30007</v>
       </c>
       <c r="C161" t="str">
-        <v>张宝-骑兵 T1</v>
+        <v>郭汜-骑兵 T1</v>
       </c>
       <c r="D161">
         <v>2</v>
@@ -16208,7 +16208,7 @@
         <v>1</v>
       </c>
       <c r="F161">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G161">
         <v>3</v>
@@ -16220,10 +16220,10 @@
         <v>1</v>
       </c>
       <c r="J161">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="K161">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L161">
         <v>1.1</v>
@@ -16235,10 +16235,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P161">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q161">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S161">
         <v>3</v>
@@ -16297,7 +16297,7 @@
         <v>30008</v>
       </c>
       <c r="C162" t="str">
-        <v>夏侯惇-骑兵 T1</v>
+        <v>张角-骑兵 T1</v>
       </c>
       <c r="D162">
         <v>2</v>
@@ -16306,7 +16306,7 @@
         <v>1</v>
       </c>
       <c r="F162">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G162">
         <v>3</v>
@@ -16318,13 +16318,13 @@
         <v>1</v>
       </c>
       <c r="J162">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="K162">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L162">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="M162" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16336,7 +16336,7 @@
         <v>79</v>
       </c>
       <c r="Q162">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="S162">
         <v>3</v>
@@ -16395,7 +16395,7 @@
         <v>30009</v>
       </c>
       <c r="C163" t="str">
-        <v>张济-骑兵 T2</v>
+        <v>曹彰-骑兵 T2</v>
       </c>
       <c r="D163">
         <v>2</v>
@@ -16404,7 +16404,7 @@
         <v>1</v>
       </c>
       <c r="F163">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G163">
         <v>4</v>
@@ -16416,13 +16416,13 @@
         <v>1</v>
       </c>
       <c r="J163">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="K163">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L163">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="M163" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16431,10 +16431,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P163">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q163">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="S163">
         <v>3</v>
@@ -16493,7 +16493,7 @@
         <v>30010</v>
       </c>
       <c r="C164" t="str">
-        <v>马玩-骑兵 T2</v>
+        <v>库察-骑兵 T2</v>
       </c>
       <c r="D164">
         <v>2</v>
@@ -16502,7 +16502,7 @@
         <v>1</v>
       </c>
       <c r="F164">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G164">
         <v>4</v>
@@ -16514,13 +16514,13 @@
         <v>1</v>
       </c>
       <c r="J164">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="K164">
         <v>25</v>
       </c>
       <c r="L164">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M164" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16529,10 +16529,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P164">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q164">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="S164">
         <v>3</v>
@@ -16591,7 +16591,7 @@
         <v>30011</v>
       </c>
       <c r="C165" t="str">
-        <v>牛辅-骑兵 T2</v>
+        <v>樊稠-骑兵 T2</v>
       </c>
       <c r="D165">
         <v>2</v>
@@ -16600,7 +16600,7 @@
         <v>1</v>
       </c>
       <c r="F165">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G165">
         <v>4</v>
@@ -16612,13 +16612,13 @@
         <v>1</v>
       </c>
       <c r="J165">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K165">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L165">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="M165" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16630,7 +16630,7 @@
         <v>76</v>
       </c>
       <c r="Q165">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="S165">
         <v>3</v>
@@ -16689,7 +16689,7 @@
         <v>30012</v>
       </c>
       <c r="C166" t="str">
-        <v>凌统-骑兵 T2</v>
+        <v>侯选-骑兵 T2</v>
       </c>
       <c r="D166">
         <v>2</v>
@@ -16698,7 +16698,7 @@
         <v>1</v>
       </c>
       <c r="F166">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="G166">
         <v>4</v>
@@ -16710,13 +16710,13 @@
         <v>1</v>
       </c>
       <c r="J166">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="K166">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L166">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="M166" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16728,7 +16728,7 @@
         <v>77</v>
       </c>
       <c r="Q166">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="S166">
         <v>3</v>
@@ -16787,7 +16787,7 @@
         <v>30013</v>
       </c>
       <c r="C167" t="str">
-        <v>蹋顿-骑兵 T2</v>
+        <v>程银-骑兵 T2</v>
       </c>
       <c r="D167">
         <v>2</v>
@@ -16796,7 +16796,7 @@
         <v>1</v>
       </c>
       <c r="F167">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -16808,13 +16808,13 @@
         <v>1</v>
       </c>
       <c r="J167">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="K167">
         <v>24</v>
       </c>
       <c r="L167">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="M167" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16823,10 +16823,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P167">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q167">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S167">
         <v>3</v>
@@ -16885,7 +16885,7 @@
         <v>30014</v>
       </c>
       <c r="C168" t="str">
-        <v>段煨-骑兵 T2</v>
+        <v>张济-骑兵 T2</v>
       </c>
       <c r="D168">
         <v>2</v>
@@ -16894,7 +16894,7 @@
         <v>1</v>
       </c>
       <c r="F168">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G168">
         <v>4</v>
@@ -16906,13 +16906,13 @@
         <v>1</v>
       </c>
       <c r="J168">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="K168">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L168">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="M168" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16924,7 +16924,7 @@
         <v>75</v>
       </c>
       <c r="Q168">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S168">
         <v>3</v>
@@ -16983,7 +16983,7 @@
         <v>30015</v>
       </c>
       <c r="C169" t="str">
-        <v>公孙瓒-骑兵 T2</v>
+        <v>孙夏-骑兵 T2</v>
       </c>
       <c r="D169">
         <v>2</v>
@@ -16992,7 +16992,7 @@
         <v>1</v>
       </c>
       <c r="F169">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G169">
         <v>4</v>
@@ -17004,13 +17004,13 @@
         <v>1</v>
       </c>
       <c r="J169">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="K169">
         <v>24</v>
       </c>
       <c r="L169">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="M169" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17019,10 +17019,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P169">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q169">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="S169">
         <v>3</v>
@@ -17081,7 +17081,7 @@
         <v>30016</v>
       </c>
       <c r="C170" t="str">
-        <v>庞德-骑兵 T2</v>
+        <v>梁兴-骑兵 T2</v>
       </c>
       <c r="D170">
         <v>2</v>
@@ -17090,7 +17090,7 @@
         <v>1</v>
       </c>
       <c r="F170">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G170">
         <v>4</v>
@@ -17102,13 +17102,13 @@
         <v>1</v>
       </c>
       <c r="J170">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="K170">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L170">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="M170" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17117,10 +17117,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P170">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q170">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="S170">
         <v>3</v>
@@ -17179,7 +17179,7 @@
         <v>30017</v>
       </c>
       <c r="C171" t="str">
-        <v>程银-骑兵 T3</v>
+        <v>花鬘-骑兵 T3</v>
       </c>
       <c r="D171">
         <v>2</v>
@@ -17188,7 +17188,7 @@
         <v>1</v>
       </c>
       <c r="F171">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G171">
         <v>5</v>
@@ -17200,13 +17200,13 @@
         <v>1</v>
       </c>
       <c r="J171">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="K171">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L171">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="M171" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17215,10 +17215,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P171">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q171">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="S171">
         <v>3</v>
@@ -17277,7 +17277,7 @@
         <v>30018</v>
       </c>
       <c r="C172" t="str">
-        <v>阎行-骑兵 T3</v>
+        <v>张卫-骑兵 T3</v>
       </c>
       <c r="D172">
         <v>2</v>
@@ -17286,7 +17286,7 @@
         <v>1</v>
       </c>
       <c r="F172">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="G172">
         <v>5</v>
@@ -17301,10 +17301,10 @@
         <v>238</v>
       </c>
       <c r="K172">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="L172">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="M172" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17313,10 +17313,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P172">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q172">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="S172">
         <v>3</v>
@@ -17375,7 +17375,7 @@
         <v>30019</v>
       </c>
       <c r="C173" t="str">
-        <v>马云禄-骑兵 T3</v>
+        <v>苏仆延-骑兵 T3</v>
       </c>
       <c r="D173">
         <v>2</v>
@@ -17384,7 +17384,7 @@
         <v>1</v>
       </c>
       <c r="F173">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G173">
         <v>5</v>
@@ -17396,13 +17396,13 @@
         <v>1</v>
       </c>
       <c r="J173">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="K173">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L173">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="M173" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17411,7 +17411,7 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P173">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q173">
         <v>111</v>
@@ -17473,7 +17473,7 @@
         <v>30020</v>
       </c>
       <c r="C174" t="str">
-        <v>苏仆延-骑兵 T3</v>
+        <v>张绣-骑兵 T3</v>
       </c>
       <c r="D174">
         <v>2</v>
@@ -17482,7 +17482,7 @@
         <v>1</v>
       </c>
       <c r="F174">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G174">
         <v>5</v>
@@ -17494,13 +17494,13 @@
         <v>1</v>
       </c>
       <c r="J174">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="K174">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L174">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="M174" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17509,10 +17509,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P174">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q174">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="S174">
         <v>3</v>
@@ -17571,7 +17571,7 @@
         <v>30021</v>
       </c>
       <c r="C175" t="str">
-        <v>张横-骑兵 T3</v>
+        <v>牛辅-骑兵 T3</v>
       </c>
       <c r="D175">
         <v>2</v>
@@ -17580,7 +17580,7 @@
         <v>1</v>
       </c>
       <c r="F175">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="G175">
         <v>5</v>
@@ -17592,13 +17592,13 @@
         <v>1</v>
       </c>
       <c r="J175">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="K175">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L175">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M175" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17610,7 +17610,7 @@
         <v>78</v>
       </c>
       <c r="Q175">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="S175">
         <v>3</v>
@@ -17669,7 +17669,7 @@
         <v>30022</v>
       </c>
       <c r="C176" t="str">
-        <v>花鬘-骑兵 T3</v>
+        <v>孙尚香-骑兵 T3</v>
       </c>
       <c r="D176">
         <v>2</v>
@@ -17678,7 +17678,7 @@
         <v>1</v>
       </c>
       <c r="F176">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="G176">
         <v>5</v>
@@ -17690,13 +17690,13 @@
         <v>1</v>
       </c>
       <c r="J176">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="K176">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L176">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="M176" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17708,7 +17708,7 @@
         <v>76</v>
       </c>
       <c r="Q176">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="S176">
         <v>3</v>
@@ -17767,7 +17767,7 @@
         <v>30023</v>
       </c>
       <c r="C177" t="str">
-        <v>马腾-骑兵 T3</v>
+        <v>段煨-骑兵 T3</v>
       </c>
       <c r="D177">
         <v>2</v>
@@ -17776,7 +17776,7 @@
         <v>1</v>
       </c>
       <c r="F177">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G177">
         <v>5</v>
@@ -17788,13 +17788,13 @@
         <v>1</v>
       </c>
       <c r="J177">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="K177">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L177">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="M177" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17803,7 +17803,7 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P177">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q177">
         <v>116</v>
@@ -17865,7 +17865,7 @@
         <v>30024</v>
       </c>
       <c r="C178" t="str">
-        <v>关索-骑兵 T3</v>
+        <v>董卓-骑兵 T3</v>
       </c>
       <c r="D178">
         <v>2</v>
@@ -17874,7 +17874,7 @@
         <v>1</v>
       </c>
       <c r="F178">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G178">
         <v>5</v>
@@ -17886,13 +17886,13 @@
         <v>1</v>
       </c>
       <c r="J178">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="K178">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L178">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="M178" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17904,7 +17904,7 @@
         <v>79</v>
       </c>
       <c r="Q178">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="S178">
         <v>3</v>
@@ -17963,7 +17963,7 @@
         <v>30025</v>
       </c>
       <c r="C179" t="str">
-        <v>邓茂-骑兵 T4</v>
+        <v>张宝-骑兵 T4</v>
       </c>
       <c r="D179">
         <v>2</v>
@@ -17972,7 +17972,7 @@
         <v>1</v>
       </c>
       <c r="F179">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="G179">
         <v>6</v>
@@ -17984,13 +17984,13 @@
         <v>1</v>
       </c>
       <c r="J179">
-        <v>359</v>
+        <v>317</v>
       </c>
       <c r="K179">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L179">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="M179" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17999,10 +17999,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P179">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q179">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="S179">
         <v>3</v>
@@ -18061,7 +18061,7 @@
         <v>30026</v>
       </c>
       <c r="C180" t="str">
-        <v>李傕-骑兵 T4</v>
+        <v>李儒-骑兵 T4</v>
       </c>
       <c r="D180">
         <v>2</v>
@@ -18070,7 +18070,7 @@
         <v>1</v>
       </c>
       <c r="F180">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="G180">
         <v>6</v>
@@ -18082,13 +18082,13 @@
         <v>1</v>
       </c>
       <c r="J180">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="K180">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L180">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M180" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18097,10 +18097,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P180">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q180">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="S180">
         <v>3</v>
@@ -18159,7 +18159,7 @@
         <v>30027</v>
       </c>
       <c r="C181" t="str">
-        <v>张梁-骑兵 T4</v>
+        <v>李堪-骑兵 T4</v>
       </c>
       <c r="D181">
         <v>2</v>
@@ -18168,7 +18168,7 @@
         <v>1</v>
       </c>
       <c r="F181">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G181">
         <v>6</v>
@@ -18180,13 +18180,13 @@
         <v>1</v>
       </c>
       <c r="J181">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="K181">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L181">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="M181" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18195,10 +18195,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P181">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q181">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="S181">
         <v>3</v>
@@ -18257,7 +18257,7 @@
         <v>30028</v>
       </c>
       <c r="C182" t="str">
-        <v>徐荣-骑兵 T4</v>
+        <v>韩遂-骑兵 T4</v>
       </c>
       <c r="D182">
         <v>2</v>
@@ -18266,7 +18266,7 @@
         <v>1</v>
       </c>
       <c r="F182">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="G182">
         <v>6</v>
@@ -18278,13 +18278,13 @@
         <v>1</v>
       </c>
       <c r="J182">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K182">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L182">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="M182" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18293,10 +18293,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P182">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q182">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="S182">
         <v>3</v>
@@ -18355,7 +18355,7 @@
         <v>30029</v>
       </c>
       <c r="C183" t="str">
-        <v>侯选-骑兵 T4</v>
+        <v>张横-骑兵 T4</v>
       </c>
       <c r="D183">
         <v>2</v>
@@ -18364,7 +18364,7 @@
         <v>1</v>
       </c>
       <c r="F183">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="G183">
         <v>6</v>
@@ -18376,13 +18376,13 @@
         <v>1</v>
       </c>
       <c r="J183">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="K183">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L183">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="M183" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18391,10 +18391,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P183">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q183">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S183">
         <v>3</v>
@@ -18453,7 +18453,7 @@
         <v>30030</v>
       </c>
       <c r="C184" t="str">
-        <v>李堪-骑兵 T4</v>
+        <v>李傕-骑兵 T4</v>
       </c>
       <c r="D184">
         <v>2</v>
@@ -18462,7 +18462,7 @@
         <v>1</v>
       </c>
       <c r="F184">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="G184">
         <v>6</v>
@@ -18474,13 +18474,13 @@
         <v>1</v>
       </c>
       <c r="J184">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="K184">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L184">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="M184" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18489,10 +18489,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P184">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q184">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="S184">
         <v>3</v>
@@ -18551,7 +18551,7 @@
         <v>30031</v>
       </c>
       <c r="C185" t="str">
-        <v>波才-骑兵 T4</v>
+        <v>程远志-骑兵 T4</v>
       </c>
       <c r="D185">
         <v>2</v>
@@ -18560,7 +18560,7 @@
         <v>1</v>
       </c>
       <c r="F185">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="G185">
         <v>6</v>
@@ -18572,13 +18572,13 @@
         <v>1</v>
       </c>
       <c r="J185">
-        <v>330</v>
+        <v>268</v>
       </c>
       <c r="K185">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L185">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="M185" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18590,7 +18590,7 @@
         <v>75</v>
       </c>
       <c r="Q185">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="S185">
         <v>3</v>
@@ -18649,7 +18649,7 @@
         <v>30032</v>
       </c>
       <c r="C186" t="str">
-        <v>张鲁-骑兵 T4</v>
+        <v>杨秋-骑兵 T4</v>
       </c>
       <c r="D186">
         <v>2</v>
@@ -18658,7 +18658,7 @@
         <v>1</v>
       </c>
       <c r="F186">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="G186">
         <v>6</v>
@@ -18670,13 +18670,13 @@
         <v>1</v>
       </c>
       <c r="J186">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="K186">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L186">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="M186" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18685,10 +18685,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P186">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q186">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="S186">
         <v>3</v>
@@ -18951,7 +18951,7 @@
         <v>40001</v>
       </c>
       <c r="C189" t="str">
-        <v>吴兰-长枪兵 T1</v>
+        <v>朱然-长枪兵 T1</v>
       </c>
       <c r="D189">
         <v>3</v>
@@ -18960,7 +18960,7 @@
         <v>1</v>
       </c>
       <c r="F189">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G189">
         <v>3</v>
@@ -18972,13 +18972,13 @@
         <v>1</v>
       </c>
       <c r="J189">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K189">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L189">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="M189" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18987,10 +18987,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P189">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q189">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="S189">
         <v>4</v>
@@ -19049,7 +19049,7 @@
         <v>40002</v>
       </c>
       <c r="C190" t="str">
-        <v>魏续-长枪兵 T1</v>
+        <v>邢道荣-长枪兵 T1</v>
       </c>
       <c r="D190">
         <v>3</v>
@@ -19058,7 +19058,7 @@
         <v>1</v>
       </c>
       <c r="F190">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G190">
         <v>3</v>
@@ -19073,10 +19073,10 @@
         <v>103</v>
       </c>
       <c r="K190">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L190">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="M190" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19085,10 +19085,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P190">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q190">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="S190">
         <v>4</v>
@@ -19147,7 +19147,7 @@
         <v>40003</v>
       </c>
       <c r="C191" t="str">
-        <v>赵范-长枪兵 T1</v>
+        <v>陈就-长枪兵 T1</v>
       </c>
       <c r="D191">
         <v>3</v>
@@ -19156,7 +19156,7 @@
         <v>1</v>
       </c>
       <c r="F191">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G191">
         <v>3</v>
@@ -19168,13 +19168,13 @@
         <v>1</v>
       </c>
       <c r="J191">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="K191">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L191">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="M191" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19186,7 +19186,7 @@
         <v>78</v>
       </c>
       <c r="Q191">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S191">
         <v>4</v>
@@ -19245,7 +19245,7 @@
         <v>40004</v>
       </c>
       <c r="C192" t="str">
-        <v>郝萌-长枪兵 T1</v>
+        <v>潘璋-长枪兵 T1</v>
       </c>
       <c r="D192">
         <v>3</v>
@@ -19266,13 +19266,13 @@
         <v>1</v>
       </c>
       <c r="J192">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="K192">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L192">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="M192" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19281,10 +19281,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P192">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q192">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="S192">
         <v>4</v>
@@ -19343,7 +19343,7 @@
         <v>40005</v>
       </c>
       <c r="C193" t="str">
-        <v>诸葛诞-长枪兵 T1</v>
+        <v>魏续-长枪兵 T1</v>
       </c>
       <c r="D193">
         <v>3</v>
@@ -19352,7 +19352,7 @@
         <v>1</v>
       </c>
       <c r="F193">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G193">
         <v>3</v>
@@ -19364,13 +19364,13 @@
         <v>1</v>
       </c>
       <c r="J193">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="K193">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L193">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="M193" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19379,10 +19379,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P193">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q193">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="S193">
         <v>4</v>
@@ -19441,7 +19441,7 @@
         <v>40006</v>
       </c>
       <c r="C194" t="str">
-        <v>朱然-长枪兵 T1</v>
+        <v>张飞-长枪兵 T1</v>
       </c>
       <c r="D194">
         <v>3</v>
@@ -19450,7 +19450,7 @@
         <v>1</v>
       </c>
       <c r="F194">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G194">
         <v>3</v>
@@ -19462,13 +19462,13 @@
         <v>1</v>
       </c>
       <c r="J194">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="K194">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L194">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="M194" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19477,10 +19477,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P194">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q194">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="S194">
         <v>4</v>
@@ -19539,7 +19539,7 @@
         <v>40007</v>
       </c>
       <c r="C195" t="str">
-        <v>全琮-长枪兵 T1</v>
+        <v>吕介-长枪兵 T1</v>
       </c>
       <c r="D195">
         <v>3</v>
@@ -19548,7 +19548,7 @@
         <v>1</v>
       </c>
       <c r="F195">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G195">
         <v>3</v>
@@ -19560,13 +19560,13 @@
         <v>1</v>
       </c>
       <c r="J195">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="K195">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L195">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="M195" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19575,10 +19575,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P195">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q195">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="S195">
         <v>4</v>
@@ -19637,7 +19637,7 @@
         <v>40008</v>
       </c>
       <c r="C196" t="str">
-        <v>孟达-长枪兵 T1</v>
+        <v>钟会-长枪兵 T1</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -19646,7 +19646,7 @@
         <v>1</v>
       </c>
       <c r="F196">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G196">
         <v>3</v>
@@ -19658,13 +19658,13 @@
         <v>1</v>
       </c>
       <c r="J196">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K196">
         <v>15</v>
       </c>
       <c r="L196">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="M196" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19676,7 +19676,7 @@
         <v>79</v>
       </c>
       <c r="Q196">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S196">
         <v>4</v>
@@ -19735,7 +19735,7 @@
         <v>40009</v>
       </c>
       <c r="C197" t="str">
-        <v>张飞-长枪兵 T2</v>
+        <v>吕据-长枪兵 T2</v>
       </c>
       <c r="D197">
         <v>3</v>
@@ -19744,7 +19744,7 @@
         <v>1</v>
       </c>
       <c r="F197">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="G197">
         <v>4</v>
@@ -19756,13 +19756,13 @@
         <v>1</v>
       </c>
       <c r="J197">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K197">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L197">
-        <v>0.99</v>
+        <v>1.19</v>
       </c>
       <c r="M197" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19771,10 +19771,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P197">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q197">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="S197">
         <v>4</v>
@@ -19833,7 +19833,7 @@
         <v>40010</v>
       </c>
       <c r="C198" t="str">
-        <v>侯成-长枪兵 T2</v>
+        <v>泠苞-长枪兵 T2</v>
       </c>
       <c r="D198">
         <v>3</v>
@@ -19842,7 +19842,7 @@
         <v>1</v>
       </c>
       <c r="F198">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G198">
         <v>4</v>
@@ -19854,13 +19854,13 @@
         <v>1</v>
       </c>
       <c r="J198">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="K198">
         <v>25</v>
       </c>
       <c r="L198">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="M198" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19869,10 +19869,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P198">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q198">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="S198">
         <v>4</v>
@@ -19931,7 +19931,7 @@
         <v>40011</v>
       </c>
       <c r="C199" t="str">
-        <v>成廉-长枪兵 T2</v>
+        <v>吴兰-长枪兵 T2</v>
       </c>
       <c r="D199">
         <v>3</v>
@@ -19940,7 +19940,7 @@
         <v>1</v>
       </c>
       <c r="F199">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="G199">
         <v>4</v>
@@ -19952,13 +19952,13 @@
         <v>1</v>
       </c>
       <c r="J199">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K199">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L199">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="M199" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19967,10 +19967,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P199">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q199">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="S199">
         <v>4</v>
@@ -20029,7 +20029,7 @@
         <v>40012</v>
       </c>
       <c r="C200" t="str">
-        <v>蒋钦-长枪兵 T2</v>
+        <v>邓艾-长枪兵 T2</v>
       </c>
       <c r="D200">
         <v>3</v>
@@ -20038,7 +20038,7 @@
         <v>1</v>
       </c>
       <c r="F200">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G200">
         <v>4</v>
@@ -20050,13 +20050,13 @@
         <v>1</v>
       </c>
       <c r="J200">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="K200">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L200">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="M200" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20068,7 +20068,7 @@
         <v>77</v>
       </c>
       <c r="Q200">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="S200">
         <v>4</v>
@@ -20127,7 +20127,7 @@
         <v>40013</v>
       </c>
       <c r="C201" t="str">
-        <v>句扶-长枪兵 T2</v>
+        <v>唐咨-长枪兵 T2</v>
       </c>
       <c r="D201">
         <v>3</v>
@@ -20136,7 +20136,7 @@
         <v>1</v>
       </c>
       <c r="F201">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="G201">
         <v>4</v>
@@ -20148,13 +20148,13 @@
         <v>1</v>
       </c>
       <c r="J201">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="K201">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L201">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="M201" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20163,10 +20163,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P201">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q201">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="S201">
         <v>4</v>
@@ -20225,7 +20225,7 @@
         <v>40014</v>
       </c>
       <c r="C202" t="str">
-        <v>胡遵-长枪兵 T2</v>
+        <v>赵范-长枪兵 T2</v>
       </c>
       <c r="D202">
         <v>3</v>
@@ -20234,7 +20234,7 @@
         <v>1</v>
       </c>
       <c r="F202">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="G202">
         <v>4</v>
@@ -20246,13 +20246,13 @@
         <v>1</v>
       </c>
       <c r="J202">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="K202">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L202">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="M202" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20261,10 +20261,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P202">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q202">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="S202">
         <v>4</v>
@@ -20323,7 +20323,7 @@
         <v>40015</v>
       </c>
       <c r="C203" t="str">
-        <v>李恢-长枪兵 T2</v>
+        <v>高翔-长枪兵 T2</v>
       </c>
       <c r="D203">
         <v>3</v>
@@ -20332,7 +20332,7 @@
         <v>1</v>
       </c>
       <c r="F203">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G203">
         <v>4</v>
@@ -20344,13 +20344,13 @@
         <v>1</v>
       </c>
       <c r="J203">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="K203">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L203">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="M203" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20359,10 +20359,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P203">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q203">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="S203">
         <v>4</v>
@@ -20421,7 +20421,7 @@
         <v>40016</v>
       </c>
       <c r="C204" t="str">
-        <v>刘贤-长枪兵 T2</v>
+        <v>高顺-长枪兵 T2</v>
       </c>
       <c r="D204">
         <v>3</v>
@@ -20430,7 +20430,7 @@
         <v>1</v>
       </c>
       <c r="F204">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G204">
         <v>4</v>
@@ -20442,13 +20442,13 @@
         <v>1</v>
       </c>
       <c r="J204">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="K204">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L204">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="M204" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20457,10 +20457,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P204">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q204">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="S204">
         <v>4</v>
@@ -20519,7 +20519,7 @@
         <v>40017</v>
       </c>
       <c r="C205" t="str">
-        <v>董袭-长枪兵 T3</v>
+        <v>胡遵-长枪兵 T3</v>
       </c>
       <c r="D205">
         <v>3</v>
@@ -20528,7 +20528,7 @@
         <v>1</v>
       </c>
       <c r="F205">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G205">
         <v>5</v>
@@ -20540,13 +20540,13 @@
         <v>1</v>
       </c>
       <c r="J205">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="K205">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L205">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="M205" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20555,10 +20555,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P205">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q205">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="S205">
         <v>4</v>
@@ -20617,7 +20617,7 @@
         <v>40018</v>
       </c>
       <c r="C206" t="str">
-        <v>王基-长枪兵 T3</v>
+        <v>陈武-长枪兵 T3</v>
       </c>
       <c r="D206">
         <v>3</v>
@@ -20626,7 +20626,7 @@
         <v>1</v>
       </c>
       <c r="F206">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="G206">
         <v>5</v>
@@ -20638,13 +20638,13 @@
         <v>1</v>
       </c>
       <c r="J206">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K206">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L206">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M206" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20653,10 +20653,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P206">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q206">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="S206">
         <v>4</v>
@@ -20715,7 +20715,7 @@
         <v>40019</v>
       </c>
       <c r="C207" t="str">
-        <v>杨龄-长枪兵 T3</v>
+        <v>任夔-长枪兵 T3</v>
       </c>
       <c r="D207">
         <v>3</v>
@@ -20724,7 +20724,7 @@
         <v>1</v>
       </c>
       <c r="F207">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G207">
         <v>5</v>
@@ -20736,13 +20736,13 @@
         <v>1</v>
       </c>
       <c r="J207">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="K207">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L207">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="M207" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20751,10 +20751,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P207">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q207">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="S207">
         <v>4</v>
@@ -20813,7 +20813,7 @@
         <v>40020</v>
       </c>
       <c r="C208" t="str">
-        <v>邢道荣-长枪兵 T3</v>
+        <v>李恢-长枪兵 T3</v>
       </c>
       <c r="D208">
         <v>3</v>
@@ -20822,7 +20822,7 @@
         <v>1</v>
       </c>
       <c r="F208">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G208">
         <v>5</v>
@@ -20834,13 +20834,13 @@
         <v>1</v>
       </c>
       <c r="J208">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="K208">
         <v>29</v>
       </c>
       <c r="L208">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="M208" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20849,10 +20849,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P208">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q208">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="S208">
         <v>4</v>
@@ -20911,7 +20911,7 @@
         <v>40021</v>
       </c>
       <c r="C209" t="str">
-        <v>黄权-长枪兵 T3</v>
+        <v>杨龄-长枪兵 T3</v>
       </c>
       <c r="D209">
         <v>3</v>
@@ -20920,7 +20920,7 @@
         <v>1</v>
       </c>
       <c r="F209">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G209">
         <v>5</v>
@@ -20932,13 +20932,13 @@
         <v>1</v>
       </c>
       <c r="J209">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="K209">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L209">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="M209" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20947,10 +20947,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P209">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q209">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S209">
         <v>4</v>
@@ -21009,7 +21009,7 @@
         <v>40022</v>
       </c>
       <c r="C210" t="str">
-        <v>邓贤-长枪兵 T3</v>
+        <v>王平-长枪兵 T3</v>
       </c>
       <c r="D210">
         <v>3</v>
@@ -21018,7 +21018,7 @@
         <v>1</v>
       </c>
       <c r="F210">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="G210">
         <v>5</v>
@@ -21030,13 +21030,13 @@
         <v>1</v>
       </c>
       <c r="J210">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="K210">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L210">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="M210" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21045,10 +21045,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P210">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q210">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="S210">
         <v>4</v>
@@ -21107,7 +21107,7 @@
         <v>40023</v>
       </c>
       <c r="C211" t="str">
-        <v>泠苞-长枪兵 T3</v>
+        <v>严颜-长枪兵 T3</v>
       </c>
       <c r="D211">
         <v>3</v>
@@ -21116,7 +21116,7 @@
         <v>1</v>
       </c>
       <c r="F211">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="G211">
         <v>5</v>
@@ -21128,13 +21128,13 @@
         <v>1</v>
       </c>
       <c r="J211">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="K211">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L211">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="M211" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21143,10 +21143,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P211">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q211">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S211">
         <v>4</v>
@@ -21205,7 +21205,7 @@
         <v>40024</v>
       </c>
       <c r="C212" t="str">
-        <v>张嶷-长枪兵 T3</v>
+        <v>鲍隆-长枪兵 T3</v>
       </c>
       <c r="D212">
         <v>3</v>
@@ -21214,7 +21214,7 @@
         <v>1</v>
       </c>
       <c r="F212">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="G212">
         <v>5</v>
@@ -21226,13 +21226,13 @@
         <v>1</v>
       </c>
       <c r="J212">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="K212">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L212">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M212" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21241,10 +21241,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P212">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q212">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="S212">
         <v>4</v>
@@ -21303,7 +21303,7 @@
         <v>40025</v>
       </c>
       <c r="C213" t="str">
-        <v>唐咨-长枪兵 T4</v>
+        <v>纪灵-长枪兵 T4</v>
       </c>
       <c r="D213">
         <v>3</v>
@@ -21312,7 +21312,7 @@
         <v>1</v>
       </c>
       <c r="F213">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="G213">
         <v>6</v>
@@ -21324,13 +21324,13 @@
         <v>1</v>
       </c>
       <c r="J213">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K213">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L213">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="M213" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21339,10 +21339,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P213">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q213">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="S213">
         <v>4</v>
@@ -21401,7 +21401,7 @@
         <v>40026</v>
       </c>
       <c r="C214" t="str">
-        <v>雷铜-长枪兵 T4</v>
+        <v>孙礼-长枪兵 T4</v>
       </c>
       <c r="D214">
         <v>3</v>
@@ -21410,7 +21410,7 @@
         <v>1</v>
       </c>
       <c r="F214">
-        <v>312</v>
+        <v>273</v>
       </c>
       <c r="G214">
         <v>6</v>
@@ -21422,13 +21422,13 @@
         <v>1</v>
       </c>
       <c r="J214">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="K214">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="L214">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M214" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21437,10 +21437,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P214">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q214">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="S214">
         <v>4</v>
@@ -21508,7 +21508,7 @@
         <v>1</v>
       </c>
       <c r="F215">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="G215">
         <v>6</v>
@@ -21520,13 +21520,13 @@
         <v>1</v>
       </c>
       <c r="J215">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="K215">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L215">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="M215" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21535,10 +21535,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P215">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q215">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="S215">
         <v>4</v>
@@ -21597,7 +21597,7 @@
         <v>40028</v>
       </c>
       <c r="C216" t="str">
-        <v>孙礼-长枪兵 T4</v>
+        <v>韩玄-长枪兵 T4</v>
       </c>
       <c r="D216">
         <v>3</v>
@@ -21606,7 +21606,7 @@
         <v>1</v>
       </c>
       <c r="F216">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="G216">
         <v>6</v>
@@ -21618,13 +21618,13 @@
         <v>1</v>
       </c>
       <c r="J216">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="K216">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L216">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M216" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21636,7 +21636,7 @@
         <v>79</v>
       </c>
       <c r="Q216">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="S216">
         <v>4</v>
@@ -21695,7 +21695,7 @@
         <v>40029</v>
       </c>
       <c r="C217" t="str">
-        <v>柳隐-长枪兵 T4</v>
+        <v>文鸯-长枪兵 T4</v>
       </c>
       <c r="D217">
         <v>3</v>
@@ -21704,7 +21704,7 @@
         <v>1</v>
       </c>
       <c r="F217">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="G217">
         <v>6</v>
@@ -21716,13 +21716,13 @@
         <v>1</v>
       </c>
       <c r="J217">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="K217">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L217">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="M217" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21734,7 +21734,7 @@
         <v>76</v>
       </c>
       <c r="Q217">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="S217">
         <v>4</v>
@@ -21793,7 +21793,7 @@
         <v>40030</v>
       </c>
       <c r="C218" t="str">
-        <v>吕据-长枪兵 T4</v>
+        <v>李严-长枪兵 T4</v>
       </c>
       <c r="D218">
         <v>3</v>
@@ -21802,7 +21802,7 @@
         <v>1</v>
       </c>
       <c r="F218">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="G218">
         <v>6</v>
@@ -21814,13 +21814,13 @@
         <v>1</v>
       </c>
       <c r="J218">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="K218">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L218">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="M218" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21829,10 +21829,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P218">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q218">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="S218">
         <v>4</v>
@@ -21891,7 +21891,7 @@
         <v>40031</v>
       </c>
       <c r="C219" t="str">
-        <v>胡济-长枪兵 T4</v>
+        <v>刘璝-长枪兵 T4</v>
       </c>
       <c r="D219">
         <v>3</v>
@@ -21900,7 +21900,7 @@
         <v>1</v>
       </c>
       <c r="F219">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="G219">
         <v>6</v>
@@ -21912,13 +21912,13 @@
         <v>1</v>
       </c>
       <c r="J219">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K219">
         <v>44</v>
       </c>
       <c r="L219">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="M219" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21927,10 +21927,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P219">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q219">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="S219">
         <v>4</v>
@@ -21989,7 +21989,7 @@
         <v>40032</v>
       </c>
       <c r="C220" t="str">
-        <v>高顺-长枪兵 T4</v>
+        <v>吴懿-长枪兵 T4</v>
       </c>
       <c r="D220">
         <v>3</v>
@@ -21998,7 +21998,7 @@
         <v>1</v>
       </c>
       <c r="F220">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="G220">
         <v>6</v>
@@ -22010,13 +22010,13 @@
         <v>1</v>
       </c>
       <c r="J220">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="K220">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L220">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="M220" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22025,10 +22025,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P220">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q220">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="S220">
         <v>4</v>
@@ -25563,7 +25563,7 @@
         <v>90001</v>
       </c>
       <c r="C256" t="str">
-        <v>【零号病毒】关樾-步兵 T1</v>
+        <v>【变异主宰】甘宁-步兵 T1</v>
       </c>
       <c r="D256">
         <v>0</v>
@@ -25572,7 +25572,7 @@
         <v>20</v>
       </c>
       <c r="F256">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="G256">
         <v>3</v>
@@ -25584,13 +25584,13 @@
         <v>1</v>
       </c>
       <c r="J256">
-        <v>483</v>
+        <v>555</v>
       </c>
       <c r="K256">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L256">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="M256" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25599,10 +25599,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P256">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q256">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="S256">
         <v>0</v>
@@ -25661,7 +25661,7 @@
         <v>90002</v>
       </c>
       <c r="C257" t="str">
-        <v>【钢铁暴君】孙策-步兵 T1</v>
+        <v>【零号病毒】张燕-步兵 T1</v>
       </c>
       <c r="D257">
         <v>0</v>
@@ -25670,7 +25670,7 @@
         <v>20</v>
       </c>
       <c r="F257">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="G257">
         <v>3</v>
@@ -25682,13 +25682,13 @@
         <v>1</v>
       </c>
       <c r="J257">
-        <v>609</v>
+        <v>527</v>
       </c>
       <c r="K257">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L257">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="M257" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25759,7 +25759,7 @@
         <v>90003</v>
       </c>
       <c r="C258" t="str">
-        <v>【极秘项目】刘备-步兵 T1</v>
+        <v>【零号病毒】马忠-步兵 T1</v>
       </c>
       <c r="D258">
         <v>0</v>
@@ -25768,7 +25768,7 @@
         <v>20</v>
       </c>
       <c r="F258">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="G258">
         <v>3</v>
@@ -25780,13 +25780,13 @@
         <v>1</v>
       </c>
       <c r="J258">
-        <v>589</v>
+        <v>666</v>
       </c>
       <c r="K258">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L258">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="M258" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25795,10 +25795,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P258">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q258">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="S258">
         <v>0</v>
@@ -25857,7 +25857,7 @@
         <v>90004</v>
       </c>
       <c r="C259" t="str">
-        <v>【末日先兆】蒋义渠-步兵 T2</v>
+        <v>【零号病毒】张南-步兵 T2</v>
       </c>
       <c r="D259">
         <v>0</v>
@@ -25866,7 +25866,7 @@
         <v>20</v>
       </c>
       <c r="F259">
-        <v>397</v>
+        <v>337</v>
       </c>
       <c r="G259">
         <v>4</v>
@@ -25878,13 +25878,13 @@
         <v>1</v>
       </c>
       <c r="J259">
-        <v>1077</v>
+        <v>873</v>
       </c>
       <c r="K259">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L259">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="M259" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25893,10 +25893,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P259">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q259">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S259">
         <v>0</v>
@@ -25955,7 +25955,7 @@
         <v>90005</v>
       </c>
       <c r="C260" t="str">
-        <v>【极秘项目】朱桓-步兵 T2</v>
+        <v>【变异主宰】关羽-步兵 T2</v>
       </c>
       <c r="D260">
         <v>0</v>
@@ -25964,7 +25964,7 @@
         <v>20</v>
       </c>
       <c r="F260">
-        <v>384</v>
+        <v>313</v>
       </c>
       <c r="G260">
         <v>4</v>
@@ -25976,13 +25976,13 @@
         <v>1</v>
       </c>
       <c r="J260">
-        <v>1023</v>
+        <v>826</v>
       </c>
       <c r="K260">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L260">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="M260" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25991,10 +25991,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P260">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q260">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="S260">
         <v>0</v>
@@ -26053,7 +26053,7 @@
         <v>90006</v>
       </c>
       <c r="C261" t="str">
-        <v>【虚空母体】关羽-步兵 T2</v>
+        <v>【末日先兆】马延-步兵 T2</v>
       </c>
       <c r="D261">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>20</v>
       </c>
       <c r="F261">
-        <v>282</v>
+        <v>349</v>
       </c>
       <c r="G261">
         <v>4</v>
@@ -26074,13 +26074,13 @@
         <v>1</v>
       </c>
       <c r="J261">
-        <v>742</v>
+        <v>999</v>
       </c>
       <c r="K261">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L261">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="M261" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26089,10 +26089,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P261">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q261">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="S261">
         <v>0</v>
@@ -26151,7 +26151,7 @@
         <v>90007</v>
       </c>
       <c r="C262" t="str">
-        <v>【零号病毒】高干-步兵 T3</v>
+        <v>【钢铁暴君】曹操-步兵 T3</v>
       </c>
       <c r="D262">
         <v>0</v>
@@ -26160,7 +26160,7 @@
         <v>20</v>
       </c>
       <c r="F262">
-        <v>450</v>
+        <v>554</v>
       </c>
       <c r="G262">
         <v>5</v>
@@ -26172,13 +26172,13 @@
         <v>1</v>
       </c>
       <c r="J262">
-        <v>1056</v>
+        <v>1417</v>
       </c>
       <c r="K262">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L262">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="M262" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26187,10 +26187,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P262">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q262">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="S262">
         <v>0</v>
@@ -26249,7 +26249,7 @@
         <v>90008</v>
       </c>
       <c r="C263" t="str">
-        <v>【变异主宰】文丑-步兵 T3</v>
+        <v>【末日先兆】刘备-步兵 T3</v>
       </c>
       <c r="D263">
         <v>0</v>
@@ -26258,7 +26258,7 @@
         <v>20</v>
       </c>
       <c r="F263">
-        <v>439</v>
+        <v>505</v>
       </c>
       <c r="G263">
         <v>5</v>
@@ -26270,13 +26270,13 @@
         <v>1</v>
       </c>
       <c r="J263">
-        <v>1008</v>
+        <v>1209</v>
       </c>
       <c r="K263">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L263">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="M263" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26285,10 +26285,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P263">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q263">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="S263">
         <v>0</v>
@@ -26347,7 +26347,7 @@
         <v>90009</v>
       </c>
       <c r="C264" t="str">
-        <v>【极秘项目】许褚-步兵 T3</v>
+        <v>【零号病毒】吕翔-步兵 T3</v>
       </c>
       <c r="D264">
         <v>0</v>
@@ -26356,7 +26356,7 @@
         <v>20</v>
       </c>
       <c r="F264">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="G264">
         <v>5</v>
@@ -26368,13 +26368,13 @@
         <v>1</v>
       </c>
       <c r="J264">
-        <v>1069</v>
+        <v>1125</v>
       </c>
       <c r="K264">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L264">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="M264" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26383,10 +26383,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P264">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q264">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="S264">
         <v>0</v>
@@ -26445,7 +26445,7 @@
         <v>90010</v>
       </c>
       <c r="C265" t="str">
-        <v>【极秘项目】焦触-步兵 T4</v>
+        <v>【末日先兆】程普-步兵 T4</v>
       </c>
       <c r="D265">
         <v>0</v>
@@ -26454,7 +26454,7 @@
         <v>20</v>
       </c>
       <c r="F265">
-        <v>554</v>
+        <v>698</v>
       </c>
       <c r="G265">
         <v>6</v>
@@ -26466,13 +26466,13 @@
         <v>1</v>
       </c>
       <c r="J265">
-        <v>1228</v>
+        <v>1536</v>
       </c>
       <c r="K265">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L265">
-        <v>0.9</v>
+        <v>1.04</v>
       </c>
       <c r="M265" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26481,10 +26481,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P265">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q265">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="S265">
         <v>0</v>
@@ -26543,7 +26543,7 @@
         <v>90011</v>
       </c>
       <c r="C266" t="str">
-        <v>【虚空母体】周泰-步兵 T4</v>
+        <v>【虚空母体】蒋舒-步兵 T4</v>
       </c>
       <c r="D266">
         <v>0</v>
@@ -26552,7 +26552,7 @@
         <v>20</v>
       </c>
       <c r="F266">
-        <v>637</v>
+        <v>594</v>
       </c>
       <c r="G266">
         <v>6</v>
@@ -26564,13 +26564,13 @@
         <v>1</v>
       </c>
       <c r="J266">
-        <v>1392</v>
+        <v>1232</v>
       </c>
       <c r="K266">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L266">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="M266" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26579,10 +26579,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P266">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q266">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="S266">
         <v>0</v>
@@ -26641,7 +26641,7 @@
         <v>90012</v>
       </c>
       <c r="C267" t="str">
-        <v>【零号病毒】胡车儿-步兵 T4</v>
+        <v>【虚空母体】祖茂-步兵 T4</v>
       </c>
       <c r="D267">
         <v>0</v>
@@ -26650,7 +26650,7 @@
         <v>20</v>
       </c>
       <c r="F267">
-        <v>559</v>
+        <v>663</v>
       </c>
       <c r="G267">
         <v>6</v>
@@ -26662,10 +26662,10 @@
         <v>1</v>
       </c>
       <c r="J267">
-        <v>1246</v>
+        <v>1434</v>
       </c>
       <c r="K267">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L267">
         <v>0.95</v>
@@ -26677,7 +26677,7 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P267">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q267">
         <v>98</v>
@@ -26739,7 +26739,7 @@
         <v>90013</v>
       </c>
       <c r="C268" t="str">
-        <v>【极秘项目】步练师-弓箭手 T1</v>
+        <v>【钢铁暴君】姜维-弓箭手 T1</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -26748,7 +26748,7 @@
         <v>20</v>
       </c>
       <c r="F268">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="G268">
         <v>3</v>
@@ -26760,13 +26760,13 @@
         <v>1</v>
       </c>
       <c r="J268">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="K268">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L268">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="M268" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26775,10 +26775,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P268">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q268">
-        <v>641</v>
+        <v>607</v>
       </c>
       <c r="S268">
         <v>1</v>
@@ -26837,7 +26837,7 @@
         <v>90014</v>
       </c>
       <c r="C269" t="str">
-        <v>【变异主宰】祝融-弓箭手 T1</v>
+        <v>【极秘项目】水镜先生-弓箭手 T1</v>
       </c>
       <c r="D269">
         <v>1</v>
@@ -26846,7 +26846,7 @@
         <v>20</v>
       </c>
       <c r="F269">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="G269">
         <v>3</v>
@@ -26858,13 +26858,13 @@
         <v>1</v>
       </c>
       <c r="J269">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="K269">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L269">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="M269" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26876,7 +26876,7 @@
         <v>78</v>
       </c>
       <c r="Q269">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="S269">
         <v>1</v>
@@ -26935,7 +26935,7 @@
         <v>90015</v>
       </c>
       <c r="C270" t="str">
-        <v>【末日先兆】廖立-弓箭手 T1</v>
+        <v>【虚空母体】步骘-弓箭手 T1</v>
       </c>
       <c r="D270">
         <v>1</v>
@@ -26944,7 +26944,7 @@
         <v>20</v>
       </c>
       <c r="F270">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="G270">
         <v>3</v>
@@ -26956,13 +26956,13 @@
         <v>1</v>
       </c>
       <c r="J270">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="K270">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L270">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="M270" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26971,10 +26971,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P270">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q270">
-        <v>592</v>
+        <v>657</v>
       </c>
       <c r="S270">
         <v>1</v>
@@ -27033,7 +27033,7 @@
         <v>90016</v>
       </c>
       <c r="C271" t="str">
-        <v>【钢铁暴君】甄姬-弓箭手 T2</v>
+        <v>【零号病毒】贾诩-弓箭手 T2</v>
       </c>
       <c r="D271">
         <v>1</v>
@@ -27042,7 +27042,7 @@
         <v>20</v>
       </c>
       <c r="F271">
-        <v>430</v>
+        <v>384</v>
       </c>
       <c r="G271">
         <v>4</v>
@@ -27054,13 +27054,13 @@
         <v>1</v>
       </c>
       <c r="J271">
-        <v>401</v>
+        <v>319</v>
       </c>
       <c r="K271">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L271">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="M271" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27069,10 +27069,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P271">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q271">
-        <v>637</v>
+        <v>573</v>
       </c>
       <c r="S271">
         <v>1</v>
@@ -27131,7 +27131,7 @@
         <v>90017</v>
       </c>
       <c r="C272" t="str">
-        <v>【虚空母体】周瑜-弓箭手 T2</v>
+        <v>【极秘项目】祝融-弓箭手 T2</v>
       </c>
       <c r="D272">
         <v>1</v>
@@ -27140,7 +27140,7 @@
         <v>20</v>
       </c>
       <c r="F272">
-        <v>478</v>
+        <v>420</v>
       </c>
       <c r="G272">
         <v>4</v>
@@ -27152,13 +27152,13 @@
         <v>1</v>
       </c>
       <c r="J272">
-        <v>417</v>
+        <v>346</v>
       </c>
       <c r="K272">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L272">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="M272" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27170,7 +27170,7 @@
         <v>76</v>
       </c>
       <c r="Q272">
-        <v>574</v>
+        <v>609</v>
       </c>
       <c r="S272">
         <v>1</v>
@@ -27229,7 +27229,7 @@
         <v>90018</v>
       </c>
       <c r="C273" t="str">
-        <v>【末日先兆】辛宪英-弓箭手 T2</v>
+        <v>【末日先兆】伊籍-弓箭手 T2</v>
       </c>
       <c r="D273">
         <v>1</v>
@@ -27238,7 +27238,7 @@
         <v>20</v>
       </c>
       <c r="F273">
-        <v>357</v>
+        <v>435</v>
       </c>
       <c r="G273">
         <v>4</v>
@@ -27250,13 +27250,13 @@
         <v>1</v>
       </c>
       <c r="J273">
-        <v>362</v>
+        <v>328</v>
       </c>
       <c r="K273">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L273">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="M273" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27265,10 +27265,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P273">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q273">
-        <v>616</v>
+        <v>558</v>
       </c>
       <c r="S273">
         <v>1</v>
@@ -27327,7 +27327,7 @@
         <v>90019</v>
       </c>
       <c r="C274" t="str">
-        <v>【极秘项目】张温-弓箭手 T3</v>
+        <v>【变异主宰】程昱-弓箭手 T3</v>
       </c>
       <c r="D274">
         <v>1</v>
@@ -27336,7 +27336,7 @@
         <v>20</v>
       </c>
       <c r="F274">
-        <v>604</v>
+        <v>631</v>
       </c>
       <c r="G274">
         <v>5</v>
@@ -27348,13 +27348,13 @@
         <v>1</v>
       </c>
       <c r="J274">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="K274">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L274">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="M274" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27363,10 +27363,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P274">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q274">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="S274">
         <v>1</v>
@@ -27425,7 +27425,7 @@
         <v>90020</v>
       </c>
       <c r="C275" t="str">
-        <v>【变异主宰】大乔-弓箭手 T3</v>
+        <v>【虚空母体】宗预-弓箭手 T3</v>
       </c>
       <c r="D275">
         <v>1</v>
@@ -27434,7 +27434,7 @@
         <v>20</v>
       </c>
       <c r="F275">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="G275">
         <v>5</v>
@@ -27446,13 +27446,13 @@
         <v>1</v>
       </c>
       <c r="J275">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="K275">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="L275">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="M275" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27464,7 +27464,7 @@
         <v>77</v>
       </c>
       <c r="Q275">
-        <v>544</v>
+        <v>605</v>
       </c>
       <c r="S275">
         <v>1</v>
@@ -27523,7 +27523,7 @@
         <v>90021</v>
       </c>
       <c r="C276" t="str">
-        <v>【零号病毒】华歆-弓箭手 T3</v>
+        <v>【变异主宰】周瑜-弓箭手 T3</v>
       </c>
       <c r="D276">
         <v>1</v>
@@ -27532,7 +27532,7 @@
         <v>20</v>
       </c>
       <c r="F276">
-        <v>600</v>
+        <v>706</v>
       </c>
       <c r="G276">
         <v>5</v>
@@ -27544,13 +27544,13 @@
         <v>1</v>
       </c>
       <c r="J276">
-        <v>437</v>
+        <v>540</v>
       </c>
       <c r="K276">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L276">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="M276" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27559,10 +27559,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P276">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q276">
-        <v>635</v>
+        <v>598</v>
       </c>
       <c r="S276">
         <v>1</v>
@@ -27621,7 +27621,7 @@
         <v>90022</v>
       </c>
       <c r="C277" t="str">
-        <v>【变异主宰】伊籍-弓箭手 T4</v>
+        <v>【虚空母体】黄忠-弓箭手 T4</v>
       </c>
       <c r="D277">
         <v>1</v>
@@ -27630,7 +27630,7 @@
         <v>20</v>
       </c>
       <c r="F277">
-        <v>743</v>
+        <v>963</v>
       </c>
       <c r="G277">
         <v>6</v>
@@ -27642,13 +27642,13 @@
         <v>1</v>
       </c>
       <c r="J277">
-        <v>579</v>
+        <v>697</v>
       </c>
       <c r="K277">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="L277">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="M277" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27657,10 +27657,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P277">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q277">
-        <v>647</v>
+        <v>572</v>
       </c>
       <c r="S277">
         <v>1</v>
@@ -27719,7 +27719,7 @@
         <v>90023</v>
       </c>
       <c r="C278" t="str">
-        <v>【零号病毒】陈群-弓箭手 T4</v>
+        <v>【末日先兆】华佗-弓箭手 T4</v>
       </c>
       <c r="D278">
         <v>1</v>
@@ -27728,7 +27728,7 @@
         <v>20</v>
       </c>
       <c r="F278">
-        <v>933</v>
+        <v>762</v>
       </c>
       <c r="G278">
         <v>6</v>
@@ -27740,13 +27740,13 @@
         <v>1</v>
       </c>
       <c r="J278">
-        <v>646</v>
+        <v>664</v>
       </c>
       <c r="K278">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L278">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="M278" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27758,7 +27758,7 @@
         <v>78</v>
       </c>
       <c r="Q278">
-        <v>574</v>
+        <v>547</v>
       </c>
       <c r="S278">
         <v>1</v>
@@ -27817,7 +27817,7 @@
         <v>90024</v>
       </c>
       <c r="C279" t="str">
-        <v>【虚空母体】诸葛瑾-弓箭手 T4</v>
+        <v>【变异主宰】太史慈-弓箭手 T4</v>
       </c>
       <c r="D279">
         <v>1</v>
@@ -27826,7 +27826,7 @@
         <v>20</v>
       </c>
       <c r="F279">
-        <v>919</v>
+        <v>838</v>
       </c>
       <c r="G279">
         <v>6</v>
@@ -27838,13 +27838,13 @@
         <v>1</v>
       </c>
       <c r="J279">
-        <v>576</v>
+        <v>676</v>
       </c>
       <c r="K279">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="L279">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="M279" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27856,7 +27856,7 @@
         <v>78</v>
       </c>
       <c r="Q279">
-        <v>615</v>
+        <v>642</v>
       </c>
       <c r="S279">
         <v>1</v>
@@ -27915,7 +27915,7 @@
         <v>90025</v>
       </c>
       <c r="C280" t="str">
-        <v>【极秘项目】韩忠-骑兵 T1</v>
+        <v>【末日先兆】张鲁-骑兵 T1</v>
       </c>
       <c r="D280">
         <v>2</v>
@@ -27924,7 +27924,7 @@
         <v>20</v>
       </c>
       <c r="F280">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="G280">
         <v>3</v>
@@ -27936,13 +27936,13 @@
         <v>1</v>
       </c>
       <c r="J280">
-        <v>492</v>
+        <v>556</v>
       </c>
       <c r="K280">
         <v>26</v>
       </c>
       <c r="L280">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="M280" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27951,10 +27951,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P280">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q280">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="S280">
         <v>3</v>
@@ -28013,7 +28013,7 @@
         <v>90026</v>
       </c>
       <c r="C281" t="str">
-        <v>【零号病毒】曹彰-骑兵 T1</v>
+        <v>【极秘项目】赵云-骑兵 T1</v>
       </c>
       <c r="D281">
         <v>2</v>
@@ -28022,7 +28022,7 @@
         <v>20</v>
       </c>
       <c r="F281">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="G281">
         <v>3</v>
@@ -28034,13 +28034,13 @@
         <v>1</v>
       </c>
       <c r="J281">
-        <v>491</v>
+        <v>413</v>
       </c>
       <c r="K281">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L281">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="M281" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28049,10 +28049,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P281">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q281">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="S281">
         <v>3</v>
@@ -28111,7 +28111,7 @@
         <v>90027</v>
       </c>
       <c r="C282" t="str">
-        <v>【极秘项目】马休-骑兵 T2</v>
+        <v>【末日先兆】张梁-骑兵 T2</v>
       </c>
       <c r="D282">
         <v>2</v>
@@ -28120,7 +28120,7 @@
         <v>20</v>
       </c>
       <c r="F282">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="G282">
         <v>4</v>
@@ -28132,13 +28132,13 @@
         <v>1</v>
       </c>
       <c r="J282">
-        <v>737</v>
+        <v>772</v>
       </c>
       <c r="K282">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L282">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="M282" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28147,10 +28147,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P282">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q282">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="S282">
         <v>3</v>
@@ -28209,7 +28209,7 @@
         <v>90028</v>
       </c>
       <c r="C283" t="str">
-        <v>【极秘项目】丘力居-骑兵 T2</v>
+        <v>【变异主宰】骨进-骑兵 T2</v>
       </c>
       <c r="D283">
         <v>2</v>
@@ -28218,7 +28218,7 @@
         <v>20</v>
       </c>
       <c r="F283">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="G283">
         <v>4</v>
@@ -28230,13 +28230,13 @@
         <v>1</v>
       </c>
       <c r="J283">
-        <v>596</v>
+        <v>799</v>
       </c>
       <c r="K283">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L283">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="M283" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28248,7 +28248,7 @@
         <v>76</v>
       </c>
       <c r="Q283">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S283">
         <v>3</v>
@@ -28307,7 +28307,7 @@
         <v>90029</v>
       </c>
       <c r="C284" t="str">
-        <v>【末日先兆】库察-骑兵 T3</v>
+        <v>【末日先兆】韩忠-骑兵 T3</v>
       </c>
       <c r="D284">
         <v>2</v>
@@ -28316,7 +28316,7 @@
         <v>20</v>
       </c>
       <c r="F284">
-        <v>572</v>
+        <v>488</v>
       </c>
       <c r="G284">
         <v>5</v>
@@ -28328,10 +28328,10 @@
         <v>1</v>
       </c>
       <c r="J284">
-        <v>1072</v>
+        <v>867</v>
       </c>
       <c r="K284">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L284">
         <v>1.26</v>
@@ -28343,10 +28343,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P284">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q284">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="S284">
         <v>3</v>
@@ -28405,7 +28405,7 @@
         <v>90030</v>
       </c>
       <c r="C285" t="str">
-        <v>【变异主宰】程远志-骑兵 T3</v>
+        <v>【末日先兆】庞德-骑兵 T3</v>
       </c>
       <c r="D285">
         <v>2</v>
@@ -28414,7 +28414,7 @@
         <v>20</v>
       </c>
       <c r="F285">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="G285">
         <v>5</v>
@@ -28426,13 +28426,13 @@
         <v>1</v>
       </c>
       <c r="J285">
-        <v>1073</v>
+        <v>898</v>
       </c>
       <c r="K285">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="L285">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="M285" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28441,10 +28441,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P285">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q285">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="S285">
         <v>3</v>
@@ -28503,7 +28503,7 @@
         <v>90031</v>
       </c>
       <c r="C286" t="str">
-        <v>【虚空母体】杨秋-骑兵 T4</v>
+        <v>【极秘项目】夏侯渊-骑兵 T4</v>
       </c>
       <c r="D286">
         <v>2</v>
@@ -28512,7 +28512,7 @@
         <v>20</v>
       </c>
       <c r="F286">
-        <v>587</v>
+        <v>704</v>
       </c>
       <c r="G286">
         <v>6</v>
@@ -28524,13 +28524,13 @@
         <v>1</v>
       </c>
       <c r="J286">
-        <v>969</v>
+        <v>1202</v>
       </c>
       <c r="K286">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L286">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="M286" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28539,10 +28539,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P286">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q286">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="S286">
         <v>3</v>
@@ -28601,7 +28601,7 @@
         <v>90032</v>
       </c>
       <c r="C287" t="str">
-        <v>【末日先兆】骨进-骑兵 T4</v>
+        <v>【变异主宰】丘力居-骑兵 T4</v>
       </c>
       <c r="D287">
         <v>2</v>
@@ -28610,7 +28610,7 @@
         <v>20</v>
       </c>
       <c r="F287">
-        <v>689</v>
+        <v>749</v>
       </c>
       <c r="G287">
         <v>6</v>
@@ -28622,13 +28622,13 @@
         <v>1</v>
       </c>
       <c r="J287">
-        <v>1139</v>
+        <v>1344</v>
       </c>
       <c r="K287">
         <v>61</v>
       </c>
       <c r="L287">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="M287" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28637,10 +28637,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P287">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q287">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="S287">
         <v>3</v>
@@ -28699,7 +28699,7 @@
         <v>90033</v>
       </c>
       <c r="C288" t="str">
-        <v>【变异主宰】施绩-长枪兵 T1</v>
+        <v>【变异主宰】王双-长枪兵 T1</v>
       </c>
       <c r="D288">
         <v>3</v>
@@ -28708,7 +28708,7 @@
         <v>20</v>
       </c>
       <c r="F288">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G288">
         <v>3</v>
@@ -28720,13 +28720,13 @@
         <v>1</v>
       </c>
       <c r="J288">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K288">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L288">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="M288" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28738,7 +28738,7 @@
         <v>78</v>
       </c>
       <c r="Q288">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="S288">
         <v>4</v>
@@ -28797,7 +28797,7 @@
         <v>90034</v>
       </c>
       <c r="C289" t="str">
-        <v>【末日先兆】宋宪-长枪兵 T1</v>
+        <v>【变异主宰】刘贤-长枪兵 T1</v>
       </c>
       <c r="D289">
         <v>3</v>
@@ -28806,7 +28806,7 @@
         <v>20</v>
       </c>
       <c r="F289">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="G289">
         <v>3</v>
@@ -28818,13 +28818,13 @@
         <v>1</v>
       </c>
       <c r="J289">
-        <v>429</v>
+        <v>333</v>
       </c>
       <c r="K289">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L289">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="M289" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28833,10 +28833,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P289">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q289">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="S289">
         <v>4</v>
@@ -28895,7 +28895,7 @@
         <v>90035</v>
       </c>
       <c r="C290" t="str">
-        <v>【钢铁暴君】陈到-长枪兵 T2</v>
+        <v>【钢铁暴君】诸葛诞-长枪兵 T2</v>
       </c>
       <c r="D290">
         <v>3</v>
@@ -28904,7 +28904,7 @@
         <v>20</v>
       </c>
       <c r="F290">
-        <v>384</v>
+        <v>450</v>
       </c>
       <c r="G290">
         <v>4</v>
@@ -28916,13 +28916,13 @@
         <v>1</v>
       </c>
       <c r="J290">
-        <v>504</v>
+        <v>640</v>
       </c>
       <c r="K290">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L290">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="M290" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28931,10 +28931,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P290">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q290">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="S290">
         <v>4</v>
@@ -28993,7 +28993,7 @@
         <v>90036</v>
       </c>
       <c r="C291" t="str">
-        <v>【钢铁暴君】郝昭-长枪兵 T2</v>
+        <v>【钢铁暴君】张任-长枪兵 T2</v>
       </c>
       <c r="D291">
         <v>3</v>
@@ -29002,7 +29002,7 @@
         <v>20</v>
       </c>
       <c r="F291">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="G291">
         <v>4</v>
@@ -29014,13 +29014,13 @@
         <v>1</v>
       </c>
       <c r="J291">
-        <v>547</v>
+        <v>640</v>
       </c>
       <c r="K291">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L291">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="M291" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -29032,7 +29032,7 @@
         <v>75</v>
       </c>
       <c r="Q291">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="S291">
         <v>4</v>
@@ -29091,7 +29091,7 @@
         <v>90037</v>
       </c>
       <c r="C292" t="str">
-        <v>【变异主宰】凌操-长枪兵 T3</v>
+        <v>【钢铁暴君】陈泰-长枪兵 T3</v>
       </c>
       <c r="D292">
         <v>3</v>
@@ -29100,7 +29100,7 @@
         <v>20</v>
       </c>
       <c r="F292">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="G292">
         <v>5</v>
@@ -29112,13 +29112,13 @@
         <v>1</v>
       </c>
       <c r="J292">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="K292">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="L292">
-        <v>0.99</v>
+        <v>1.19</v>
       </c>
       <c r="M292" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -29127,10 +29127,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P292">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q292">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="S292">
         <v>4</v>
@@ -29189,7 +29189,7 @@
         <v>90038</v>
       </c>
       <c r="C293" t="str">
-        <v>【末日先兆】马谡-长枪兵 T3</v>
+        <v>【极秘项目】沙摩柯-长枪兵 T3</v>
       </c>
       <c r="D293">
         <v>3</v>
@@ -29198,7 +29198,7 @@
         <v>20</v>
       </c>
       <c r="F293">
-        <v>546</v>
+        <v>585</v>
       </c>
       <c r="G293">
         <v>5</v>
@@ -29210,13 +29210,13 @@
         <v>1</v>
       </c>
       <c r="J293">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="K293">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="L293">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="M293" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -29225,10 +29225,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P293">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q293">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="S293">
         <v>4</v>
@@ -29287,7 +29287,7 @@
         <v>90039</v>
       </c>
       <c r="C294" t="str">
-        <v>【末日先兆】陈就-长枪兵 T4</v>
+        <v>【变异主宰】邓贤-长枪兵 T4</v>
       </c>
       <c r="D294">
         <v>3</v>
@@ -29296,7 +29296,7 @@
         <v>20</v>
       </c>
       <c r="F294">
-        <v>857</v>
+        <v>990</v>
       </c>
       <c r="G294">
         <v>6</v>
@@ -29308,13 +29308,13 @@
         <v>1</v>
       </c>
       <c r="J294">
-        <v>957</v>
+        <v>1134</v>
       </c>
       <c r="K294">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L294">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="M294" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -29326,7 +29326,7 @@
         <v>75</v>
       </c>
       <c r="Q294">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="S294">
         <v>4</v>
@@ -29385,7 +29385,7 @@
         <v>90040</v>
       </c>
       <c r="C295" t="str">
-        <v>【钢铁暴君】曹性-长枪兵 T4</v>
+        <v>【变异主宰】卓膺-长枪兵 T4</v>
       </c>
       <c r="D295">
         <v>3</v>
@@ -29394,7 +29394,7 @@
         <v>20</v>
       </c>
       <c r="F295">
-        <v>959</v>
+        <v>863</v>
       </c>
       <c r="G295">
         <v>6</v>
@@ -29406,13 +29406,13 @@
         <v>1</v>
       </c>
       <c r="J295">
-        <v>1107</v>
+        <v>884</v>
       </c>
       <c r="K295">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L295">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="M295" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -29421,10 +29421,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P295">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q295">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="S295">
         <v>4</v>

--- a/public/ArmyTable.xlsx
+++ b/public/ArmyTable.xlsx
@@ -914,7 +914,7 @@
         <v>75</v>
       </c>
       <c r="Q6">
-        <v>684</v>
+        <v>1284</v>
       </c>
       <c r="S6">
         <v>1</v>
@@ -3058,7 +3058,7 @@
         <v>10001</v>
       </c>
       <c r="C28" t="str">
-        <v>关羽-步兵 T1</v>
+        <v>王颀-步兵 T1</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3067,7 +3067,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="G28">
         <v>3</v>
@@ -3079,13 +3079,13 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="K28">
         <v>9</v>
       </c>
       <c r="L28">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="M28" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3094,10 +3094,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P28">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="Q28">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -3156,7 +3156,7 @@
         <v>10002</v>
       </c>
       <c r="C29" t="str">
-        <v>徐晃-步兵 T1</v>
+        <v>胡车儿-步兵 T1</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -3165,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="G29">
         <v>3</v>
@@ -3177,13 +3177,13 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>0.93</v>
+        <v>1.1</v>
       </c>
       <c r="M29" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3192,10 +3192,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P29">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="Q29">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>10003</v>
       </c>
       <c r="C30" t="str">
-        <v>苏由-步兵 T1</v>
+        <v>牵招-步兵 T1</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -3263,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -3275,13 +3275,13 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="K30">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L30">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="M30" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3290,10 +3290,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P30">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q30">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -3352,7 +3352,7 @@
         <v>10004</v>
       </c>
       <c r="C31" t="str">
-        <v>孙策-步兵 T1</v>
+        <v>朱桓-步兵 T1</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -3373,13 +3373,13 @@
         <v>1</v>
       </c>
       <c r="J31">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="K31">
         <v>8</v>
       </c>
       <c r="L31">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="M31" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3388,10 +3388,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P31">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="Q31">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -3450,7 +3450,7 @@
         <v>10005</v>
       </c>
       <c r="C32" t="str">
-        <v>高干-步兵 T1</v>
+        <v>曹洪-步兵 T1</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -3471,13 +3471,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="M32" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3486,10 +3486,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P32">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Q32">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -3548,7 +3548,7 @@
         <v>10006</v>
       </c>
       <c r="C33" t="str">
-        <v>蒋义渠-步兵 T1</v>
+        <v>张郃-步兵 T1</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -3557,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -3569,13 +3569,13 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="K33">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L33">
-        <v>0.92</v>
+        <v>1.1</v>
       </c>
       <c r="M33" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3584,10 +3584,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P33">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q33">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>10007</v>
       </c>
       <c r="C34" t="str">
-        <v>潘凤-步兵 T1</v>
+        <v>向宠-步兵 T1</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -3655,7 +3655,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -3667,13 +3667,13 @@
         <v>1</v>
       </c>
       <c r="J34">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="K34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L34">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="M34" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3682,10 +3682,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P34">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Q34">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>10008</v>
       </c>
       <c r="C35" t="str">
-        <v>田豫-步兵 T1</v>
+        <v>吕凯-步兵 T1</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -3765,13 +3765,13 @@
         <v>1</v>
       </c>
       <c r="J35">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="K35">
         <v>10</v>
       </c>
       <c r="L35">
-        <v>1.05</v>
+        <v>0.93</v>
       </c>
       <c r="M35" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3780,10 +3780,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P35">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="Q35">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -3842,7 +3842,7 @@
         <v>10009</v>
       </c>
       <c r="C36" t="str">
-        <v>向宠-步兵 T1</v>
+        <v>严白虎-步兵 T1</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -3863,13 +3863,13 @@
         <v>1</v>
       </c>
       <c r="J36">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="K36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L36">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="M36" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3878,10 +3878,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P36">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Q36">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -3940,7 +3940,7 @@
         <v>10010</v>
       </c>
       <c r="C37" t="str">
-        <v>胡车儿-步兵 T1</v>
+        <v>李典-步兵 T1</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -3961,13 +3961,13 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="K37">
         <v>9</v>
       </c>
       <c r="L37">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="M37" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3976,10 +3976,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P37">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="Q37">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -4038,7 +4038,7 @@
         <v>10011</v>
       </c>
       <c r="C38" t="str">
-        <v>霍峻-步兵 T1</v>
+        <v>华雄-步兵 T1</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="G38">
         <v>3</v>
@@ -4059,13 +4059,13 @@
         <v>1</v>
       </c>
       <c r="J38">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="K38">
         <v>8</v>
       </c>
       <c r="L38">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="M38" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4074,10 +4074,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P38">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q38">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -4136,7 +4136,7 @@
         <v>10012</v>
       </c>
       <c r="C39" t="str">
-        <v>麴义-步兵 T1</v>
+        <v>许褚-步兵 T1</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -4145,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -4157,13 +4157,13 @@
         <v>1</v>
       </c>
       <c r="J39">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="M39" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4172,10 +4172,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P39">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="Q39">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -4234,7 +4234,7 @@
         <v>10013</v>
       </c>
       <c r="C40" t="str">
-        <v>刘备-步兵 T2</v>
+        <v>张翼-步兵 T2</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -4243,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -4255,13 +4255,13 @@
         <v>1</v>
       </c>
       <c r="J40">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="K40">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L40">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="M40" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4270,10 +4270,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P40">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="Q40">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -4332,7 +4332,7 @@
         <v>10014</v>
       </c>
       <c r="C41" t="str">
-        <v>丁奉-步兵 T2</v>
+        <v>曹仁-步兵 T2</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -4341,7 +4341,7 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -4353,13 +4353,13 @@
         <v>1</v>
       </c>
       <c r="J41">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="K41">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L41">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="M41" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4368,10 +4368,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P41">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q41">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>10015</v>
       </c>
       <c r="C42" t="str">
-        <v>张南-步兵 T2</v>
+        <v>典韦-步兵 T2</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -4451,13 +4451,13 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L42">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="M42" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4466,10 +4466,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P42">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="Q42">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -4528,7 +4528,7 @@
         <v>10016</v>
       </c>
       <c r="C43" t="str">
-        <v>文丑-步兵 T2</v>
+        <v>张燕-步兵 T2</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -4549,13 +4549,13 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="K43">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L43">
-        <v>0.98</v>
+        <v>1.09</v>
       </c>
       <c r="M43" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4564,10 +4564,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P43">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q43">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -4626,7 +4626,7 @@
         <v>10017</v>
       </c>
       <c r="C44" t="str">
-        <v>郭援-步兵 T2</v>
+        <v>关羽-步兵 T2</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -4635,7 +4635,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -4647,13 +4647,13 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="K44">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L44">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="M44" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4662,10 +4662,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P44">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Q44">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -4724,7 +4724,7 @@
         <v>10018</v>
       </c>
       <c r="C45" t="str">
-        <v>华雄-步兵 T2</v>
+        <v>焦触-步兵 T2</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -4733,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -4745,13 +4745,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="K45">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L45">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="M45" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4760,10 +4760,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P45">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q45">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -4822,7 +4822,7 @@
         <v>10019</v>
       </c>
       <c r="C46" t="str">
-        <v>王威-步兵 T2</v>
+        <v>曹操-步兵 T2</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -4831,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -4843,13 +4843,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="K46">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L46">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="M46" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4858,10 +4858,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P46">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="Q46">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -4920,7 +4920,7 @@
         <v>10020</v>
       </c>
       <c r="C47" t="str">
-        <v>吴班-步兵 T2</v>
+        <v>吕翔-步兵 T2</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -4929,7 +4929,7 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -4941,13 +4941,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="K47">
         <v>14</v>
       </c>
       <c r="L47">
-        <v>1.06</v>
+        <v>0.9</v>
       </c>
       <c r="M47" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4956,10 +4956,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P47">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="Q47">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -5018,7 +5018,7 @@
         <v>10021</v>
       </c>
       <c r="C48" t="str">
-        <v>孙坚-步兵 T2</v>
+        <v>蒋义渠-步兵 T2</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -5027,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="G48">
         <v>4</v>
@@ -5039,13 +5039,13 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K48">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L48">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="M48" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5054,10 +5054,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P48">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Q48">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -5116,7 +5116,7 @@
         <v>10022</v>
       </c>
       <c r="C49" t="str">
-        <v>朱桓-步兵 T2</v>
+        <v>张允-步兵 T2</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -5137,10 +5137,10 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="K49">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L49">
         <v>1.05</v>
@@ -5152,10 +5152,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P49">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Q49">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -5214,7 +5214,7 @@
         <v>10023</v>
       </c>
       <c r="C50" t="str">
-        <v>刘封-步兵 T2</v>
+        <v>管亥-步兵 T2</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -5223,7 +5223,7 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -5235,13 +5235,13 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>190</v>
+        <v>254</v>
       </c>
       <c r="K50">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L50">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="M50" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5250,10 +5250,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P50">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Q50">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -5312,7 +5312,7 @@
         <v>10024</v>
       </c>
       <c r="C51" t="str">
-        <v>马延-步兵 T2</v>
+        <v>吴班-步兵 T2</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -5321,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="F51">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="G51">
         <v>4</v>
@@ -5333,13 +5333,13 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>185</v>
+        <v>246</v>
       </c>
       <c r="K51">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L51">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="M51" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5348,10 +5348,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P51">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="Q51">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -5410,7 +5410,7 @@
         <v>10025</v>
       </c>
       <c r="C52" t="str">
-        <v>韩猛-步兵 T3</v>
+        <v>周仓-步兵 T3</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="F52">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -5431,13 +5431,13 @@
         <v>1</v>
       </c>
       <c r="J52">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="K52">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L52">
-        <v>1.09</v>
+        <v>0.91</v>
       </c>
       <c r="M52" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5446,10 +5446,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P52">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q52">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         <v>10026</v>
       </c>
       <c r="C53" t="str">
-        <v>曹洪-步兵 T3</v>
+        <v>徐晃-步兵 T3</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -5517,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="F53">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -5529,13 +5529,13 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>353</v>
+        <v>270</v>
       </c>
       <c r="K53">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L53">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="M53" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5544,10 +5544,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P53">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="Q53">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>10027</v>
       </c>
       <c r="C54" t="str">
-        <v>张允-步兵 T3</v>
+        <v>孙权-步兵 T3</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -5615,7 +5615,7 @@
         <v>1</v>
       </c>
       <c r="F54">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="G54">
         <v>5</v>
@@ -5627,13 +5627,13 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>306</v>
+        <v>358</v>
       </c>
       <c r="K54">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L54">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="M54" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5642,10 +5642,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P54">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Q54">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -5704,7 +5704,7 @@
         <v>10028</v>
       </c>
       <c r="C55" t="str">
-        <v>傅佥-步兵 T3</v>
+        <v>廖化-步兵 T3</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>1</v>
       </c>
       <c r="F55">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="G55">
         <v>5</v>
@@ -5725,13 +5725,13 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="K55">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L55">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="M55" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5740,10 +5740,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P55">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Q55">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -5802,7 +5802,7 @@
         <v>10029</v>
       </c>
       <c r="C56" t="str">
-        <v>于禁-步兵 T3</v>
+        <v>蔡瑁-步兵 T3</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -5811,7 +5811,7 @@
         <v>1</v>
       </c>
       <c r="F56">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="G56">
         <v>5</v>
@@ -5823,13 +5823,13 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <v>325</v>
+        <v>246</v>
       </c>
       <c r="K56">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L56">
-        <v>0.94</v>
+        <v>1.07</v>
       </c>
       <c r="M56" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5838,10 +5838,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P56">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="Q56">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -5900,7 +5900,7 @@
         <v>10030</v>
       </c>
       <c r="C57" t="str">
-        <v>曹仁-步兵 T3</v>
+        <v>傅彤-步兵 T3</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -5909,7 +5909,7 @@
         <v>1</v>
       </c>
       <c r="F57">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="G57">
         <v>5</v>
@@ -5921,13 +5921,13 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="K57">
         <v>21</v>
       </c>
       <c r="L57">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="M57" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5936,10 +5936,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P57">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q57">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -5998,7 +5998,7 @@
         <v>10031</v>
       </c>
       <c r="C58" t="str">
-        <v>淳于琼-步兵 T3</v>
+        <v>刘备-步兵 T3</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -6007,7 +6007,7 @@
         <v>1</v>
       </c>
       <c r="F58">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="G58">
         <v>5</v>
@@ -6019,13 +6019,13 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <v>310</v>
+        <v>278</v>
       </c>
       <c r="K58">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L58">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="M58" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6034,10 +6034,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P58">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q58">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -6096,7 +6096,7 @@
         <v>10032</v>
       </c>
       <c r="C59" t="str">
-        <v>吕公-步兵 T3</v>
+        <v>曹真-步兵 T3</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -6105,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="F59">
-        <v>129</v>
+        <v>184</v>
       </c>
       <c r="G59">
         <v>5</v>
@@ -6117,13 +6117,13 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="K59">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L59">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="M59" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6132,10 +6132,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P59">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="Q59">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -6194,7 +6194,7 @@
         <v>10033</v>
       </c>
       <c r="C60" t="str">
-        <v>张苞-步兵 T3</v>
+        <v>马延-步兵 T3</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -6203,7 +6203,7 @@
         <v>1</v>
       </c>
       <c r="F60">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="G60">
         <v>5</v>
@@ -6215,13 +6215,13 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <v>333</v>
+        <v>278</v>
       </c>
       <c r="K60">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L60">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="M60" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6230,10 +6230,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P60">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Q60">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -6292,7 +6292,7 @@
         <v>10034</v>
       </c>
       <c r="C61" t="str">
-        <v>颜良-步兵 T3</v>
+        <v>麴义-步兵 T3</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -6301,7 +6301,7 @@
         <v>1</v>
       </c>
       <c r="F61">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="G61">
         <v>5</v>
@@ -6313,13 +6313,13 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="K61">
         <v>17</v>
       </c>
       <c r="L61">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="M61" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6328,10 +6328,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P61">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q61">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -6390,7 +6390,7 @@
         <v>10035</v>
       </c>
       <c r="C62" t="str">
-        <v>乐进-步兵 T3</v>
+        <v>文丑-步兵 T3</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="F62">
-        <v>94</v>
+        <v>188</v>
       </c>
       <c r="G62">
         <v>5</v>
@@ -6411,13 +6411,13 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>246</v>
+        <v>303</v>
       </c>
       <c r="K62">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L62">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="M62" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6426,10 +6426,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P62">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="Q62">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>10036</v>
       </c>
       <c r="C63" t="str">
-        <v>徐盛-步兵 T3</v>
+        <v>蒋舒-步兵 T3</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -6497,7 +6497,7 @@
         <v>1</v>
       </c>
       <c r="F63">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G63">
         <v>5</v>
@@ -6509,13 +6509,13 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="K63">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L63">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="M63" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6524,10 +6524,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P63">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q63">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -6586,7 +6586,7 @@
         <v>10037</v>
       </c>
       <c r="C64" t="str">
-        <v>蔡瑁-步兵 T4</v>
+        <v>王威-步兵 T4</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -6595,7 +6595,7 @@
         <v>1</v>
       </c>
       <c r="F64">
-        <v>148</v>
+        <v>230</v>
       </c>
       <c r="G64">
         <v>6</v>
@@ -6607,13 +6607,13 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>312</v>
+        <v>387</v>
       </c>
       <c r="K64">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L64">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="M64" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6622,10 +6622,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P64">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q64">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -6684,7 +6684,7 @@
         <v>10038</v>
       </c>
       <c r="C65" t="str">
-        <v>曹休-步兵 T4</v>
+        <v>关兴-步兵 T4</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -6693,7 +6693,7 @@
         <v>1</v>
       </c>
       <c r="F65">
-        <v>154</v>
+        <v>270</v>
       </c>
       <c r="G65">
         <v>6</v>
@@ -6705,13 +6705,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>332</v>
+        <v>416</v>
       </c>
       <c r="K65">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L65">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="M65" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6720,10 +6720,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P65">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="Q65">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -6782,7 +6782,7 @@
         <v>10039</v>
       </c>
       <c r="C66" t="str">
-        <v>高览-步兵 T4</v>
+        <v>张苞-步兵 T4</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -6791,7 +6791,7 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="G66">
         <v>6</v>
@@ -6803,13 +6803,13 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="K66">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L66">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="M66" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6818,10 +6818,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P66">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Q66">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -6880,7 +6880,7 @@
         <v>10040</v>
       </c>
       <c r="C67" t="str">
-        <v>廖化-步兵 T4</v>
+        <v>甘宁-步兵 T4</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -6889,7 +6889,7 @@
         <v>1</v>
       </c>
       <c r="F67">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="G67">
         <v>6</v>
@@ -6901,13 +6901,13 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>313</v>
+        <v>433</v>
       </c>
       <c r="K67">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L67">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="M67" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6916,10 +6916,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P67">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="Q67">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -6978,7 +6978,7 @@
         <v>10041</v>
       </c>
       <c r="C68" t="str">
-        <v>马忠-步兵 T4</v>
+        <v>张南-步兵 T4</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -6987,7 +6987,7 @@
         <v>1</v>
       </c>
       <c r="F68">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -6999,10 +6999,10 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="K68">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L68">
         <v>1.07</v>
@@ -7014,10 +7014,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P68">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Q68">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -7076,7 +7076,7 @@
         <v>10042</v>
       </c>
       <c r="C69" t="str">
-        <v>关平-步兵 T4</v>
+        <v>苏由-步兵 T4</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -7085,7 +7085,7 @@
         <v>1</v>
       </c>
       <c r="F69">
-        <v>176</v>
+        <v>235</v>
       </c>
       <c r="G69">
         <v>6</v>
@@ -7097,13 +7097,13 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <v>414</v>
+        <v>327</v>
       </c>
       <c r="K69">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L69">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="M69" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7112,10 +7112,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P69">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Q69">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -7174,7 +7174,7 @@
         <v>10043</v>
       </c>
       <c r="C70" t="str">
-        <v>牵招-步兵 T4</v>
+        <v>吕旷-步兵 T4</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -7183,7 +7183,7 @@
         <v>1</v>
       </c>
       <c r="F70">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="G70">
         <v>6</v>
@@ -7195,13 +7195,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>440</v>
+        <v>366</v>
       </c>
       <c r="K70">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L70">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="M70" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7210,10 +7210,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P70">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q70">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -7272,7 +7272,7 @@
         <v>10044</v>
       </c>
       <c r="C71" t="str">
-        <v>吕凯-步兵 T4</v>
+        <v>高干-步兵 T4</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -7281,7 +7281,7 @@
         <v>1</v>
       </c>
       <c r="F71">
-        <v>191</v>
+        <v>257</v>
       </c>
       <c r="G71">
         <v>6</v>
@@ -7293,13 +7293,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="K71">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L71">
-        <v>1.08</v>
+        <v>0.97</v>
       </c>
       <c r="M71" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7308,10 +7308,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P71">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Q71">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -7370,7 +7370,7 @@
         <v>10045</v>
       </c>
       <c r="C72" t="str">
-        <v>黄盖-步兵 T4</v>
+        <v>周泰-步兵 T4</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -7379,7 +7379,7 @@
         <v>1</v>
       </c>
       <c r="F72">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="G72">
         <v>6</v>
@@ -7391,13 +7391,13 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <v>411</v>
+        <v>372</v>
       </c>
       <c r="K72">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L72">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="M72" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7406,10 +7406,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P72">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Q72">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -7468,7 +7468,7 @@
         <v>10046</v>
       </c>
       <c r="C73" t="str">
-        <v>祖茂-步兵 T4</v>
+        <v>乐进-步兵 T4</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>1</v>
       </c>
       <c r="F73">
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="G73">
         <v>6</v>
@@ -7489,13 +7489,13 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>408</v>
+        <v>373</v>
       </c>
       <c r="K73">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L73">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="M73" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7504,10 +7504,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P73">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Q73">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -7566,7 +7566,7 @@
         <v>10047</v>
       </c>
       <c r="C74" t="str">
-        <v>张燕-步兵 T4</v>
+        <v>田豫-步兵 T4</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>1</v>
       </c>
       <c r="F74">
-        <v>149</v>
+        <v>277</v>
       </c>
       <c r="G74">
         <v>6</v>
@@ -7587,13 +7587,13 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <v>309</v>
+        <v>415</v>
       </c>
       <c r="K74">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L74">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="M74" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7602,10 +7602,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P74">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="Q74">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -7664,7 +7664,7 @@
         <v>10048</v>
       </c>
       <c r="C75" t="str">
-        <v>王颀-步兵 T4</v>
+        <v>韩猛-步兵 T4</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -7673,7 +7673,7 @@
         <v>1</v>
       </c>
       <c r="F75">
-        <v>151</v>
+        <v>225</v>
       </c>
       <c r="G75">
         <v>6</v>
@@ -7685,13 +7685,13 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K75">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L75">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="M75" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7700,10 +7700,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P75">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Q75">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -7857,7 +7857,7 @@
         <v>20001</v>
       </c>
       <c r="C77" t="str">
-        <v>戏志才-弓箭手 T1</v>
+        <v>宗预-弓箭手 T1</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -7866,7 +7866,7 @@
         <v>1</v>
       </c>
       <c r="F77">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="G77">
         <v>3</v>
@@ -7878,13 +7878,13 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K77">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L77">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="M77" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7893,10 +7893,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P77">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Q77">
-        <v>1234</v>
+        <v>2316</v>
       </c>
       <c r="S77">
         <v>1</v>
@@ -7955,7 +7955,7 @@
         <v>20002</v>
       </c>
       <c r="C78" t="str">
-        <v>郭嘉-弓箭手 T1</v>
+        <v>费祎-弓箭手 T1</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -7964,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="G78">
         <v>3</v>
@@ -7976,13 +7976,13 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="K78">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L78">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="M78" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7991,10 +7991,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P78">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Q78">
-        <v>1314</v>
+        <v>2179</v>
       </c>
       <c r="S78">
         <v>1</v>
@@ -8053,7 +8053,7 @@
         <v>20003</v>
       </c>
       <c r="C79" t="str">
-        <v>黄忠-弓箭手 T1</v>
+        <v>孙乾-弓箭手 T1</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -8062,7 +8062,7 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="G79">
         <v>3</v>
@@ -8074,13 +8074,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K79">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L79">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="M79" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8089,10 +8089,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P79">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Q79">
-        <v>1247</v>
+        <v>2011</v>
       </c>
       <c r="S79">
         <v>1</v>
@@ -8151,7 +8151,7 @@
         <v>20004</v>
       </c>
       <c r="C80" t="str">
-        <v>蒯良-弓箭手 T1</v>
+        <v>周瑜-弓箭手 T1</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -8160,7 +8160,7 @@
         <v>1</v>
       </c>
       <c r="F80">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="G80">
         <v>3</v>
@@ -8172,13 +8172,13 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K80">
         <v>24</v>
       </c>
       <c r="L80">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="M80" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8187,10 +8187,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P80">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Q80">
-        <v>1231</v>
+        <v>2078</v>
       </c>
       <c r="S80">
         <v>1</v>
@@ -8249,7 +8249,7 @@
         <v>20005</v>
       </c>
       <c r="C81" t="str">
-        <v>田丰-弓箭手 T1</v>
+        <v>蒯良-弓箭手 T1</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -8258,7 +8258,7 @@
         <v>1</v>
       </c>
       <c r="F81">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="G81">
         <v>3</v>
@@ -8273,10 +8273,10 @@
         <v>62</v>
       </c>
       <c r="K81">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L81">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="M81" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8285,10 +8285,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P81">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Q81">
-        <v>1300</v>
+        <v>2298</v>
       </c>
       <c r="S81">
         <v>1</v>
@@ -8347,7 +8347,7 @@
         <v>20006</v>
       </c>
       <c r="C82" t="str">
-        <v>司马懿-弓箭手 T1</v>
+        <v>郑玄-弓箭手 T1</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -8356,7 +8356,7 @@
         <v>1</v>
       </c>
       <c r="F82">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="G82">
         <v>3</v>
@@ -8368,13 +8368,13 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K82">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L82">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="M82" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8383,10 +8383,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P82">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="Q82">
-        <v>1122</v>
+        <v>2393</v>
       </c>
       <c r="S82">
         <v>1</v>
@@ -8445,7 +8445,7 @@
         <v>20007</v>
       </c>
       <c r="C83" t="str">
-        <v>张温-弓箭手 T1</v>
+        <v>太史慈-弓箭手 T1</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -8454,7 +8454,7 @@
         <v>1</v>
       </c>
       <c r="F83">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G83">
         <v>3</v>
@@ -8466,13 +8466,13 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="K83">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L83">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="M83" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8481,10 +8481,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P83">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Q83">
-        <v>1259</v>
+        <v>2415</v>
       </c>
       <c r="S83">
         <v>1</v>
@@ -8543,7 +8543,7 @@
         <v>20008</v>
       </c>
       <c r="C84" t="str">
-        <v>华歆-弓箭手 T1</v>
+        <v>刘晔-弓箭手 T1</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -8552,7 +8552,7 @@
         <v>1</v>
       </c>
       <c r="F84">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G84">
         <v>3</v>
@@ -8564,13 +8564,13 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K84">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L84">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="M84" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8579,10 +8579,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P84">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Q84">
-        <v>1311</v>
+        <v>2312</v>
       </c>
       <c r="S84">
         <v>1</v>
@@ -8641,7 +8641,7 @@
         <v>20009</v>
       </c>
       <c r="C85" t="str">
-        <v>顾雍-弓箭手 T1</v>
+        <v>蒯越-弓箭手 T1</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -8650,7 +8650,7 @@
         <v>1</v>
       </c>
       <c r="F85">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="G85">
         <v>3</v>
@@ -8662,13 +8662,13 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="K85">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L85">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="M85" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8677,10 +8677,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P85">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Q85">
-        <v>1308</v>
+        <v>2068</v>
       </c>
       <c r="S85">
         <v>1</v>
@@ -8739,7 +8739,7 @@
         <v>20010</v>
       </c>
       <c r="C86" t="str">
-        <v>荀彧-弓箭手 T1</v>
+        <v>陈震-弓箭手 T1</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -8748,7 +8748,7 @@
         <v>1</v>
       </c>
       <c r="F86">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="G86">
         <v>3</v>
@@ -8760,13 +8760,13 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="K86">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L86">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="M86" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8775,10 +8775,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P86">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Q86">
-        <v>1182</v>
+        <v>1990</v>
       </c>
       <c r="S86">
         <v>1</v>
@@ -8837,7 +8837,7 @@
         <v>20011</v>
       </c>
       <c r="C87" t="str">
-        <v>王朗-弓箭手 T1</v>
+        <v>陈宫-弓箭手 T1</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -8846,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="F87">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="G87">
         <v>3</v>
@@ -8858,13 +8858,13 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K87">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L87">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="M87" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8873,10 +8873,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P87">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="Q87">
-        <v>1234</v>
+        <v>2125</v>
       </c>
       <c r="S87">
         <v>1</v>
@@ -8935,7 +8935,7 @@
         <v>20012</v>
       </c>
       <c r="C88" t="str">
-        <v>周瑜-弓箭手 T1</v>
+        <v>贾诩-弓箭手 T1</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -8944,7 +8944,7 @@
         <v>1</v>
       </c>
       <c r="F88">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="G88">
         <v>3</v>
@@ -8956,13 +8956,13 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K88">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L88">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="M88" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8971,10 +8971,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P88">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="Q88">
-        <v>1273</v>
+        <v>2214</v>
       </c>
       <c r="S88">
         <v>1</v>
@@ -9033,7 +9033,7 @@
         <v>20013</v>
       </c>
       <c r="C89" t="str">
-        <v>刘晔-弓箭手 T2</v>
+        <v>庞统-弓箭手 T2</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -9042,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="F89">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="G89">
         <v>4</v>
@@ -9054,13 +9054,13 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="K89">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L89">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="M89" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9069,10 +9069,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P89">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Q89">
-        <v>1168</v>
+        <v>2093</v>
       </c>
       <c r="S89">
         <v>1</v>
@@ -9131,7 +9131,7 @@
         <v>20014</v>
       </c>
       <c r="C90" t="str">
-        <v>糜芳-弓箭手 T2</v>
+        <v>荀彧-弓箭手 T2</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -9140,7 +9140,7 @@
         <v>1</v>
       </c>
       <c r="F90">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="G90">
         <v>4</v>
@@ -9152,13 +9152,13 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K90">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L90">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="M90" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9167,10 +9167,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P90">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Q90">
-        <v>1294</v>
+        <v>2222</v>
       </c>
       <c r="S90">
         <v>1</v>
@@ -9229,7 +9229,7 @@
         <v>20015</v>
       </c>
       <c r="C91" t="str">
-        <v>蔡文姬-弓箭手 T2</v>
+        <v>田丰-弓箭手 T2</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -9238,7 +9238,7 @@
         <v>1</v>
       </c>
       <c r="F91">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="G91">
         <v>4</v>
@@ -9250,13 +9250,13 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="K91">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L91">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="M91" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9265,10 +9265,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P91">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Q91">
-        <v>1101</v>
+        <v>2154</v>
       </c>
       <c r="S91">
         <v>1</v>
@@ -9327,7 +9327,7 @@
         <v>20016</v>
       </c>
       <c r="C92" t="str">
-        <v>廖立-弓箭手 T2</v>
+        <v>张春华-弓箭手 T2</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -9336,7 +9336,7 @@
         <v>1</v>
       </c>
       <c r="F92">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="G92">
         <v>4</v>
@@ -9348,13 +9348,13 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="K92">
         <v>29</v>
       </c>
       <c r="L92">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="M92" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9363,10 +9363,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P92">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="Q92">
-        <v>1086</v>
+        <v>2418</v>
       </c>
       <c r="S92">
         <v>1</v>
@@ -9425,7 +9425,7 @@
         <v>20017</v>
       </c>
       <c r="C93" t="str">
-        <v>董昭-弓箭手 T2</v>
+        <v>张温-弓箭手 T2</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -9434,7 +9434,7 @@
         <v>1</v>
       </c>
       <c r="F93">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="G93">
         <v>4</v>
@@ -9446,13 +9446,13 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="K93">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L93">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="M93" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9461,10 +9461,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P93">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q93">
-        <v>1274</v>
+        <v>2344</v>
       </c>
       <c r="S93">
         <v>1</v>
@@ -9523,7 +9523,7 @@
         <v>20018</v>
       </c>
       <c r="C94" t="str">
-        <v>陈震-弓箭手 T2</v>
+        <v>阚泽-弓箭手 T2</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -9532,7 +9532,7 @@
         <v>1</v>
       </c>
       <c r="F94">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="G94">
         <v>4</v>
@@ -9544,13 +9544,13 @@
         <v>1</v>
       </c>
       <c r="J94">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="K94">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L94">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="M94" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9559,10 +9559,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P94">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Q94">
-        <v>1260</v>
+        <v>1984</v>
       </c>
       <c r="S94">
         <v>1</v>
@@ -9621,7 +9621,7 @@
         <v>20019</v>
       </c>
       <c r="C95" t="str">
-        <v>管辂-弓箭手 T2</v>
+        <v>陆逊-弓箭手 T2</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -9630,7 +9630,7 @@
         <v>1</v>
       </c>
       <c r="F95">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="G95">
         <v>4</v>
@@ -9642,13 +9642,13 @@
         <v>1</v>
       </c>
       <c r="J95">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="K95">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L95">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="M95" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9657,10 +9657,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P95">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q95">
-        <v>1262</v>
+        <v>2214</v>
       </c>
       <c r="S95">
         <v>1</v>
@@ -9719,7 +9719,7 @@
         <v>20020</v>
       </c>
       <c r="C96" t="str">
-        <v>审配-弓箭手 T2</v>
+        <v>华佗-弓箭手 T2</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -9728,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="F96">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G96">
         <v>4</v>
@@ -9740,13 +9740,13 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K96">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="L96">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="M96" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9755,10 +9755,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P96">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Q96">
-        <v>1184</v>
+        <v>2010</v>
       </c>
       <c r="S96">
         <v>1</v>
@@ -9817,7 +9817,7 @@
         <v>20021</v>
       </c>
       <c r="C97" t="str">
-        <v>伊籍-弓箭手 T2</v>
+        <v>陈群-弓箭手 T2</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -9826,7 +9826,7 @@
         <v>1</v>
       </c>
       <c r="F97">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="G97">
         <v>4</v>
@@ -9841,10 +9841,10 @@
         <v>75</v>
       </c>
       <c r="K97">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L97">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="M97" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9853,10 +9853,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P97">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Q97">
-        <v>1277</v>
+        <v>2029</v>
       </c>
       <c r="S97">
         <v>1</v>
@@ -9915,7 +9915,7 @@
         <v>20022</v>
       </c>
       <c r="C98" t="str">
-        <v>蒯越-弓箭手 T2</v>
+        <v>满宠-弓箭手 T2</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -9924,7 +9924,7 @@
         <v>1</v>
       </c>
       <c r="F98">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="G98">
         <v>4</v>
@@ -9936,13 +9936,13 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K98">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L98">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="M98" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9951,10 +9951,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P98">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="Q98">
-        <v>1281</v>
+        <v>2110</v>
       </c>
       <c r="S98">
         <v>1</v>
@@ -10013,7 +10013,7 @@
         <v>20023</v>
       </c>
       <c r="C99" t="str">
-        <v>满宠-弓箭手 T2</v>
+        <v>糜竺-弓箭手 T2</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -10022,7 +10022,7 @@
         <v>1</v>
       </c>
       <c r="F99">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="G99">
         <v>4</v>
@@ -10034,13 +10034,13 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K99">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L99">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="M99" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10049,10 +10049,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P99">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q99">
-        <v>1144</v>
+        <v>2261</v>
       </c>
       <c r="S99">
         <v>1</v>
@@ -10111,7 +10111,7 @@
         <v>20024</v>
       </c>
       <c r="C100" t="str">
-        <v>诸葛亮-弓箭手 T2</v>
+        <v>姜维-弓箭手 T2</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -10120,7 +10120,7 @@
         <v>1</v>
       </c>
       <c r="F100">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="G100">
         <v>4</v>
@@ -10132,13 +10132,13 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="K100">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L100">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="M100" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10147,10 +10147,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P100">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="Q100">
-        <v>1142</v>
+        <v>2074</v>
       </c>
       <c r="S100">
         <v>1</v>
@@ -10209,7 +10209,7 @@
         <v>20025</v>
       </c>
       <c r="C101" t="str">
-        <v>小乔-弓箭手 T3</v>
+        <v>徐庶-弓箭手 T3</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -10218,7 +10218,7 @@
         <v>1</v>
       </c>
       <c r="F101">
-        <v>205</v>
+        <v>363</v>
       </c>
       <c r="G101">
         <v>5</v>
@@ -10230,13 +10230,13 @@
         <v>1</v>
       </c>
       <c r="J101">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="K101">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L101">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="M101" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10245,10 +10245,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P101">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Q101">
-        <v>1285</v>
+        <v>2350</v>
       </c>
       <c r="S101">
         <v>1</v>
@@ -10307,7 +10307,7 @@
         <v>20026</v>
       </c>
       <c r="C102" t="str">
-        <v>贾诩-弓箭手 T3</v>
+        <v>祝融-弓箭手 T3</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -10316,7 +10316,7 @@
         <v>1</v>
       </c>
       <c r="F102">
-        <v>247</v>
+        <v>301</v>
       </c>
       <c r="G102">
         <v>5</v>
@@ -10328,13 +10328,13 @@
         <v>1</v>
       </c>
       <c r="J102">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="K102">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L102">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M102" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10343,10 +10343,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P102">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q102">
-        <v>1315</v>
+        <v>2150</v>
       </c>
       <c r="S102">
         <v>1</v>
@@ -10405,7 +10405,7 @@
         <v>20027</v>
       </c>
       <c r="C103" t="str">
-        <v>糜竺-弓箭手 T3</v>
+        <v>廖立-弓箭手 T3</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>1</v>
       </c>
       <c r="F103">
-        <v>215</v>
+        <v>381</v>
       </c>
       <c r="G103">
         <v>5</v>
@@ -10426,13 +10426,13 @@
         <v>1</v>
       </c>
       <c r="J103">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="K103">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L103">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="M103" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10441,10 +10441,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P103">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="Q103">
-        <v>1187</v>
+        <v>2192</v>
       </c>
       <c r="S103">
         <v>1</v>
@@ -10503,7 +10503,7 @@
         <v>20028</v>
       </c>
       <c r="C104" t="str">
-        <v>薛综-弓箭手 T3</v>
+        <v>管辂-弓箭手 T3</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -10512,7 +10512,7 @@
         <v>1</v>
       </c>
       <c r="F104">
-        <v>233</v>
+        <v>290</v>
       </c>
       <c r="G104">
         <v>5</v>
@@ -10524,13 +10524,13 @@
         <v>1</v>
       </c>
       <c r="J104">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="K104">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L104">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="M104" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10539,10 +10539,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P104">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="Q104">
-        <v>1217</v>
+        <v>2343</v>
       </c>
       <c r="S104">
         <v>1</v>
@@ -10610,7 +10610,7 @@
         <v>1</v>
       </c>
       <c r="F105">
-        <v>286</v>
+        <v>437</v>
       </c>
       <c r="G105">
         <v>5</v>
@@ -10622,13 +10622,13 @@
         <v>1</v>
       </c>
       <c r="J105">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="K105">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L105">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="M105" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10637,10 +10637,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P105">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Q105">
-        <v>1110</v>
+        <v>2351</v>
       </c>
       <c r="S105">
         <v>1</v>
@@ -10699,7 +10699,7 @@
         <v>20030</v>
       </c>
       <c r="C106" t="str">
-        <v>陈宫-弓箭手 T3</v>
+        <v>逢纪-弓箭手 T3</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -10708,7 +10708,7 @@
         <v>1</v>
       </c>
       <c r="F106">
-        <v>228</v>
+        <v>354</v>
       </c>
       <c r="G106">
         <v>5</v>
@@ -10720,10 +10720,10 @@
         <v>1</v>
       </c>
       <c r="J106">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K106">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L106">
         <v>1.94</v>
@@ -10735,10 +10735,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P106">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Q106">
-        <v>1084</v>
+        <v>2335</v>
       </c>
       <c r="S106">
         <v>1</v>
@@ -10797,7 +10797,7 @@
         <v>20031</v>
       </c>
       <c r="C107" t="str">
-        <v>甄姬-弓箭手 T3</v>
+        <v>糜芳-弓箭手 T3</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -10806,7 +10806,7 @@
         <v>1</v>
       </c>
       <c r="F107">
-        <v>231</v>
+        <v>315</v>
       </c>
       <c r="G107">
         <v>5</v>
@@ -10818,13 +10818,13 @@
         <v>1</v>
       </c>
       <c r="J107">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="K107">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L107">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="M107" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10833,10 +10833,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P107">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Q107">
-        <v>1185</v>
+        <v>2404</v>
       </c>
       <c r="S107">
         <v>1</v>
@@ -10895,7 +10895,7 @@
         <v>20032</v>
       </c>
       <c r="C108" t="str">
-        <v>姜维-弓箭手 T3</v>
+        <v>郭嘉-弓箭手 T3</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -10904,7 +10904,7 @@
         <v>1</v>
       </c>
       <c r="F108">
-        <v>213</v>
+        <v>362</v>
       </c>
       <c r="G108">
         <v>5</v>
@@ -10916,13 +10916,13 @@
         <v>1</v>
       </c>
       <c r="J108">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="K108">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L108">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="M108" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10931,10 +10931,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P108">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Q108">
-        <v>1147</v>
+        <v>2280</v>
       </c>
       <c r="S108">
         <v>1</v>
@@ -10993,7 +10993,7 @@
         <v>20033</v>
       </c>
       <c r="C109" t="str">
-        <v>虞翻-弓箭手 T3</v>
+        <v>程昱-弓箭手 T3</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -11002,7 +11002,7 @@
         <v>1</v>
       </c>
       <c r="F109">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="G109">
         <v>5</v>
@@ -11014,13 +11014,13 @@
         <v>1</v>
       </c>
       <c r="J109">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K109">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L109">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="M109" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11029,10 +11029,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P109">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="Q109">
-        <v>1102</v>
+        <v>2040</v>
       </c>
       <c r="S109">
         <v>1</v>
@@ -11091,7 +11091,7 @@
         <v>20034</v>
       </c>
       <c r="C110" t="str">
-        <v>邓芝-弓箭手 T3</v>
+        <v>鲁肃-弓箭手 T3</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -11100,7 +11100,7 @@
         <v>1</v>
       </c>
       <c r="F110">
-        <v>261</v>
+        <v>375</v>
       </c>
       <c r="G110">
         <v>5</v>
@@ -11112,13 +11112,13 @@
         <v>1</v>
       </c>
       <c r="J110">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="K110">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L110">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="M110" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11127,10 +11127,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P110">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Q110">
-        <v>1208</v>
+        <v>2102</v>
       </c>
       <c r="S110">
         <v>1</v>
@@ -11189,7 +11189,7 @@
         <v>20035</v>
       </c>
       <c r="C111" t="str">
-        <v>阚泽-弓箭手 T3</v>
+        <v>诸葛瑾-弓箭手 T3</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -11198,7 +11198,7 @@
         <v>1</v>
       </c>
       <c r="F111">
-        <v>258</v>
+        <v>375</v>
       </c>
       <c r="G111">
         <v>5</v>
@@ -11210,13 +11210,13 @@
         <v>1</v>
       </c>
       <c r="J111">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="K111">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L111">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="M111" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11225,10 +11225,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P111">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Q111">
-        <v>1247</v>
+        <v>2318</v>
       </c>
       <c r="S111">
         <v>1</v>
@@ -11287,7 +11287,7 @@
         <v>20036</v>
       </c>
       <c r="C112" t="str">
-        <v>左慈-弓箭手 T3</v>
+        <v>戏志才-弓箭手 T3</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -11296,7 +11296,7 @@
         <v>1</v>
       </c>
       <c r="F112">
-        <v>273</v>
+        <v>429</v>
       </c>
       <c r="G112">
         <v>5</v>
@@ -11308,13 +11308,13 @@
         <v>1</v>
       </c>
       <c r="J112">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="K112">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L112">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="M112" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11323,10 +11323,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P112">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="Q112">
-        <v>1194</v>
+        <v>2160</v>
       </c>
       <c r="S112">
         <v>1</v>
@@ -11385,7 +11385,7 @@
         <v>20037</v>
       </c>
       <c r="C113" t="str">
-        <v>鲁肃-弓箭手 T4</v>
+        <v>庞德公-弓箭手 T4</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -11394,7 +11394,7 @@
         <v>1</v>
       </c>
       <c r="F113">
-        <v>402</v>
+        <v>504</v>
       </c>
       <c r="G113">
         <v>6</v>
@@ -11406,13 +11406,13 @@
         <v>1</v>
       </c>
       <c r="J113">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="K113">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L113">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="M113" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11421,10 +11421,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P113">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="Q113">
-        <v>1162</v>
+        <v>2405</v>
       </c>
       <c r="S113">
         <v>1</v>
@@ -11483,7 +11483,7 @@
         <v>20038</v>
       </c>
       <c r="C114" t="str">
-        <v>张春华-弓箭手 T4</v>
+        <v>黄月英-弓箭手 T4</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -11492,7 +11492,7 @@
         <v>1</v>
       </c>
       <c r="F114">
-        <v>390</v>
+        <v>535</v>
       </c>
       <c r="G114">
         <v>6</v>
@@ -11504,13 +11504,13 @@
         <v>1</v>
       </c>
       <c r="J114">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="K114">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L114">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="M114" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11519,10 +11519,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P114">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q114">
-        <v>1255</v>
+        <v>2405</v>
       </c>
       <c r="S114">
         <v>1</v>
@@ -11581,7 +11581,7 @@
         <v>20039</v>
       </c>
       <c r="C115" t="str">
-        <v>杨修-弓箭手 T4</v>
+        <v>蒋琬-弓箭手 T4</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -11590,7 +11590,7 @@
         <v>1</v>
       </c>
       <c r="F115">
-        <v>379</v>
+        <v>588</v>
       </c>
       <c r="G115">
         <v>6</v>
@@ -11602,13 +11602,13 @@
         <v>1</v>
       </c>
       <c r="J115">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K115">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="L115">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="M115" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11617,10 +11617,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P115">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Q115">
-        <v>1159</v>
+        <v>2163</v>
       </c>
       <c r="S115">
         <v>1</v>
@@ -11679,7 +11679,7 @@
         <v>20040</v>
       </c>
       <c r="C116" t="str">
-        <v>王异-弓箭手 T4</v>
+        <v>邓芝-弓箭手 T4</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -11688,7 +11688,7 @@
         <v>1</v>
       </c>
       <c r="F116">
-        <v>389</v>
+        <v>551</v>
       </c>
       <c r="G116">
         <v>6</v>
@@ -11700,13 +11700,13 @@
         <v>1</v>
       </c>
       <c r="J116">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K116">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="L116">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="M116" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11715,10 +11715,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P116">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="Q116">
-        <v>1318</v>
+        <v>2147</v>
       </c>
       <c r="S116">
         <v>1</v>
@@ -11777,7 +11777,7 @@
         <v>20041</v>
       </c>
       <c r="C117" t="str">
-        <v>逢纪-弓箭手 T4</v>
+        <v>诸葛亮-弓箭手 T4</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -11786,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="F117">
-        <v>397</v>
+        <v>547</v>
       </c>
       <c r="G117">
         <v>6</v>
@@ -11798,13 +11798,13 @@
         <v>1</v>
       </c>
       <c r="J117">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="K117">
         <v>61</v>
       </c>
       <c r="L117">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="M117" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11813,10 +11813,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P117">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q117">
-        <v>1268</v>
+        <v>2018</v>
       </c>
       <c r="S117">
         <v>1</v>
@@ -11875,7 +11875,7 @@
         <v>20042</v>
       </c>
       <c r="C118" t="str">
-        <v>徐庶-弓箭手 T4</v>
+        <v>司马懿-弓箭手 T4</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -11884,7 +11884,7 @@
         <v>1</v>
       </c>
       <c r="F118">
-        <v>389</v>
+        <v>432</v>
       </c>
       <c r="G118">
         <v>6</v>
@@ -11896,13 +11896,13 @@
         <v>1</v>
       </c>
       <c r="J118">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="K118">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L118">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="M118" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11911,10 +11911,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P118">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Q118">
-        <v>1129</v>
+        <v>1997</v>
       </c>
       <c r="S118">
         <v>1</v>
@@ -11973,7 +11973,7 @@
         <v>20043</v>
       </c>
       <c r="C119" t="str">
-        <v>步骘-弓箭手 T4</v>
+        <v>钟繇-弓箭手 T4</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -11982,7 +11982,7 @@
         <v>1</v>
       </c>
       <c r="F119">
-        <v>331</v>
+        <v>621</v>
       </c>
       <c r="G119">
         <v>6</v>
@@ -11994,13 +11994,13 @@
         <v>1</v>
       </c>
       <c r="J119">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="K119">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L119">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="M119" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12009,10 +12009,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P119">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="Q119">
-        <v>1273</v>
+        <v>2273</v>
       </c>
       <c r="S119">
         <v>1</v>
@@ -12071,7 +12071,7 @@
         <v>20044</v>
       </c>
       <c r="C120" t="str">
-        <v>程昱-弓箭手 T4</v>
+        <v>王朗-弓箭手 T4</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -12080,7 +12080,7 @@
         <v>1</v>
       </c>
       <c r="F120">
-        <v>320</v>
+        <v>511</v>
       </c>
       <c r="G120">
         <v>6</v>
@@ -12092,13 +12092,13 @@
         <v>1</v>
       </c>
       <c r="J120">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="K120">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L120">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="M120" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12107,10 +12107,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P120">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="Q120">
-        <v>1125</v>
+        <v>2401</v>
       </c>
       <c r="S120">
         <v>1</v>
@@ -12169,7 +12169,7 @@
         <v>20045</v>
       </c>
       <c r="C121" t="str">
-        <v>庞德公-弓箭手 T4</v>
+        <v>蔡文姬-弓箭手 T4</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -12178,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="F121">
-        <v>360</v>
+        <v>581</v>
       </c>
       <c r="G121">
         <v>6</v>
@@ -12190,13 +12190,13 @@
         <v>1</v>
       </c>
       <c r="J121">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="K121">
         <v>55</v>
       </c>
       <c r="L121">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="M121" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12205,10 +12205,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P121">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Q121">
-        <v>1247</v>
+        <v>2345</v>
       </c>
       <c r="S121">
         <v>1</v>
@@ -12267,7 +12267,7 @@
         <v>20046</v>
       </c>
       <c r="C122" t="str">
-        <v>步练师-弓箭手 T4</v>
+        <v>小乔-弓箭手 T4</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -12276,7 +12276,7 @@
         <v>1</v>
       </c>
       <c r="F122">
-        <v>324</v>
+        <v>577</v>
       </c>
       <c r="G122">
         <v>6</v>
@@ -12288,13 +12288,13 @@
         <v>1</v>
       </c>
       <c r="J122">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="K122">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L122">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="M122" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12303,10 +12303,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P122">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="Q122">
-        <v>1283</v>
+        <v>1984</v>
       </c>
       <c r="S122">
         <v>1</v>
@@ -12365,7 +12365,7 @@
         <v>20047</v>
       </c>
       <c r="C123" t="str">
-        <v>孙乾-弓箭手 T4</v>
+        <v>大乔-弓箭手 T4</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -12374,7 +12374,7 @@
         <v>1</v>
       </c>
       <c r="F123">
-        <v>322</v>
+        <v>476</v>
       </c>
       <c r="G123">
         <v>6</v>
@@ -12386,13 +12386,13 @@
         <v>1</v>
       </c>
       <c r="J123">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="K123">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L123">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="M123" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12401,10 +12401,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P123">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q123">
-        <v>1315</v>
+        <v>2070</v>
       </c>
       <c r="S123">
         <v>1</v>
@@ -12463,7 +12463,7 @@
         <v>20048</v>
       </c>
       <c r="C124" t="str">
-        <v>蒋琬-弓箭手 T4</v>
+        <v>貂蝉-弓箭手 T4</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -12472,7 +12472,7 @@
         <v>1</v>
       </c>
       <c r="F124">
-        <v>385</v>
+        <v>501</v>
       </c>
       <c r="G124">
         <v>6</v>
@@ -12484,13 +12484,13 @@
         <v>1</v>
       </c>
       <c r="J124">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="K124">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L124">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="M124" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12499,10 +12499,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P124">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Q124">
-        <v>1190</v>
+        <v>2007</v>
       </c>
       <c r="S124">
         <v>1</v>
@@ -12775,7 +12775,7 @@
       </c>
       <c r="F127">
         <f>ROUND(SQRT(J105*K105*L105)/400,1)</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="F129">
         <f>ROUND(SQRT(J107*K107*L107)/400,1)</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -13282,7 +13282,7 @@
       </c>
       <c r="F132">
         <f>ROUND(SQRT(J110*K110*L110)/400,1)</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="F134">
         <f>ROUND(SQRT(J112*K112*L112)/400,1)</f>
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -15615,7 +15615,7 @@
         <v>30001</v>
       </c>
       <c r="C155" t="str">
-        <v>马铁-骑兵 T1</v>
+        <v>杨奉-骑兵 T1</v>
       </c>
       <c r="D155">
         <v>2</v>
@@ -15624,7 +15624,7 @@
         <v>1</v>
       </c>
       <c r="F155">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="G155">
         <v>3</v>
@@ -15636,13 +15636,13 @@
         <v>1</v>
       </c>
       <c r="J155">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="K155">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L155">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="M155" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15651,10 +15651,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P155">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="Q155">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="S155">
         <v>3</v>
@@ -15713,7 +15713,7 @@
         <v>30002</v>
       </c>
       <c r="C156" t="str">
-        <v>马腾-骑兵 T1</v>
+        <v>兀突骨-骑兵 T1</v>
       </c>
       <c r="D156">
         <v>2</v>
@@ -15722,7 +15722,7 @@
         <v>1</v>
       </c>
       <c r="F156">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G156">
         <v>3</v>
@@ -15734,13 +15734,13 @@
         <v>1</v>
       </c>
       <c r="J156">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="K156">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L156">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="M156" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15749,10 +15749,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P156">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Q156">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S156">
         <v>3</v>
@@ -15811,7 +15811,7 @@
         <v>30003</v>
       </c>
       <c r="C157" t="str">
-        <v>李堪-骑兵 T1</v>
+        <v>梁兴-骑兵 T1</v>
       </c>
       <c r="D157">
         <v>2</v>
@@ -15820,7 +15820,7 @@
         <v>1</v>
       </c>
       <c r="F157">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="G157">
         <v>3</v>
@@ -15832,13 +15832,13 @@
         <v>1</v>
       </c>
       <c r="J157">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="K157">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L157">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="M157" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15847,10 +15847,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P157">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="Q157">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="S157">
         <v>3</v>
@@ -15909,7 +15909,7 @@
         <v>30004</v>
       </c>
       <c r="C158" t="str">
-        <v>张角-骑兵 T1</v>
+        <v>张辽-骑兵 T1</v>
       </c>
       <c r="D158">
         <v>2</v>
@@ -15918,7 +15918,7 @@
         <v>1</v>
       </c>
       <c r="F158">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="G158">
         <v>3</v>
@@ -15930,13 +15930,13 @@
         <v>1</v>
       </c>
       <c r="J158">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="K158">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L158">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M158" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15945,10 +15945,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P158">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q158">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="S158">
         <v>3</v>
@@ -16007,7 +16007,7 @@
         <v>30005</v>
       </c>
       <c r="C159" t="str">
-        <v>牛辅-骑兵 T1</v>
+        <v>邓茂-骑兵 T1</v>
       </c>
       <c r="D159">
         <v>2</v>
@@ -16016,7 +16016,7 @@
         <v>1</v>
       </c>
       <c r="F159">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G159">
         <v>3</v>
@@ -16028,13 +16028,13 @@
         <v>1</v>
       </c>
       <c r="J159">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="K159">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L159">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="M159" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16043,10 +16043,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P159">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Q159">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="S159">
         <v>3</v>
@@ -16105,7 +16105,7 @@
         <v>30006</v>
       </c>
       <c r="C160" t="str">
-        <v>孙尚香-骑兵 T1</v>
+        <v>丘力居-骑兵 T1</v>
       </c>
       <c r="D160">
         <v>2</v>
@@ -16114,7 +16114,7 @@
         <v>1</v>
       </c>
       <c r="F160">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="G160">
         <v>3</v>
@@ -16126,13 +16126,13 @@
         <v>1</v>
       </c>
       <c r="J160">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K160">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L160">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="M160" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16141,10 +16141,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P160">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q160">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="S160">
         <v>3</v>
@@ -16203,7 +16203,7 @@
         <v>30007</v>
       </c>
       <c r="C161" t="str">
-        <v>张横-骑兵 T1</v>
+        <v>李儒-骑兵 T1</v>
       </c>
       <c r="D161">
         <v>2</v>
@@ -16212,7 +16212,7 @@
         <v>1</v>
       </c>
       <c r="F161">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="G161">
         <v>3</v>
@@ -16224,13 +16224,13 @@
         <v>1</v>
       </c>
       <c r="J161">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="K161">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L161">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="M161" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16239,10 +16239,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P161">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="Q161">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="S161">
         <v>3</v>
@@ -16301,7 +16301,7 @@
         <v>30008</v>
       </c>
       <c r="C162" t="str">
-        <v>赵云-骑兵 T1</v>
+        <v>杨秋-骑兵 T1</v>
       </c>
       <c r="D162">
         <v>2</v>
@@ -16310,7 +16310,7 @@
         <v>1</v>
       </c>
       <c r="F162">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="G162">
         <v>3</v>
@@ -16322,13 +16322,13 @@
         <v>1</v>
       </c>
       <c r="J162">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="K162">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L162">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="M162" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16337,10 +16337,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P162">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="Q162">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="S162">
         <v>3</v>
@@ -16399,7 +16399,7 @@
         <v>30009</v>
       </c>
       <c r="C163" t="str">
-        <v>波才-骑兵 T2</v>
+        <v>曹纯-骑兵 T2</v>
       </c>
       <c r="D163">
         <v>2</v>
@@ -16408,7 +16408,7 @@
         <v>1</v>
       </c>
       <c r="F163">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="G163">
         <v>4</v>
@@ -16420,13 +16420,13 @@
         <v>1</v>
       </c>
       <c r="J163">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="K163">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L163">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="M163" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16435,10 +16435,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P163">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Q163">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="S163">
         <v>3</v>
@@ -16497,7 +16497,7 @@
         <v>30010</v>
       </c>
       <c r="C164" t="str">
-        <v>楼班-骑兵 T2</v>
+        <v>阎行-骑兵 T2</v>
       </c>
       <c r="D164">
         <v>2</v>
@@ -16506,7 +16506,7 @@
         <v>1</v>
       </c>
       <c r="F164">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="G164">
         <v>4</v>
@@ -16518,13 +16518,13 @@
         <v>1</v>
       </c>
       <c r="J164">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="K164">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="L164">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="M164" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16533,10 +16533,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P164">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="Q164">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="S164">
         <v>3</v>
@@ -16595,7 +16595,7 @@
         <v>30011</v>
       </c>
       <c r="C165" t="str">
-        <v>高升-骑兵 T2</v>
+        <v>樊稠-骑兵 T2</v>
       </c>
       <c r="D165">
         <v>2</v>
@@ -16604,7 +16604,7 @@
         <v>1</v>
       </c>
       <c r="F165">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="G165">
         <v>4</v>
@@ -16616,13 +16616,13 @@
         <v>1</v>
       </c>
       <c r="J165">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="K165">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L165">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="M165" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16631,10 +16631,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P165">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q165">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="S165">
         <v>3</v>
@@ -16693,7 +16693,7 @@
         <v>30012</v>
       </c>
       <c r="C166" t="str">
-        <v>马岱-骑兵 T2</v>
+        <v>程银-骑兵 T2</v>
       </c>
       <c r="D166">
         <v>2</v>
@@ -16702,7 +16702,7 @@
         <v>1</v>
       </c>
       <c r="F166">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="G166">
         <v>4</v>
@@ -16714,10 +16714,10 @@
         <v>1</v>
       </c>
       <c r="J166">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="K166">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L166">
         <v>1.12</v>
@@ -16729,10 +16729,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P166">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q166">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="S166">
         <v>3</v>
@@ -16791,7 +16791,7 @@
         <v>30013</v>
       </c>
       <c r="C167" t="str">
-        <v>邓茂-骑兵 T2</v>
+        <v>苏仆延-骑兵 T2</v>
       </c>
       <c r="D167">
         <v>2</v>
@@ -16800,7 +16800,7 @@
         <v>1</v>
       </c>
       <c r="F167">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -16812,13 +16812,13 @@
         <v>1</v>
       </c>
       <c r="J167">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="K167">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L167">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="M167" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16827,10 +16827,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P167">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="Q167">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="S167">
         <v>3</v>
@@ -16889,7 +16889,7 @@
         <v>30014</v>
       </c>
       <c r="C168" t="str">
-        <v>花鬘-骑兵 T2</v>
+        <v>韩暹-骑兵 T2</v>
       </c>
       <c r="D168">
         <v>2</v>
@@ -16898,7 +16898,7 @@
         <v>1</v>
       </c>
       <c r="F168">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="G168">
         <v>4</v>
@@ -16910,13 +16910,13 @@
         <v>1</v>
       </c>
       <c r="J168">
-        <v>215</v>
+        <v>148</v>
       </c>
       <c r="K168">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L168">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M168" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16925,10 +16925,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P168">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Q168">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="S168">
         <v>3</v>
@@ -16987,7 +16987,7 @@
         <v>30015</v>
       </c>
       <c r="C169" t="str">
-        <v>梁兴-骑兵 T2</v>
+        <v>赵弘-骑兵 T2</v>
       </c>
       <c r="D169">
         <v>2</v>
@@ -16996,7 +16996,7 @@
         <v>1</v>
       </c>
       <c r="F169">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G169">
         <v>4</v>
@@ -17008,13 +17008,13 @@
         <v>1</v>
       </c>
       <c r="J169">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="K169">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L169">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="M169" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17023,10 +17023,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P169">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Q169">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="S169">
         <v>3</v>
@@ -17085,7 +17085,7 @@
         <v>30016</v>
       </c>
       <c r="C170" t="str">
-        <v>韩忠-骑兵 T2</v>
+        <v>凌统-骑兵 T2</v>
       </c>
       <c r="D170">
         <v>2</v>
@@ -17094,7 +17094,7 @@
         <v>1</v>
       </c>
       <c r="F170">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="G170">
         <v>4</v>
@@ -17106,13 +17106,13 @@
         <v>1</v>
       </c>
       <c r="J170">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K170">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L170">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="M170" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17121,10 +17121,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P170">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Q170">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S170">
         <v>3</v>
@@ -17183,7 +17183,7 @@
         <v>30017</v>
       </c>
       <c r="C171" t="str">
-        <v>徐荣-骑兵 T3</v>
+        <v>波才-骑兵 T3</v>
       </c>
       <c r="D171">
         <v>2</v>
@@ -17192,7 +17192,7 @@
         <v>1</v>
       </c>
       <c r="F171">
-        <v>141</v>
+        <v>242</v>
       </c>
       <c r="G171">
         <v>5</v>
@@ -17204,13 +17204,13 @@
         <v>1</v>
       </c>
       <c r="J171">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="K171">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L171">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M171" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17219,7 +17219,7 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P171">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Q171">
         <v>119</v>
@@ -17281,7 +17281,7 @@
         <v>30018</v>
       </c>
       <c r="C172" t="str">
-        <v>马云禄-骑兵 T3</v>
+        <v>张横-骑兵 T3</v>
       </c>
       <c r="D172">
         <v>2</v>
@@ -17290,7 +17290,7 @@
         <v>1</v>
       </c>
       <c r="F172">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="G172">
         <v>5</v>
@@ -17305,10 +17305,10 @@
         <v>201</v>
       </c>
       <c r="K172">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L172">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M172" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17317,10 +17317,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P172">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="Q172">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="S172">
         <v>3</v>
@@ -17379,7 +17379,7 @@
         <v>30019</v>
       </c>
       <c r="C173" t="str">
-        <v>丘力居-骑兵 T3</v>
+        <v>马玩-骑兵 T3</v>
       </c>
       <c r="D173">
         <v>2</v>
@@ -17388,7 +17388,7 @@
         <v>1</v>
       </c>
       <c r="F173">
-        <v>172</v>
+        <v>255</v>
       </c>
       <c r="G173">
         <v>5</v>
@@ -17400,13 +17400,13 @@
         <v>1</v>
       </c>
       <c r="J173">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="K173">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L173">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M173" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17415,10 +17415,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P173">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="Q173">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="S173">
         <v>3</v>
@@ -17477,7 +17477,7 @@
         <v>30020</v>
       </c>
       <c r="C174" t="str">
-        <v>董卓-骑兵 T3</v>
+        <v>马岱-骑兵 T3</v>
       </c>
       <c r="D174">
         <v>2</v>
@@ -17486,7 +17486,7 @@
         <v>1</v>
       </c>
       <c r="F174">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="G174">
         <v>5</v>
@@ -17498,13 +17498,13 @@
         <v>1</v>
       </c>
       <c r="J174">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="K174">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L174">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M174" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17513,10 +17513,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P174">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q174">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="S174">
         <v>3</v>
@@ -17575,7 +17575,7 @@
         <v>30021</v>
       </c>
       <c r="C175" t="str">
-        <v>张绣-骑兵 T3</v>
+        <v>吕蒙-骑兵 T3</v>
       </c>
       <c r="D175">
         <v>2</v>
@@ -17584,7 +17584,7 @@
         <v>1</v>
       </c>
       <c r="F175">
-        <v>157</v>
+        <v>232</v>
       </c>
       <c r="G175">
         <v>5</v>
@@ -17596,13 +17596,13 @@
         <v>1</v>
       </c>
       <c r="J175">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K175">
         <v>34</v>
       </c>
       <c r="L175">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="M175" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17611,10 +17611,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P175">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="Q175">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="S175">
         <v>3</v>
@@ -17673,7 +17673,7 @@
         <v>30022</v>
       </c>
       <c r="C176" t="str">
-        <v>骨进-骑兵 T3</v>
+        <v>李堪-骑兵 T3</v>
       </c>
       <c r="D176">
         <v>2</v>
@@ -17682,7 +17682,7 @@
         <v>1</v>
       </c>
       <c r="F176">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="G176">
         <v>5</v>
@@ -17694,13 +17694,13 @@
         <v>1</v>
       </c>
       <c r="J176">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="K176">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="L176">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="M176" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17709,10 +17709,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P176">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Q176">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S176">
         <v>3</v>
@@ -17771,7 +17771,7 @@
         <v>30023</v>
       </c>
       <c r="C177" t="str">
-        <v>杨奉-骑兵 T3</v>
+        <v>楼班-骑兵 T3</v>
       </c>
       <c r="D177">
         <v>2</v>
@@ -17780,7 +17780,7 @@
         <v>1</v>
       </c>
       <c r="F177">
-        <v>146</v>
+        <v>218</v>
       </c>
       <c r="G177">
         <v>5</v>
@@ -17792,13 +17792,13 @@
         <v>1</v>
       </c>
       <c r="J177">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="K177">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L177">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="M177" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17807,10 +17807,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P177">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="Q177">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="S177">
         <v>3</v>
@@ -17869,7 +17869,7 @@
         <v>30024</v>
       </c>
       <c r="C178" t="str">
-        <v>成公英-骑兵 T3</v>
+        <v>韩忠-骑兵 T3</v>
       </c>
       <c r="D178">
         <v>2</v>
@@ -17878,7 +17878,7 @@
         <v>1</v>
       </c>
       <c r="F178">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="G178">
         <v>5</v>
@@ -17890,13 +17890,13 @@
         <v>1</v>
       </c>
       <c r="J178">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="K178">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L178">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="M178" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17905,10 +17905,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P178">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Q178">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="S178">
         <v>3</v>
@@ -17967,7 +17967,7 @@
         <v>30025</v>
       </c>
       <c r="C179" t="str">
-        <v>张鲁-骑兵 T4</v>
+        <v>郭汜-骑兵 T4</v>
       </c>
       <c r="D179">
         <v>2</v>
@@ -17976,7 +17976,7 @@
         <v>1</v>
       </c>
       <c r="F179">
-        <v>229</v>
+        <v>290</v>
       </c>
       <c r="G179">
         <v>6</v>
@@ -17988,10 +17988,10 @@
         <v>1</v>
       </c>
       <c r="J179">
-        <v>248</v>
+        <v>304</v>
       </c>
       <c r="K179">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="L179">
         <v>1.2</v>
@@ -18003,10 +18003,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P179">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="Q179">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S179">
         <v>3</v>
@@ -18065,7 +18065,7 @@
         <v>30026</v>
       </c>
       <c r="C180" t="str">
-        <v>杨秋-骑兵 T4</v>
+        <v>吕玲绮-骑兵 T4</v>
       </c>
       <c r="D180">
         <v>2</v>
@@ -18074,7 +18074,7 @@
         <v>1</v>
       </c>
       <c r="F180">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="G180">
         <v>6</v>
@@ -18086,13 +18086,13 @@
         <v>1</v>
       </c>
       <c r="J180">
-        <v>339</v>
+        <v>242</v>
       </c>
       <c r="K180">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="L180">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="M180" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18101,10 +18101,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P180">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Q180">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S180">
         <v>3</v>
@@ -18163,7 +18163,7 @@
         <v>30027</v>
       </c>
       <c r="C181" t="str">
-        <v>吕布-骑兵 T4</v>
+        <v>高升-骑兵 T4</v>
       </c>
       <c r="D181">
         <v>2</v>
@@ -18172,7 +18172,7 @@
         <v>1</v>
       </c>
       <c r="F181">
-        <v>252</v>
+        <v>331</v>
       </c>
       <c r="G181">
         <v>6</v>
@@ -18184,13 +18184,13 @@
         <v>1</v>
       </c>
       <c r="J181">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="K181">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="L181">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="M181" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18199,10 +18199,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P181">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q181">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="S181">
         <v>3</v>
@@ -18261,7 +18261,7 @@
         <v>30028</v>
       </c>
       <c r="C182" t="str">
-        <v>兀突骨-骑兵 T4</v>
+        <v>骨进-骑兵 T4</v>
       </c>
       <c r="D182">
         <v>2</v>
@@ -18270,7 +18270,7 @@
         <v>1</v>
       </c>
       <c r="F182">
-        <v>210</v>
+        <v>312</v>
       </c>
       <c r="G182">
         <v>6</v>
@@ -18282,13 +18282,13 @@
         <v>1</v>
       </c>
       <c r="J182">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K182">
         <v>42</v>
       </c>
       <c r="L182">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="M182" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18297,10 +18297,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P182">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Q182">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="S182">
         <v>3</v>
@@ -18359,7 +18359,7 @@
         <v>30029</v>
       </c>
       <c r="C183" t="str">
-        <v>胡轸-骑兵 T4</v>
+        <v>韩遂-骑兵 T4</v>
       </c>
       <c r="D183">
         <v>2</v>
@@ -18368,7 +18368,7 @@
         <v>1</v>
       </c>
       <c r="F183">
-        <v>210</v>
+        <v>302</v>
       </c>
       <c r="G183">
         <v>6</v>
@@ -18380,13 +18380,13 @@
         <v>1</v>
       </c>
       <c r="J183">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="K183">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L183">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M183" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18395,10 +18395,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P183">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="Q183">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S183">
         <v>3</v>
@@ -18457,7 +18457,7 @@
         <v>30030</v>
       </c>
       <c r="C184" t="str">
-        <v>阎行-骑兵 T4</v>
+        <v>胡轸-骑兵 T4</v>
       </c>
       <c r="D184">
         <v>2</v>
@@ -18466,7 +18466,7 @@
         <v>1</v>
       </c>
       <c r="F184">
-        <v>204</v>
+        <v>325</v>
       </c>
       <c r="G184">
         <v>6</v>
@@ -18478,13 +18478,13 @@
         <v>1</v>
       </c>
       <c r="J184">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="K184">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L184">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="M184" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18493,10 +18493,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P184">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q184">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S184">
         <v>3</v>
@@ -18555,7 +18555,7 @@
         <v>30031</v>
       </c>
       <c r="C185" t="str">
-        <v>程远志-骑兵 T4</v>
+        <v>李傕-骑兵 T4</v>
       </c>
       <c r="D185">
         <v>2</v>
@@ -18564,7 +18564,7 @@
         <v>1</v>
       </c>
       <c r="F185">
-        <v>236</v>
+        <v>342</v>
       </c>
       <c r="G185">
         <v>6</v>
@@ -18576,13 +18576,13 @@
         <v>1</v>
       </c>
       <c r="J185">
-        <v>346</v>
+        <v>318</v>
       </c>
       <c r="K185">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L185">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="M185" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18591,10 +18591,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P185">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="Q185">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="S185">
         <v>3</v>
@@ -18653,7 +18653,7 @@
         <v>30032</v>
       </c>
       <c r="C186" t="str">
-        <v>公孙瓒-骑兵 T4</v>
+        <v>孙尚香-骑兵 T4</v>
       </c>
       <c r="D186">
         <v>2</v>
@@ -18662,7 +18662,7 @@
         <v>1</v>
       </c>
       <c r="F186">
-        <v>176</v>
+        <v>285</v>
       </c>
       <c r="G186">
         <v>6</v>
@@ -18674,13 +18674,13 @@
         <v>1</v>
       </c>
       <c r="J186">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="K186">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L186">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="M186" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -18689,10 +18689,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P186">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="Q186">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="S186">
         <v>3</v>
@@ -18955,7 +18955,7 @@
         <v>40001</v>
       </c>
       <c r="C189" t="str">
-        <v>成廉-长枪兵 T1</v>
+        <v>陈武-长枪兵 T1</v>
       </c>
       <c r="D189">
         <v>3</v>
@@ -18964,7 +18964,7 @@
         <v>1</v>
       </c>
       <c r="F189">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="G189">
         <v>3</v>
@@ -18976,7 +18976,7 @@
         <v>1</v>
       </c>
       <c r="J189">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="K189">
         <v>15</v>
@@ -18991,10 +18991,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P189">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="Q189">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="S189">
         <v>4</v>
@@ -19053,7 +19053,7 @@
         <v>40002</v>
       </c>
       <c r="C190" t="str">
-        <v>卓膺-长枪兵 T1</v>
+        <v>成廉-长枪兵 T1</v>
       </c>
       <c r="D190">
         <v>3</v>
@@ -19062,7 +19062,7 @@
         <v>1</v>
       </c>
       <c r="F190">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="G190">
         <v>3</v>
@@ -19077,10 +19077,10 @@
         <v>90</v>
       </c>
       <c r="K190">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L190">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="M190" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19089,10 +19089,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P190">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="Q190">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="S190">
         <v>4</v>
@@ -19151,7 +19151,7 @@
         <v>40003</v>
       </c>
       <c r="C191" t="str">
-        <v>文钦-长枪兵 T1</v>
+        <v>张飞-长枪兵 T1</v>
       </c>
       <c r="D191">
         <v>3</v>
@@ -19160,7 +19160,7 @@
         <v>1</v>
       </c>
       <c r="F191">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="G191">
         <v>3</v>
@@ -19172,13 +19172,13 @@
         <v>1</v>
       </c>
       <c r="J191">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K191">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L191">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="M191" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19187,10 +19187,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P191">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Q191">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="S191">
         <v>4</v>
@@ -19249,7 +19249,7 @@
         <v>40004</v>
       </c>
       <c r="C192" t="str">
-        <v>钟会-长枪兵 T1</v>
+        <v>施绩-长枪兵 T1</v>
       </c>
       <c r="D192">
         <v>3</v>
@@ -19258,7 +19258,7 @@
         <v>1</v>
       </c>
       <c r="F192">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="G192">
         <v>3</v>
@@ -19270,13 +19270,13 @@
         <v>1</v>
       </c>
       <c r="J192">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="K192">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L192">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="M192" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19285,10 +19285,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P192">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Q192">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="S192">
         <v>4</v>
@@ -19347,7 +19347,7 @@
         <v>40005</v>
       </c>
       <c r="C193" t="str">
-        <v>吕据-长枪兵 T1</v>
+        <v>泠苞-长枪兵 T1</v>
       </c>
       <c r="D193">
         <v>3</v>
@@ -19356,7 +19356,7 @@
         <v>1</v>
       </c>
       <c r="F193">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G193">
         <v>3</v>
@@ -19368,13 +19368,13 @@
         <v>1</v>
       </c>
       <c r="J193">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K193">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L193">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M193" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19383,10 +19383,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P193">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q193">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="S193">
         <v>4</v>
@@ -19445,7 +19445,7 @@
         <v>40006</v>
       </c>
       <c r="C194" t="str">
-        <v>文鸯-长枪兵 T1</v>
+        <v>唐咨-长枪兵 T1</v>
       </c>
       <c r="D194">
         <v>3</v>
@@ -19454,7 +19454,7 @@
         <v>1</v>
       </c>
       <c r="F194">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="G194">
         <v>3</v>
@@ -19466,13 +19466,13 @@
         <v>1</v>
       </c>
       <c r="J194">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="K194">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L194">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="M194" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19481,10 +19481,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P194">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Q194">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="S194">
         <v>4</v>
@@ -19543,7 +19543,7 @@
         <v>40007</v>
       </c>
       <c r="C195" t="str">
-        <v>费诗-长枪兵 T1</v>
+        <v>杨龄-长枪兵 T1</v>
       </c>
       <c r="D195">
         <v>3</v>
@@ -19552,7 +19552,7 @@
         <v>1</v>
       </c>
       <c r="F195">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="G195">
         <v>3</v>
@@ -19567,10 +19567,10 @@
         <v>115</v>
       </c>
       <c r="K195">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L195">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="M195" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19579,10 +19579,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P195">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="Q195">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="S195">
         <v>4</v>
@@ -19641,7 +19641,7 @@
         <v>40008</v>
       </c>
       <c r="C196" t="str">
-        <v>高顺-长枪兵 T1</v>
+        <v>郝萌-长枪兵 T1</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -19650,7 +19650,7 @@
         <v>1</v>
       </c>
       <c r="F196">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="G196">
         <v>3</v>
@@ -19662,13 +19662,13 @@
         <v>1</v>
       </c>
       <c r="J196">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="K196">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L196">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="M196" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19677,10 +19677,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P196">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Q196">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="S196">
         <v>4</v>
@@ -19739,7 +19739,7 @@
         <v>40009</v>
       </c>
       <c r="C197" t="str">
-        <v>任夔-长枪兵 T2</v>
+        <v>鲍隆-长枪兵 T2</v>
       </c>
       <c r="D197">
         <v>3</v>
@@ -19748,7 +19748,7 @@
         <v>1</v>
       </c>
       <c r="F197">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="G197">
         <v>4</v>
@@ -19760,13 +19760,13 @@
         <v>1</v>
       </c>
       <c r="J197">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K197">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L197">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="M197" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19775,10 +19775,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P197">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q197">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="S197">
         <v>4</v>
@@ -19837,7 +19837,7 @@
         <v>40010</v>
       </c>
       <c r="C198" t="str">
-        <v>潘璋-长枪兵 T2</v>
+        <v>韩玄-长枪兵 T2</v>
       </c>
       <c r="D198">
         <v>3</v>
@@ -19846,7 +19846,7 @@
         <v>1</v>
       </c>
       <c r="F198">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="G198">
         <v>4</v>
@@ -19858,13 +19858,13 @@
         <v>1</v>
       </c>
       <c r="J198">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="K198">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L198">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="M198" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19873,10 +19873,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P198">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Q198">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="S198">
         <v>4</v>
@@ -19935,7 +19935,7 @@
         <v>40011</v>
       </c>
       <c r="C199" t="str">
-        <v>董袭-长枪兵 T2</v>
+        <v>曹性-长枪兵 T2</v>
       </c>
       <c r="D199">
         <v>3</v>
@@ -19944,7 +19944,7 @@
         <v>1</v>
       </c>
       <c r="F199">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="G199">
         <v>4</v>
@@ -19956,13 +19956,13 @@
         <v>1</v>
       </c>
       <c r="J199">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="K199">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L199">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="M199" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -19971,10 +19971,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P199">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="Q199">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="S199">
         <v>4</v>
@@ -20033,7 +20033,7 @@
         <v>40012</v>
       </c>
       <c r="C200" t="str">
-        <v>邢道荣-长枪兵 T2</v>
+        <v>李恢-长枪兵 T2</v>
       </c>
       <c r="D200">
         <v>3</v>
@@ -20042,7 +20042,7 @@
         <v>1</v>
       </c>
       <c r="F200">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="G200">
         <v>4</v>
@@ -20054,13 +20054,13 @@
         <v>1</v>
       </c>
       <c r="J200">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K200">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L200">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="M200" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20069,10 +20069,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P200">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q200">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="S200">
         <v>4</v>
@@ -20131,7 +20131,7 @@
         <v>40013</v>
       </c>
       <c r="C201" t="str">
-        <v>孟达-长枪兵 T2</v>
+        <v>吴兰-长枪兵 T2</v>
       </c>
       <c r="D201">
         <v>3</v>
@@ -20140,7 +20140,7 @@
         <v>1</v>
       </c>
       <c r="F201">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G201">
         <v>4</v>
@@ -20152,13 +20152,13 @@
         <v>1</v>
       </c>
       <c r="J201">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K201">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L201">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="M201" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20167,10 +20167,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P201">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="Q201">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S201">
         <v>4</v>
@@ -20229,7 +20229,7 @@
         <v>40014</v>
       </c>
       <c r="C202" t="str">
-        <v>王基-长枪兵 T2</v>
+        <v>魏续-长枪兵 T2</v>
       </c>
       <c r="D202">
         <v>3</v>
@@ -20238,7 +20238,7 @@
         <v>1</v>
       </c>
       <c r="F202">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="G202">
         <v>4</v>
@@ -20250,13 +20250,13 @@
         <v>1</v>
       </c>
       <c r="J202">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="K202">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L202">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="M202" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20265,10 +20265,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P202">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q202">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="S202">
         <v>4</v>
@@ -20327,7 +20327,7 @@
         <v>40015</v>
       </c>
       <c r="C203" t="str">
-        <v>郝昭-长枪兵 T2</v>
+        <v>胡济-长枪兵 T2</v>
       </c>
       <c r="D203">
         <v>3</v>
@@ -20336,7 +20336,7 @@
         <v>1</v>
       </c>
       <c r="F203">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="G203">
         <v>4</v>
@@ -20348,13 +20348,13 @@
         <v>1</v>
       </c>
       <c r="J203">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="K203">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L203">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="M203" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20363,10 +20363,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P203">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Q203">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="S203">
         <v>4</v>
@@ -20425,7 +20425,7 @@
         <v>40016</v>
       </c>
       <c r="C204" t="str">
-        <v>彭羕-长枪兵 T2</v>
+        <v>钟会-长枪兵 T2</v>
       </c>
       <c r="D204">
         <v>3</v>
@@ -20434,7 +20434,7 @@
         <v>1</v>
       </c>
       <c r="F204">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="G204">
         <v>4</v>
@@ -20446,13 +20446,13 @@
         <v>1</v>
       </c>
       <c r="J204">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="K204">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L204">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="M204" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20461,10 +20461,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P204">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Q204">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="S204">
         <v>4</v>
@@ -20523,7 +20523,7 @@
         <v>40017</v>
       </c>
       <c r="C205" t="str">
-        <v>赵范-长枪兵 T3</v>
+        <v>胡遵-长枪兵 T3</v>
       </c>
       <c r="D205">
         <v>3</v>
@@ -20532,7 +20532,7 @@
         <v>1</v>
       </c>
       <c r="F205">
-        <v>201</v>
+        <v>284</v>
       </c>
       <c r="G205">
         <v>5</v>
@@ -20544,13 +20544,13 @@
         <v>1</v>
       </c>
       <c r="J205">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="K205">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L205">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="M205" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20559,10 +20559,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P205">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q205">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="S205">
         <v>4</v>
@@ -20621,7 +20621,7 @@
         <v>40018</v>
       </c>
       <c r="C206" t="str">
-        <v>盛曼-长枪兵 T3</v>
+        <v>赵范-长枪兵 T3</v>
       </c>
       <c r="D206">
         <v>3</v>
@@ -20630,7 +20630,7 @@
         <v>1</v>
       </c>
       <c r="F206">
-        <v>200</v>
+        <v>311</v>
       </c>
       <c r="G206">
         <v>5</v>
@@ -20642,13 +20642,13 @@
         <v>1</v>
       </c>
       <c r="J206">
-        <v>171</v>
+        <v>223</v>
       </c>
       <c r="K206">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L206">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="M206" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20657,10 +20657,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P206">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="Q206">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="S206">
         <v>4</v>
@@ -20719,7 +20719,7 @@
         <v>40019</v>
       </c>
       <c r="C207" t="str">
-        <v>蒋钦-长枪兵 T3</v>
+        <v>沙摩柯-长枪兵 T3</v>
       </c>
       <c r="D207">
         <v>3</v>
@@ -20728,7 +20728,7 @@
         <v>1</v>
       </c>
       <c r="F207">
-        <v>203</v>
+        <v>264</v>
       </c>
       <c r="G207">
         <v>5</v>
@@ -20740,13 +20740,13 @@
         <v>1</v>
       </c>
       <c r="J207">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="K207">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L207">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="M207" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20755,10 +20755,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P207">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="Q207">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S207">
         <v>4</v>
@@ -20817,7 +20817,7 @@
         <v>40020</v>
       </c>
       <c r="C208" t="str">
-        <v>黄权-长枪兵 T3</v>
+        <v>吕据-长枪兵 T3</v>
       </c>
       <c r="D208">
         <v>3</v>
@@ -20826,7 +20826,7 @@
         <v>1</v>
       </c>
       <c r="F208">
-        <v>168</v>
+        <v>269</v>
       </c>
       <c r="G208">
         <v>5</v>
@@ -20838,13 +20838,13 @@
         <v>1</v>
       </c>
       <c r="J208">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="K208">
         <v>26</v>
       </c>
       <c r="L208">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M208" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20853,10 +20853,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P208">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Q208">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="S208">
         <v>4</v>
@@ -20915,7 +20915,7 @@
         <v>40021</v>
       </c>
       <c r="C209" t="str">
-        <v>毋丘俭-长枪兵 T3</v>
+        <v>盛曼-长枪兵 T3</v>
       </c>
       <c r="D209">
         <v>3</v>
@@ -20924,7 +20924,7 @@
         <v>1</v>
       </c>
       <c r="F209">
-        <v>234</v>
+        <v>327</v>
       </c>
       <c r="G209">
         <v>5</v>
@@ -20936,13 +20936,13 @@
         <v>1</v>
       </c>
       <c r="J209">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="K209">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L209">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="M209" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20951,10 +20951,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P209">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q209">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="S209">
         <v>4</v>
@@ -21013,7 +21013,7 @@
         <v>40022</v>
       </c>
       <c r="C210" t="str">
-        <v>孙礼-长枪兵 T3</v>
+        <v>毋丘俭-长枪兵 T3</v>
       </c>
       <c r="D210">
         <v>3</v>
@@ -21022,7 +21022,7 @@
         <v>1</v>
       </c>
       <c r="F210">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="G210">
         <v>5</v>
@@ -21034,13 +21034,13 @@
         <v>1</v>
       </c>
       <c r="J210">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="K210">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L210">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="M210" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21049,10 +21049,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P210">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q210">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="S210">
         <v>4</v>
@@ -21111,7 +21111,7 @@
         <v>40023</v>
       </c>
       <c r="C211" t="str">
-        <v>吴兰-长枪兵 T3</v>
+        <v>刘贤-长枪兵 T3</v>
       </c>
       <c r="D211">
         <v>3</v>
@@ -21120,7 +21120,7 @@
         <v>1</v>
       </c>
       <c r="F211">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="G211">
         <v>5</v>
@@ -21132,13 +21132,13 @@
         <v>1</v>
       </c>
       <c r="J211">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="K211">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L211">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="M211" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21147,10 +21147,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P211">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q211">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="S211">
         <v>4</v>
@@ -21209,7 +21209,7 @@
         <v>40024</v>
       </c>
       <c r="C212" t="str">
-        <v>张飞-长枪兵 T3</v>
+        <v>潘璋-长枪兵 T3</v>
       </c>
       <c r="D212">
         <v>3</v>
@@ -21218,7 +21218,7 @@
         <v>1</v>
       </c>
       <c r="F212">
-        <v>185</v>
+        <v>338</v>
       </c>
       <c r="G212">
         <v>5</v>
@@ -21230,13 +21230,13 @@
         <v>1</v>
       </c>
       <c r="J212">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="K212">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L212">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="M212" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21245,10 +21245,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P212">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="Q212">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="S212">
         <v>4</v>
@@ -21307,7 +21307,7 @@
         <v>40025</v>
       </c>
       <c r="C213" t="str">
-        <v>吴懿-长枪兵 T4</v>
+        <v>郝昭-长枪兵 T4</v>
       </c>
       <c r="D213">
         <v>3</v>
@@ -21316,7 +21316,7 @@
         <v>1</v>
       </c>
       <c r="F213">
-        <v>279</v>
+        <v>429</v>
       </c>
       <c r="G213">
         <v>6</v>
@@ -21328,13 +21328,13 @@
         <v>1</v>
       </c>
       <c r="J213">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="K213">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L213">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="M213" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21343,10 +21343,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P213">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q213">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="S213">
         <v>4</v>
@@ -21405,7 +21405,7 @@
         <v>40026</v>
       </c>
       <c r="C214" t="str">
-        <v>刘璝-长枪兵 T4</v>
+        <v>吴懿-长枪兵 T4</v>
       </c>
       <c r="D214">
         <v>3</v>
@@ -21414,7 +21414,7 @@
         <v>1</v>
       </c>
       <c r="F214">
-        <v>303</v>
+        <v>411</v>
       </c>
       <c r="G214">
         <v>6</v>
@@ -21426,13 +21426,13 @@
         <v>1</v>
       </c>
       <c r="J214">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K214">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="L214">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M214" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21441,10 +21441,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P214">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Q214">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="S214">
         <v>4</v>
@@ -21503,7 +21503,7 @@
         <v>40027</v>
       </c>
       <c r="C215" t="str">
-        <v>诸葛诞-长枪兵 T4</v>
+        <v>刘璝-长枪兵 T4</v>
       </c>
       <c r="D215">
         <v>3</v>
@@ -21512,7 +21512,7 @@
         <v>1</v>
       </c>
       <c r="F215">
-        <v>341</v>
+        <v>410</v>
       </c>
       <c r="G215">
         <v>6</v>
@@ -21524,13 +21524,13 @@
         <v>1</v>
       </c>
       <c r="J215">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K215">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L215">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M215" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21539,7 +21539,7 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P215">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q215">
         <v>139</v>
@@ -21601,7 +21601,7 @@
         <v>40028</v>
       </c>
       <c r="C216" t="str">
-        <v>宋宪-长枪兵 T4</v>
+        <v>朱然-长枪兵 T4</v>
       </c>
       <c r="D216">
         <v>3</v>
@@ -21610,7 +21610,7 @@
         <v>1</v>
       </c>
       <c r="F216">
-        <v>252</v>
+        <v>389</v>
       </c>
       <c r="G216">
         <v>6</v>
@@ -21622,13 +21622,13 @@
         <v>1</v>
       </c>
       <c r="J216">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="K216">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L216">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="M216" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21637,10 +21637,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P216">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="Q216">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="S216">
         <v>4</v>
@@ -21699,7 +21699,7 @@
         <v>40029</v>
       </c>
       <c r="C217" t="str">
-        <v>陈武-长枪兵 T4</v>
+        <v>文鸯-长枪兵 T4</v>
       </c>
       <c r="D217">
         <v>3</v>
@@ -21708,7 +21708,7 @@
         <v>1</v>
       </c>
       <c r="F217">
-        <v>287</v>
+        <v>444</v>
       </c>
       <c r="G217">
         <v>6</v>
@@ -21720,13 +21720,13 @@
         <v>1</v>
       </c>
       <c r="J217">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="K217">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L217">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="M217" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21735,10 +21735,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P217">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Q217">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S217">
         <v>4</v>
@@ -21797,7 +21797,7 @@
         <v>40030</v>
       </c>
       <c r="C218" t="str">
-        <v>魏延-长枪兵 T4</v>
+        <v>王基-长枪兵 T4</v>
       </c>
       <c r="D218">
         <v>3</v>
@@ -21806,7 +21806,7 @@
         <v>1</v>
       </c>
       <c r="F218">
-        <v>254</v>
+        <v>357</v>
       </c>
       <c r="G218">
         <v>6</v>
@@ -21818,13 +21818,13 @@
         <v>1</v>
       </c>
       <c r="J218">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="K218">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L218">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="M218" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21833,10 +21833,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P218">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="Q218">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="S218">
         <v>4</v>
@@ -21895,7 +21895,7 @@
         <v>40031</v>
       </c>
       <c r="C219" t="str">
-        <v>邓艾-长枪兵 T4</v>
+        <v>陈应-长枪兵 T4</v>
       </c>
       <c r="D219">
         <v>3</v>
@@ -21904,7 +21904,7 @@
         <v>1</v>
       </c>
       <c r="F219">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="G219">
         <v>6</v>
@@ -21916,13 +21916,13 @@
         <v>1</v>
       </c>
       <c r="J219">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="K219">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="L219">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="M219" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21931,10 +21931,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P219">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="Q219">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="S219">
         <v>4</v>
@@ -21993,7 +21993,7 @@
         <v>40032</v>
       </c>
       <c r="C220" t="str">
-        <v>全琮-长枪兵 T4</v>
+        <v>任夔-长枪兵 T4</v>
       </c>
       <c r="D220">
         <v>3</v>
@@ -22002,7 +22002,7 @@
         <v>1</v>
       </c>
       <c r="F220">
-        <v>297</v>
+        <v>420</v>
       </c>
       <c r="G220">
         <v>6</v>
@@ -22014,13 +22014,13 @@
         <v>1</v>
       </c>
       <c r="J220">
-        <v>207</v>
+        <v>300</v>
       </c>
       <c r="K220">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L220">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M220" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22029,10 +22029,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P220">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q220">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="S220">
         <v>4</v>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="F254">
         <f>ROUND(SQRT(J101*K101*L101)/400,1)</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G254">
         <v>0</v>
@@ -25567,7 +25567,7 @@
         <v>90001</v>
       </c>
       <c r="C256" t="str">
-        <v>【零号病毒】张郃-步兵 T1</v>
+        <v>【变异主宰】霍峻-步兵 T1</v>
       </c>
       <c r="D256">
         <v>0</v>
@@ -25576,7 +25576,7 @@
         <v>20</v>
       </c>
       <c r="F256">
-        <v>184</v>
+        <v>311</v>
       </c>
       <c r="G256">
         <v>3</v>
@@ -25588,13 +25588,13 @@
         <v>1</v>
       </c>
       <c r="J256">
-        <v>564</v>
+        <v>693</v>
       </c>
       <c r="K256">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L256">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="M256" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25603,10 +25603,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P256">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Q256">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="S256">
         <v>0</v>
@@ -25665,7 +25665,7 @@
         <v>90002</v>
       </c>
       <c r="C257" t="str">
-        <v>【虚空母体】管亥-步兵 T1</v>
+        <v>【零号病毒】颜良-步兵 T1</v>
       </c>
       <c r="D257">
         <v>0</v>
@@ -25674,7 +25674,7 @@
         <v>20</v>
       </c>
       <c r="F257">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="G257">
         <v>3</v>
@@ -25686,13 +25686,13 @@
         <v>1</v>
       </c>
       <c r="J257">
-        <v>613</v>
+        <v>521</v>
       </c>
       <c r="K257">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L257">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="M257" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25701,10 +25701,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P257">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Q257">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="S257">
         <v>0</v>
@@ -25763,7 +25763,7 @@
         <v>90003</v>
       </c>
       <c r="C258" t="str">
-        <v>【虚空母体】吕翔-步兵 T1</v>
+        <v>【末日先兆】马忠-步兵 T1</v>
       </c>
       <c r="D258">
         <v>0</v>
@@ -25772,7 +25772,7 @@
         <v>20</v>
       </c>
       <c r="F258">
-        <v>206</v>
+        <v>273</v>
       </c>
       <c r="G258">
         <v>3</v>
@@ -25784,13 +25784,13 @@
         <v>1</v>
       </c>
       <c r="J258">
-        <v>607</v>
+        <v>557</v>
       </c>
       <c r="K258">
         <v>16</v>
       </c>
       <c r="L258">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="M258" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25799,10 +25799,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P258">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Q258">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="S258">
         <v>0</v>
@@ -25861,7 +25861,7 @@
         <v>90004</v>
       </c>
       <c r="C259" t="str">
-        <v>【钢铁暴君】周泰-步兵 T2</v>
+        <v>【钢铁暴君】关樾-步兵 T2</v>
       </c>
       <c r="D259">
         <v>0</v>
@@ -25870,7 +25870,7 @@
         <v>20</v>
       </c>
       <c r="F259">
-        <v>349</v>
+        <v>422</v>
       </c>
       <c r="G259">
         <v>4</v>
@@ -25882,13 +25882,13 @@
         <v>1</v>
       </c>
       <c r="J259">
-        <v>927</v>
+        <v>755</v>
       </c>
       <c r="K259">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L259">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="M259" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25897,10 +25897,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P259">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Q259">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="S259">
         <v>0</v>
@@ -25959,7 +25959,7 @@
         <v>90005</v>
       </c>
       <c r="C260" t="str">
-        <v>【虚空母体】严白虎-步兵 T2</v>
+        <v>【变异主宰】孙坚-步兵 T2</v>
       </c>
       <c r="D260">
         <v>0</v>
@@ -25968,7 +25968,7 @@
         <v>20</v>
       </c>
       <c r="F260">
-        <v>378</v>
+        <v>508</v>
       </c>
       <c r="G260">
         <v>4</v>
@@ -25980,13 +25980,13 @@
         <v>1</v>
       </c>
       <c r="J260">
-        <v>1046</v>
+        <v>990</v>
       </c>
       <c r="K260">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L260">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="M260" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25995,10 +25995,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P260">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Q260">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S260">
         <v>0</v>
@@ -26057,7 +26057,7 @@
         <v>90006</v>
       </c>
       <c r="C261" t="str">
-        <v>【变异主宰】关兴-步兵 T2</v>
+        <v>【钢铁暴君】祖茂-步兵 T2</v>
       </c>
       <c r="D261">
         <v>0</v>
@@ -26066,7 +26066,7 @@
         <v>20</v>
       </c>
       <c r="F261">
-        <v>342</v>
+        <v>513</v>
       </c>
       <c r="G261">
         <v>4</v>
@@ -26078,13 +26078,13 @@
         <v>1</v>
       </c>
       <c r="J261">
-        <v>900</v>
+        <v>1007</v>
       </c>
       <c r="K261">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L261">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="M261" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26093,10 +26093,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P261">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q261">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="S261">
         <v>0</v>
@@ -26155,7 +26155,7 @@
         <v>90007</v>
       </c>
       <c r="C262" t="str">
-        <v>【末日先兆】张翼-步兵 T3</v>
+        <v>【零号病毒】淳于琼-步兵 T3</v>
       </c>
       <c r="D262">
         <v>0</v>
@@ -26164,7 +26164,7 @@
         <v>20</v>
       </c>
       <c r="F262">
-        <v>549</v>
+        <v>807</v>
       </c>
       <c r="G262">
         <v>5</v>
@@ -26176,13 +26176,13 @@
         <v>1</v>
       </c>
       <c r="J262">
-        <v>1369</v>
+        <v>1418</v>
       </c>
       <c r="K262">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L262">
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="M262" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26191,10 +26191,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P262">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="Q262">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S262">
         <v>0</v>
@@ -26253,7 +26253,7 @@
         <v>90008</v>
       </c>
       <c r="C263" t="str">
-        <v>【钢铁暴君】关樾-步兵 T3</v>
+        <v>【极秘项目】郭援-步兵 T3</v>
       </c>
       <c r="D263">
         <v>0</v>
@@ -26262,7 +26262,7 @@
         <v>20</v>
       </c>
       <c r="F263">
-        <v>484</v>
+        <v>666</v>
       </c>
       <c r="G263">
         <v>5</v>
@@ -26274,13 +26274,13 @@
         <v>1</v>
       </c>
       <c r="J263">
-        <v>1237</v>
+        <v>1198</v>
       </c>
       <c r="K263">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L263">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="M263" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26289,10 +26289,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P263">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="Q263">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="S263">
         <v>0</v>
@@ -26351,7 +26351,7 @@
         <v>90009</v>
       </c>
       <c r="C264" t="str">
-        <v>【钢铁暴君】焦触-步兵 T3</v>
+        <v>【钢铁暴君】裴元绍-步兵 T3</v>
       </c>
       <c r="D264">
         <v>0</v>
@@ -26360,7 +26360,7 @@
         <v>20</v>
       </c>
       <c r="F264">
-        <v>470</v>
+        <v>611</v>
       </c>
       <c r="G264">
         <v>5</v>
@@ -26372,13 +26372,13 @@
         <v>1</v>
       </c>
       <c r="J264">
-        <v>1138</v>
+        <v>1039</v>
       </c>
       <c r="K264">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L264">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="M264" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26387,7 +26387,7 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P264">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Q264">
         <v>91</v>
@@ -26449,7 +26449,7 @@
         <v>90010</v>
       </c>
       <c r="C265" t="str">
-        <v>【钢铁暴君】程普-步兵 T4</v>
+        <v>【变异主宰】孙策-步兵 T4</v>
       </c>
       <c r="D265">
         <v>0</v>
@@ -26458,7 +26458,7 @@
         <v>20</v>
       </c>
       <c r="F265">
-        <v>741</v>
+        <v>897</v>
       </c>
       <c r="G265">
         <v>6</v>
@@ -26470,13 +26470,13 @@
         <v>1</v>
       </c>
       <c r="J265">
-        <v>1626</v>
+        <v>1409</v>
       </c>
       <c r="K265">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="L265">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="M265" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26485,10 +26485,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P265">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Q265">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="S265">
         <v>0</v>
@@ -26547,7 +26547,7 @@
         <v>90011</v>
       </c>
       <c r="C266" t="str">
-        <v>【极秘项目】孙权-步兵 T4</v>
+        <v>【虚空母体】于禁-步兵 T4</v>
       </c>
       <c r="D266">
         <v>0</v>
@@ -26556,7 +26556,7 @@
         <v>20</v>
       </c>
       <c r="F266">
-        <v>674</v>
+        <v>1072</v>
       </c>
       <c r="G266">
         <v>6</v>
@@ -26568,13 +26568,13 @@
         <v>1</v>
       </c>
       <c r="J266">
-        <v>1557</v>
+        <v>1664</v>
       </c>
       <c r="K266">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L266">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="M266" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26583,7 +26583,7 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P266">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="Q266">
         <v>105</v>
@@ -26645,7 +26645,7 @@
         <v>90012</v>
       </c>
       <c r="C267" t="str">
-        <v>【钢铁暴君】周仓-步兵 T4</v>
+        <v>【虚空母体】曹休-步兵 T4</v>
       </c>
       <c r="D267">
         <v>0</v>
@@ -26654,7 +26654,7 @@
         <v>20</v>
       </c>
       <c r="F267">
-        <v>815</v>
+        <v>1116</v>
       </c>
       <c r="G267">
         <v>6</v>
@@ -26666,13 +26666,13 @@
         <v>1</v>
       </c>
       <c r="J267">
-        <v>1774</v>
+        <v>1762</v>
       </c>
       <c r="K267">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L267">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="M267" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26681,10 +26681,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P267">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Q267">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S267">
         <v>0</v>
@@ -26743,7 +26743,7 @@
         <v>90013</v>
       </c>
       <c r="C268" t="str">
-        <v>【虚空母体】大乔-弓箭手 T1</v>
+        <v>【极秘项目】沮授-弓箭手 T1</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -26752,7 +26752,7 @@
         <v>20</v>
       </c>
       <c r="F268">
-        <v>247</v>
+        <v>335</v>
       </c>
       <c r="G268">
         <v>3</v>
@@ -26764,13 +26764,13 @@
         <v>1</v>
       </c>
       <c r="J268">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K268">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L268">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="M268" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26779,10 +26779,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P268">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="Q268">
-        <v>1190</v>
+        <v>2292</v>
       </c>
       <c r="S268">
         <v>1</v>
@@ -26841,7 +26841,7 @@
         <v>90014</v>
       </c>
       <c r="C269" t="str">
-        <v>【极秘项目】宗预-弓箭手 T1</v>
+        <v>【变异主宰】黄忠-弓箭手 T1</v>
       </c>
       <c r="D269">
         <v>1</v>
@@ -26850,7 +26850,7 @@
         <v>20</v>
       </c>
       <c r="F269">
-        <v>261</v>
+        <v>373</v>
       </c>
       <c r="G269">
         <v>3</v>
@@ -26862,13 +26862,13 @@
         <v>1</v>
       </c>
       <c r="J269">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="K269">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L269">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="M269" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -26877,10 +26877,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P269">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Q269">
-        <v>1283</v>
+        <v>2417</v>
       </c>
       <c r="S269">
         <v>1</v>
@@ -26939,7 +26939,7 @@
         <v>90015</v>
       </c>
       <c r="C270" t="str">
-        <v>【变异主宰】太史慈-弓箭手 T1</v>
+        <v>【零号病毒】伊籍-弓箭手 T1</v>
       </c>
       <c r="D270">
         <v>1</v>
@@ -26948,7 +26948,7 @@
         <v>20</v>
       </c>
       <c r="F270">
-        <v>248</v>
+        <v>357</v>
       </c>
       <c r="G270">
         <v>3</v>
@@ -26960,10 +26960,10 @@
         <v>1</v>
       </c>
       <c r="J270">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K270">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L270">
         <v>1.91</v>
@@ -26975,10 +26975,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P270">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q270">
-        <v>1231</v>
+        <v>2226</v>
       </c>
       <c r="S270">
         <v>1</v>
@@ -27037,7 +27037,7 @@
         <v>90016</v>
       </c>
       <c r="C271" t="str">
-        <v>【极秘项目】钟繇-弓箭手 T2</v>
+        <v>【变异主宰】简雍-弓箭手 T2</v>
       </c>
       <c r="D271">
         <v>1</v>
@@ -27046,7 +27046,7 @@
         <v>20</v>
       </c>
       <c r="F271">
-        <v>455</v>
+        <v>637</v>
       </c>
       <c r="G271">
         <v>4</v>
@@ -27058,13 +27058,13 @@
         <v>1</v>
       </c>
       <c r="J271">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="K271">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L271">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="M271" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27073,10 +27073,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P271">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="Q271">
-        <v>1270</v>
+        <v>2336</v>
       </c>
       <c r="S271">
         <v>1</v>
@@ -27135,7 +27135,7 @@
         <v>90017</v>
       </c>
       <c r="C272" t="str">
-        <v>【末日先兆】庞统-弓箭手 T2</v>
+        <v>【零号病毒】薛综-弓箭手 T2</v>
       </c>
       <c r="D272">
         <v>1</v>
@@ -27144,7 +27144,7 @@
         <v>20</v>
       </c>
       <c r="F272">
-        <v>381</v>
+        <v>569</v>
       </c>
       <c r="G272">
         <v>4</v>
@@ -27156,13 +27156,13 @@
         <v>1</v>
       </c>
       <c r="J272">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="K272">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L272">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="M272" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27171,10 +27171,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P272">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Q272">
-        <v>1162</v>
+        <v>2152</v>
       </c>
       <c r="S272">
         <v>1</v>
@@ -27233,7 +27233,7 @@
         <v>90018</v>
       </c>
       <c r="C273" t="str">
-        <v>【极秘项目】陆逊-弓箭手 T2</v>
+        <v>【极秘项目】审配-弓箭手 T2</v>
       </c>
       <c r="D273">
         <v>1</v>
@@ -27242,7 +27242,7 @@
         <v>20</v>
       </c>
       <c r="F273">
-        <v>350</v>
+        <v>555</v>
       </c>
       <c r="G273">
         <v>4</v>
@@ -27254,13 +27254,13 @@
         <v>1</v>
       </c>
       <c r="J273">
-        <v>327</v>
+        <v>290</v>
       </c>
       <c r="K273">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="L273">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="M273" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27269,10 +27269,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P273">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="Q273">
-        <v>1101</v>
+        <v>2218</v>
       </c>
       <c r="S273">
         <v>1</v>
@@ -27331,7 +27331,7 @@
         <v>90019</v>
       </c>
       <c r="C274" t="str">
-        <v>【零号病毒】貂蝉-弓箭手 T3</v>
+        <v>【变异主宰】杨修-弓箭手 T3</v>
       </c>
       <c r="D274">
         <v>1</v>
@@ -27340,7 +27340,7 @@
         <v>20</v>
       </c>
       <c r="F274">
-        <v>578</v>
+        <v>772</v>
       </c>
       <c r="G274">
         <v>5</v>
@@ -27352,13 +27352,13 @@
         <v>1</v>
       </c>
       <c r="J274">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="K274">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L274">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="M274" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27367,10 +27367,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P274">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q274">
-        <v>1156</v>
+        <v>2257</v>
       </c>
       <c r="S274">
         <v>1</v>
@@ -27429,7 +27429,7 @@
         <v>90020</v>
       </c>
       <c r="C275" t="str">
-        <v>【末日先兆】辛宪英-弓箭手 T3</v>
+        <v>【虚空母体】水镜先生-弓箭手 T3</v>
       </c>
       <c r="D275">
         <v>1</v>
@@ -27438,7 +27438,7 @@
         <v>20</v>
       </c>
       <c r="F275">
-        <v>564</v>
+        <v>941</v>
       </c>
       <c r="G275">
         <v>5</v>
@@ -27450,13 +27450,13 @@
         <v>1</v>
       </c>
       <c r="J275">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="K275">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="L275">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="M275" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27465,10 +27465,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P275">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="Q275">
-        <v>1082</v>
+        <v>2220</v>
       </c>
       <c r="S275">
         <v>1</v>
@@ -27527,7 +27527,7 @@
         <v>90021</v>
       </c>
       <c r="C276" t="str">
-        <v>【极秘项目】水镜先生-弓箭手 T3</v>
+        <v>【零号病毒】董昭-弓箭手 T3</v>
       </c>
       <c r="D276">
         <v>1</v>
@@ -27536,7 +27536,7 @@
         <v>20</v>
       </c>
       <c r="F276">
-        <v>618</v>
+        <v>877</v>
       </c>
       <c r="G276">
         <v>5</v>
@@ -27548,13 +27548,13 @@
         <v>1</v>
       </c>
       <c r="J276">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="K276">
         <v>57</v>
       </c>
       <c r="L276">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M276" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27563,10 +27563,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P276">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Q276">
-        <v>1307</v>
+        <v>2251</v>
       </c>
       <c r="S276">
         <v>1</v>
@@ -27625,7 +27625,7 @@
         <v>90022</v>
       </c>
       <c r="C277" t="str">
-        <v>【虚空母体】郑玄-弓箭手 T4</v>
+        <v>【变异主宰】张昭-弓箭手 T4</v>
       </c>
       <c r="D277">
         <v>1</v>
@@ -27634,7 +27634,7 @@
         <v>20</v>
       </c>
       <c r="F277">
-        <v>889</v>
+        <v>1182</v>
       </c>
       <c r="G277">
         <v>6</v>
@@ -27646,13 +27646,13 @@
         <v>1</v>
       </c>
       <c r="J277">
-        <v>535</v>
+        <v>560</v>
       </c>
       <c r="K277">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="L277">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="M277" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27661,10 +27661,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P277">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Q277">
-        <v>1248</v>
+        <v>2020</v>
       </c>
       <c r="S277">
         <v>1</v>
@@ -27723,7 +27723,7 @@
         <v>90023</v>
       </c>
       <c r="C278" t="str">
-        <v>【钢铁暴君】祝融-弓箭手 T4</v>
+        <v>【钢铁暴君】左慈-弓箭手 T4</v>
       </c>
       <c r="D278">
         <v>1</v>
@@ -27732,7 +27732,7 @@
         <v>20</v>
       </c>
       <c r="F278">
-        <v>896</v>
+        <v>1308</v>
       </c>
       <c r="G278">
         <v>6</v>
@@ -27744,13 +27744,13 @@
         <v>1</v>
       </c>
       <c r="J278">
-        <v>508</v>
+        <v>704</v>
       </c>
       <c r="K278">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L278">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="M278" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27759,10 +27759,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P278">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Q278">
-        <v>1203</v>
+        <v>2400</v>
       </c>
       <c r="S278">
         <v>1</v>
@@ -27821,7 +27821,7 @@
         <v>90024</v>
       </c>
       <c r="C279" t="str">
-        <v>【钢铁暴君】黄月英-弓箭手 T4</v>
+        <v>【虚空母体】甄姬-弓箭手 T4</v>
       </c>
       <c r="D279">
         <v>1</v>
@@ -27830,7 +27830,7 @@
         <v>20</v>
       </c>
       <c r="F279">
-        <v>791</v>
+        <v>1450</v>
       </c>
       <c r="G279">
         <v>6</v>
@@ -27842,13 +27842,13 @@
         <v>1</v>
       </c>
       <c r="J279">
-        <v>633</v>
+        <v>591</v>
       </c>
       <c r="K279">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="L279">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M279" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27857,10 +27857,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P279">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="Q279">
-        <v>1094</v>
+        <v>2003</v>
       </c>
       <c r="S279">
         <v>1</v>
@@ -27919,7 +27919,7 @@
         <v>90025</v>
       </c>
       <c r="C280" t="str">
-        <v>【变异主宰】韩暹-骑兵 T1</v>
+        <v>【末日先兆】曹彰-骑兵 T1</v>
       </c>
       <c r="D280">
         <v>2</v>
@@ -27928,7 +27928,7 @@
         <v>20</v>
       </c>
       <c r="F280">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="G280">
         <v>3</v>
@@ -27940,13 +27940,13 @@
         <v>1</v>
       </c>
       <c r="J280">
-        <v>572</v>
+        <v>411</v>
       </c>
       <c r="K280">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L280">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="M280" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -27955,10 +27955,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P280">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Q280">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="S280">
         <v>3</v>
@@ -28017,7 +28017,7 @@
         <v>90026</v>
       </c>
       <c r="C281" t="str">
-        <v>【末日先兆】李傕-骑兵 T1</v>
+        <v>【变异主宰】程远志-骑兵 T1</v>
       </c>
       <c r="D281">
         <v>2</v>
@@ -28026,7 +28026,7 @@
         <v>20</v>
       </c>
       <c r="F281">
-        <v>199</v>
+        <v>309</v>
       </c>
       <c r="G281">
         <v>3</v>
@@ -28038,13 +28038,13 @@
         <v>1</v>
       </c>
       <c r="J281">
-        <v>464</v>
+        <v>532</v>
       </c>
       <c r="K281">
         <v>26</v>
       </c>
       <c r="L281">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="M281" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28053,10 +28053,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P281">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="Q281">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="S281">
         <v>3</v>
@@ -28115,7 +28115,7 @@
         <v>90027</v>
       </c>
       <c r="C282" t="str">
-        <v>【零号病毒】吕蒙-骑兵 T2</v>
+        <v>【虚空母体】张曼成-骑兵 T2</v>
       </c>
       <c r="D282">
         <v>2</v>
@@ -28124,7 +28124,7 @@
         <v>20</v>
       </c>
       <c r="F282">
-        <v>303</v>
+        <v>494</v>
       </c>
       <c r="G282">
         <v>4</v>
@@ -28136,13 +28136,13 @@
         <v>1</v>
       </c>
       <c r="J282">
-        <v>607</v>
+        <v>735</v>
       </c>
       <c r="K282">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L282">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="M282" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28151,10 +28151,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P282">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Q282">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="S282">
         <v>3</v>
@@ -28213,7 +28213,7 @@
         <v>90028</v>
       </c>
       <c r="C283" t="str">
-        <v>【末日先兆】郭淮-骑兵 T2</v>
+        <v>【钢铁暴君】郭淮-骑兵 T2</v>
       </c>
       <c r="D283">
         <v>2</v>
@@ -28222,7 +28222,7 @@
         <v>20</v>
       </c>
       <c r="F283">
-        <v>332</v>
+        <v>602</v>
       </c>
       <c r="G283">
         <v>4</v>
@@ -28234,13 +28234,13 @@
         <v>1</v>
       </c>
       <c r="J283">
-        <v>656</v>
+        <v>852</v>
       </c>
       <c r="K283">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L283">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="M283" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28249,10 +28249,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P283">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="Q283">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="S283">
         <v>3</v>
@@ -28311,7 +28311,7 @@
         <v>90029</v>
       </c>
       <c r="C284" t="str">
-        <v>【末日先兆】马玩-骑兵 T3</v>
+        <v>【末日先兆】吕布-骑兵 T3</v>
       </c>
       <c r="D284">
         <v>2</v>
@@ -28320,7 +28320,7 @@
         <v>20</v>
       </c>
       <c r="F284">
-        <v>502</v>
+        <v>721</v>
       </c>
       <c r="G284">
         <v>5</v>
@@ -28332,13 +28332,13 @@
         <v>1</v>
       </c>
       <c r="J284">
-        <v>806</v>
+        <v>889</v>
       </c>
       <c r="K284">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L284">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="M284" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28347,10 +28347,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P284">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Q284">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="S284">
         <v>3</v>
@@ -28409,7 +28409,7 @@
         <v>90030</v>
       </c>
       <c r="C285" t="str">
-        <v>【极秘项目】李儒-骑兵 T3</v>
+        <v>【变异主宰】夏侯渊-骑兵 T3</v>
       </c>
       <c r="D285">
         <v>2</v>
@@ -28418,7 +28418,7 @@
         <v>20</v>
       </c>
       <c r="F285">
-        <v>484</v>
+        <v>780</v>
       </c>
       <c r="G285">
         <v>5</v>
@@ -28430,13 +28430,13 @@
         <v>1</v>
       </c>
       <c r="J285">
-        <v>835</v>
+        <v>987</v>
       </c>
       <c r="K285">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="L285">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="M285" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28445,10 +28445,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P285">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Q285">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="S285">
         <v>3</v>
@@ -28507,7 +28507,7 @@
         <v>90031</v>
       </c>
       <c r="C286" t="str">
-        <v>【零号病毒】苏仆延-骑兵 T4</v>
+        <v>【变异主宰】董卓-骑兵 T4</v>
       </c>
       <c r="D286">
         <v>2</v>
@@ -28516,7 +28516,7 @@
         <v>20</v>
       </c>
       <c r="F286">
-        <v>683</v>
+        <v>1014</v>
       </c>
       <c r="G286">
         <v>6</v>
@@ -28528,13 +28528,13 @@
         <v>1</v>
       </c>
       <c r="J286">
-        <v>1168</v>
+        <v>1190</v>
       </c>
       <c r="K286">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="L286">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="M286" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28543,10 +28543,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P286">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Q286">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S286">
         <v>3</v>
@@ -28605,7 +28605,7 @@
         <v>90032</v>
       </c>
       <c r="C287" t="str">
-        <v>【零号病毒】郭汜-骑兵 T4</v>
+        <v>【变异主宰】张角-骑兵 T4</v>
       </c>
       <c r="D287">
         <v>2</v>
@@ -28614,7 +28614,7 @@
         <v>20</v>
       </c>
       <c r="F287">
-        <v>766</v>
+        <v>1041</v>
       </c>
       <c r="G287">
         <v>6</v>
@@ -28626,13 +28626,13 @@
         <v>1</v>
       </c>
       <c r="J287">
-        <v>1396</v>
+        <v>1337</v>
       </c>
       <c r="K287">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="L287">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M287" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28641,10 +28641,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P287">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Q287">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="S287">
         <v>3</v>
@@ -28703,7 +28703,7 @@
         <v>90033</v>
       </c>
       <c r="C288" t="str">
-        <v>【虚空母体】魏续-长枪兵 T1</v>
+        <v>【末日先兆】诸葛诞-长枪兵 T1</v>
       </c>
       <c r="D288">
         <v>3</v>
@@ -28712,7 +28712,7 @@
         <v>20</v>
       </c>
       <c r="F288">
-        <v>257</v>
+        <v>393</v>
       </c>
       <c r="G288">
         <v>3</v>
@@ -28724,13 +28724,13 @@
         <v>1</v>
       </c>
       <c r="J288">
-        <v>382</v>
+        <v>449</v>
       </c>
       <c r="K288">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L288">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="M288" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28739,10 +28739,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P288">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="Q288">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="S288">
         <v>4</v>
@@ -28801,7 +28801,7 @@
         <v>90034</v>
       </c>
       <c r="C289" t="str">
-        <v>【钢铁暴君】唐咨-长枪兵 T1</v>
+        <v>【极秘项目】孙礼-长枪兵 T1</v>
       </c>
       <c r="D289">
         <v>3</v>
@@ -28810,7 +28810,7 @@
         <v>20</v>
       </c>
       <c r="F289">
-        <v>263</v>
+        <v>423</v>
       </c>
       <c r="G289">
         <v>3</v>
@@ -28822,13 +28822,13 @@
         <v>1</v>
       </c>
       <c r="J289">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K289">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L289">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="M289" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28837,10 +28837,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P289">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Q289">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="S289">
         <v>4</v>
@@ -28899,7 +28899,7 @@
         <v>90035</v>
       </c>
       <c r="C290" t="str">
-        <v>【极秘项目】李恢-长枪兵 T2</v>
+        <v>【变异主宰】彭羕-长枪兵 T2</v>
       </c>
       <c r="D290">
         <v>3</v>
@@ -28908,7 +28908,7 @@
         <v>20</v>
       </c>
       <c r="F290">
-        <v>393</v>
+        <v>593</v>
       </c>
       <c r="G290">
         <v>4</v>
@@ -28920,13 +28920,13 @@
         <v>1</v>
       </c>
       <c r="J290">
-        <v>544</v>
+        <v>621</v>
       </c>
       <c r="K290">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L290">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="M290" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -28935,10 +28935,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P290">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="Q290">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="S290">
         <v>4</v>
@@ -28997,7 +28997,7 @@
         <v>90036</v>
       </c>
       <c r="C291" t="str">
-        <v>【零号病毒】胡遵-长枪兵 T2</v>
+        <v>【虚空母体】金旋-长枪兵 T2</v>
       </c>
       <c r="D291">
         <v>3</v>
@@ -29006,7 +29006,7 @@
         <v>20</v>
       </c>
       <c r="F291">
-        <v>486</v>
+        <v>626</v>
       </c>
       <c r="G291">
         <v>4</v>
@@ -29018,13 +29018,13 @@
         <v>1</v>
       </c>
       <c r="J291">
-        <v>716</v>
+        <v>641</v>
       </c>
       <c r="K291">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L291">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="M291" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -29033,10 +29033,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P291">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="Q291">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="S291">
         <v>4</v>
@@ -29095,7 +29095,7 @@
         <v>90037</v>
       </c>
       <c r="C292" t="str">
-        <v>【变异主宰】吕介-长枪兵 T3</v>
+        <v>【钢铁暴君】陈就-长枪兵 T3</v>
       </c>
       <c r="D292">
         <v>3</v>
@@ -29104,7 +29104,7 @@
         <v>20</v>
       </c>
       <c r="F292">
-        <v>596</v>
+        <v>1025</v>
       </c>
       <c r="G292">
         <v>5</v>
@@ -29116,10 +29116,10 @@
         <v>1</v>
       </c>
       <c r="J292">
-        <v>738</v>
+        <v>902</v>
       </c>
       <c r="K292">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L292">
         <v>1.07</v>
@@ -29131,10 +29131,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P292">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="Q292">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="S292">
         <v>4</v>
@@ -29193,7 +29193,7 @@
         <v>90038</v>
       </c>
       <c r="C293" t="str">
-        <v>【钢铁暴君】高翔-长枪兵 T3</v>
+        <v>【钢铁暴君】宋宪-长枪兵 T3</v>
       </c>
       <c r="D293">
         <v>3</v>
@@ -29202,7 +29202,7 @@
         <v>20</v>
       </c>
       <c r="F293">
-        <v>665</v>
+        <v>962</v>
       </c>
       <c r="G293">
         <v>5</v>
@@ -29214,10 +29214,10 @@
         <v>1</v>
       </c>
       <c r="J293">
-        <v>817</v>
+        <v>859</v>
       </c>
       <c r="K293">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L293">
         <v>1.2</v>
@@ -29229,10 +29229,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P293">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="Q293">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S293">
         <v>4</v>
@@ -29291,7 +29291,7 @@
         <v>90039</v>
       </c>
       <c r="C294" t="str">
-        <v>【虚空母体】张任-长枪兵 T4</v>
+        <v>【极秘项目】陈泰-长枪兵 T4</v>
       </c>
       <c r="D294">
         <v>3</v>
@@ -29300,7 +29300,7 @@
         <v>20</v>
       </c>
       <c r="F294">
-        <v>980</v>
+        <v>1302</v>
       </c>
       <c r="G294">
         <v>6</v>
@@ -29312,13 +29312,13 @@
         <v>1</v>
       </c>
       <c r="J294">
-        <v>1127</v>
+        <v>1008</v>
       </c>
       <c r="K294">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L294">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="M294" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -29327,10 +29327,10 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P294">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Q294">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="S294">
         <v>4</v>
@@ -29389,7 +29389,7 @@
         <v>90040</v>
       </c>
       <c r="C295" t="str">
-        <v>【虚空母体】王平-长枪兵 T4</v>
+        <v>【末日先兆】张任-长枪兵 T4</v>
       </c>
       <c r="D295">
         <v>3</v>
@@ -29398,7 +29398,7 @@
         <v>20</v>
       </c>
       <c r="F295">
-        <v>972</v>
+        <v>1418</v>
       </c>
       <c r="G295">
         <v>6</v>
@@ -29410,13 +29410,13 @@
         <v>1</v>
       </c>
       <c r="J295">
-        <v>1180</v>
+        <v>1198</v>
       </c>
       <c r="K295">
         <v>54</v>
       </c>
       <c r="L295">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="M295" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -29425,7 +29425,7 @@
         <v>[[2,2],[20,3],[40,4],[60,5],[80,6],[100,7],[120,8],[140,9],[160,10],[180,11],[200,12]]</v>
       </c>
       <c r="P295">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="Q295">
         <v>150</v>

--- a/public/ArmyTable.xlsx
+++ b/public/ArmyTable.xlsx
@@ -797,7 +797,7 @@
         <v>10001</v>
       </c>
       <c r="C5" t="str">
-        <v>张翼-步兵 T1</v>
+        <v>傅彤-步兵 T1</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -818,13 +818,13 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="M5" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -836,10 +836,10 @@
         <v>[]</v>
       </c>
       <c r="P5">
-        <v>321</v>
+        <v>523</v>
       </c>
       <c r="Q5">
-        <v>103</v>
+        <v>398</v>
       </c>
       <c r="R5" t="str">
         <v>[1,800]</v>
@@ -893,7 +893,7 @@
         <v>1</v>
       </c>
       <c r="AI5" t="str">
-        <v>[91001,91013]</v>
+        <v>[92001,91013]</v>
       </c>
       <c r="AJ5" t="str">
         <v>2|1</v>
@@ -907,7 +907,7 @@
         <v>10002</v>
       </c>
       <c r="C6" t="str">
-        <v>曹操-步兵 T1</v>
+        <v>朱桓-步兵 T1</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="M6" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -946,10 +946,10 @@
         <v>[]</v>
       </c>
       <c r="P6">
-        <v>309</v>
+        <v>522</v>
       </c>
       <c r="Q6">
-        <v>102</v>
+        <v>378</v>
       </c>
       <c r="R6" t="str">
         <v>[1,800]</v>
@@ -1017,7 +1017,7 @@
         <v>10003</v>
       </c>
       <c r="C7" t="str">
-        <v>张南-步兵 T1</v>
+        <v>蒋舒-步兵 T1</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1038,13 +1038,13 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="K7">
         <v>7</v>
       </c>
       <c r="L7">
-        <v>0.94</v>
+        <v>0.96</v>
       </c>
       <c r="M7" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1056,10 +1056,10 @@
         <v>[]</v>
       </c>
       <c r="P7">
-        <v>319</v>
+        <v>516</v>
       </c>
       <c r="Q7">
-        <v>97</v>
+        <v>415</v>
       </c>
       <c r="R7" t="str">
         <v>[1,800]</v>
@@ -1127,7 +1127,7 @@
         <v>10004</v>
       </c>
       <c r="C8" t="str">
-        <v>霍峻-步兵 T1</v>
+        <v>周泰-步兵 T1</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1148,13 +1148,13 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L8">
-        <v>0.91</v>
+        <v>1.09</v>
       </c>
       <c r="M8" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1166,10 +1166,10 @@
         <v>[]</v>
       </c>
       <c r="P8">
-        <v>312</v>
+        <v>539</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>364</v>
       </c>
       <c r="R8" t="str">
         <v>[1,800]</v>
@@ -1237,7 +1237,7 @@
         <v>10005</v>
       </c>
       <c r="C9" t="str">
-        <v>吕凯-步兵 T1</v>
+        <v>程普-步兵 T1</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -1258,13 +1258,13 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="K9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="M9" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1276,10 +1276,10 @@
         <v>[]</v>
       </c>
       <c r="P9">
-        <v>318</v>
+        <v>525</v>
       </c>
       <c r="Q9">
-        <v>91</v>
+        <v>418</v>
       </c>
       <c r="R9" t="str">
         <v>[1,800]</v>
@@ -1347,7 +1347,7 @@
         <v>10006</v>
       </c>
       <c r="C10" t="str">
-        <v>傅彤-步兵 T1</v>
+        <v>关兴-步兵 T1</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -1368,13 +1368,13 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="K10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="M10" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1386,10 +1386,10 @@
         <v>[]</v>
       </c>
       <c r="P10">
-        <v>306</v>
+        <v>538</v>
       </c>
       <c r="Q10">
-        <v>96</v>
+        <v>431</v>
       </c>
       <c r="R10" t="str">
         <v>[1,800]</v>
@@ -1457,7 +1457,7 @@
         <v>10007</v>
       </c>
       <c r="C11" t="str">
-        <v>甘宁-步兵 T1</v>
+        <v>乐进-步兵 T1</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>101</v>
+        <v>197</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -1478,13 +1478,13 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="K11">
         <v>11</v>
       </c>
       <c r="L11">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="M11" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1496,10 +1496,10 @@
         <v>[]</v>
       </c>
       <c r="P11">
-        <v>308</v>
+        <v>522</v>
       </c>
       <c r="Q11">
-        <v>95</v>
+        <v>402</v>
       </c>
       <c r="R11" t="str">
         <v>[1,800]</v>
@@ -1567,7 +1567,7 @@
         <v>10008</v>
       </c>
       <c r="C12" t="str">
-        <v>裴元绍-步兵 T1</v>
+        <v>苏由-步兵 T1</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1576,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -1588,13 +1588,13 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="M12" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1606,10 +1606,10 @@
         <v>[]</v>
       </c>
       <c r="P12">
-        <v>318</v>
+        <v>539</v>
       </c>
       <c r="Q12">
-        <v>94</v>
+        <v>381</v>
       </c>
       <c r="R12" t="str">
         <v>[1,800]</v>
@@ -1677,7 +1677,7 @@
         <v>10009</v>
       </c>
       <c r="C13" t="str">
-        <v>孙坚-步兵 T1</v>
+        <v>高干-步兵 T1</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -1698,13 +1698,13 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="M13" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1716,10 +1716,10 @@
         <v>[]</v>
       </c>
       <c r="P13">
-        <v>322</v>
+        <v>537</v>
       </c>
       <c r="Q13">
-        <v>92</v>
+        <v>398</v>
       </c>
       <c r="R13" t="str">
         <v>[1,800]</v>
@@ -1787,7 +1787,7 @@
         <v>10010</v>
       </c>
       <c r="C14" t="str">
-        <v>许褚-步兵 T1</v>
+        <v>张翼-步兵 T1</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -1808,13 +1808,13 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="K14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="M14" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1826,10 +1826,10 @@
         <v>[]</v>
       </c>
       <c r="P14">
-        <v>307</v>
+        <v>536</v>
       </c>
       <c r="Q14">
-        <v>104</v>
+        <v>393</v>
       </c>
       <c r="R14" t="str">
         <v>[1,800]</v>
@@ -1897,7 +1897,7 @@
         <v>10011</v>
       </c>
       <c r="C15" t="str">
-        <v>关羽-步兵 T2</v>
+        <v>高览-步兵 T2</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="G15">
         <v>4</v>
@@ -1918,13 +1918,13 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L15">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="M15" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1936,10 +1936,10 @@
         <v>[]</v>
       </c>
       <c r="P15">
-        <v>309</v>
+        <v>514</v>
       </c>
       <c r="Q15">
-        <v>93</v>
+        <v>427</v>
       </c>
       <c r="R15" t="str">
         <v>[1,800]</v>
@@ -2016,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>183</v>
+        <v>306</v>
       </c>
       <c r="G16">
         <v>4</v>
@@ -2028,13 +2028,13 @@
         <v>1</v>
       </c>
       <c r="J16">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="K16">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L16">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="M16" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2046,10 +2046,10 @@
         <v>[]</v>
       </c>
       <c r="P16">
-        <v>322</v>
+        <v>538</v>
       </c>
       <c r="Q16">
-        <v>97</v>
+        <v>437</v>
       </c>
       <c r="R16" t="str">
         <v>[1,800]</v>
@@ -2117,7 +2117,7 @@
         <v>10013</v>
       </c>
       <c r="C17" t="str">
-        <v>孙权-步兵 T2</v>
+        <v>华雄-步兵 T2</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2126,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>197</v>
+        <v>284</v>
       </c>
       <c r="G17">
         <v>4</v>
@@ -2138,13 +2138,13 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>259</v>
+        <v>191</v>
       </c>
       <c r="K17">
         <v>14</v>
       </c>
       <c r="L17">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="M17" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2156,10 +2156,10 @@
         <v>[]</v>
       </c>
       <c r="P17">
-        <v>319</v>
+        <v>527</v>
       </c>
       <c r="Q17">
-        <v>96</v>
+        <v>412</v>
       </c>
       <c r="R17" t="str">
         <v>[1,800]</v>
@@ -2227,7 +2227,7 @@
         <v>10014</v>
       </c>
       <c r="C18" t="str">
-        <v>傅佥-步兵 T2</v>
+        <v>麴义-步兵 T2</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>149</v>
+        <v>258</v>
       </c>
       <c r="G18">
         <v>4</v>
@@ -2248,13 +2248,13 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="K18">
         <v>13</v>
       </c>
       <c r="L18">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="M18" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2266,10 +2266,10 @@
         <v>[]</v>
       </c>
       <c r="P18">
-        <v>309</v>
+        <v>523</v>
       </c>
       <c r="Q18">
-        <v>98</v>
+        <v>390</v>
       </c>
       <c r="R18" t="str">
         <v>[1,800]</v>
@@ -2337,7 +2337,7 @@
         <v>10015</v>
       </c>
       <c r="C19" t="str">
-        <v>曹真-步兵 T2</v>
+        <v>管亥-步兵 T2</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -2346,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>180</v>
+        <v>337</v>
       </c>
       <c r="G19">
         <v>4</v>
@@ -2358,13 +2358,13 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="K19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L19">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="M19" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2376,10 +2376,10 @@
         <v>[]</v>
       </c>
       <c r="P19">
-        <v>322</v>
+        <v>531</v>
       </c>
       <c r="Q19">
-        <v>101</v>
+        <v>413</v>
       </c>
       <c r="R19" t="str">
         <v>[1,800]</v>
@@ -2447,7 +2447,7 @@
         <v>10016</v>
       </c>
       <c r="C20" t="str">
-        <v>刘备-步兵 T2</v>
+        <v>颜良-步兵 T2</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2456,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>200</v>
+        <v>354</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -2468,13 +2468,13 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="K20">
         <v>15</v>
       </c>
       <c r="L20">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="M20" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2486,10 +2486,10 @@
         <v>[]</v>
       </c>
       <c r="P20">
-        <v>314</v>
+        <v>511</v>
       </c>
       <c r="Q20">
-        <v>96</v>
+        <v>438</v>
       </c>
       <c r="R20" t="str">
         <v>[1,800]</v>
@@ -2557,7 +2557,7 @@
         <v>10017</v>
       </c>
       <c r="C21" t="str">
-        <v>吕公-步兵 T2</v>
+        <v>胡车儿-步兵 T2</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>195</v>
+        <v>299</v>
       </c>
       <c r="G21">
         <v>4</v>
@@ -2578,13 +2578,13 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="K21">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L21">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="M21" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2596,10 +2596,10 @@
         <v>[]</v>
       </c>
       <c r="P21">
-        <v>322</v>
+        <v>514</v>
       </c>
       <c r="Q21">
-        <v>95</v>
+        <v>415</v>
       </c>
       <c r="R21" t="str">
         <v>[1,800]</v>
@@ -2667,7 +2667,7 @@
         <v>10018</v>
       </c>
       <c r="C22" t="str">
-        <v>田豫-步兵 T2</v>
+        <v>韩猛-步兵 T2</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>157</v>
+        <v>298</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -2688,13 +2688,13 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="K22">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L22">
-        <v>0.91</v>
+        <v>1.04</v>
       </c>
       <c r="M22" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2706,10 +2706,10 @@
         <v>[]</v>
       </c>
       <c r="P22">
-        <v>313</v>
+        <v>520</v>
       </c>
       <c r="Q22">
-        <v>98</v>
+        <v>365</v>
       </c>
       <c r="R22" t="str">
         <v>[1,800]</v>
@@ -2777,7 +2777,7 @@
         <v>10019</v>
       </c>
       <c r="C23" t="str">
-        <v>马忠-步兵 T2</v>
+        <v>徐盛-步兵 T2</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2786,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>167</v>
+        <v>262</v>
       </c>
       <c r="G23">
         <v>4</v>
@@ -2798,13 +2798,13 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K23">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="M23" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2816,10 +2816,10 @@
         <v>[]</v>
       </c>
       <c r="P23">
-        <v>322</v>
+        <v>520</v>
       </c>
       <c r="Q23">
-        <v>108</v>
+        <v>373</v>
       </c>
       <c r="R23" t="str">
         <v>[1,800]</v>
@@ -2887,7 +2887,7 @@
         <v>10020</v>
       </c>
       <c r="C24" t="str">
-        <v>李典-步兵 T2</v>
+        <v>张南-步兵 T2</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>161</v>
+        <v>258</v>
       </c>
       <c r="G24">
         <v>4</v>
@@ -2908,13 +2908,13 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="K24">
         <v>12</v>
       </c>
       <c r="L24">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="M24" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2926,10 +2926,10 @@
         <v>[]</v>
       </c>
       <c r="P24">
-        <v>312</v>
+        <v>529</v>
       </c>
       <c r="Q24">
-        <v>96</v>
+        <v>388</v>
       </c>
       <c r="R24" t="str">
         <v>[1,800]</v>
@@ -2997,7 +2997,7 @@
         <v>10021</v>
       </c>
       <c r="C25" t="str">
-        <v>华雄-步兵 T3</v>
+        <v>严白虎-步兵 T3</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>324</v>
+        <v>434</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -3018,13 +3018,13 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>330</v>
+        <v>279</v>
       </c>
       <c r="K25">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L25">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="M25" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3036,10 +3036,10 @@
         <v>[]</v>
       </c>
       <c r="P25">
-        <v>320</v>
+        <v>520</v>
       </c>
       <c r="Q25">
-        <v>90</v>
+        <v>411</v>
       </c>
       <c r="R25" t="str">
         <v>[1,800]</v>
@@ -3107,7 +3107,7 @@
         <v>10022</v>
       </c>
       <c r="C26" t="str">
-        <v>牵招-步兵 T3</v>
+        <v>张允-步兵 T3</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -3116,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>245</v>
+        <v>494</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -3128,13 +3128,13 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="K26">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L26">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="M26" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3146,10 +3146,10 @@
         <v>[]</v>
       </c>
       <c r="P26">
-        <v>323</v>
+        <v>520</v>
       </c>
       <c r="Q26">
-        <v>95</v>
+        <v>427</v>
       </c>
       <c r="R26" t="str">
         <v>[1,800]</v>
@@ -3217,7 +3217,7 @@
         <v>10023</v>
       </c>
       <c r="C27" t="str">
-        <v>苏由-步兵 T3</v>
+        <v>臧霸-步兵 T3</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>242</v>
+        <v>454</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -3238,13 +3238,13 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="K27">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L27">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="M27" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3256,10 +3256,10 @@
         <v>[]</v>
       </c>
       <c r="P27">
-        <v>312</v>
+        <v>529</v>
       </c>
       <c r="Q27">
-        <v>102</v>
+        <v>433</v>
       </c>
       <c r="R27" t="str">
         <v>[1,800]</v>
@@ -3327,7 +3327,7 @@
         <v>10024</v>
       </c>
       <c r="C28" t="str">
-        <v>典韦-步兵 T3</v>
+        <v>刘封-步兵 T3</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>246</v>
+        <v>457</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -3348,13 +3348,13 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="K28">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L28">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="M28" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3366,10 +3366,10 @@
         <v>[]</v>
       </c>
       <c r="P28">
-        <v>311</v>
+        <v>538</v>
       </c>
       <c r="Q28">
-        <v>109</v>
+        <v>409</v>
       </c>
       <c r="R28" t="str">
         <v>[1,800]</v>
@@ -3437,7 +3437,7 @@
         <v>10025</v>
       </c>
       <c r="C29" t="str">
-        <v>张苞-步兵 T3</v>
+        <v>祖茂-步兵 T3</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -3446,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>251</v>
+        <v>534</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -3458,13 +3458,13 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>251</v>
+        <v>346</v>
       </c>
       <c r="K29">
         <v>19</v>
       </c>
       <c r="L29">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="M29" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3476,10 +3476,10 @@
         <v>[]</v>
       </c>
       <c r="P29">
-        <v>320</v>
+        <v>539</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>418</v>
       </c>
       <c r="R29" t="str">
         <v>[1,800]</v>
@@ -3547,7 +3547,7 @@
         <v>10026</v>
       </c>
       <c r="C30" t="str">
-        <v>程普-步兵 T3</v>
+        <v>焦触-步兵 T3</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -3556,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>289</v>
+        <v>352</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3568,13 +3568,13 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="K30">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L30">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="M30" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3586,10 +3586,10 @@
         <v>[]</v>
       </c>
       <c r="P30">
-        <v>318</v>
+        <v>517</v>
       </c>
       <c r="Q30">
-        <v>102</v>
+        <v>382</v>
       </c>
       <c r="R30" t="str">
         <v>[1,800]</v>
@@ -3657,7 +3657,7 @@
         <v>10027</v>
       </c>
       <c r="C31" t="str">
-        <v>潘凤-步兵 T3</v>
+        <v>郭援-步兵 T3</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -3666,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>242</v>
+        <v>438</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -3678,13 +3678,13 @@
         <v>1</v>
       </c>
       <c r="J31">
-        <v>242</v>
+        <v>285</v>
       </c>
       <c r="K31">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L31">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="M31" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3696,10 +3696,10 @@
         <v>[]</v>
       </c>
       <c r="P31">
-        <v>316</v>
+        <v>520</v>
       </c>
       <c r="Q31">
-        <v>92</v>
+        <v>435</v>
       </c>
       <c r="R31" t="str">
         <v>[1,800]</v>
@@ -3767,7 +3767,7 @@
         <v>10028</v>
       </c>
       <c r="C32" t="str">
-        <v>徐盛-步兵 T3</v>
+        <v>王威-步兵 T3</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>280</v>
+        <v>431</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -3788,13 +3788,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="K32">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L32">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="M32" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3806,10 +3806,10 @@
         <v>[]</v>
       </c>
       <c r="P32">
-        <v>314</v>
+        <v>514</v>
       </c>
       <c r="Q32">
-        <v>105</v>
+        <v>387</v>
       </c>
       <c r="R32" t="str">
         <v>[1,800]</v>
@@ -3877,7 +3877,7 @@
         <v>10029</v>
       </c>
       <c r="C33" t="str">
-        <v>关兴-步兵 T3</v>
+        <v>关平-步兵 T3</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -3886,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>294</v>
+        <v>499</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -3898,13 +3898,13 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="K33">
         <v>20</v>
       </c>
       <c r="L33">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="M33" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3916,10 +3916,10 @@
         <v>[]</v>
       </c>
       <c r="P33">
-        <v>313</v>
+        <v>537</v>
       </c>
       <c r="Q33">
-        <v>108</v>
+        <v>370</v>
       </c>
       <c r="R33" t="str">
         <v>[1,800]</v>
@@ -3987,7 +3987,7 @@
         <v>10030</v>
       </c>
       <c r="C34" t="str">
-        <v>曹仁-步兵 T3</v>
+        <v>裴元绍-步兵 T3</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -3996,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>293</v>
+        <v>476</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -4008,13 +4008,13 @@
         <v>1</v>
       </c>
       <c r="J34">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="K34">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L34">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="M34" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4026,10 +4026,10 @@
         <v>[]</v>
       </c>
       <c r="P34">
-        <v>318</v>
+        <v>513</v>
       </c>
       <c r="Q34">
-        <v>104</v>
+        <v>411</v>
       </c>
       <c r="R34" t="str">
         <v>[1,800]</v>
@@ -4097,7 +4097,7 @@
         <v>10031</v>
       </c>
       <c r="C35" t="str">
-        <v>胡车儿-步兵 T4</v>
+        <v>廖化-步兵 T4</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -4106,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>396</v>
+        <v>760</v>
       </c>
       <c r="G35">
         <v>6</v>
@@ -4118,13 +4118,13 @@
         <v>1</v>
       </c>
       <c r="J35">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="K35">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L35">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="M35" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4136,10 +4136,10 @@
         <v>[]</v>
       </c>
       <c r="P35">
-        <v>306</v>
+        <v>518</v>
       </c>
       <c r="Q35">
-        <v>110</v>
+        <v>429</v>
       </c>
       <c r="R35" t="str">
         <v>[1,800]</v>
@@ -4207,7 +4207,7 @@
         <v>10032</v>
       </c>
       <c r="C36" t="str">
-        <v>蒋舒-步兵 T4</v>
+        <v>马忠-步兵 T4</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -4216,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>376</v>
+        <v>772</v>
       </c>
       <c r="G36">
         <v>6</v>
@@ -4228,13 +4228,13 @@
         <v>1</v>
       </c>
       <c r="J36">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="K36">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="M36" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4246,10 +4246,10 @@
         <v>[]</v>
       </c>
       <c r="P36">
-        <v>316</v>
+        <v>535</v>
       </c>
       <c r="Q36">
-        <v>110</v>
+        <v>403</v>
       </c>
       <c r="R36" t="str">
         <v>[1,800]</v>
@@ -4317,7 +4317,7 @@
         <v>10033</v>
       </c>
       <c r="C37" t="str">
-        <v>韩猛-步兵 T4</v>
+        <v>关樾-步兵 T4</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>366</v>
+        <v>772</v>
       </c>
       <c r="G37">
         <v>6</v>
@@ -4338,13 +4338,13 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>307</v>
+        <v>424</v>
       </c>
       <c r="K37">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L37">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="M37" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4356,10 +4356,10 @@
         <v>[]</v>
       </c>
       <c r="P37">
-        <v>312</v>
+        <v>535</v>
       </c>
       <c r="Q37">
-        <v>98</v>
+        <v>428</v>
       </c>
       <c r="R37" t="str">
         <v>[1,800]</v>
@@ -4427,7 +4427,7 @@
         <v>10034</v>
       </c>
       <c r="C38" t="str">
-        <v>麴义-步兵 T4</v>
+        <v>牵招-步兵 T4</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -4436,7 +4436,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>383</v>
+        <v>802</v>
       </c>
       <c r="G38">
         <v>6</v>
@@ -4448,13 +4448,13 @@
         <v>1</v>
       </c>
       <c r="J38">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="K38">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L38">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="M38" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4466,10 +4466,10 @@
         <v>[]</v>
       </c>
       <c r="P38">
-        <v>318</v>
+        <v>528</v>
       </c>
       <c r="Q38">
-        <v>91</v>
+        <v>412</v>
       </c>
       <c r="R38" t="str">
         <v>[1,800]</v>
@@ -4537,7 +4537,7 @@
         <v>10035</v>
       </c>
       <c r="C39" t="str">
-        <v>臧霸-步兵 T4</v>
+        <v>周仓-步兵 T4</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -4546,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>371</v>
+        <v>718</v>
       </c>
       <c r="G39">
         <v>6</v>
@@ -4558,10 +4558,10 @@
         <v>1</v>
       </c>
       <c r="J39">
-        <v>310</v>
+        <v>433</v>
       </c>
       <c r="K39">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L39">
         <v>1.05</v>
@@ -4576,10 +4576,10 @@
         <v>[]</v>
       </c>
       <c r="P39">
-        <v>321</v>
+        <v>527</v>
       </c>
       <c r="Q39">
-        <v>92</v>
+        <v>423</v>
       </c>
       <c r="R39" t="str">
         <v>[1,800]</v>
@@ -4647,7 +4647,7 @@
         <v>10036</v>
       </c>
       <c r="C40" t="str">
-        <v>颜良-步兵 T4</v>
+        <v>黄盖-步兵 T4</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -4656,7 +4656,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>329</v>
+        <v>612</v>
       </c>
       <c r="G40">
         <v>6</v>
@@ -4668,13 +4668,13 @@
         <v>1</v>
       </c>
       <c r="J40">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K40">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L40">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="M40" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4686,10 +4686,10 @@
         <v>[]</v>
       </c>
       <c r="P40">
-        <v>308</v>
+        <v>527</v>
       </c>
       <c r="Q40">
-        <v>95</v>
+        <v>407</v>
       </c>
       <c r="R40" t="str">
         <v>[1,800]</v>
@@ -4757,7 +4757,7 @@
         <v>10037</v>
       </c>
       <c r="C41" t="str">
-        <v>管亥-步兵 T4</v>
+        <v>马延-步兵 T4</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>338</v>
+        <v>660</v>
       </c>
       <c r="G41">
         <v>6</v>
@@ -4778,13 +4778,13 @@
         <v>1</v>
       </c>
       <c r="J41">
-        <v>322</v>
+        <v>357</v>
       </c>
       <c r="K41">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L41">
-        <v>1.04</v>
+        <v>0.95</v>
       </c>
       <c r="M41" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4796,10 +4796,10 @@
         <v>[]</v>
       </c>
       <c r="P41">
-        <v>307</v>
+        <v>534</v>
       </c>
       <c r="Q41">
-        <v>97</v>
+        <v>437</v>
       </c>
       <c r="R41" t="str">
         <v>[1,800]</v>
@@ -4867,7 +4867,7 @@
         <v>10038</v>
       </c>
       <c r="C42" t="str">
-        <v>徐晃-步兵 T4</v>
+        <v>吴班-步兵 T4</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>374</v>
+        <v>743</v>
       </c>
       <c r="G42">
         <v>6</v>
@@ -4888,13 +4888,13 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <v>332</v>
+        <v>417</v>
       </c>
       <c r="K42">
         <v>22</v>
       </c>
       <c r="L42">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="M42" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4906,10 +4906,10 @@
         <v>[]</v>
       </c>
       <c r="P42">
-        <v>310</v>
+        <v>527</v>
       </c>
       <c r="Q42">
-        <v>93</v>
+        <v>420</v>
       </c>
       <c r="R42" t="str">
         <v>[1,800]</v>
@@ -4977,7 +4977,7 @@
         <v>10039</v>
       </c>
       <c r="C43" t="str">
-        <v>周泰-步兵 T4</v>
+        <v>吕旷-步兵 T4</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -4986,7 +4986,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>396</v>
+        <v>666</v>
       </c>
       <c r="G43">
         <v>6</v>
@@ -4998,13 +4998,13 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="K43">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L43">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="M43" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5016,10 +5016,10 @@
         <v>[]</v>
       </c>
       <c r="P43">
-        <v>313</v>
+        <v>537</v>
       </c>
       <c r="Q43">
-        <v>100</v>
+        <v>431</v>
       </c>
       <c r="R43" t="str">
         <v>[1,800]</v>
@@ -5087,7 +5087,7 @@
         <v>10040</v>
       </c>
       <c r="C44" t="str">
-        <v>于禁-步兵 T4</v>
+        <v>韩当-步兵 T4</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>375</v>
+        <v>643</v>
       </c>
       <c r="G44">
         <v>6</v>
@@ -5108,10 +5108,10 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>309</v>
+        <v>414</v>
       </c>
       <c r="K44">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L44">
         <v>1</v>
@@ -5126,10 +5126,10 @@
         <v>[]</v>
       </c>
       <c r="P44">
-        <v>312</v>
+        <v>534</v>
       </c>
       <c r="Q44">
-        <v>105</v>
+        <v>372</v>
       </c>
       <c r="R44" t="str">
         <v>[1,800]</v>
@@ -6029,7 +6029,7 @@
         <v>20001</v>
       </c>
       <c r="C53" t="str">
-        <v>郭嘉-弓箭手 T1</v>
+        <v>黄月英-弓箭手 T1</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -6038,7 +6038,7 @@
         <v>1</v>
       </c>
       <c r="F53">
-        <v>190</v>
+        <v>247</v>
       </c>
       <c r="G53">
         <v>3</v>
@@ -6050,13 +6050,13 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K53">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L53">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="M53" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6068,10 +6068,10 @@
         <v>[]</v>
       </c>
       <c r="P53">
-        <v>255</v>
+        <v>426</v>
       </c>
       <c r="Q53">
-        <v>2197</v>
+        <v>2300</v>
       </c>
       <c r="R53" t="str">
         <v>[1,800]</v>
@@ -6125,7 +6125,7 @@
         <v>1</v>
       </c>
       <c r="AI53" t="str">
-        <v>[91003,91016]</v>
+        <v>[92002]</v>
       </c>
       <c r="AJ53" t="str">
         <v>9|8</v>
@@ -6139,7 +6139,7 @@
         <v>20002</v>
       </c>
       <c r="C54" t="str">
-        <v>秦宓-弓箭手 T1</v>
+        <v>薛综-弓箭手 T1</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -6148,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="F54">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="G54">
         <v>3</v>
@@ -6160,13 +6160,13 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K54">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L54">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="M54" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6178,10 +6178,10 @@
         <v>[]</v>
       </c>
       <c r="P54">
-        <v>262</v>
+        <v>437</v>
       </c>
       <c r="Q54">
-        <v>2157</v>
+        <v>2201</v>
       </c>
       <c r="R54" t="str">
         <v>[1,800]</v>
@@ -6249,7 +6249,7 @@
         <v>20003</v>
       </c>
       <c r="C55" t="str">
-        <v>荀彧-弓箭手 T1</v>
+        <v>田丰-弓箭手 T1</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -6258,7 +6258,7 @@
         <v>1</v>
       </c>
       <c r="F55">
-        <v>181</v>
+        <v>292</v>
       </c>
       <c r="G55">
         <v>3</v>
@@ -6270,13 +6270,13 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="K55">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L55">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="M55" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6288,10 +6288,10 @@
         <v>[]</v>
       </c>
       <c r="P55">
-        <v>257</v>
+        <v>430</v>
       </c>
       <c r="Q55">
-        <v>2104</v>
+        <v>2230</v>
       </c>
       <c r="R55" t="str">
         <v>[1,800]</v>
@@ -6359,7 +6359,7 @@
         <v>20004</v>
       </c>
       <c r="C56" t="str">
-        <v>孙乾-弓箭手 T1</v>
+        <v>王异-弓箭手 T1</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -6368,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="F56">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="G56">
         <v>3</v>
@@ -6380,13 +6380,13 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K56">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L56">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="M56" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6398,10 +6398,10 @@
         <v>[]</v>
       </c>
       <c r="P56">
-        <v>255</v>
+        <v>439</v>
       </c>
       <c r="Q56">
-        <v>2028</v>
+        <v>2398</v>
       </c>
       <c r="R56" t="str">
         <v>[1,800]</v>
@@ -6469,7 +6469,7 @@
         <v>20005</v>
       </c>
       <c r="C57" t="str">
-        <v>钟繇-弓箭手 T1</v>
+        <v>陈群-弓箭手 T1</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -6478,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="F57">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G57">
         <v>3</v>
@@ -6490,13 +6490,13 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="K57">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L57">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="M57" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6508,10 +6508,10 @@
         <v>[]</v>
       </c>
       <c r="P57">
-        <v>261</v>
+        <v>435</v>
       </c>
       <c r="Q57">
-        <v>2035</v>
+        <v>2094</v>
       </c>
       <c r="R57" t="str">
         <v>[1,800]</v>
@@ -6579,7 +6579,7 @@
         <v>20006</v>
       </c>
       <c r="C58" t="str">
-        <v>田丰-弓箭手 T1</v>
+        <v>大乔-弓箭手 T1</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -6588,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="F58">
-        <v>182</v>
+        <v>331</v>
       </c>
       <c r="G58">
         <v>3</v>
@@ -6600,13 +6600,13 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K58">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L58">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="M58" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6618,10 +6618,10 @@
         <v>[]</v>
       </c>
       <c r="P58">
-        <v>262</v>
+        <v>430</v>
       </c>
       <c r="Q58">
-        <v>2251</v>
+        <v>2164</v>
       </c>
       <c r="R58" t="str">
         <v>[1,800]</v>
@@ -6689,7 +6689,7 @@
         <v>20007</v>
       </c>
       <c r="C59" t="str">
-        <v>郑玄-弓箭手 T1</v>
+        <v>沮授-弓箭手 T1</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -6698,7 +6698,7 @@
         <v>1</v>
       </c>
       <c r="F59">
-        <v>222</v>
+        <v>314</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -6716,7 +6716,7 @@
         <v>25</v>
       </c>
       <c r="L59">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="M59" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6728,10 +6728,10 @@
         <v>[]</v>
       </c>
       <c r="P59">
-        <v>264</v>
+        <v>410</v>
       </c>
       <c r="Q59">
-        <v>2173</v>
+        <v>2291</v>
       </c>
       <c r="R59" t="str">
         <v>[1,800]</v>
@@ -6799,7 +6799,7 @@
         <v>20008</v>
       </c>
       <c r="C60" t="str">
-        <v>刘晔-弓箭手 T1</v>
+        <v>张昭-弓箭手 T1</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -6808,7 +6808,7 @@
         <v>1</v>
       </c>
       <c r="F60">
-        <v>173</v>
+        <v>329</v>
       </c>
       <c r="G60">
         <v>3</v>
@@ -6820,13 +6820,13 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K60">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L60">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6838,10 +6838,10 @@
         <v>[]</v>
       </c>
       <c r="P60">
-        <v>256</v>
+        <v>427</v>
       </c>
       <c r="Q60">
-        <v>2160</v>
+        <v>2354</v>
       </c>
       <c r="R60" t="str">
         <v>[1,800]</v>
@@ -6909,7 +6909,7 @@
         <v>20009</v>
       </c>
       <c r="C61" t="str">
-        <v>蒋琬-弓箭手 T1</v>
+        <v>王朗-弓箭手 T1</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -6918,7 +6918,7 @@
         <v>1</v>
       </c>
       <c r="F61">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="G61">
         <v>3</v>
@@ -6930,13 +6930,13 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K61">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L61">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="M61" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6948,10 +6948,10 @@
         <v>[]</v>
       </c>
       <c r="P61">
-        <v>257</v>
+        <v>420</v>
       </c>
       <c r="Q61">
-        <v>2226</v>
+        <v>2271</v>
       </c>
       <c r="R61" t="str">
         <v>[1,800]</v>
@@ -7019,7 +7019,7 @@
         <v>20010</v>
       </c>
       <c r="C62" t="str">
-        <v>糜芳-弓箭手 T1</v>
+        <v>水镜先生-弓箭手 T1</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -7028,7 +7028,7 @@
         <v>1</v>
       </c>
       <c r="F62">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="G62">
         <v>3</v>
@@ -7040,13 +7040,13 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="K62">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L62">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="M62" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7058,10 +7058,10 @@
         <v>[]</v>
       </c>
       <c r="P62">
-        <v>262</v>
+        <v>439</v>
       </c>
       <c r="Q62">
-        <v>2074</v>
+        <v>2301</v>
       </c>
       <c r="R62" t="str">
         <v>[1,800]</v>
@@ -7129,7 +7129,7 @@
         <v>20011</v>
       </c>
       <c r="C63" t="str">
-        <v>简雍-弓箭手 T2</v>
+        <v>姜维-弓箭手 T2</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -7138,7 +7138,7 @@
         <v>1</v>
       </c>
       <c r="F63">
-        <v>288</v>
+        <v>442</v>
       </c>
       <c r="G63">
         <v>4</v>
@@ -7150,13 +7150,13 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="K63">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L63">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="M63" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7168,10 +7168,10 @@
         <v>[]</v>
       </c>
       <c r="P63">
-        <v>259</v>
+        <v>411</v>
       </c>
       <c r="Q63">
-        <v>2105</v>
+        <v>2172</v>
       </c>
       <c r="R63" t="str">
         <v>[1,800]</v>
@@ -7239,7 +7239,7 @@
         <v>20012</v>
       </c>
       <c r="C64" t="str">
-        <v>小乔-弓箭手 T2</v>
+        <v>步练师-弓箭手 T2</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -7248,7 +7248,7 @@
         <v>1</v>
       </c>
       <c r="F64">
-        <v>268</v>
+        <v>590</v>
       </c>
       <c r="G64">
         <v>4</v>
@@ -7260,13 +7260,13 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="K64">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L64">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="M64" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7278,10 +7278,10 @@
         <v>[]</v>
       </c>
       <c r="P64">
-        <v>255</v>
+        <v>439</v>
       </c>
       <c r="Q64">
-        <v>2043</v>
+        <v>2186</v>
       </c>
       <c r="R64" t="str">
         <v>[1,800]</v>
@@ -7349,7 +7349,7 @@
         <v>20013</v>
       </c>
       <c r="C65" t="str">
-        <v>左慈-弓箭手 T2</v>
+        <v>顾雍-弓箭手 T2</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -7358,7 +7358,7 @@
         <v>1</v>
       </c>
       <c r="F65">
-        <v>312</v>
+        <v>524</v>
       </c>
       <c r="G65">
         <v>4</v>
@@ -7370,13 +7370,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K65">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L65">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="M65" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7388,10 +7388,10 @@
         <v>[]</v>
       </c>
       <c r="P65">
-        <v>252</v>
+        <v>414</v>
       </c>
       <c r="Q65">
-        <v>2377</v>
+        <v>2162</v>
       </c>
       <c r="R65" t="str">
         <v>[1,800]</v>
@@ -7459,7 +7459,7 @@
         <v>20014</v>
       </c>
       <c r="C66" t="str">
-        <v>华佗-弓箭手 T2</v>
+        <v>刘晔-弓箭手 T2</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -7468,7 +7468,7 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>314</v>
+        <v>566</v>
       </c>
       <c r="G66">
         <v>4</v>
@@ -7483,10 +7483,10 @@
         <v>98</v>
       </c>
       <c r="K66">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L66">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="M66" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7498,10 +7498,10 @@
         <v>[]</v>
       </c>
       <c r="P66">
-        <v>257</v>
+        <v>430</v>
       </c>
       <c r="Q66">
-        <v>2147</v>
+        <v>2071</v>
       </c>
       <c r="R66" t="str">
         <v>[1,800]</v>
@@ -7569,7 +7569,7 @@
         <v>20015</v>
       </c>
       <c r="C67" t="str">
-        <v>程昱-弓箭手 T2</v>
+        <v>逢纪-弓箭手 T2</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -7578,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="F67">
-        <v>294</v>
+        <v>494</v>
       </c>
       <c r="G67">
         <v>4</v>
@@ -7590,13 +7590,13 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K67">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L67">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="M67" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7608,10 +7608,10 @@
         <v>[]</v>
       </c>
       <c r="P67">
-        <v>250</v>
+        <v>426</v>
       </c>
       <c r="Q67">
-        <v>2216</v>
+        <v>2065</v>
       </c>
       <c r="R67" t="str">
         <v>[1,800]</v>
@@ -7679,7 +7679,7 @@
         <v>20016</v>
       </c>
       <c r="C68" t="str">
-        <v>张温-弓箭手 T2</v>
+        <v>庞统-弓箭手 T2</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -7688,7 +7688,7 @@
         <v>1</v>
       </c>
       <c r="F68">
-        <v>388</v>
+        <v>344</v>
       </c>
       <c r="G68">
         <v>4</v>
@@ -7700,13 +7700,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="K68">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="L68">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="M68" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7718,10 +7718,10 @@
         <v>[]</v>
       </c>
       <c r="P68">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="Q68">
-        <v>2134</v>
+        <v>2156</v>
       </c>
       <c r="R68" t="str">
         <v>[1,800]</v>
@@ -7789,7 +7789,7 @@
         <v>20017</v>
       </c>
       <c r="C69" t="str">
-        <v>鲁肃-弓箭手 T2</v>
+        <v>宗预-弓箭手 T2</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -7798,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="F69">
-        <v>308</v>
+        <v>522</v>
       </c>
       <c r="G69">
         <v>4</v>
@@ -7810,13 +7810,13 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K69">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L69">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="M69" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7828,10 +7828,10 @@
         <v>[]</v>
       </c>
       <c r="P69">
-        <v>261</v>
+        <v>433</v>
       </c>
       <c r="Q69">
-        <v>2144</v>
+        <v>2021</v>
       </c>
       <c r="R69" t="str">
         <v>[1,800]</v>
@@ -7899,7 +7899,7 @@
         <v>20018</v>
       </c>
       <c r="C70" t="str">
-        <v>阚泽-弓箭手 T2</v>
+        <v>司马懿-弓箭手 T2</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -7908,7 +7908,7 @@
         <v>1</v>
       </c>
       <c r="F70">
-        <v>348</v>
+        <v>463</v>
       </c>
       <c r="G70">
         <v>4</v>
@@ -7920,13 +7920,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K70">
         <v>34</v>
       </c>
       <c r="L70">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="M70" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7938,10 +7938,10 @@
         <v>[]</v>
       </c>
       <c r="P70">
-        <v>253</v>
+        <v>418</v>
       </c>
       <c r="Q70">
-        <v>2326</v>
+        <v>2332</v>
       </c>
       <c r="R70" t="str">
         <v>[1,800]</v>
@@ -8009,7 +8009,7 @@
         <v>20019</v>
       </c>
       <c r="C71" t="str">
-        <v>貂蝉-弓箭手 T2</v>
+        <v>蒯越-弓箭手 T2</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -8018,7 +8018,7 @@
         <v>1</v>
       </c>
       <c r="F71">
-        <v>368</v>
+        <v>440</v>
       </c>
       <c r="G71">
         <v>4</v>
@@ -8030,13 +8030,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K71">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L71">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="M71" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8048,10 +8048,10 @@
         <v>[]</v>
       </c>
       <c r="P71">
-        <v>248</v>
+        <v>439</v>
       </c>
       <c r="Q71">
-        <v>2344</v>
+        <v>2273</v>
       </c>
       <c r="R71" t="str">
         <v>[1,800]</v>
@@ -8119,7 +8119,7 @@
         <v>20020</v>
       </c>
       <c r="C72" t="str">
-        <v>黄月英-弓箭手 T2</v>
+        <v>孙乾-弓箭手 T2</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -8128,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="F72">
-        <v>312</v>
+        <v>388</v>
       </c>
       <c r="G72">
         <v>4</v>
@@ -8140,13 +8140,13 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K72">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L72">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="M72" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8158,10 +8158,10 @@
         <v>[]</v>
       </c>
       <c r="P72">
-        <v>260</v>
+        <v>420</v>
       </c>
       <c r="Q72">
-        <v>2257</v>
+        <v>2275</v>
       </c>
       <c r="R72" t="str">
         <v>[1,800]</v>
@@ -8229,7 +8229,7 @@
         <v>20021</v>
       </c>
       <c r="C73" t="str">
-        <v>诸葛亮-弓箭手 T3</v>
+        <v>钟繇-弓箭手 T3</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -8238,7 +8238,7 @@
         <v>1</v>
       </c>
       <c r="F73">
-        <v>436</v>
+        <v>764</v>
       </c>
       <c r="G73">
         <v>5</v>
@@ -8250,13 +8250,13 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="K73">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="L73">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="M73" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8268,10 +8268,10 @@
         <v>[]</v>
       </c>
       <c r="P73">
-        <v>258</v>
+        <v>412</v>
       </c>
       <c r="Q73">
-        <v>2103</v>
+        <v>2222</v>
       </c>
       <c r="R73" t="str">
         <v>[1,800]</v>
@@ -8339,7 +8339,7 @@
         <v>20022</v>
       </c>
       <c r="C74" t="str">
-        <v>步骘-弓箭手 T3</v>
+        <v>左慈-弓箭手 T3</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -8348,7 +8348,7 @@
         <v>1</v>
       </c>
       <c r="F74">
-        <v>518</v>
+        <v>672</v>
       </c>
       <c r="G74">
         <v>5</v>
@@ -8360,13 +8360,13 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="K74">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L74">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M74" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8378,10 +8378,10 @@
         <v>[]</v>
       </c>
       <c r="P74">
-        <v>263</v>
+        <v>418</v>
       </c>
       <c r="Q74">
-        <v>2401</v>
+        <v>1998</v>
       </c>
       <c r="R74" t="str">
         <v>[1,800]</v>
@@ -8449,7 +8449,7 @@
         <v>20023</v>
       </c>
       <c r="C75" t="str">
-        <v>王异-弓箭手 T3</v>
+        <v>蒋琬-弓箭手 T3</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -8458,7 +8458,7 @@
         <v>1</v>
       </c>
       <c r="F75">
-        <v>379</v>
+        <v>673</v>
       </c>
       <c r="G75">
         <v>5</v>
@@ -8470,13 +8470,13 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="K75">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L75">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="M75" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8488,10 +8488,10 @@
         <v>[]</v>
       </c>
       <c r="P75">
-        <v>256</v>
+        <v>434</v>
       </c>
       <c r="Q75">
-        <v>2390</v>
+        <v>2381</v>
       </c>
       <c r="R75" t="str">
         <v>[1,800]</v>
@@ -8559,7 +8559,7 @@
         <v>20024</v>
       </c>
       <c r="C76" t="str">
-        <v>张春华-弓箭手 T3</v>
+        <v>简雍-弓箭手 T3</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -8568,7 +8568,7 @@
         <v>1</v>
       </c>
       <c r="F76">
-        <v>459</v>
+        <v>647</v>
       </c>
       <c r="G76">
         <v>5</v>
@@ -8580,13 +8580,13 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="K76">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L76">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="M76" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8598,10 +8598,10 @@
         <v>[]</v>
       </c>
       <c r="P76">
-        <v>256</v>
+        <v>439</v>
       </c>
       <c r="Q76">
-        <v>2087</v>
+        <v>2165</v>
       </c>
       <c r="R76" t="str">
         <v>[1,800]</v>
@@ -8669,7 +8669,7 @@
         <v>20025</v>
       </c>
       <c r="C77" t="str">
-        <v>辛宪英-弓箭手 T3</v>
+        <v>费祎-弓箭手 T3</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -8678,7 +8678,7 @@
         <v>1</v>
       </c>
       <c r="F77">
-        <v>448</v>
+        <v>849</v>
       </c>
       <c r="G77">
         <v>5</v>
@@ -8690,13 +8690,13 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="K77">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L77">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="M77" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8708,10 +8708,10 @@
         <v>[]</v>
       </c>
       <c r="P77">
-        <v>247</v>
+        <v>412</v>
       </c>
       <c r="Q77">
-        <v>2103</v>
+        <v>2184</v>
       </c>
       <c r="R77" t="str">
         <v>[1,800]</v>
@@ -8779,7 +8779,7 @@
         <v>20026</v>
       </c>
       <c r="C78" t="str">
-        <v>糜竺-弓箭手 T3</v>
+        <v>黄忠-弓箭手 T3</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -8788,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>436</v>
+        <v>827</v>
       </c>
       <c r="G78">
         <v>5</v>
@@ -8800,13 +8800,13 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K78">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L78">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="M78" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8818,10 +8818,10 @@
         <v>[]</v>
       </c>
       <c r="P78">
-        <v>250</v>
+        <v>413</v>
       </c>
       <c r="Q78">
-        <v>2415</v>
+        <v>2068</v>
       </c>
       <c r="R78" t="str">
         <v>[1,800]</v>
@@ -8889,7 +8889,7 @@
         <v>20027</v>
       </c>
       <c r="C79" t="str">
-        <v>费祎-弓箭手 T3</v>
+        <v>郭嘉-弓箭手 T3</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -8898,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>520</v>
+        <v>728</v>
       </c>
       <c r="G79">
         <v>5</v>
@@ -8910,13 +8910,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="K79">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L79">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="M79" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8928,10 +8928,10 @@
         <v>[]</v>
       </c>
       <c r="P79">
-        <v>255</v>
+        <v>438</v>
       </c>
       <c r="Q79">
-        <v>2045</v>
+        <v>2207</v>
       </c>
       <c r="R79" t="str">
         <v>[1,800]</v>
@@ -8999,7 +8999,7 @@
         <v>20028</v>
       </c>
       <c r="C80" t="str">
-        <v>司马懿-弓箭手 T3</v>
+        <v>郑玄-弓箭手 T3</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -9008,7 +9008,7 @@
         <v>1</v>
       </c>
       <c r="F80">
-        <v>559</v>
+        <v>713</v>
       </c>
       <c r="G80">
         <v>5</v>
@@ -9020,13 +9020,13 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K80">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L80">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="M80" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9038,10 +9038,10 @@
         <v>[]</v>
       </c>
       <c r="P80">
-        <v>257</v>
+        <v>429</v>
       </c>
       <c r="Q80">
-        <v>2272</v>
+        <v>2237</v>
       </c>
       <c r="R80" t="str">
         <v>[1,800]</v>
@@ -9109,7 +9109,7 @@
         <v>20029</v>
       </c>
       <c r="C81" t="str">
-        <v>陈宫-弓箭手 T3</v>
+        <v>小乔-弓箭手 T3</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -9118,7 +9118,7 @@
         <v>1</v>
       </c>
       <c r="F81">
-        <v>509</v>
+        <v>845</v>
       </c>
       <c r="G81">
         <v>5</v>
@@ -9130,13 +9130,13 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="K81">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L81">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="M81" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9148,10 +9148,10 @@
         <v>[]</v>
       </c>
       <c r="P81">
-        <v>254</v>
+        <v>411</v>
       </c>
       <c r="Q81">
-        <v>2358</v>
+        <v>2201</v>
       </c>
       <c r="R81" t="str">
         <v>[1,800]</v>
@@ -9219,7 +9219,7 @@
         <v>20030</v>
       </c>
       <c r="C82" t="str">
-        <v>伊籍-弓箭手 T3</v>
+        <v>阚泽-弓箭手 T3</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -9228,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="F82">
-        <v>452</v>
+        <v>660</v>
       </c>
       <c r="G82">
         <v>5</v>
@@ -9240,13 +9240,13 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K82">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L82">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="M82" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9258,10 +9258,10 @@
         <v>[]</v>
       </c>
       <c r="P82">
-        <v>246</v>
+        <v>414</v>
       </c>
       <c r="Q82">
-        <v>2163</v>
+        <v>2375</v>
       </c>
       <c r="R82" t="str">
         <v>[1,800]</v>
@@ -9329,7 +9329,7 @@
         <v>20031</v>
       </c>
       <c r="C83" t="str">
-        <v>廖立-弓箭手 T4</v>
+        <v>华佗-弓箭手 T4</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -9338,7 +9338,7 @@
         <v>1</v>
       </c>
       <c r="F83">
-        <v>606</v>
+        <v>887</v>
       </c>
       <c r="G83">
         <v>6</v>
@@ -9350,13 +9350,13 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="K83">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L83">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="M83" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9368,10 +9368,10 @@
         <v>[]</v>
       </c>
       <c r="P83">
-        <v>259</v>
+        <v>419</v>
       </c>
       <c r="Q83">
-        <v>2063</v>
+        <v>2057</v>
       </c>
       <c r="R83" t="str">
         <v>[1,800]</v>
@@ -9439,7 +9439,7 @@
         <v>20032</v>
       </c>
       <c r="C84" t="str">
-        <v>庞统-弓箭手 T4</v>
+        <v>虞翻-弓箭手 T4</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -9448,7 +9448,7 @@
         <v>1</v>
       </c>
       <c r="F84">
-        <v>662</v>
+        <v>854</v>
       </c>
       <c r="G84">
         <v>6</v>
@@ -9460,13 +9460,13 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="K84">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L84">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="M84" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9478,10 +9478,10 @@
         <v>[]</v>
       </c>
       <c r="P84">
-        <v>256</v>
+        <v>432</v>
       </c>
       <c r="Q84">
-        <v>2299</v>
+        <v>2323</v>
       </c>
       <c r="R84" t="str">
         <v>[1,800]</v>
@@ -9549,7 +9549,7 @@
         <v>20033</v>
       </c>
       <c r="C85" t="str">
-        <v>陈震-弓箭手 T4</v>
+        <v>蔡文姬-弓箭手 T4</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -9558,7 +9558,7 @@
         <v>1</v>
       </c>
       <c r="F85">
-        <v>610</v>
+        <v>1268</v>
       </c>
       <c r="G85">
         <v>6</v>
@@ -9570,13 +9570,13 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="K85">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="L85">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="M85" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9588,10 +9588,10 @@
         <v>[]</v>
       </c>
       <c r="P85">
-        <v>253</v>
+        <v>425</v>
       </c>
       <c r="Q85">
-        <v>2216</v>
+        <v>2116</v>
       </c>
       <c r="R85" t="str">
         <v>[1,800]</v>
@@ -9659,7 +9659,7 @@
         <v>20034</v>
       </c>
       <c r="C86" t="str">
-        <v>逢纪-弓箭手 T4</v>
+        <v>管辂-弓箭手 T4</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -9668,7 +9668,7 @@
         <v>1</v>
       </c>
       <c r="F86">
-        <v>661</v>
+        <v>1048</v>
       </c>
       <c r="G86">
         <v>6</v>
@@ -9680,13 +9680,13 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="K86">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="L86">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="M86" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9698,10 +9698,10 @@
         <v>[]</v>
       </c>
       <c r="P86">
-        <v>262</v>
+        <v>433</v>
       </c>
       <c r="Q86">
-        <v>2357</v>
+        <v>2081</v>
       </c>
       <c r="R86" t="str">
         <v>[1,800]</v>
@@ -9769,7 +9769,7 @@
         <v>20035</v>
       </c>
       <c r="C87" t="str">
-        <v>戏志才-弓箭手 T4</v>
+        <v>貂蝉-弓箭手 T4</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -9778,7 +9778,7 @@
         <v>1</v>
       </c>
       <c r="F87">
-        <v>729</v>
+        <v>942</v>
       </c>
       <c r="G87">
         <v>6</v>
@@ -9790,13 +9790,13 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="K87">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L87">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="M87" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9808,10 +9808,10 @@
         <v>[]</v>
       </c>
       <c r="P87">
-        <v>263</v>
+        <v>435</v>
       </c>
       <c r="Q87">
-        <v>2230</v>
+        <v>2006</v>
       </c>
       <c r="R87" t="str">
         <v>[1,800]</v>
@@ -9879,7 +9879,7 @@
         <v>20036</v>
       </c>
       <c r="C88" t="str">
-        <v>陆逊-弓箭手 T4</v>
+        <v>廖立-弓箭手 T4</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -9888,7 +9888,7 @@
         <v>1</v>
       </c>
       <c r="F88">
-        <v>704</v>
+        <v>1167</v>
       </c>
       <c r="G88">
         <v>6</v>
@@ -9900,13 +9900,13 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="K88">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L88">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="M88" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9918,10 +9918,10 @@
         <v>[]</v>
       </c>
       <c r="P88">
-        <v>258</v>
+        <v>426</v>
       </c>
       <c r="Q88">
-        <v>2283</v>
+        <v>2153</v>
       </c>
       <c r="R88" t="str">
         <v>[1,800]</v>
@@ -9989,7 +9989,7 @@
         <v>20037</v>
       </c>
       <c r="C89" t="str">
-        <v>张昭-弓箭手 T4</v>
+        <v>荀彧-弓箭手 T4</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -9998,7 +9998,7 @@
         <v>1</v>
       </c>
       <c r="F89">
-        <v>803</v>
+        <v>1021</v>
       </c>
       <c r="G89">
         <v>6</v>
@@ -10010,13 +10010,13 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="K89">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L89">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="M89" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10028,10 +10028,10 @@
         <v>[]</v>
       </c>
       <c r="P89">
-        <v>250</v>
+        <v>415</v>
       </c>
       <c r="Q89">
-        <v>2186</v>
+        <v>2017</v>
       </c>
       <c r="R89" t="str">
         <v>[1,800]</v>
@@ -10099,7 +10099,7 @@
         <v>20038</v>
       </c>
       <c r="C90" t="str">
-        <v>杨修-弓箭手 T4</v>
+        <v>程昱-弓箭手 T4</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -10108,7 +10108,7 @@
         <v>1</v>
       </c>
       <c r="F90">
-        <v>601</v>
+        <v>1099</v>
       </c>
       <c r="G90">
         <v>6</v>
@@ -10120,13 +10120,13 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="K90">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="L90">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="M90" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10138,10 +10138,10 @@
         <v>[]</v>
       </c>
       <c r="P90">
-        <v>253</v>
+        <v>428</v>
       </c>
       <c r="Q90">
-        <v>2264</v>
+        <v>2327</v>
       </c>
       <c r="R90" t="str">
         <v>[1,800]</v>
@@ -10209,7 +10209,7 @@
         <v>20039</v>
       </c>
       <c r="C91" t="str">
-        <v>薛综-弓箭手 T4</v>
+        <v>张春华-弓箭手 T4</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -10218,7 +10218,7 @@
         <v>1</v>
       </c>
       <c r="F91">
-        <v>813</v>
+        <v>914</v>
       </c>
       <c r="G91">
         <v>6</v>
@@ -10230,13 +10230,13 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <v>175</v>
+        <v>128</v>
       </c>
       <c r="K91">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L91">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M91" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10248,10 +10248,10 @@
         <v>[]</v>
       </c>
       <c r="P91">
-        <v>254</v>
+        <v>436</v>
       </c>
       <c r="Q91">
-        <v>2356</v>
+        <v>2157</v>
       </c>
       <c r="R91" t="str">
         <v>[1,800]</v>
@@ -10319,7 +10319,7 @@
         <v>20040</v>
       </c>
       <c r="C92" t="str">
-        <v>庞德公-弓箭手 T4</v>
+        <v>陆逊-弓箭手 T4</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -10328,7 +10328,7 @@
         <v>1</v>
       </c>
       <c r="F92">
-        <v>725</v>
+        <v>907</v>
       </c>
       <c r="G92">
         <v>6</v>
@@ -10340,13 +10340,13 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="K92">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L92">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="M92" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10358,10 +10358,10 @@
         <v>[]</v>
       </c>
       <c r="P92">
-        <v>250</v>
+        <v>412</v>
       </c>
       <c r="Q92">
-        <v>2221</v>
+        <v>2328</v>
       </c>
       <c r="R92" t="str">
         <v>[1,800]</v>
@@ -10521,6 +10521,12 @@
       <c r="AI93" t="str">
         <v>[91003,91004]</v>
       </c>
+      <c r="AJ93" t="str">
+        <v>9|8</v>
+      </c>
+      <c r="AK93" t="str">
+        <v>8</v>
+      </c>
     </row>
     <row r="94">
       <c r="B94" t="str">
@@ -10619,6 +10625,12 @@
       <c r="AI94" t="str">
         <v>[91003,91004]</v>
       </c>
+      <c r="AJ94" t="str">
+        <v>9|8</v>
+      </c>
+      <c r="AK94" t="str">
+        <v>8</v>
+      </c>
     </row>
     <row r="95">
       <c r="B95" t="str">
@@ -10717,6 +10729,12 @@
       <c r="AI95" t="str">
         <v>[91003,91016]</v>
       </c>
+      <c r="AJ95" t="str">
+        <v>9|8</v>
+      </c>
+      <c r="AK95" t="str">
+        <v>8</v>
+      </c>
     </row>
     <row r="96">
       <c r="B96" t="str">
@@ -10815,6 +10833,12 @@
       <c r="AI96" t="str">
         <v>[91003,91017]</v>
       </c>
+      <c r="AJ96" t="str">
+        <v>9|8</v>
+      </c>
+      <c r="AK96" t="str">
+        <v>8</v>
+      </c>
     </row>
     <row r="97">
       <c r="B97" t="str">
@@ -10913,6 +10937,12 @@
       <c r="AI97" t="str">
         <v>[91003,91015]</v>
       </c>
+      <c r="AJ97" t="str">
+        <v>9|8</v>
+      </c>
+      <c r="AK97" t="str">
+        <v>8</v>
+      </c>
     </row>
     <row r="98">
       <c r="B98" t="str">
@@ -11011,6 +11041,12 @@
       <c r="AI98" t="str">
         <v>[91003,91004]</v>
       </c>
+      <c r="AJ98" t="str">
+        <v>9|8</v>
+      </c>
+      <c r="AK98" t="str">
+        <v>8</v>
+      </c>
     </row>
     <row r="99">
       <c r="B99" t="str">
@@ -11109,6 +11145,12 @@
       <c r="AI99" t="str">
         <v>[91003,91017]</v>
       </c>
+      <c r="AJ99" t="str">
+        <v>9|8</v>
+      </c>
+      <c r="AK99" t="str">
+        <v>8</v>
+      </c>
     </row>
     <row r="100">
       <c r="B100" t="str">
@@ -11207,13 +11249,19 @@
       <c r="AI100" t="str">
         <v>[91003,91015]</v>
       </c>
+      <c r="AJ100" t="str">
+        <v>9|8</v>
+      </c>
+      <c r="AK100" t="str">
+        <v>8</v>
+      </c>
     </row>
     <row r="101">
       <c r="B101" t="str">
         <v>30001</v>
       </c>
       <c r="C101" t="str">
-        <v>马玩-骑兵 T1</v>
+        <v>张绣-骑兵 T1</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -11222,7 +11270,7 @@
         <v>1</v>
       </c>
       <c r="F101">
-        <v>159</v>
+        <v>282</v>
       </c>
       <c r="G101">
         <v>3</v>
@@ -11234,13 +11282,13 @@
         <v>1</v>
       </c>
       <c r="J101">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K101">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L101">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="M101" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11252,10 +11300,10 @@
         <v>[]</v>
       </c>
       <c r="P101">
-        <v>373</v>
+        <v>627</v>
       </c>
       <c r="Q101">
-        <v>124</v>
+        <v>460</v>
       </c>
       <c r="R101" t="str">
         <v>[1,800]</v>
@@ -11323,7 +11371,7 @@
         <v>30002</v>
       </c>
       <c r="C102" t="str">
-        <v>波才-骑兵 T1</v>
+        <v>徐荣-骑兵 T1</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -11332,7 +11380,7 @@
         <v>1</v>
       </c>
       <c r="F102">
-        <v>119</v>
+        <v>231</v>
       </c>
       <c r="G102">
         <v>3</v>
@@ -11344,13 +11392,13 @@
         <v>1</v>
       </c>
       <c r="J102">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K102">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L102">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="M102" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11362,10 +11410,10 @@
         <v>[]</v>
       </c>
       <c r="P102">
-        <v>360</v>
+        <v>618</v>
       </c>
       <c r="Q102">
-        <v>115</v>
+        <v>437</v>
       </c>
       <c r="R102" t="str">
         <v>[1,800]</v>
@@ -11433,7 +11481,7 @@
         <v>30003</v>
       </c>
       <c r="C103" t="str">
-        <v>马休-骑兵 T1</v>
+        <v>胡轸-骑兵 T1</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -11442,7 +11490,7 @@
         <v>1</v>
       </c>
       <c r="F103">
-        <v>153</v>
+        <v>290</v>
       </c>
       <c r="G103">
         <v>3</v>
@@ -11454,13 +11502,13 @@
         <v>1</v>
       </c>
       <c r="J103">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="K103">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L103">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="M103" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11472,10 +11520,10 @@
         <v>[]</v>
       </c>
       <c r="P103">
-        <v>362</v>
+        <v>613</v>
       </c>
       <c r="Q103">
-        <v>132</v>
+        <v>401</v>
       </c>
       <c r="R103" t="str">
         <v>[1,800]</v>
@@ -11543,7 +11591,7 @@
         <v>30004</v>
       </c>
       <c r="C104" t="str">
-        <v>韩遂-骑兵 T1</v>
+        <v>韩忠-骑兵 T1</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -11552,7 +11600,7 @@
         <v>1</v>
       </c>
       <c r="F104">
-        <v>147</v>
+        <v>257</v>
       </c>
       <c r="G104">
         <v>3</v>
@@ -11564,13 +11612,13 @@
         <v>1</v>
       </c>
       <c r="J104">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K104">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L104">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="M104" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11582,10 +11630,10 @@
         <v>[]</v>
       </c>
       <c r="P104">
-        <v>374</v>
+        <v>630</v>
       </c>
       <c r="Q104">
-        <v>109</v>
+        <v>388</v>
       </c>
       <c r="R104" t="str">
         <v>[1,800]</v>
@@ -11653,7 +11701,7 @@
         <v>30005</v>
       </c>
       <c r="C105" t="str">
-        <v>韩暹-骑兵 T1</v>
+        <v>董卓-骑兵 T1</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -11662,7 +11710,7 @@
         <v>1</v>
       </c>
       <c r="F105">
-        <v>136</v>
+        <v>288</v>
       </c>
       <c r="G105">
         <v>3</v>
@@ -11674,13 +11722,13 @@
         <v>1</v>
       </c>
       <c r="J105">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="K105">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L105">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="M105" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11692,10 +11740,10 @@
         <v>[]</v>
       </c>
       <c r="P105">
-        <v>374</v>
+        <v>633</v>
       </c>
       <c r="Q105">
-        <v>128</v>
+        <v>447</v>
       </c>
       <c r="R105" t="str">
         <v>[1,800]</v>
@@ -11763,7 +11811,7 @@
         <v>30006</v>
       </c>
       <c r="C106" t="str">
-        <v>丘力居-骑兵 T1</v>
+        <v>邓茂-骑兵 T1</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -11772,7 +11820,7 @@
         <v>1</v>
       </c>
       <c r="F106">
-        <v>143</v>
+        <v>246</v>
       </c>
       <c r="G106">
         <v>3</v>
@@ -11784,13 +11832,13 @@
         <v>1</v>
       </c>
       <c r="J106">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K106">
         <v>16</v>
       </c>
       <c r="L106">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="M106" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11802,10 +11850,10 @@
         <v>[]</v>
       </c>
       <c r="P106">
-        <v>376</v>
+        <v>636</v>
       </c>
       <c r="Q106">
-        <v>119</v>
+        <v>446</v>
       </c>
       <c r="R106" t="str">
         <v>[1,800]</v>
@@ -11873,7 +11921,7 @@
         <v>30007</v>
       </c>
       <c r="C107" t="str">
-        <v>张梁-骑兵 T1</v>
+        <v>楼班-骑兵 T1</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -11882,7 +11930,7 @@
         <v>1</v>
       </c>
       <c r="F107">
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="G107">
         <v>3</v>
@@ -11894,13 +11942,13 @@
         <v>1</v>
       </c>
       <c r="J107">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="K107">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L107">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="M107" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11912,10 +11960,10 @@
         <v>[]</v>
       </c>
       <c r="P107">
-        <v>374</v>
+        <v>626</v>
       </c>
       <c r="Q107">
-        <v>113</v>
+        <v>390</v>
       </c>
       <c r="R107" t="str">
         <v>[1,800]</v>
@@ -11983,7 +12031,7 @@
         <v>30008</v>
       </c>
       <c r="C108" t="str">
-        <v>张宝-骑兵 T1</v>
+        <v>马玩-骑兵 T1</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -11992,7 +12040,7 @@
         <v>1</v>
       </c>
       <c r="F108">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="G108">
         <v>3</v>
@@ -12004,13 +12052,13 @@
         <v>1</v>
       </c>
       <c r="J108">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="K108">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L108">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="M108" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12022,10 +12070,10 @@
         <v>[]</v>
       </c>
       <c r="P108">
-        <v>379</v>
+        <v>634</v>
       </c>
       <c r="Q108">
-        <v>120</v>
+        <v>436</v>
       </c>
       <c r="R108" t="str">
         <v>[1,800]</v>
@@ -12093,7 +12141,7 @@
         <v>30009</v>
       </c>
       <c r="C109" t="str">
-        <v>骨进-骑兵 T2</v>
+        <v>张曼成-骑兵 T2</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -12102,7 +12150,7 @@
         <v>1</v>
       </c>
       <c r="F109">
-        <v>241</v>
+        <v>501</v>
       </c>
       <c r="G109">
         <v>4</v>
@@ -12114,13 +12162,13 @@
         <v>1</v>
       </c>
       <c r="J109">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K109">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L109">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="M109" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12132,10 +12180,10 @@
         <v>[]</v>
       </c>
       <c r="P109">
-        <v>376</v>
+        <v>601</v>
       </c>
       <c r="Q109">
-        <v>123</v>
+        <v>416</v>
       </c>
       <c r="R109" t="str">
         <v>[1,800]</v>
@@ -12203,7 +12251,7 @@
         <v>30010</v>
       </c>
       <c r="C110" t="str">
-        <v>蹋顿-骑兵 T2</v>
+        <v>韩遂-骑兵 T2</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -12212,7 +12260,7 @@
         <v>1</v>
       </c>
       <c r="F110">
-        <v>301</v>
+        <v>412</v>
       </c>
       <c r="G110">
         <v>4</v>
@@ -12224,13 +12272,13 @@
         <v>1</v>
       </c>
       <c r="J110">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="K110">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L110">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="M110" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12242,10 +12290,10 @@
         <v>[]</v>
       </c>
       <c r="P110">
-        <v>377</v>
+        <v>626</v>
       </c>
       <c r="Q110">
-        <v>113</v>
+        <v>439</v>
       </c>
       <c r="R110" t="str">
         <v>[1,800]</v>
@@ -12313,7 +12361,7 @@
         <v>30011</v>
       </c>
       <c r="C111" t="str">
-        <v>马云禄-骑兵 T2</v>
+        <v>孟获-骑兵 T2</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -12322,7 +12370,7 @@
         <v>1</v>
       </c>
       <c r="F111">
-        <v>286</v>
+        <v>438</v>
       </c>
       <c r="G111">
         <v>4</v>
@@ -12334,13 +12382,13 @@
         <v>1</v>
       </c>
       <c r="J111">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="K111">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L111">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="M111" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12352,10 +12400,10 @@
         <v>[]</v>
       </c>
       <c r="P111">
-        <v>374</v>
+        <v>621</v>
       </c>
       <c r="Q111">
-        <v>122</v>
+        <v>433</v>
       </c>
       <c r="R111" t="str">
         <v>[1,800]</v>
@@ -12423,7 +12471,7 @@
         <v>30012</v>
       </c>
       <c r="C112" t="str">
-        <v>张济-骑兵 T2</v>
+        <v>牛辅-骑兵 T2</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -12432,7 +12480,7 @@
         <v>1</v>
       </c>
       <c r="F112">
-        <v>301</v>
+        <v>424</v>
       </c>
       <c r="G112">
         <v>4</v>
@@ -12444,13 +12492,13 @@
         <v>1</v>
       </c>
       <c r="J112">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="K112">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="L112">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="M112" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12462,10 +12510,10 @@
         <v>[]</v>
       </c>
       <c r="P112">
-        <v>378</v>
+        <v>638</v>
       </c>
       <c r="Q112">
-        <v>117</v>
+        <v>401</v>
       </c>
       <c r="R112" t="str">
         <v>[1,800]</v>
@@ -12533,7 +12581,7 @@
         <v>30013</v>
       </c>
       <c r="C113" t="str">
-        <v>花鬘-骑兵 T2</v>
+        <v>张卫-骑兵 T2</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -12542,7 +12590,7 @@
         <v>1</v>
       </c>
       <c r="F113">
-        <v>292</v>
+        <v>537</v>
       </c>
       <c r="G113">
         <v>4</v>
@@ -12554,13 +12602,13 @@
         <v>1</v>
       </c>
       <c r="J113">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="K113">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L113">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M113" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12572,10 +12620,10 @@
         <v>[]</v>
       </c>
       <c r="P113">
-        <v>362</v>
+        <v>638</v>
       </c>
       <c r="Q113">
-        <v>128</v>
+        <v>449</v>
       </c>
       <c r="R113" t="str">
         <v>[1,800]</v>
@@ -12643,7 +12691,7 @@
         <v>30014</v>
       </c>
       <c r="C114" t="str">
-        <v>马超-骑兵 T2</v>
+        <v>骨进-骑兵 T2</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -12652,7 +12700,7 @@
         <v>1</v>
       </c>
       <c r="F114">
-        <v>264</v>
+        <v>477</v>
       </c>
       <c r="G114">
         <v>4</v>
@@ -12664,13 +12712,13 @@
         <v>1</v>
       </c>
       <c r="J114">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="K114">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L114">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M114" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12682,10 +12730,10 @@
         <v>[]</v>
       </c>
       <c r="P114">
-        <v>365</v>
+        <v>629</v>
       </c>
       <c r="Q114">
-        <v>116</v>
+        <v>426</v>
       </c>
       <c r="R114" t="str">
         <v>[1,800]</v>
@@ -12753,7 +12801,7 @@
         <v>30015</v>
       </c>
       <c r="C115" t="str">
-        <v>李傕-骑兵 T2</v>
+        <v>蹋顿-骑兵 T2</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -12762,7 +12810,7 @@
         <v>1</v>
       </c>
       <c r="F115">
-        <v>284</v>
+        <v>442</v>
       </c>
       <c r="G115">
         <v>4</v>
@@ -12774,13 +12822,13 @@
         <v>1</v>
       </c>
       <c r="J115">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="K115">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L115">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="M115" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12792,10 +12840,10 @@
         <v>[]</v>
       </c>
       <c r="P115">
-        <v>380</v>
+        <v>609</v>
       </c>
       <c r="Q115">
-        <v>118</v>
+        <v>431</v>
       </c>
       <c r="R115" t="str">
         <v>[1,800]</v>
@@ -12863,7 +12911,7 @@
         <v>30016</v>
       </c>
       <c r="C116" t="str">
-        <v>胡轸-骑兵 T2</v>
+        <v>程远志-骑兵 T2</v>
       </c>
       <c r="D116">
         <v>2</v>
@@ -12872,7 +12920,7 @@
         <v>1</v>
       </c>
       <c r="F116">
-        <v>272</v>
+        <v>434</v>
       </c>
       <c r="G116">
         <v>4</v>
@@ -12884,13 +12932,13 @@
         <v>1</v>
       </c>
       <c r="J116">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K116">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L116">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="M116" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12902,10 +12950,10 @@
         <v>[]</v>
       </c>
       <c r="P116">
-        <v>376</v>
+        <v>614</v>
       </c>
       <c r="Q116">
-        <v>132</v>
+        <v>395</v>
       </c>
       <c r="R116" t="str">
         <v>[1,800]</v>
@@ -12973,7 +13021,7 @@
         <v>30017</v>
       </c>
       <c r="C117" t="str">
-        <v>张辽-骑兵 T3</v>
+        <v>韩暹-骑兵 T3</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -12982,7 +13030,7 @@
         <v>1</v>
       </c>
       <c r="F117">
-        <v>384</v>
+        <v>831</v>
       </c>
       <c r="G117">
         <v>5</v>
@@ -12994,13 +13042,13 @@
         <v>1</v>
       </c>
       <c r="J117">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="K117">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L117">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="M117" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13012,10 +13060,10 @@
         <v>[]</v>
       </c>
       <c r="P117">
-        <v>369</v>
+        <v>620</v>
       </c>
       <c r="Q117">
-        <v>109</v>
+        <v>409</v>
       </c>
       <c r="R117" t="str">
         <v>[1,800]</v>
@@ -13083,7 +13131,7 @@
         <v>30018</v>
       </c>
       <c r="C118" t="str">
-        <v>库察-骑兵 T3</v>
+        <v>杨奉-骑兵 T3</v>
       </c>
       <c r="D118">
         <v>2</v>
@@ -13092,7 +13140,7 @@
         <v>1</v>
       </c>
       <c r="F118">
-        <v>425</v>
+        <v>674</v>
       </c>
       <c r="G118">
         <v>5</v>
@@ -13104,13 +13152,13 @@
         <v>1</v>
       </c>
       <c r="J118">
-        <v>265</v>
+        <v>210</v>
       </c>
       <c r="K118">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L118">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="M118" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13122,10 +13170,10 @@
         <v>[]</v>
       </c>
       <c r="P118">
-        <v>368</v>
+        <v>627</v>
       </c>
       <c r="Q118">
-        <v>123</v>
+        <v>415</v>
       </c>
       <c r="R118" t="str">
         <v>[1,800]</v>
@@ -13193,7 +13241,7 @@
         <v>30019</v>
       </c>
       <c r="C119" t="str">
-        <v>郭淮-骑兵 T3</v>
+        <v>张横-骑兵 T3</v>
       </c>
       <c r="D119">
         <v>2</v>
@@ -13202,7 +13250,7 @@
         <v>1</v>
       </c>
       <c r="F119">
-        <v>384</v>
+        <v>736</v>
       </c>
       <c r="G119">
         <v>5</v>
@@ -13214,13 +13262,13 @@
         <v>1</v>
       </c>
       <c r="J119">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="K119">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L119">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="M119" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13232,10 +13280,10 @@
         <v>[]</v>
       </c>
       <c r="P119">
-        <v>368</v>
+        <v>616</v>
       </c>
       <c r="Q119">
-        <v>129</v>
+        <v>448</v>
       </c>
       <c r="R119" t="str">
         <v>[1,800]</v>
@@ -13303,7 +13351,7 @@
         <v>30020</v>
       </c>
       <c r="C120" t="str">
-        <v>高升-骑兵 T3</v>
+        <v>严政-骑兵 T3</v>
       </c>
       <c r="D120">
         <v>2</v>
@@ -13312,7 +13360,7 @@
         <v>1</v>
       </c>
       <c r="F120">
-        <v>403</v>
+        <v>673</v>
       </c>
       <c r="G120">
         <v>5</v>
@@ -13324,13 +13372,13 @@
         <v>1</v>
       </c>
       <c r="J120">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="K120">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L120">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="M120" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13342,10 +13390,10 @@
         <v>[]</v>
       </c>
       <c r="P120">
-        <v>372</v>
+        <v>603</v>
       </c>
       <c r="Q120">
-        <v>109</v>
+        <v>400</v>
       </c>
       <c r="R120" t="str">
         <v>[1,800]</v>
@@ -13413,7 +13461,7 @@
         <v>30021</v>
       </c>
       <c r="C121" t="str">
-        <v>程银-骑兵 T3</v>
+        <v>吕玲绮-骑兵 T3</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -13422,7 +13470,7 @@
         <v>1</v>
       </c>
       <c r="F121">
-        <v>489</v>
+        <v>595</v>
       </c>
       <c r="G121">
         <v>5</v>
@@ -13434,13 +13482,13 @@
         <v>1</v>
       </c>
       <c r="J121">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="K121">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="L121">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="M121" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13452,10 +13500,10 @@
         <v>[]</v>
       </c>
       <c r="P121">
-        <v>379</v>
+        <v>604</v>
       </c>
       <c r="Q121">
-        <v>131</v>
+        <v>448</v>
       </c>
       <c r="R121" t="str">
         <v>[1,800]</v>
@@ -13523,7 +13571,7 @@
         <v>30022</v>
       </c>
       <c r="C122" t="str">
-        <v>吕蒙-骑兵 T3</v>
+        <v>杨秋-骑兵 T3</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -13532,7 +13580,7 @@
         <v>1</v>
       </c>
       <c r="F122">
-        <v>411</v>
+        <v>691</v>
       </c>
       <c r="G122">
         <v>5</v>
@@ -13544,13 +13592,13 @@
         <v>1</v>
       </c>
       <c r="J122">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K122">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L122">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="M122" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13562,10 +13610,10 @@
         <v>[]</v>
       </c>
       <c r="P122">
-        <v>373</v>
+        <v>629</v>
       </c>
       <c r="Q122">
-        <v>123</v>
+        <v>415</v>
       </c>
       <c r="R122" t="str">
         <v>[1,800]</v>
@@ -13633,7 +13681,7 @@
         <v>30023</v>
       </c>
       <c r="C123" t="str">
-        <v>段煨-骑兵 T3</v>
+        <v>花鬘-骑兵 T3</v>
       </c>
       <c r="D123">
         <v>2</v>
@@ -13642,7 +13690,7 @@
         <v>1</v>
       </c>
       <c r="F123">
-        <v>366</v>
+        <v>895</v>
       </c>
       <c r="G123">
         <v>5</v>
@@ -13654,13 +13702,13 @@
         <v>1</v>
       </c>
       <c r="J123">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="K123">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L123">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="M123" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13672,10 +13720,10 @@
         <v>[]</v>
       </c>
       <c r="P123">
-        <v>365</v>
+        <v>628</v>
       </c>
       <c r="Q123">
-        <v>130</v>
+        <v>412</v>
       </c>
       <c r="R123" t="str">
         <v>[1,800]</v>
@@ -13743,7 +13791,7 @@
         <v>30024</v>
       </c>
       <c r="C124" t="str">
-        <v>牛辅-骑兵 T3</v>
+        <v>马超-骑兵 T3</v>
       </c>
       <c r="D124">
         <v>2</v>
@@ -13752,7 +13800,7 @@
         <v>1</v>
       </c>
       <c r="F124">
-        <v>416</v>
+        <v>708</v>
       </c>
       <c r="G124">
         <v>5</v>
@@ -13764,13 +13812,13 @@
         <v>1</v>
       </c>
       <c r="J124">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K124">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L124">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="M124" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13782,10 +13830,10 @@
         <v>[]</v>
       </c>
       <c r="P124">
-        <v>375</v>
+        <v>624</v>
       </c>
       <c r="Q124">
-        <v>112</v>
+        <v>400</v>
       </c>
       <c r="R124" t="str">
         <v>[1,800]</v>
@@ -13853,7 +13901,7 @@
         <v>30025</v>
       </c>
       <c r="C125" t="str">
-        <v>樊稠-骑兵 T4</v>
+        <v>夏侯渊-骑兵 T4</v>
       </c>
       <c r="D125">
         <v>2</v>
@@ -13862,7 +13910,7 @@
         <v>1</v>
       </c>
       <c r="F125">
-        <v>516</v>
+        <v>873</v>
       </c>
       <c r="G125">
         <v>6</v>
@@ -13874,13 +13922,13 @@
         <v>1</v>
       </c>
       <c r="J125">
-        <v>310</v>
+        <v>244</v>
       </c>
       <c r="K125">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L125">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="M125" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13892,10 +13940,10 @@
         <v>[]</v>
       </c>
       <c r="P125">
-        <v>369</v>
+        <v>618</v>
       </c>
       <c r="Q125">
-        <v>125</v>
+        <v>378</v>
       </c>
       <c r="R125" t="str">
         <v>[1,800]</v>
@@ -13963,7 +14011,7 @@
         <v>30026</v>
       </c>
       <c r="C126" t="str">
-        <v>成公英-骑兵 T4</v>
+        <v>兀突骨-骑兵 T4</v>
       </c>
       <c r="D126">
         <v>2</v>
@@ -13972,7 +14020,7 @@
         <v>1</v>
       </c>
       <c r="F126">
-        <v>571</v>
+        <v>1057</v>
       </c>
       <c r="G126">
         <v>6</v>
@@ -13984,13 +14032,13 @@
         <v>1</v>
       </c>
       <c r="J126">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="K126">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L126">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="M126" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14002,10 +14050,10 @@
         <v>[]</v>
       </c>
       <c r="P126">
-        <v>365</v>
+        <v>640</v>
       </c>
       <c r="Q126">
-        <v>126</v>
+        <v>416</v>
       </c>
       <c r="R126" t="str">
         <v>[1,800]</v>
@@ -14073,7 +14121,7 @@
         <v>30027</v>
       </c>
       <c r="C127" t="str">
-        <v>侯选-骑兵 T4</v>
+        <v>吕蒙-骑兵 T4</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -14082,7 +14130,7 @@
         <v>1</v>
       </c>
       <c r="F127">
-        <v>612</v>
+        <v>971</v>
       </c>
       <c r="G127">
         <v>6</v>
@@ -14094,13 +14142,13 @@
         <v>1</v>
       </c>
       <c r="J127">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="K127">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L127">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="M127" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14112,10 +14160,10 @@
         <v>[]</v>
       </c>
       <c r="P127">
-        <v>382</v>
+        <v>626</v>
       </c>
       <c r="Q127">
-        <v>126</v>
+        <v>384</v>
       </c>
       <c r="R127" t="str">
         <v>[1,800]</v>
@@ -14183,7 +14231,7 @@
         <v>30028</v>
       </c>
       <c r="C128" t="str">
-        <v>郭汜-骑兵 T4</v>
+        <v>库察-骑兵 T4</v>
       </c>
       <c r="D128">
         <v>2</v>
@@ -14192,7 +14240,7 @@
         <v>1</v>
       </c>
       <c r="F128">
-        <v>669</v>
+        <v>1012</v>
       </c>
       <c r="G128">
         <v>6</v>
@@ -14204,13 +14252,13 @@
         <v>1</v>
       </c>
       <c r="J128">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="K128">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="L128">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M128" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14222,10 +14270,10 @@
         <v>[]</v>
       </c>
       <c r="P128">
-        <v>374</v>
+        <v>632</v>
       </c>
       <c r="Q128">
-        <v>121</v>
+        <v>441</v>
       </c>
       <c r="R128" t="str">
         <v>[1,800]</v>
@@ -14293,7 +14341,7 @@
         <v>30029</v>
       </c>
       <c r="C129" t="str">
-        <v>张曼成-骑兵 T4</v>
+        <v>李傕-骑兵 T4</v>
       </c>
       <c r="D129">
         <v>2</v>
@@ -14302,7 +14350,7 @@
         <v>1</v>
       </c>
       <c r="F129">
-        <v>581</v>
+        <v>911</v>
       </c>
       <c r="G129">
         <v>6</v>
@@ -14314,13 +14362,13 @@
         <v>1</v>
       </c>
       <c r="J129">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="K129">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L129">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="M129" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14332,10 +14380,10 @@
         <v>[]</v>
       </c>
       <c r="P129">
-        <v>384</v>
+        <v>639</v>
       </c>
       <c r="Q129">
-        <v>120</v>
+        <v>388</v>
       </c>
       <c r="R129" t="str">
         <v>[1,800]</v>
@@ -14403,7 +14451,7 @@
         <v>30030</v>
       </c>
       <c r="C130" t="str">
-        <v>孟获-骑兵 T4</v>
+        <v>马云禄-骑兵 T4</v>
       </c>
       <c r="D130">
         <v>2</v>
@@ -14412,7 +14460,7 @@
         <v>1</v>
       </c>
       <c r="F130">
-        <v>593</v>
+        <v>1004</v>
       </c>
       <c r="G130">
         <v>6</v>
@@ -14424,13 +14472,13 @@
         <v>1</v>
       </c>
       <c r="J130">
-        <v>284</v>
+        <v>347</v>
       </c>
       <c r="K130">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L130">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="M130" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14442,10 +14490,10 @@
         <v>[]</v>
       </c>
       <c r="P130">
-        <v>364</v>
+        <v>623</v>
       </c>
       <c r="Q130">
-        <v>114</v>
+        <v>389</v>
       </c>
       <c r="R130" t="str">
         <v>[1,800]</v>
@@ -14513,7 +14561,7 @@
         <v>30031</v>
       </c>
       <c r="C131" t="str">
-        <v>吕布-骑兵 T4</v>
+        <v>公孙瓒-骑兵 T4</v>
       </c>
       <c r="D131">
         <v>2</v>
@@ -14522,7 +14570,7 @@
         <v>1</v>
       </c>
       <c r="F131">
-        <v>632</v>
+        <v>906</v>
       </c>
       <c r="G131">
         <v>6</v>
@@ -14534,13 +14582,13 @@
         <v>1</v>
       </c>
       <c r="J131">
-        <v>315</v>
+        <v>243</v>
       </c>
       <c r="K131">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L131">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="M131" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14552,10 +14600,10 @@
         <v>[]</v>
       </c>
       <c r="P131">
-        <v>361</v>
+        <v>638</v>
       </c>
       <c r="Q131">
-        <v>108</v>
+        <v>397</v>
       </c>
       <c r="R131" t="str">
         <v>[1,800]</v>
@@ -14623,7 +14671,7 @@
         <v>30032</v>
       </c>
       <c r="C132" t="str">
-        <v>马铁-骑兵 T4</v>
+        <v>波才-骑兵 T4</v>
       </c>
       <c r="D132">
         <v>2</v>
@@ -14632,7 +14680,7 @@
         <v>1</v>
       </c>
       <c r="F132">
-        <v>616</v>
+        <v>1023</v>
       </c>
       <c r="G132">
         <v>6</v>
@@ -14644,13 +14692,13 @@
         <v>1</v>
       </c>
       <c r="J132">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="K132">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L132">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M132" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14662,10 +14710,10 @@
         <v>[]</v>
       </c>
       <c r="P132">
-        <v>361</v>
+        <v>618</v>
       </c>
       <c r="Q132">
-        <v>110</v>
+        <v>408</v>
       </c>
       <c r="R132" t="str">
         <v>[1,800]</v>
@@ -14733,7 +14781,7 @@
         <v>40001</v>
       </c>
       <c r="C133" t="str">
-        <v>邢道荣-长枪兵 T1</v>
+        <v>黄权-长枪兵 T1</v>
       </c>
       <c r="D133">
         <v>3</v>
@@ -14742,7 +14790,7 @@
         <v>1</v>
       </c>
       <c r="F133">
-        <v>134</v>
+        <v>287</v>
       </c>
       <c r="G133">
         <v>3</v>
@@ -14754,13 +14802,13 @@
         <v>1</v>
       </c>
       <c r="J133">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="K133">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L133">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="M133" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14772,10 +14820,10 @@
         <v>[]</v>
       </c>
       <c r="P133">
-        <v>276</v>
+        <v>470</v>
       </c>
       <c r="Q133">
-        <v>153</v>
+        <v>444</v>
       </c>
       <c r="R133" t="str">
         <v>[1,800]</v>
@@ -14843,7 +14891,7 @@
         <v>40002</v>
       </c>
       <c r="C134" t="str">
-        <v>纪灵-长枪兵 T1</v>
+        <v>郝萌-长枪兵 T1</v>
       </c>
       <c r="D134">
         <v>3</v>
@@ -14852,7 +14900,7 @@
         <v>1</v>
       </c>
       <c r="F134">
-        <v>138</v>
+        <v>246</v>
       </c>
       <c r="G134">
         <v>3</v>
@@ -14864,13 +14912,13 @@
         <v>1</v>
       </c>
       <c r="J134">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="K134">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L134">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="M134" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14882,10 +14930,10 @@
         <v>[]</v>
       </c>
       <c r="P134">
-        <v>287</v>
+        <v>467</v>
       </c>
       <c r="Q134">
-        <v>139</v>
+        <v>449</v>
       </c>
       <c r="R134" t="str">
         <v>[1,800]</v>
@@ -14953,7 +15001,7 @@
         <v>40003</v>
       </c>
       <c r="C135" t="str">
-        <v>侯成-长枪兵 T1</v>
+        <v>孟达-长枪兵 T1</v>
       </c>
       <c r="D135">
         <v>3</v>
@@ -14962,7 +15010,7 @@
         <v>1</v>
       </c>
       <c r="F135">
-        <v>153</v>
+        <v>276</v>
       </c>
       <c r="G135">
         <v>3</v>
@@ -14974,13 +15022,13 @@
         <v>1</v>
       </c>
       <c r="J135">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="K135">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L135">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="M135" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14992,10 +15040,10 @@
         <v>[]</v>
       </c>
       <c r="P135">
-        <v>281</v>
+        <v>473</v>
       </c>
       <c r="Q135">
-        <v>152</v>
+        <v>484</v>
       </c>
       <c r="R135" t="str">
         <v>[1,800]</v>
@@ -15063,7 +15111,7 @@
         <v>40004</v>
       </c>
       <c r="C136" t="str">
-        <v>胡遵-长枪兵 T1</v>
+        <v>宋宪-长枪兵 T1</v>
       </c>
       <c r="D136">
         <v>3</v>
@@ -15072,7 +15120,7 @@
         <v>1</v>
       </c>
       <c r="F136">
-        <v>150</v>
+        <v>264</v>
       </c>
       <c r="G136">
         <v>3</v>
@@ -15084,13 +15132,13 @@
         <v>1</v>
       </c>
       <c r="J136">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="K136">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L136">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="M136" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15102,10 +15150,10 @@
         <v>[]</v>
       </c>
       <c r="P136">
-        <v>283</v>
+        <v>477</v>
       </c>
       <c r="Q136">
-        <v>155</v>
+        <v>425</v>
       </c>
       <c r="R136" t="str">
         <v>[1,800]</v>
@@ -15173,7 +15221,7 @@
         <v>40005</v>
       </c>
       <c r="C137" t="str">
-        <v>成廉-长枪兵 T1</v>
+        <v>侯成-长枪兵 T1</v>
       </c>
       <c r="D137">
         <v>3</v>
@@ -15182,7 +15230,7 @@
         <v>1</v>
       </c>
       <c r="F137">
-        <v>162</v>
+        <v>276</v>
       </c>
       <c r="G137">
         <v>3</v>
@@ -15194,13 +15242,13 @@
         <v>1</v>
       </c>
       <c r="J137">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K137">
         <v>16</v>
       </c>
       <c r="L137">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="M137" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15212,10 +15260,10 @@
         <v>[]</v>
       </c>
       <c r="P137">
-        <v>284</v>
+        <v>461</v>
       </c>
       <c r="Q137">
-        <v>139</v>
+        <v>417</v>
       </c>
       <c r="R137" t="str">
         <v>[1,800]</v>
@@ -15283,7 +15331,7 @@
         <v>40006</v>
       </c>
       <c r="C138" t="str">
-        <v>施绩-长枪兵 T1</v>
+        <v>钟会-长枪兵 T1</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -15292,7 +15340,7 @@
         <v>1</v>
       </c>
       <c r="F138">
-        <v>126</v>
+        <v>234</v>
       </c>
       <c r="G138">
         <v>3</v>
@@ -15304,13 +15352,13 @@
         <v>1</v>
       </c>
       <c r="J138">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K138">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L138">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="M138" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15322,10 +15370,10 @@
         <v>[]</v>
       </c>
       <c r="P138">
-        <v>280</v>
+        <v>474</v>
       </c>
       <c r="Q138">
-        <v>137</v>
+        <v>414</v>
       </c>
       <c r="R138" t="str">
         <v>[1,800]</v>
@@ -15393,7 +15441,7 @@
         <v>40007</v>
       </c>
       <c r="C139" t="str">
-        <v>凌操-长枪兵 T2</v>
+        <v>纪灵-长枪兵 T2</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -15402,7 +15450,7 @@
         <v>1</v>
       </c>
       <c r="F139">
-        <v>252</v>
+        <v>509</v>
       </c>
       <c r="G139">
         <v>4</v>
@@ -15414,13 +15462,13 @@
         <v>1</v>
       </c>
       <c r="J139">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="K139">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L139">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="M139" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15432,10 +15480,10 @@
         <v>[]</v>
       </c>
       <c r="P139">
-        <v>284</v>
+        <v>481</v>
       </c>
       <c r="Q139">
-        <v>145</v>
+        <v>473</v>
       </c>
       <c r="R139" t="str">
         <v>[1,800]</v>
@@ -15503,7 +15551,7 @@
         <v>40008</v>
       </c>
       <c r="C140" t="str">
-        <v>雷铜-长枪兵 T2</v>
+        <v>成廉-长枪兵 T2</v>
       </c>
       <c r="D140">
         <v>3</v>
@@ -15512,7 +15560,7 @@
         <v>1</v>
       </c>
       <c r="F140">
-        <v>272</v>
+        <v>441</v>
       </c>
       <c r="G140">
         <v>4</v>
@@ -15524,13 +15572,13 @@
         <v>1</v>
       </c>
       <c r="J140">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K140">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L140">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="M140" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15542,10 +15590,10 @@
         <v>[]</v>
       </c>
       <c r="P140">
-        <v>281</v>
+        <v>483</v>
       </c>
       <c r="Q140">
-        <v>136</v>
+        <v>450</v>
       </c>
       <c r="R140" t="str">
         <v>[1,800]</v>
@@ -15613,7 +15661,7 @@
         <v>40009</v>
       </c>
       <c r="C141" t="str">
-        <v>陈就-长枪兵 T2</v>
+        <v>张嶷-长枪兵 T2</v>
       </c>
       <c r="D141">
         <v>3</v>
@@ -15622,7 +15670,7 @@
         <v>1</v>
       </c>
       <c r="F141">
-        <v>266</v>
+        <v>482</v>
       </c>
       <c r="G141">
         <v>4</v>
@@ -15634,13 +15682,13 @@
         <v>1</v>
       </c>
       <c r="J141">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="K141">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L141">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="M141" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15652,10 +15700,10 @@
         <v>[]</v>
       </c>
       <c r="P141">
-        <v>290</v>
+        <v>481</v>
       </c>
       <c r="Q141">
-        <v>140</v>
+        <v>410</v>
       </c>
       <c r="R141" t="str">
         <v>[1,800]</v>
@@ -15723,7 +15771,7 @@
         <v>40010</v>
       </c>
       <c r="C142" t="str">
-        <v>吕介-长枪兵 T2</v>
+        <v>邢道荣-长枪兵 T2</v>
       </c>
       <c r="D142">
         <v>3</v>
@@ -15732,7 +15780,7 @@
         <v>1</v>
       </c>
       <c r="F142">
-        <v>252</v>
+        <v>438</v>
       </c>
       <c r="G142">
         <v>4</v>
@@ -15744,13 +15792,13 @@
         <v>1</v>
       </c>
       <c r="J142">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K142">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L142">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="M142" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15762,10 +15810,10 @@
         <v>[]</v>
       </c>
       <c r="P142">
-        <v>282</v>
+        <v>461</v>
       </c>
       <c r="Q142">
-        <v>136</v>
+        <v>471</v>
       </c>
       <c r="R142" t="str">
         <v>[1,800]</v>
@@ -15833,7 +15881,7 @@
         <v>40011</v>
       </c>
       <c r="C143" t="str">
-        <v>全琮-长枪兵 T2</v>
+        <v>陈应-长枪兵 T2</v>
       </c>
       <c r="D143">
         <v>3</v>
@@ -15842,7 +15890,7 @@
         <v>1</v>
       </c>
       <c r="F143">
-        <v>249</v>
+        <v>392</v>
       </c>
       <c r="G143">
         <v>4</v>
@@ -15854,13 +15902,13 @@
         <v>1</v>
       </c>
       <c r="J143">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K143">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L143">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="M143" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15872,10 +15920,10 @@
         <v>[]</v>
       </c>
       <c r="P143">
-        <v>284</v>
+        <v>464</v>
       </c>
       <c r="Q143">
-        <v>162</v>
+        <v>437</v>
       </c>
       <c r="R143" t="str">
         <v>[1,800]</v>
@@ -15943,7 +15991,7 @@
         <v>40012</v>
       </c>
       <c r="C144" t="str">
-        <v>蒋钦-长枪兵 T2</v>
+        <v>陈到-长枪兵 T2</v>
       </c>
       <c r="D144">
         <v>3</v>
@@ -15952,7 +16000,7 @@
         <v>1</v>
       </c>
       <c r="F144">
-        <v>245</v>
+        <v>519</v>
       </c>
       <c r="G144">
         <v>4</v>
@@ -15964,13 +16012,13 @@
         <v>1</v>
       </c>
       <c r="J144">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="K144">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L144">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="M144" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15982,10 +16030,10 @@
         <v>[]</v>
       </c>
       <c r="P144">
-        <v>282</v>
+        <v>482</v>
       </c>
       <c r="Q144">
-        <v>149</v>
+        <v>417</v>
       </c>
       <c r="R144" t="str">
         <v>[1,800]</v>
@@ -16053,7 +16101,7 @@
         <v>40013</v>
       </c>
       <c r="C145" t="str">
-        <v>文钦-长枪兵 T3</v>
+        <v>金旋-长枪兵 T3</v>
       </c>
       <c r="D145">
         <v>3</v>
@@ -16062,7 +16110,7 @@
         <v>1</v>
       </c>
       <c r="F145">
-        <v>375</v>
+        <v>813</v>
       </c>
       <c r="G145">
         <v>5</v>
@@ -16074,13 +16122,13 @@
         <v>1</v>
       </c>
       <c r="J145">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="K145">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L145">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="M145" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16092,10 +16140,10 @@
         <v>[]</v>
       </c>
       <c r="P145">
-        <v>286</v>
+        <v>470</v>
       </c>
       <c r="Q145">
-        <v>143</v>
+        <v>408</v>
       </c>
       <c r="R145" t="str">
         <v>[1,800]</v>
@@ -16163,7 +16211,7 @@
         <v>40014</v>
       </c>
       <c r="C146" t="str">
-        <v>黄权-长枪兵 T3</v>
+        <v>王基-长枪兵 T3</v>
       </c>
       <c r="D146">
         <v>3</v>
@@ -16172,7 +16220,7 @@
         <v>1</v>
       </c>
       <c r="F146">
-        <v>471</v>
+        <v>701</v>
       </c>
       <c r="G146">
         <v>5</v>
@@ -16184,13 +16232,13 @@
         <v>1</v>
       </c>
       <c r="J146">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="K146">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L146">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="M146" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16202,10 +16250,10 @@
         <v>[]</v>
       </c>
       <c r="P146">
-        <v>289</v>
+        <v>467</v>
       </c>
       <c r="Q146">
-        <v>154</v>
+        <v>459</v>
       </c>
       <c r="R146" t="str">
         <v>[1,800]</v>
@@ -16273,7 +16321,7 @@
         <v>40015</v>
       </c>
       <c r="C147" t="str">
-        <v>泠苞-长枪兵 T3</v>
+        <v>唐咨-长枪兵 T3</v>
       </c>
       <c r="D147">
         <v>3</v>
@@ -16282,7 +16330,7 @@
         <v>1</v>
       </c>
       <c r="F147">
-        <v>450</v>
+        <v>723</v>
       </c>
       <c r="G147">
         <v>5</v>
@@ -16294,13 +16342,13 @@
         <v>1</v>
       </c>
       <c r="J147">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="K147">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L147">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="M147" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16312,10 +16360,10 @@
         <v>[]</v>
       </c>
       <c r="P147">
-        <v>288</v>
+        <v>474</v>
       </c>
       <c r="Q147">
-        <v>162</v>
+        <v>440</v>
       </c>
       <c r="R147" t="str">
         <v>[1,800]</v>
@@ -16383,7 +16431,7 @@
         <v>40016</v>
       </c>
       <c r="C148" t="str">
-        <v>孙礼-长枪兵 T3</v>
+        <v>吕据-长枪兵 T3</v>
       </c>
       <c r="D148">
         <v>3</v>
@@ -16392,7 +16440,7 @@
         <v>1</v>
       </c>
       <c r="F148">
-        <v>399</v>
+        <v>789</v>
       </c>
       <c r="G148">
         <v>5</v>
@@ -16404,13 +16452,13 @@
         <v>1</v>
       </c>
       <c r="J148">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="K148">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L148">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="M148" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16422,10 +16470,10 @@
         <v>[]</v>
       </c>
       <c r="P148">
-        <v>280</v>
+        <v>475</v>
       </c>
       <c r="Q148">
-        <v>145</v>
+        <v>484</v>
       </c>
       <c r="R148" t="str">
         <v>[1,800]</v>
@@ -16493,7 +16541,7 @@
         <v>40017</v>
       </c>
       <c r="C149" t="str">
-        <v>胡济-长枪兵 T3</v>
+        <v>李严-长枪兵 T3</v>
       </c>
       <c r="D149">
         <v>3</v>
@@ -16502,7 +16550,7 @@
         <v>1</v>
       </c>
       <c r="F149">
-        <v>383</v>
+        <v>806</v>
       </c>
       <c r="G149">
         <v>5</v>
@@ -16514,13 +16562,13 @@
         <v>1</v>
       </c>
       <c r="J149">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K149">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L149">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="M149" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16532,10 +16580,10 @@
         <v>[]</v>
       </c>
       <c r="P149">
-        <v>278</v>
+        <v>475</v>
       </c>
       <c r="Q149">
-        <v>162</v>
+        <v>447</v>
       </c>
       <c r="R149" t="str">
         <v>[1,800]</v>
@@ -16603,7 +16651,7 @@
         <v>40018</v>
       </c>
       <c r="C150" t="str">
-        <v>毋丘俭-长枪兵 T3</v>
+        <v>诸葛诞-长枪兵 T3</v>
       </c>
       <c r="D150">
         <v>3</v>
@@ -16612,7 +16660,7 @@
         <v>1</v>
       </c>
       <c r="F150">
-        <v>429</v>
+        <v>819</v>
       </c>
       <c r="G150">
         <v>5</v>
@@ -16624,13 +16672,13 @@
         <v>1</v>
       </c>
       <c r="J150">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="K150">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L150">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="M150" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16642,10 +16690,10 @@
         <v>[]</v>
       </c>
       <c r="P150">
-        <v>284</v>
+        <v>476</v>
       </c>
       <c r="Q150">
-        <v>138</v>
+        <v>445</v>
       </c>
       <c r="R150" t="str">
         <v>[1,800]</v>
@@ -16713,7 +16761,7 @@
         <v>40019</v>
       </c>
       <c r="C151" t="str">
-        <v>曹性-长枪兵 T4</v>
+        <v>吴懿-长枪兵 T4</v>
       </c>
       <c r="D151">
         <v>3</v>
@@ -16722,7 +16770,7 @@
         <v>1</v>
       </c>
       <c r="F151">
-        <v>617</v>
+        <v>1130</v>
       </c>
       <c r="G151">
         <v>6</v>
@@ -16734,13 +16782,13 @@
         <v>1</v>
       </c>
       <c r="J151">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="K151">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L151">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="M151" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16752,10 +16800,10 @@
         <v>[]</v>
       </c>
       <c r="P151">
-        <v>292</v>
+        <v>471</v>
       </c>
       <c r="Q151">
-        <v>135</v>
+        <v>447</v>
       </c>
       <c r="R151" t="str">
         <v>[1,800]</v>
@@ -16823,7 +16871,7 @@
         <v>40020</v>
       </c>
       <c r="C152" t="str">
-        <v>陈泰-长枪兵 T4</v>
+        <v>孙礼-长枪兵 T4</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -16832,7 +16880,7 @@
         <v>1</v>
       </c>
       <c r="F152">
-        <v>524</v>
+        <v>935</v>
       </c>
       <c r="G152">
         <v>6</v>
@@ -16844,13 +16892,13 @@
         <v>1</v>
       </c>
       <c r="J152">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="K152">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L152">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M152" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16862,10 +16910,10 @@
         <v>[]</v>
       </c>
       <c r="P152">
-        <v>285</v>
+        <v>486</v>
       </c>
       <c r="Q152">
-        <v>157</v>
+        <v>479</v>
       </c>
       <c r="R152" t="str">
         <v>[1,800]</v>
@@ -16933,7 +16981,7 @@
         <v>40021</v>
       </c>
       <c r="C153" t="str">
-        <v>陈武-长枪兵 T4</v>
+        <v>泠苞-长枪兵 T4</v>
       </c>
       <c r="D153">
         <v>3</v>
@@ -16942,7 +16990,7 @@
         <v>1</v>
       </c>
       <c r="F153">
-        <v>642</v>
+        <v>1050</v>
       </c>
       <c r="G153">
         <v>6</v>
@@ -16954,13 +17002,13 @@
         <v>1</v>
       </c>
       <c r="J153">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="K153">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L153">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="M153" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16972,10 +17020,10 @@
         <v>[]</v>
       </c>
       <c r="P153">
-        <v>286</v>
+        <v>475</v>
       </c>
       <c r="Q153">
-        <v>156</v>
+        <v>422</v>
       </c>
       <c r="R153" t="str">
         <v>[1,800]</v>
@@ -17043,7 +17091,7 @@
         <v>40022</v>
       </c>
       <c r="C154" t="str">
-        <v>吕据-长枪兵 T4</v>
+        <v>彭羕-长枪兵 T4</v>
       </c>
       <c r="D154">
         <v>3</v>
@@ -17052,7 +17100,7 @@
         <v>1</v>
       </c>
       <c r="F154">
-        <v>675</v>
+        <v>875</v>
       </c>
       <c r="G154">
         <v>6</v>
@@ -17064,13 +17112,13 @@
         <v>1</v>
       </c>
       <c r="J154">
-        <v>293</v>
+        <v>225</v>
       </c>
       <c r="K154">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L154">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="M154" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17082,10 +17130,10 @@
         <v>[]</v>
       </c>
       <c r="P154">
-        <v>285</v>
+        <v>476</v>
       </c>
       <c r="Q154">
-        <v>144</v>
+        <v>475</v>
       </c>
       <c r="R154" t="str">
         <v>[1,800]</v>
@@ -17153,7 +17201,7 @@
         <v>40023</v>
       </c>
       <c r="C155" t="str">
-        <v>吴懿-长枪兵 T4</v>
+        <v>句扶-长枪兵 T4</v>
       </c>
       <c r="D155">
         <v>3</v>
@@ -17162,7 +17210,7 @@
         <v>1</v>
       </c>
       <c r="F155">
-        <v>678</v>
+        <v>1028</v>
       </c>
       <c r="G155">
         <v>6</v>
@@ -17174,13 +17222,13 @@
         <v>1</v>
       </c>
       <c r="J155">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="K155">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L155">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="M155" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17192,10 +17240,10 @@
         <v>[]</v>
       </c>
       <c r="P155">
-        <v>291</v>
+        <v>471</v>
       </c>
       <c r="Q155">
-        <v>146</v>
+        <v>450</v>
       </c>
       <c r="R155" t="str">
         <v>[1,800]</v>
@@ -17263,7 +17311,7 @@
         <v>40024</v>
       </c>
       <c r="C156" t="str">
-        <v>李恢-长枪兵 T4</v>
+        <v>鲍隆-长枪兵 T4</v>
       </c>
       <c r="D156">
         <v>3</v>
@@ -17272,7 +17320,7 @@
         <v>1</v>
       </c>
       <c r="F156">
-        <v>590</v>
+        <v>1037</v>
       </c>
       <c r="G156">
         <v>6</v>
@@ -17284,13 +17332,13 @@
         <v>1</v>
       </c>
       <c r="J156">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="K156">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L156">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="M156" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17302,10 +17350,10 @@
         <v>[]</v>
       </c>
       <c r="P156">
-        <v>290</v>
+        <v>483</v>
       </c>
       <c r="Q156">
-        <v>141</v>
+        <v>482</v>
       </c>
       <c r="R156" t="str">
         <v>[1,800]</v>
@@ -18205,7 +18253,7 @@
         <v>50001</v>
       </c>
       <c r="C165" t="str">
-        <v>宗预-法师 T1</v>
+        <v>诸葛亮-法师 T1</v>
       </c>
       <c r="D165">
         <v>4</v>
@@ -18214,7 +18262,7 @@
         <v>1</v>
       </c>
       <c r="F165">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="G165">
         <v>3</v>
@@ -18226,13 +18274,13 @@
         <v>15</v>
       </c>
       <c r="J165">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="K165">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L165">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="M165" t="str">
         <v>[[2,252],[20,378],[40,504],[60,630],[80,756],[100,882],[120,1008],[140,1134],[160,1260],[180,1386],[200,1512]]</v>
@@ -18244,10 +18292,10 @@
         <v>[]</v>
       </c>
       <c r="P165">
-        <v>204</v>
+        <v>365</v>
       </c>
       <c r="Q165">
-        <v>2141</v>
+        <v>1909</v>
       </c>
       <c r="R165" t="str">
         <v>[1,800]</v>
@@ -18315,7 +18363,7 @@
         <v>50002</v>
       </c>
       <c r="C166" t="str">
-        <v>徐庶-法师 T1</v>
+        <v>糜芳-法师 T1</v>
       </c>
       <c r="D166">
         <v>4</v>
@@ -18324,7 +18372,7 @@
         <v>1</v>
       </c>
       <c r="F166">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="G166">
         <v>3</v>
@@ -18336,13 +18384,13 @@
         <v>20</v>
       </c>
       <c r="J166">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="K166">
         <v>21</v>
       </c>
       <c r="L166">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="M166" t="str">
         <v>[[2,239],[20,359],[40,478],[60,598],[80,718],[100,837],[120,957],[140,1076],[160,1196],[180,1316],[200,1435]]</v>
@@ -18354,10 +18402,10 @@
         <v>[]</v>
       </c>
       <c r="P166">
-        <v>228</v>
+        <v>367</v>
       </c>
       <c r="Q166">
-        <v>2008</v>
+        <v>2054</v>
       </c>
       <c r="R166" t="str">
         <v>[1,800]</v>
@@ -18425,7 +18473,7 @@
         <v>50003</v>
       </c>
       <c r="C167" t="str">
-        <v>祝融-法师 T1</v>
+        <v>周瑜-法师 T1</v>
       </c>
       <c r="D167">
         <v>4</v>
@@ -18434,7 +18482,7 @@
         <v>1</v>
       </c>
       <c r="F167">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="G167">
         <v>3</v>
@@ -18446,13 +18494,13 @@
         <v>20</v>
       </c>
       <c r="J167">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K167">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L167">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="M167" t="str">
         <v>[[2,179],[20,269],[40,359],[60,449],[80,538],[100,628],[120,718],[140,807],[160,897],[180,987],[200,1076]]</v>
@@ -18464,10 +18512,10 @@
         <v>[]</v>
       </c>
       <c r="P167">
-        <v>224</v>
+        <v>379</v>
       </c>
       <c r="Q167">
-        <v>1934</v>
+        <v>2138</v>
       </c>
       <c r="R167" t="str">
         <v>[1,800]</v>
@@ -18535,7 +18583,7 @@
         <v>50004</v>
       </c>
       <c r="C168" t="str">
-        <v>陈群-法师 T1</v>
+        <v>秦宓-法师 T1</v>
       </c>
       <c r="D168">
         <v>4</v>
@@ -18544,7 +18592,7 @@
         <v>1</v>
       </c>
       <c r="F168">
-        <v>176</v>
+        <v>255</v>
       </c>
       <c r="G168">
         <v>3</v>
@@ -18556,13 +18604,13 @@
         <v>20</v>
       </c>
       <c r="J168">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K168">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L168">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M168" t="str">
         <v>[[2,347],[20,520],[40,694],[60,867],[80,1041],[100,1214],[120,1387],[140,1561],[160,1734],[180,1908],[200,2081]]</v>
@@ -18574,10 +18622,10 @@
         <v>[]</v>
       </c>
       <c r="P168">
-        <v>222</v>
+        <v>352</v>
       </c>
       <c r="Q168">
-        <v>1942</v>
+        <v>1989</v>
       </c>
       <c r="R168" t="str">
         <v>[1,800]</v>
@@ -18645,7 +18693,7 @@
         <v>50005</v>
       </c>
       <c r="C169" t="str">
-        <v>姜维-法师 T1</v>
+        <v>糜竺-法师 T1</v>
       </c>
       <c r="D169">
         <v>4</v>
@@ -18654,7 +18702,7 @@
         <v>1</v>
       </c>
       <c r="F169">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="G169">
         <v>3</v>
@@ -18666,13 +18714,13 @@
         <v>20</v>
       </c>
       <c r="J169">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K169">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L169">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="M169" t="str">
         <v>[[2,150],[20,224],[40,299],[60,374],[80,449],[100,523],[120,598],[140,673],[160,748],[180,822],[200,897]]</v>
@@ -18684,10 +18732,10 @@
         <v>[]</v>
       </c>
       <c r="P169">
-        <v>209</v>
+        <v>345</v>
       </c>
       <c r="Q169">
-        <v>2063</v>
+        <v>1801</v>
       </c>
       <c r="R169" t="str">
         <v>[1,800]</v>
@@ -18755,7 +18803,7 @@
         <v>50006</v>
       </c>
       <c r="C170" t="str">
-        <v>满宠-法师 T1</v>
+        <v>陈震-法师 T1</v>
       </c>
       <c r="D170">
         <v>4</v>
@@ -18764,7 +18812,7 @@
         <v>1</v>
       </c>
       <c r="F170">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="G170">
         <v>3</v>
@@ -18776,13 +18824,13 @@
         <v>20</v>
       </c>
       <c r="J170">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K170">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L170">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="M170" t="str">
         <v>[[2,275],[20,413],[40,550],[60,688],[80,825],[100,963],[120,1100],[140,1238],[160,1375],[180,1513],[200,1650]]</v>
@@ -18794,10 +18842,10 @@
         <v>[]</v>
       </c>
       <c r="P170">
-        <v>216</v>
+        <v>355</v>
       </c>
       <c r="Q170">
-        <v>2034</v>
+        <v>1905</v>
       </c>
       <c r="R170" t="str">
         <v>[1,800]</v>
@@ -18865,7 +18913,7 @@
         <v>50007</v>
       </c>
       <c r="C171" t="str">
-        <v>顾雍-法师 T2</v>
+        <v>步骘-法师 T2</v>
       </c>
       <c r="D171">
         <v>4</v>
@@ -18874,7 +18922,7 @@
         <v>1</v>
       </c>
       <c r="F171">
-        <v>354</v>
+        <v>432</v>
       </c>
       <c r="G171">
         <v>4</v>
@@ -18886,13 +18934,13 @@
         <v>20</v>
       </c>
       <c r="J171">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="K171">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L171">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="M171" t="str">
         <v>[[2,311],[20,466],[40,622],[60,777],[80,933],[100,1088],[120,1244],[140,1399],[160,1555],[180,1710],[200,1866]]</v>
@@ -18904,10 +18952,10 @@
         <v>[]</v>
       </c>
       <c r="P171">
-        <v>218</v>
+        <v>362</v>
       </c>
       <c r="Q171">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="R171" t="str">
         <v>[1,800]</v>
@@ -18975,7 +19023,7 @@
         <v>50008</v>
       </c>
       <c r="C172" t="str">
-        <v>华歆-法师 T2</v>
+        <v>蒯良-法师 T2</v>
       </c>
       <c r="D172">
         <v>4</v>
@@ -18984,7 +19032,7 @@
         <v>1</v>
       </c>
       <c r="F172">
-        <v>277</v>
+        <v>358</v>
       </c>
       <c r="G172">
         <v>4</v>
@@ -18996,13 +19044,13 @@
         <v>25</v>
       </c>
       <c r="J172">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K172">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L172">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="M172" t="str">
         <v>[[2,594],[20,891],[40,1188],[60,1485],[80,1782],[100,2079],[120,2376],[140,2673],[160,2970],[180,3267],[200,3564]]</v>
@@ -19014,10 +19062,10 @@
         <v>[]</v>
       </c>
       <c r="P172">
-        <v>227</v>
+        <v>372</v>
       </c>
       <c r="Q172">
-        <v>1888</v>
+        <v>1946</v>
       </c>
       <c r="R172" t="str">
         <v>[1,800]</v>
@@ -19085,7 +19133,7 @@
         <v>50009</v>
       </c>
       <c r="C173" t="str">
-        <v>水镜先生-法师 T2</v>
+        <v>审配-法师 T2</v>
       </c>
       <c r="D173">
         <v>4</v>
@@ -19094,7 +19142,7 @@
         <v>1</v>
       </c>
       <c r="F173">
-        <v>279</v>
+        <v>422</v>
       </c>
       <c r="G173">
         <v>4</v>
@@ -19106,13 +19154,13 @@
         <v>25</v>
       </c>
       <c r="J173">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K173">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L173">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="M173" t="str">
         <v>[[2,288],[20,432],[40,576],[60,720],[80,864],[100,1008],[120,1152],[140,1296],[160,1440],[180,1584],[200,1728]]</v>
@@ -19124,10 +19172,10 @@
         <v>[]</v>
       </c>
       <c r="P173">
-        <v>225</v>
+        <v>353</v>
       </c>
       <c r="Q173">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="R173" t="str">
         <v>[1,800]</v>
@@ -19195,7 +19243,7 @@
         <v>50010</v>
       </c>
       <c r="C174" t="str">
-        <v>蒯越-法师 T2</v>
+        <v>陈宫-法师 T2</v>
       </c>
       <c r="D174">
         <v>4</v>
@@ -19204,7 +19252,7 @@
         <v>1</v>
       </c>
       <c r="F174">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G174">
         <v>4</v>
@@ -19216,10 +19264,10 @@
         <v>25</v>
       </c>
       <c r="J174">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="K174">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="L174">
         <v>1.3</v>
@@ -19234,10 +19282,10 @@
         <v>[]</v>
       </c>
       <c r="P174">
-        <v>216</v>
+        <v>349</v>
       </c>
       <c r="Q174">
-        <v>1803</v>
+        <v>2089</v>
       </c>
       <c r="R174" t="str">
         <v>[1,800]</v>
@@ -19305,7 +19353,7 @@
         <v>50011</v>
       </c>
       <c r="C175" t="str">
-        <v>董昭-法师 T2</v>
+        <v>庞德公-法师 T2</v>
       </c>
       <c r="D175">
         <v>4</v>
@@ -19314,7 +19362,7 @@
         <v>1</v>
       </c>
       <c r="F175">
-        <v>297</v>
+        <v>400</v>
       </c>
       <c r="G175">
         <v>4</v>
@@ -19326,13 +19374,13 @@
         <v>25</v>
       </c>
       <c r="J175">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="K175">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L175">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="M175" t="str">
         <v>[[2,495],[20,743],[40,990],[60,1238],[80,1485],[100,1733],[120,1980],[140,2228],[160,2475],[180,2723],[200,2970]]</v>
@@ -19344,10 +19392,10 @@
         <v>[]</v>
       </c>
       <c r="P175">
-        <v>210</v>
+        <v>371</v>
       </c>
       <c r="Q175">
-        <v>1807</v>
+        <v>1927</v>
       </c>
       <c r="R175" t="str">
         <v>[1,800]</v>
@@ -19415,7 +19463,7 @@
         <v>50012</v>
       </c>
       <c r="C176" t="str">
-        <v>王朗-法师 T2</v>
+        <v>董昭-法师 T2</v>
       </c>
       <c r="D176">
         <v>4</v>
@@ -19424,7 +19472,7 @@
         <v>1</v>
       </c>
       <c r="F176">
-        <v>266</v>
+        <v>431</v>
       </c>
       <c r="G176">
         <v>4</v>
@@ -19436,13 +19484,13 @@
         <v>25</v>
       </c>
       <c r="J176">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="K176">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L176">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="M176" t="str">
         <v>[[2,257],[20,386],[40,515],[60,644],[80,772],[100,901],[120,1030],[140,1158],[160,1287],[180,1416],[200,1544]]</v>
@@ -19454,10 +19502,10 @@
         <v>[]</v>
       </c>
       <c r="P176">
-        <v>224</v>
+        <v>342</v>
       </c>
       <c r="Q176">
-        <v>2118</v>
+        <v>2140</v>
       </c>
       <c r="R176" t="str">
         <v>[1,800]</v>
@@ -19525,7 +19573,7 @@
         <v>50013</v>
       </c>
       <c r="C177" t="str">
-        <v>虞翻-法师 T3</v>
+        <v>鲁肃-法师 T3</v>
       </c>
       <c r="D177">
         <v>4</v>
@@ -19534,7 +19582,7 @@
         <v>1</v>
       </c>
       <c r="F177">
-        <v>375</v>
+        <v>520</v>
       </c>
       <c r="G177">
         <v>5</v>
@@ -19546,13 +19594,13 @@
         <v>25</v>
       </c>
       <c r="J177">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="K177">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L177">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="M177" t="str">
         <v>[[2,441],[20,662],[40,882],[60,1103],[80,1323],[100,1544],[120,1764],[140,1985],[160,2205],[180,2426],[200,2646]]</v>
@@ -19564,10 +19612,10 @@
         <v>[]</v>
       </c>
       <c r="P177">
-        <v>223</v>
+        <v>351</v>
       </c>
       <c r="Q177">
-        <v>2096</v>
+        <v>1842</v>
       </c>
       <c r="R177" t="str">
         <v>[1,800]</v>
@@ -19635,7 +19683,7 @@
         <v>50014</v>
       </c>
       <c r="C178" t="str">
-        <v>步练师-法师 T3</v>
+        <v>徐庶-法师 T3</v>
       </c>
       <c r="D178">
         <v>4</v>
@@ -19644,7 +19692,7 @@
         <v>1</v>
       </c>
       <c r="F178">
-        <v>429</v>
+        <v>667</v>
       </c>
       <c r="G178">
         <v>5</v>
@@ -19656,13 +19704,13 @@
         <v>30</v>
       </c>
       <c r="J178">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="K178">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L178">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M178" t="str">
         <v>[[2,770],[20,1155],[40,1540],[60,1925],[80,2310],[100,2695],[120,3080],[140,3465],[160,3850],[180,4235],[200,4620]]</v>
@@ -19674,10 +19722,10 @@
         <v>[]</v>
       </c>
       <c r="P178">
-        <v>227</v>
+        <v>379</v>
       </c>
       <c r="Q178">
-        <v>1867</v>
+        <v>1923</v>
       </c>
       <c r="R178" t="str">
         <v>[1,800]</v>
@@ -19745,7 +19793,7 @@
         <v>50015</v>
       </c>
       <c r="C179" t="str">
-        <v>荀彧-2-法师 T3</v>
+        <v>程昱-2-法师 T3</v>
       </c>
       <c r="D179">
         <v>4</v>
@@ -19754,7 +19802,7 @@
         <v>1</v>
       </c>
       <c r="F179">
-        <v>454</v>
+        <v>650</v>
       </c>
       <c r="G179">
         <v>5</v>
@@ -19766,13 +19814,13 @@
         <v>30</v>
       </c>
       <c r="J179">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="K179">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L179">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M179" t="str">
         <v>[[2,812],[20,1218],[40,1624],[60,2030],[80,2436],[100,2842],[120,3248],[140,3654],[160,4060],[180,4466],[200,4872]]</v>
@@ -19784,10 +19832,10 @@
         <v>[]</v>
       </c>
       <c r="P179">
-        <v>211</v>
+        <v>376</v>
       </c>
       <c r="Q179">
-        <v>1805</v>
+        <v>1838</v>
       </c>
       <c r="R179" t="str">
         <v>[1,800]</v>
@@ -19855,7 +19903,7 @@
         <v>50016</v>
       </c>
       <c r="C180" t="str">
-        <v>司马懿-2-法师 T3</v>
+        <v>祝融-2-法师 T3</v>
       </c>
       <c r="D180">
         <v>4</v>
@@ -19864,7 +19912,7 @@
         <v>1</v>
       </c>
       <c r="F180">
-        <v>402</v>
+        <v>508</v>
       </c>
       <c r="G180">
         <v>5</v>
@@ -19876,13 +19924,13 @@
         <v>30</v>
       </c>
       <c r="J180">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="K180">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L180">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="M180" t="str">
         <v>[[2,728],[20,1092],[40,1456],[60,1820],[80,2184],[100,2548],[120,2912],[140,3276],[160,3640],[180,4004],[200,4368]]</v>
@@ -19894,10 +19942,10 @@
         <v>[]</v>
       </c>
       <c r="P180">
-        <v>212</v>
+        <v>345</v>
       </c>
       <c r="Q180">
-        <v>2044</v>
+        <v>1839</v>
       </c>
       <c r="R180" t="str">
         <v>[1,800]</v>
@@ -19965,7 +20013,7 @@
         <v>50017</v>
       </c>
       <c r="C181" t="str">
-        <v>貂蝉-2-法师 T3</v>
+        <v>辛宪英-2-法师 T3</v>
       </c>
       <c r="D181">
         <v>4</v>
@@ -19974,7 +20022,7 @@
         <v>1</v>
       </c>
       <c r="F181">
-        <v>505</v>
+        <v>646</v>
       </c>
       <c r="G181">
         <v>5</v>
@@ -19986,13 +20034,13 @@
         <v>30</v>
       </c>
       <c r="J181">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="K181">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L181">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="M181" t="str">
         <v>[[2,854],[20,1281],[40,1708],[60,2135],[80,2562],[100,2989],[120,3416],[140,3843],[160,4270],[180,4697],[200,5124]]</v>
@@ -20004,10 +20052,10 @@
         <v>[]</v>
       </c>
       <c r="P181">
-        <v>220</v>
+        <v>360</v>
       </c>
       <c r="Q181">
-        <v>2164</v>
+        <v>2000</v>
       </c>
       <c r="R181" t="str">
         <v>[1,800]</v>
@@ -20075,7 +20123,7 @@
         <v>50018</v>
       </c>
       <c r="C182" t="str">
-        <v>鲁肃-2-法师 T3</v>
+        <v>蒯越-2-法师 T3</v>
       </c>
       <c r="D182">
         <v>4</v>
@@ -20084,7 +20132,7 @@
         <v>1</v>
       </c>
       <c r="F182">
-        <v>466</v>
+        <v>608</v>
       </c>
       <c r="G182">
         <v>5</v>
@@ -20096,13 +20144,13 @@
         <v>30</v>
       </c>
       <c r="J182">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K182">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L182">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="M182" t="str">
         <v>[[2,700],[20,1050],[40,1400],[60,1750],[80,2100],[100,2450],[120,2800],[140,3150],[160,3500],[180,3850],[200,4200]]</v>
@@ -20114,10 +20162,10 @@
         <v>[]</v>
       </c>
       <c r="P182">
-        <v>223</v>
+        <v>342</v>
       </c>
       <c r="Q182">
-        <v>1862</v>
+        <v>1949</v>
       </c>
       <c r="R182" t="str">
         <v>[1,800]</v>
@@ -20185,7 +20233,7 @@
         <v>50019</v>
       </c>
       <c r="C183" t="str">
-        <v>秦宓-2-法师 T4</v>
+        <v>大乔-2-法师 T4</v>
       </c>
       <c r="D183">
         <v>4</v>
@@ -20194,7 +20242,7 @@
         <v>1</v>
       </c>
       <c r="F183">
-        <v>598</v>
+        <v>881</v>
       </c>
       <c r="G183">
         <v>6</v>
@@ -20206,13 +20254,13 @@
         <v>30</v>
       </c>
       <c r="J183">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="K183">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L183">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="M183" t="str">
         <v>[[2,532],[20,798],[40,1064],[60,1330],[80,1596],[100,1862],[120,2128],[140,2394],[160,2660],[180,2926],[200,3192]]</v>
@@ -20224,10 +20272,10 @@
         <v>[]</v>
       </c>
       <c r="P183">
-        <v>209</v>
+        <v>348</v>
       </c>
       <c r="Q183">
-        <v>1828</v>
+        <v>2033</v>
       </c>
       <c r="R183" t="str">
         <v>[1,800]</v>
@@ -20295,7 +20343,7 @@
         <v>50020</v>
       </c>
       <c r="C184" t="str">
-        <v>徐庶-2-法师 T4</v>
+        <v>贾诩-2-法师 T4</v>
       </c>
       <c r="D184">
         <v>4</v>
@@ -20304,7 +20352,7 @@
         <v>1</v>
       </c>
       <c r="F184">
-        <v>652</v>
+        <v>885</v>
       </c>
       <c r="G184">
         <v>6</v>
@@ -20316,10 +20364,10 @@
         <v>30</v>
       </c>
       <c r="J184">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K184">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="L184">
         <v>1.28</v>
@@ -20334,10 +20382,10 @@
         <v>[]</v>
       </c>
       <c r="P184">
-        <v>218</v>
+        <v>377</v>
       </c>
       <c r="Q184">
-        <v>1945</v>
+        <v>1936</v>
       </c>
       <c r="R184" t="str">
         <v>[1,800]</v>
@@ -20405,7 +20453,7 @@
         <v>50021</v>
       </c>
       <c r="C185" t="str">
-        <v>糜芳-2-法师 T4</v>
+        <v>徐庶-2-法师 T4</v>
       </c>
       <c r="D185">
         <v>4</v>
@@ -20414,7 +20462,7 @@
         <v>1</v>
       </c>
       <c r="F185">
-        <v>469</v>
+        <v>839</v>
       </c>
       <c r="G185">
         <v>6</v>
@@ -20426,13 +20474,13 @@
         <v>30</v>
       </c>
       <c r="J185">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="K185">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L185">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M185" t="str">
         <v>[[2,504],[20,756],[40,1008],[60,1260],[80,1512],[100,1764],[120,2016],[140,2268],[160,2520],[180,2772],[200,3024]]</v>
@@ -20444,10 +20492,10 @@
         <v>[]</v>
       </c>
       <c r="P185">
-        <v>207</v>
+        <v>371</v>
       </c>
       <c r="Q185">
-        <v>2197</v>
+        <v>1915</v>
       </c>
       <c r="R185" t="str">
         <v>[1,800]</v>
@@ -20515,7 +20563,7 @@
         <v>50022</v>
       </c>
       <c r="C186" t="str">
-        <v>华佗-2-法师 T4</v>
+        <v>蒯良-2-法师 T4</v>
       </c>
       <c r="D186">
         <v>4</v>
@@ -20524,7 +20572,7 @@
         <v>1</v>
       </c>
       <c r="F186">
-        <v>530</v>
+        <v>998</v>
       </c>
       <c r="G186">
         <v>6</v>
@@ -20536,13 +20584,13 @@
         <v>30</v>
       </c>
       <c r="J186">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="K186">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L186">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="M186" t="str">
         <v>[[2,532],[20,798],[40,1064],[60,1330],[80,1596],[100,1862],[120,2128],[140,2394],[160,2660],[180,2926],[200,3192]]</v>
@@ -20554,10 +20602,10 @@
         <v>[]</v>
       </c>
       <c r="P186">
-        <v>216</v>
+        <v>372</v>
       </c>
       <c r="Q186">
-        <v>1832</v>
+        <v>2165</v>
       </c>
       <c r="R186" t="str">
         <v>[1,800]</v>
@@ -20625,7 +20673,7 @@
         <v>50023</v>
       </c>
       <c r="C187" t="str">
-        <v>步骘-2-法师 T4</v>
+        <v>徐庶-3-法师 T4</v>
       </c>
       <c r="D187">
         <v>4</v>
@@ -20634,7 +20682,7 @@
         <v>1</v>
       </c>
       <c r="F187">
-        <v>515</v>
+        <v>700</v>
       </c>
       <c r="G187">
         <v>6</v>
@@ -20646,13 +20694,13 @@
         <v>30</v>
       </c>
       <c r="J187">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="K187">
         <v>37</v>
       </c>
       <c r="L187">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="M187" t="str">
         <v>[[2,532],[20,798],[40,1064],[60,1330],[80,1596],[100,1862],[120,2128],[140,2394],[160,2660],[180,2926],[200,3192]]</v>
@@ -20664,10 +20712,10 @@
         <v>[]</v>
       </c>
       <c r="P187">
-        <v>226</v>
+        <v>362</v>
       </c>
       <c r="Q187">
-        <v>2044</v>
+        <v>2013</v>
       </c>
       <c r="R187" t="str">
         <v>[1,800]</v>
@@ -20735,7 +20783,7 @@
         <v>50024</v>
       </c>
       <c r="C188" t="str">
-        <v>宗预-2-法师 T4</v>
+        <v>徐庶-4-法师 T4</v>
       </c>
       <c r="D188">
         <v>4</v>
@@ -20744,7 +20792,7 @@
         <v>1</v>
       </c>
       <c r="F188">
-        <v>538</v>
+        <v>690</v>
       </c>
       <c r="G188">
         <v>6</v>
@@ -20756,13 +20804,13 @@
         <v>30</v>
       </c>
       <c r="J188">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K188">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="L188">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="M188" t="str">
         <v>[[2,532],[20,798],[40,1064],[60,1330],[80,1596],[100,1862],[120,2128],[140,2394],[160,2660],[180,2926],[200,3192]]</v>
@@ -20774,10 +20822,10 @@
         <v>[]</v>
       </c>
       <c r="P188">
-        <v>219</v>
+        <v>371</v>
       </c>
       <c r="Q188">
-        <v>1895</v>
+        <v>1948</v>
       </c>
       <c r="R188" t="str">
         <v>[1,800]</v>
@@ -20845,7 +20893,7 @@
         <v>90001</v>
       </c>
       <c r="C189" t="str">
-        <v>【钢铁暴君】吕翔-步兵 T1</v>
+        <v>【虚空母体】淳于琼-步兵 T1</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -20854,7 +20902,7 @@
         <v>20</v>
       </c>
       <c r="F189">
-        <v>491</v>
+        <v>679</v>
       </c>
       <c r="G189">
         <v>3</v>
@@ -20866,13 +20914,13 @@
         <v>1</v>
       </c>
       <c r="J189">
-        <v>672</v>
+        <v>592</v>
       </c>
       <c r="K189">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L189">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="M189" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20884,10 +20932,10 @@
         <v>[]</v>
       </c>
       <c r="P189">
-        <v>313</v>
+        <v>527</v>
       </c>
       <c r="Q189">
-        <v>91</v>
+        <v>387</v>
       </c>
       <c r="R189" t="str">
         <v>[1,800]</v>
@@ -20955,7 +21003,7 @@
         <v>90002</v>
       </c>
       <c r="C190" t="str">
-        <v>【零号病毒】王颀-步兵 T1</v>
+        <v>【钢铁暴君】徐晃-步兵 T1</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -20964,7 +21012,7 @@
         <v>20</v>
       </c>
       <c r="F190">
-        <v>546</v>
+        <v>696</v>
       </c>
       <c r="G190">
         <v>3</v>
@@ -20976,13 +21024,13 @@
         <v>1</v>
       </c>
       <c r="J190">
-        <v>699</v>
+        <v>499</v>
       </c>
       <c r="K190">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L190">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="M190" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20994,10 +21042,10 @@
         <v>[]</v>
       </c>
       <c r="P190">
-        <v>322</v>
+        <v>532</v>
       </c>
       <c r="Q190">
-        <v>98</v>
+        <v>438</v>
       </c>
       <c r="R190" t="str">
         <v>[1,800]</v>
@@ -21065,7 +21113,7 @@
         <v>90003</v>
       </c>
       <c r="C191" t="str">
-        <v>【虚空母体】严白虎-步兵 T2</v>
+        <v>【虚空母体】向宠-步兵 T2</v>
       </c>
       <c r="D191">
         <v>0</v>
@@ -21074,7 +21122,7 @@
         <v>20</v>
       </c>
       <c r="F191">
-        <v>881</v>
+        <v>1190</v>
       </c>
       <c r="G191">
         <v>4</v>
@@ -21086,13 +21134,13 @@
         <v>1</v>
       </c>
       <c r="J191">
-        <v>1005</v>
+        <v>763</v>
       </c>
       <c r="K191">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L191">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="M191" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21104,10 +21152,10 @@
         <v>[]</v>
       </c>
       <c r="P191">
-        <v>321</v>
+        <v>514</v>
       </c>
       <c r="Q191">
-        <v>107</v>
+        <v>418</v>
       </c>
       <c r="R191" t="str">
         <v>[1,800]</v>
@@ -21175,7 +21223,7 @@
         <v>90004</v>
       </c>
       <c r="C192" t="str">
-        <v>【零号病毒】蒋义渠-步兵 T2</v>
+        <v>【变异主宰】张苞-步兵 T2</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -21184,7 +21232,7 @@
         <v>20</v>
       </c>
       <c r="F192">
-        <v>808</v>
+        <v>1498</v>
       </c>
       <c r="G192">
         <v>4</v>
@@ -21196,13 +21244,13 @@
         <v>1</v>
       </c>
       <c r="J192">
-        <v>945</v>
+        <v>1064</v>
       </c>
       <c r="K192">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L192">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="M192" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21214,10 +21262,10 @@
         <v>[]</v>
       </c>
       <c r="P192">
-        <v>314</v>
+        <v>522</v>
       </c>
       <c r="Q192">
-        <v>102</v>
+        <v>414</v>
       </c>
       <c r="R192" t="str">
         <v>[1,800]</v>
@@ -21285,7 +21333,7 @@
         <v>90005</v>
       </c>
       <c r="C193" t="str">
-        <v>【变异主宰】张郃-步兵 T2</v>
+        <v>【末日先兆】蔡瑁-步兵 T2</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -21294,7 +21342,7 @@
         <v>20</v>
       </c>
       <c r="F193">
-        <v>750</v>
+        <v>1336</v>
       </c>
       <c r="G193">
         <v>4</v>
@@ -21306,13 +21354,13 @@
         <v>1</v>
       </c>
       <c r="J193">
-        <v>827</v>
+        <v>1047</v>
       </c>
       <c r="K193">
         <v>23</v>
       </c>
       <c r="L193">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="M193" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21324,10 +21372,10 @@
         <v>[]</v>
       </c>
       <c r="P193">
-        <v>322</v>
+        <v>520</v>
       </c>
       <c r="Q193">
-        <v>100</v>
+        <v>361</v>
       </c>
       <c r="R193" t="str">
         <v>[1,800]</v>
@@ -21395,7 +21443,7 @@
         <v>90006</v>
       </c>
       <c r="C194" t="str">
-        <v>【钢铁暴君】朱桓-步兵 T3</v>
+        <v>【钢铁暴君】王颀-步兵 T3</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -21404,7 +21452,7 @@
         <v>20</v>
       </c>
       <c r="F194">
-        <v>1187</v>
+        <v>2253</v>
       </c>
       <c r="G194">
         <v>5</v>
@@ -21416,10 +21464,10 @@
         <v>1</v>
       </c>
       <c r="J194">
-        <v>1215</v>
+        <v>1322</v>
       </c>
       <c r="K194">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L194">
         <v>1.05</v>
@@ -21434,10 +21482,10 @@
         <v>[]</v>
       </c>
       <c r="P194">
-        <v>323</v>
+        <v>530</v>
       </c>
       <c r="Q194">
-        <v>98</v>
+        <v>411</v>
       </c>
       <c r="R194" t="str">
         <v>[1,800]</v>
@@ -21505,7 +21553,7 @@
         <v>90007</v>
       </c>
       <c r="C195" t="str">
-        <v>【零号病毒】韩当-步兵 T3</v>
+        <v>【零号病毒】霍峻-步兵 T3</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -21514,7 +21562,7 @@
         <v>20</v>
       </c>
       <c r="F195">
-        <v>1264</v>
+        <v>1754</v>
       </c>
       <c r="G195">
         <v>5</v>
@@ -21526,13 +21574,13 @@
         <v>1</v>
       </c>
       <c r="J195">
-        <v>1294</v>
+        <v>1226</v>
       </c>
       <c r="K195">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L195">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="M195" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21544,10 +21592,10 @@
         <v>[]</v>
       </c>
       <c r="P195">
-        <v>321</v>
+        <v>516</v>
       </c>
       <c r="Q195">
-        <v>109</v>
+        <v>394</v>
       </c>
       <c r="R195" t="str">
         <v>[1,800]</v>
@@ -21615,7 +21663,7 @@
         <v>90008</v>
       </c>
       <c r="C196" t="str">
-        <v>【虚空母体】孙策-步兵 T4</v>
+        <v>【变异主宰】吕凯-步兵 T4</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -21624,7 +21672,7 @@
         <v>20</v>
       </c>
       <c r="F196">
-        <v>1567</v>
+        <v>2597</v>
       </c>
       <c r="G196">
         <v>6</v>
@@ -21636,13 +21684,13 @@
         <v>1</v>
       </c>
       <c r="J196">
-        <v>1413</v>
+        <v>1596</v>
       </c>
       <c r="K196">
         <v>38</v>
       </c>
       <c r="L196">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="M196" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21654,10 +21702,10 @@
         <v>[]</v>
       </c>
       <c r="P196">
-        <v>317</v>
+        <v>532</v>
       </c>
       <c r="Q196">
-        <v>97</v>
+        <v>383</v>
       </c>
       <c r="R196" t="str">
         <v>[1,800]</v>
@@ -21725,7 +21773,7 @@
         <v>90009</v>
       </c>
       <c r="C197" t="str">
-        <v>【虚空母体】文丑-步兵 T4</v>
+        <v>【虚空母体】潘凤-步兵 T4</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -21734,7 +21782,7 @@
         <v>20</v>
       </c>
       <c r="F197">
-        <v>1512</v>
+        <v>2845</v>
       </c>
       <c r="G197">
         <v>6</v>
@@ -21746,13 +21794,13 @@
         <v>1</v>
       </c>
       <c r="J197">
-        <v>1396</v>
+        <v>1534</v>
       </c>
       <c r="K197">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L197">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="M197" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21764,10 +21812,10 @@
         <v>[]</v>
       </c>
       <c r="P197">
-        <v>311</v>
+        <v>532</v>
       </c>
       <c r="Q197">
-        <v>99</v>
+        <v>429</v>
       </c>
       <c r="R197" t="str">
         <v>[1,800]</v>
@@ -21835,7 +21883,7 @@
         <v>90010</v>
       </c>
       <c r="C198" t="str">
-        <v>【虚空母体】祖茂-步兵 T4</v>
+        <v>【零号病毒】吕翔-步兵 T4</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -21844,7 +21892,7 @@
         <v>20</v>
       </c>
       <c r="F198">
-        <v>1393</v>
+        <v>2730</v>
       </c>
       <c r="G198">
         <v>6</v>
@@ -21856,13 +21904,13 @@
         <v>1</v>
       </c>
       <c r="J198">
-        <v>1256</v>
+        <v>1679</v>
       </c>
       <c r="K198">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L198">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="M198" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21874,10 +21922,10 @@
         <v>[]</v>
       </c>
       <c r="P198">
-        <v>312</v>
+        <v>517</v>
       </c>
       <c r="Q198">
-        <v>99</v>
+        <v>398</v>
       </c>
       <c r="R198" t="str">
         <v>[1,800]</v>
@@ -21945,7 +21993,7 @@
         <v>90011</v>
       </c>
       <c r="C199" t="str">
-        <v>【变异主宰】大乔-弓箭手 T1</v>
+        <v>【末日先兆】诸葛瑾-弓箭手 T1</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -21954,7 +22002,7 @@
         <v>20</v>
       </c>
       <c r="F199">
-        <v>504</v>
+        <v>706</v>
       </c>
       <c r="G199">
         <v>3</v>
@@ -21966,13 +22014,13 @@
         <v>1</v>
       </c>
       <c r="J199">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K199">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L199">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="M199" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21984,10 +22032,10 @@
         <v>[]</v>
       </c>
       <c r="P199">
-        <v>261</v>
+        <v>438</v>
       </c>
       <c r="Q199">
-        <v>2192</v>
+        <v>2380</v>
       </c>
       <c r="R199" t="str">
         <v>[1,800]</v>
@@ -22055,7 +22103,7 @@
         <v>90012</v>
       </c>
       <c r="C200" t="str">
-        <v>【虚空母体】沮授-弓箭手 T1</v>
+        <v>【零号病毒】戏志才-弓箭手 T1</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -22064,7 +22112,7 @@
         <v>20</v>
       </c>
       <c r="F200">
-        <v>543</v>
+        <v>750</v>
       </c>
       <c r="G200">
         <v>3</v>
@@ -22076,13 +22124,13 @@
         <v>1</v>
       </c>
       <c r="J200">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="K200">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L200">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="M200" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22094,10 +22142,10 @@
         <v>[]</v>
       </c>
       <c r="P200">
-        <v>251</v>
+        <v>430</v>
       </c>
       <c r="Q200">
-        <v>2144</v>
+        <v>2174</v>
       </c>
       <c r="R200" t="str">
         <v>[1,800]</v>
@@ -22165,7 +22213,7 @@
         <v>90013</v>
       </c>
       <c r="C201" t="str">
-        <v>【极秘项目】蔡文姬-弓箭手 T2</v>
+        <v>【极秘项目】辛宪英-弓箭手 T2</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -22174,7 +22222,7 @@
         <v>20</v>
       </c>
       <c r="F201">
-        <v>795</v>
+        <v>1197</v>
       </c>
       <c r="G201">
         <v>4</v>
@@ -22186,13 +22234,13 @@
         <v>1</v>
       </c>
       <c r="J201">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="K201">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L201">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="M201" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22204,10 +22252,10 @@
         <v>[]</v>
       </c>
       <c r="P201">
-        <v>256</v>
+        <v>437</v>
       </c>
       <c r="Q201">
-        <v>2392</v>
+        <v>2363</v>
       </c>
       <c r="R201" t="str">
         <v>[1,800]</v>
@@ -22275,7 +22323,7 @@
         <v>90014</v>
       </c>
       <c r="C202" t="str">
-        <v>【钢铁暴君】黄忠-弓箭手 T2</v>
+        <v>【极秘项目】满宠-弓箭手 T2</v>
       </c>
       <c r="D202">
         <v>1</v>
@@ -22284,7 +22332,7 @@
         <v>20</v>
       </c>
       <c r="F202">
-        <v>902</v>
+        <v>1372</v>
       </c>
       <c r="G202">
         <v>4</v>
@@ -22296,13 +22344,13 @@
         <v>1</v>
       </c>
       <c r="J202">
-        <v>330</v>
+        <v>430</v>
       </c>
       <c r="K202">
         <v>49</v>
       </c>
       <c r="L202">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M202" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22314,10 +22362,10 @@
         <v>[]</v>
       </c>
       <c r="P202">
-        <v>260</v>
+        <v>435</v>
       </c>
       <c r="Q202">
-        <v>1996</v>
+        <v>2255</v>
       </c>
       <c r="R202" t="str">
         <v>[1,800]</v>
@@ -22385,7 +22433,7 @@
         <v>90015</v>
       </c>
       <c r="C203" t="str">
-        <v>【虚空母体】贾诩-弓箭手 T2</v>
+        <v>【末日先兆】祝融-弓箭手 T2</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -22394,7 +22442,7 @@
         <v>20</v>
       </c>
       <c r="F203">
-        <v>722</v>
+        <v>1249</v>
       </c>
       <c r="G203">
         <v>4</v>
@@ -22406,13 +22454,13 @@
         <v>1</v>
       </c>
       <c r="J203">
-        <v>343</v>
+        <v>298</v>
       </c>
       <c r="K203">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L203">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="M203" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22424,10 +22472,10 @@
         <v>[]</v>
       </c>
       <c r="P203">
-        <v>252</v>
+        <v>428</v>
       </c>
       <c r="Q203">
-        <v>2110</v>
+        <v>2394</v>
       </c>
       <c r="R203" t="str">
         <v>[1,800]</v>
@@ -22495,7 +22543,7 @@
         <v>90016</v>
       </c>
       <c r="C204" t="str">
-        <v>【变异主宰】太史慈-弓箭手 T3</v>
+        <v>【末日先兆】贾诩-弓箭手 T3</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -22504,7 +22552,7 @@
         <v>20</v>
       </c>
       <c r="F204">
-        <v>1248</v>
+        <v>1480</v>
       </c>
       <c r="G204">
         <v>5</v>
@@ -22516,10 +22564,10 @@
         <v>1</v>
       </c>
       <c r="J204">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="K204">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L204">
         <v>1.73</v>
@@ -22534,10 +22582,10 @@
         <v>[]</v>
       </c>
       <c r="P204">
-        <v>255</v>
+        <v>412</v>
       </c>
       <c r="Q204">
-        <v>1991</v>
+        <v>2091</v>
       </c>
       <c r="R204" t="str">
         <v>[1,800]</v>
@@ -22605,7 +22653,7 @@
         <v>90017</v>
       </c>
       <c r="C205" t="str">
-        <v>【虚空母体】甄姬-弓箭手 T3</v>
+        <v>【零号病毒】甄姬-弓箭手 T3</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -22614,7 +22662,7 @@
         <v>20</v>
       </c>
       <c r="F205">
-        <v>1258</v>
+        <v>1630</v>
       </c>
       <c r="G205">
         <v>5</v>
@@ -22626,13 +22674,13 @@
         <v>1</v>
       </c>
       <c r="J205">
-        <v>480</v>
+        <v>388</v>
       </c>
       <c r="K205">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L205">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="M205" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22644,10 +22692,10 @@
         <v>[]</v>
       </c>
       <c r="P205">
-        <v>256</v>
+        <v>411</v>
       </c>
       <c r="Q205">
-        <v>2272</v>
+        <v>2106</v>
       </c>
       <c r="R205" t="str">
         <v>[1,800]</v>
@@ -22715,7 +22763,7 @@
         <v>90018</v>
       </c>
       <c r="C206" t="str">
-        <v>【零号病毒】周瑜-弓箭手 T4</v>
+        <v>【虚空母体】太史慈-弓箭手 T4</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -22724,7 +22772,7 @@
         <v>20</v>
       </c>
       <c r="F206">
-        <v>2078</v>
+        <v>2228</v>
       </c>
       <c r="G206">
         <v>6</v>
@@ -22736,13 +22784,13 @@
         <v>1</v>
       </c>
       <c r="J206">
-        <v>554</v>
+        <v>629</v>
       </c>
       <c r="K206">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="L206">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="M206" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22754,10 +22802,10 @@
         <v>[]</v>
       </c>
       <c r="P206">
-        <v>262</v>
+        <v>436</v>
       </c>
       <c r="Q206">
-        <v>2170</v>
+        <v>2212</v>
       </c>
       <c r="R206" t="str">
         <v>[1,800]</v>
@@ -22825,7 +22873,7 @@
         <v>90019</v>
       </c>
       <c r="C207" t="str">
-        <v>【末日先兆】审配-弓箭手 T4</v>
+        <v>【末日先兆】华歆-弓箭手 T4</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -22834,7 +22882,7 @@
         <v>20</v>
       </c>
       <c r="F207">
-        <v>1896</v>
+        <v>2826</v>
       </c>
       <c r="G207">
         <v>6</v>
@@ -22846,10 +22894,10 @@
         <v>1</v>
       </c>
       <c r="J207">
-        <v>655</v>
+        <v>590</v>
       </c>
       <c r="K207">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L207">
         <v>1.77</v>
@@ -22864,10 +22912,10 @@
         <v>[]</v>
       </c>
       <c r="P207">
-        <v>252</v>
+        <v>436</v>
       </c>
       <c r="Q207">
-        <v>2259</v>
+        <v>1999</v>
       </c>
       <c r="R207" t="str">
         <v>[1,800]</v>
@@ -22935,7 +22983,7 @@
         <v>90020</v>
       </c>
       <c r="C208" t="str">
-        <v>【钢铁暴君】邓芝-弓箭手 T4</v>
+        <v>【零号病毒】杨修-弓箭手 T4</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -22944,7 +22992,7 @@
         <v>20</v>
       </c>
       <c r="F208">
-        <v>1544</v>
+        <v>2586</v>
       </c>
       <c r="G208">
         <v>6</v>
@@ -22956,13 +23004,13 @@
         <v>1</v>
       </c>
       <c r="J208">
-        <v>617</v>
+        <v>700</v>
       </c>
       <c r="K208">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L208">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="M208" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22974,10 +23022,10 @@
         <v>[]</v>
       </c>
       <c r="P208">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="Q208">
-        <v>2222</v>
+        <v>2368</v>
       </c>
       <c r="R208" t="str">
         <v>[1,800]</v>
@@ -23045,7 +23093,7 @@
         <v>90021</v>
       </c>
       <c r="C209" t="str">
-        <v>【虚空母体】孙夏-骑兵 T1</v>
+        <v>【极秘项目】张辽-骑兵 T1</v>
       </c>
       <c r="D209">
         <v>2</v>
@@ -23054,7 +23102,7 @@
         <v>20</v>
       </c>
       <c r="F209">
-        <v>571</v>
+        <v>954</v>
       </c>
       <c r="G209">
         <v>3</v>
@@ -23066,13 +23114,13 @@
         <v>1</v>
       </c>
       <c r="J209">
-        <v>473</v>
+        <v>524</v>
       </c>
       <c r="K209">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L209">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="M209" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23084,10 +23132,10 @@
         <v>[]</v>
       </c>
       <c r="P209">
-        <v>372</v>
+        <v>607</v>
       </c>
       <c r="Q209">
-        <v>120</v>
+        <v>451</v>
       </c>
       <c r="R209" t="str">
         <v>[1,800]</v>
@@ -23155,7 +23203,7 @@
         <v>90022</v>
       </c>
       <c r="C210" t="str">
-        <v>【钢铁暴君】夏侯渊-骑兵 T1</v>
+        <v>【变异主宰】张济-骑兵 T1</v>
       </c>
       <c r="D210">
         <v>2</v>
@@ -23164,7 +23212,7 @@
         <v>20</v>
       </c>
       <c r="F210">
-        <v>472</v>
+        <v>911</v>
       </c>
       <c r="G210">
         <v>3</v>
@@ -23176,13 +23224,13 @@
         <v>1</v>
       </c>
       <c r="J210">
-        <v>398</v>
+        <v>576</v>
       </c>
       <c r="K210">
         <v>22</v>
       </c>
       <c r="L210">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="M210" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23194,10 +23242,10 @@
         <v>[]</v>
       </c>
       <c r="P210">
-        <v>374</v>
+        <v>633</v>
       </c>
       <c r="Q210">
-        <v>119</v>
+        <v>397</v>
       </c>
       <c r="R210" t="str">
         <v>[1,800]</v>
@@ -23265,7 +23313,7 @@
         <v>90023</v>
       </c>
       <c r="C211" t="str">
-        <v>【末日先兆】庞德-骑兵 T2</v>
+        <v>【零号病毒】侯选-骑兵 T2</v>
       </c>
       <c r="D211">
         <v>2</v>
@@ -23274,7 +23322,7 @@
         <v>20</v>
       </c>
       <c r="F211">
-        <v>940</v>
+        <v>1554</v>
       </c>
       <c r="G211">
         <v>4</v>
@@ -23286,13 +23334,13 @@
         <v>1</v>
       </c>
       <c r="J211">
-        <v>720</v>
+        <v>671</v>
       </c>
       <c r="K211">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L211">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="M211" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23304,10 +23352,10 @@
         <v>[]</v>
       </c>
       <c r="P211">
-        <v>372</v>
+        <v>610</v>
       </c>
       <c r="Q211">
-        <v>109</v>
+        <v>437</v>
       </c>
       <c r="R211" t="str">
         <v>[1,800]</v>
@@ -23375,7 +23423,7 @@
         <v>90024</v>
       </c>
       <c r="C212" t="str">
-        <v>【末日先兆】张横-骑兵 T2</v>
+        <v>【末日先兆】张宝-骑兵 T2</v>
       </c>
       <c r="D212">
         <v>2</v>
@@ -23384,7 +23432,7 @@
         <v>20</v>
       </c>
       <c r="F212">
-        <v>886</v>
+        <v>1472</v>
       </c>
       <c r="G212">
         <v>4</v>
@@ -23396,13 +23444,13 @@
         <v>1</v>
       </c>
       <c r="J212">
-        <v>726</v>
+        <v>647</v>
       </c>
       <c r="K212">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L212">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="M212" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23414,10 +23462,10 @@
         <v>[]</v>
       </c>
       <c r="P212">
-        <v>371</v>
+        <v>607</v>
       </c>
       <c r="Q212">
-        <v>126</v>
+        <v>410</v>
       </c>
       <c r="R212" t="str">
         <v>[1,800]</v>
@@ -23485,7 +23533,7 @@
         <v>90025</v>
       </c>
       <c r="C213" t="str">
-        <v>【虚空母体】曹纯-骑兵 T3</v>
+        <v>【虚空母体】孙尚香-骑兵 T3</v>
       </c>
       <c r="D213">
         <v>2</v>
@@ -23494,7 +23542,7 @@
         <v>20</v>
       </c>
       <c r="F213">
-        <v>1541</v>
+        <v>2356</v>
       </c>
       <c r="G213">
         <v>5</v>
@@ -23506,13 +23554,13 @@
         <v>1</v>
       </c>
       <c r="J213">
-        <v>1140</v>
+        <v>1021</v>
       </c>
       <c r="K213">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L213">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="M213" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23524,10 +23572,10 @@
         <v>[]</v>
       </c>
       <c r="P213">
-        <v>378</v>
+        <v>607</v>
       </c>
       <c r="Q213">
-        <v>116</v>
+        <v>417</v>
       </c>
       <c r="R213" t="str">
         <v>[1,800]</v>
@@ -23595,7 +23643,7 @@
         <v>90026</v>
       </c>
       <c r="C214" t="str">
-        <v>【钢铁暴君】苏仆延-骑兵 T3</v>
+        <v>【末日先兆】高升-骑兵 T3</v>
       </c>
       <c r="D214">
         <v>2</v>
@@ -23604,7 +23652,7 @@
         <v>20</v>
       </c>
       <c r="F214">
-        <v>1264</v>
+        <v>2597</v>
       </c>
       <c r="G214">
         <v>5</v>
@@ -23616,13 +23664,13 @@
         <v>1</v>
       </c>
       <c r="J214">
-        <v>840</v>
+        <v>1071</v>
       </c>
       <c r="K214">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L214">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="M214" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23634,10 +23682,10 @@
         <v>[]</v>
       </c>
       <c r="P214">
-        <v>374</v>
+        <v>602</v>
       </c>
       <c r="Q214">
-        <v>109</v>
+        <v>452</v>
       </c>
       <c r="R214" t="str">
         <v>[1,800]</v>
@@ -23705,7 +23753,7 @@
         <v>90027</v>
       </c>
       <c r="C215" t="str">
-        <v>【变异主宰】韩忠-骑兵 T4</v>
+        <v>【零号病毒】张角-骑兵 T4</v>
       </c>
       <c r="D215">
         <v>2</v>
@@ -23714,7 +23762,7 @@
         <v>20</v>
       </c>
       <c r="F215">
-        <v>1837</v>
+        <v>3380</v>
       </c>
       <c r="G215">
         <v>6</v>
@@ -23726,13 +23774,13 @@
         <v>1</v>
       </c>
       <c r="J215">
-        <v>1118</v>
+        <v>1390</v>
       </c>
       <c r="K215">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="L215">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="M215" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23744,10 +23792,10 @@
         <v>[]</v>
       </c>
       <c r="P215">
-        <v>361</v>
+        <v>605</v>
       </c>
       <c r="Q215">
-        <v>115</v>
+        <v>417</v>
       </c>
       <c r="R215" t="str">
         <v>[1,800]</v>
@@ -23815,7 +23863,7 @@
         <v>90028</v>
       </c>
       <c r="C216" t="str">
-        <v>【极秘项目】凌统-骑兵 T4</v>
+        <v>【末日先兆】赵弘-骑兵 T4</v>
       </c>
       <c r="D216">
         <v>2</v>
@@ -23824,7 +23872,7 @@
         <v>20</v>
       </c>
       <c r="F216">
-        <v>1953</v>
+        <v>3149</v>
       </c>
       <c r="G216">
         <v>6</v>
@@ -23836,13 +23884,13 @@
         <v>1</v>
       </c>
       <c r="J216">
-        <v>1194</v>
+        <v>1023</v>
       </c>
       <c r="K216">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L216">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="M216" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23854,10 +23902,10 @@
         <v>[]</v>
       </c>
       <c r="P216">
-        <v>381</v>
+        <v>603</v>
       </c>
       <c r="Q216">
-        <v>125</v>
+        <v>415</v>
       </c>
       <c r="R216" t="str">
         <v>[1,800]</v>
@@ -23925,7 +23973,7 @@
         <v>90029</v>
       </c>
       <c r="C217" t="str">
-        <v>【钢铁暴君】刘贤-长枪兵 T1</v>
+        <v>【虚空母体】胡遵-长枪兵 T1</v>
       </c>
       <c r="D217">
         <v>3</v>
@@ -23934,7 +23982,7 @@
         <v>20</v>
       </c>
       <c r="F217">
-        <v>557</v>
+        <v>974</v>
       </c>
       <c r="G217">
         <v>3</v>
@@ -23946,13 +23994,13 @@
         <v>1</v>
       </c>
       <c r="J217">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K217">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L217">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="M217" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23964,10 +24012,10 @@
         <v>[]</v>
       </c>
       <c r="P217">
-        <v>287</v>
+        <v>484</v>
       </c>
       <c r="Q217">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="R217" t="str">
         <v>[1,800]</v>
@@ -24035,7 +24083,7 @@
         <v>90030</v>
       </c>
       <c r="C218" t="str">
-        <v>【变异主宰】陈应-长枪兵 T2</v>
+        <v>【变异主宰】朱然-长枪兵 T2</v>
       </c>
       <c r="D218">
         <v>3</v>
@@ -24044,7 +24092,7 @@
         <v>20</v>
       </c>
       <c r="F218">
-        <v>921</v>
+        <v>1583</v>
       </c>
       <c r="G218">
         <v>4</v>
@@ -24056,13 +24104,13 @@
         <v>1</v>
       </c>
       <c r="J218">
-        <v>583</v>
+        <v>527</v>
       </c>
       <c r="K218">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L218">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="M218" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24074,10 +24122,10 @@
         <v>[]</v>
       </c>
       <c r="P218">
-        <v>288</v>
+        <v>460</v>
       </c>
       <c r="Q218">
-        <v>158</v>
+        <v>412</v>
       </c>
       <c r="R218" t="str">
         <v>[1,800]</v>
@@ -24145,7 +24193,7 @@
         <v>90031</v>
       </c>
       <c r="C219" t="str">
-        <v>【极秘项目】马谡-长枪兵 T2</v>
+        <v>【钢铁暴君】潘璋-长枪兵 T2</v>
       </c>
       <c r="D219">
         <v>3</v>
@@ -24154,7 +24202,7 @@
         <v>20</v>
       </c>
       <c r="F219">
-        <v>912</v>
+        <v>1901</v>
       </c>
       <c r="G219">
         <v>4</v>
@@ -24166,13 +24214,13 @@
         <v>1</v>
       </c>
       <c r="J219">
-        <v>514</v>
+        <v>696</v>
       </c>
       <c r="K219">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L219">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="M219" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24184,10 +24232,10 @@
         <v>[]</v>
       </c>
       <c r="P219">
-        <v>278</v>
+        <v>488</v>
       </c>
       <c r="Q219">
-        <v>162</v>
+        <v>468</v>
       </c>
       <c r="R219" t="str">
         <v>[1,800]</v>
@@ -24255,7 +24303,7 @@
         <v>90032</v>
       </c>
       <c r="C220" t="str">
-        <v>【变异主宰】卓膺-长枪兵 T3</v>
+        <v>【虚空母体】邓贤-长枪兵 T3</v>
       </c>
       <c r="D220">
         <v>3</v>
@@ -24264,7 +24312,7 @@
         <v>20</v>
       </c>
       <c r="F220">
-        <v>1527</v>
+        <v>2538</v>
       </c>
       <c r="G220">
         <v>5</v>
@@ -24276,13 +24324,13 @@
         <v>1</v>
       </c>
       <c r="J220">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="K220">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L220">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="M220" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24294,10 +24342,10 @@
         <v>[]</v>
       </c>
       <c r="P220">
-        <v>282</v>
+        <v>468</v>
       </c>
       <c r="Q220">
-        <v>153</v>
+        <v>494</v>
       </c>
       <c r="R220" t="str">
         <v>[1,800]</v>
@@ -24365,7 +24413,7 @@
         <v>90033</v>
       </c>
       <c r="C221" t="str">
-        <v>【零号病毒】柳隐-长枪兵 T4</v>
+        <v>【变异主宰】费诗-长枪兵 T4</v>
       </c>
       <c r="D221">
         <v>3</v>
@@ -24374,7 +24422,7 @@
         <v>20</v>
       </c>
       <c r="F221">
-        <v>1787</v>
+        <v>3425</v>
       </c>
       <c r="G221">
         <v>6</v>
@@ -24386,13 +24434,13 @@
         <v>1</v>
       </c>
       <c r="J221">
-        <v>860</v>
+        <v>930</v>
       </c>
       <c r="K221">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L221">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="M221" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24404,10 +24452,10 @@
         <v>[]</v>
       </c>
       <c r="P221">
-        <v>283</v>
+        <v>477</v>
       </c>
       <c r="Q221">
-        <v>144</v>
+        <v>419</v>
       </c>
       <c r="R221" t="str">
         <v>[1,800]</v>
@@ -24475,7 +24523,7 @@
         <v>90034</v>
       </c>
       <c r="C222" t="str">
-        <v>【零号病毒】高顺-长枪兵 T4</v>
+        <v>【钢铁暴君】盛曼-长枪兵 T4</v>
       </c>
       <c r="D222">
         <v>3</v>
@@ -24484,7 +24532,7 @@
         <v>20</v>
       </c>
       <c r="F222">
-        <v>1797</v>
+        <v>3803</v>
       </c>
       <c r="G222">
         <v>6</v>
@@ -24496,13 +24544,13 @@
         <v>1</v>
       </c>
       <c r="J222">
-        <v>915</v>
+        <v>1182</v>
       </c>
       <c r="K222">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L222">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="M222" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24514,10 +24562,10 @@
         <v>[]</v>
       </c>
       <c r="P222">
-        <v>284</v>
+        <v>477</v>
       </c>
       <c r="Q222">
-        <v>139</v>
+        <v>447</v>
       </c>
       <c r="R222" t="str">
         <v>[1,800]</v>
@@ -24585,7 +24633,7 @@
         <v>90035</v>
       </c>
       <c r="C223" t="str">
-        <v>【虚空母体】诸葛瑾-法师 T1</v>
+        <v>【零号病毒】邓芝-法师 T1</v>
       </c>
       <c r="D223">
         <v>4</v>
@@ -24594,7 +24642,7 @@
         <v>20</v>
       </c>
       <c r="F223">
-        <v>413</v>
+        <v>654</v>
       </c>
       <c r="G223">
         <v>3</v>
@@ -24606,13 +24654,13 @@
         <v>1</v>
       </c>
       <c r="J223">
-        <v>240</v>
+        <v>281</v>
       </c>
       <c r="K223">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L223">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="M223" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24624,10 +24672,10 @@
         <v>[]</v>
       </c>
       <c r="P223">
-        <v>211</v>
+        <v>379</v>
       </c>
       <c r="Q223">
-        <v>1948</v>
+        <v>2188</v>
       </c>
       <c r="R223" t="str">
         <v>[1,800]</v>
@@ -24695,7 +24743,7 @@
         <v>90036</v>
       </c>
       <c r="C224" t="str">
-        <v>【虚空母体】蒯良-法师 T2</v>
+        <v>【虚空母体】伊籍-法师 T2</v>
       </c>
       <c r="D224">
         <v>4</v>
@@ -24704,7 +24752,7 @@
         <v>20</v>
       </c>
       <c r="F224">
-        <v>841</v>
+        <v>1081</v>
       </c>
       <c r="G224">
         <v>4</v>
@@ -24716,13 +24764,13 @@
         <v>1</v>
       </c>
       <c r="J224">
-        <v>403</v>
+        <v>468</v>
       </c>
       <c r="K224">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="L224">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="M224" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24734,10 +24782,10 @@
         <v>[]</v>
       </c>
       <c r="P224">
-        <v>212</v>
+        <v>373</v>
       </c>
       <c r="Q224">
-        <v>1923</v>
+        <v>2096</v>
       </c>
       <c r="R224" t="str">
         <v>[1,800]</v>
@@ -24805,7 +24853,7 @@
         <v>90037</v>
       </c>
       <c r="C225" t="str">
-        <v>【虚空母体】管辂-法师 T2</v>
+        <v>【零号病毒】张温-法师 T2</v>
       </c>
       <c r="D225">
         <v>4</v>
@@ -24814,7 +24862,7 @@
         <v>20</v>
       </c>
       <c r="F225">
-        <v>834</v>
+        <v>1010</v>
       </c>
       <c r="G225">
         <v>4</v>
@@ -24826,13 +24874,13 @@
         <v>1</v>
       </c>
       <c r="J225">
-        <v>437</v>
+        <v>346</v>
       </c>
       <c r="K225">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L225">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="M225" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24844,10 +24892,10 @@
         <v>[]</v>
       </c>
       <c r="P225">
-        <v>213</v>
+        <v>356</v>
       </c>
       <c r="Q225">
-        <v>1919</v>
+        <v>1873</v>
       </c>
       <c r="R225" t="str">
         <v>[1,800]</v>
@@ -24915,7 +24963,7 @@
         <v>90038</v>
       </c>
       <c r="C226" t="str">
-        <v>【极秘项目】蒯良-2-法师 T3</v>
+        <v>【极秘项目】郭嘉-2-法师 T3</v>
       </c>
       <c r="D226">
         <v>4</v>
@@ -24924,7 +24972,7 @@
         <v>20</v>
       </c>
       <c r="F226">
-        <v>1278</v>
+        <v>1608</v>
       </c>
       <c r="G226">
         <v>5</v>
@@ -24936,13 +24984,13 @@
         <v>1</v>
       </c>
       <c r="J226">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="K226">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="L226">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M226" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24954,10 +25002,10 @@
         <v>[]</v>
       </c>
       <c r="P226">
-        <v>208</v>
+        <v>364</v>
       </c>
       <c r="Q226">
-        <v>1934</v>
+        <v>2061</v>
       </c>
       <c r="R226" t="str">
         <v>[1,800]</v>
@@ -25025,7 +25073,7 @@
         <v>90039</v>
       </c>
       <c r="C227" t="str">
-        <v>【变异主宰】辛宪英-2-法师 T4</v>
+        <v>【极秘项目】郑玄-2-法师 T4</v>
       </c>
       <c r="D227">
         <v>4</v>
@@ -25034,7 +25082,7 @@
         <v>20</v>
       </c>
       <c r="F227">
-        <v>1667</v>
+        <v>1964</v>
       </c>
       <c r="G227">
         <v>6</v>
@@ -25046,13 +25094,13 @@
         <v>1</v>
       </c>
       <c r="J227">
-        <v>814</v>
+        <v>671</v>
       </c>
       <c r="K227">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="L227">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="M227" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25064,10 +25112,10 @@
         <v>[]</v>
       </c>
       <c r="P227">
-        <v>213</v>
+        <v>371</v>
       </c>
       <c r="Q227">
-        <v>2137</v>
+        <v>2101</v>
       </c>
       <c r="R227" t="str">
         <v>[1,800]</v>
@@ -25135,7 +25183,7 @@
         <v>90040</v>
       </c>
       <c r="C228" t="str">
-        <v>【零号病毒】甄姬-2-法师 T4</v>
+        <v>【末日先兆】田丰-2-法师 T4</v>
       </c>
       <c r="D228">
         <v>4</v>
@@ -25144,7 +25192,7 @@
         <v>20</v>
       </c>
       <c r="F228">
-        <v>1395</v>
+        <v>2000</v>
       </c>
       <c r="G228">
         <v>6</v>
@@ -25156,13 +25204,13 @@
         <v>1</v>
       </c>
       <c r="J228">
-        <v>575</v>
+        <v>666</v>
       </c>
       <c r="K228">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="L228">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="M228" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25174,10 +25222,10 @@
         <v>[]</v>
       </c>
       <c r="P228">
-        <v>227</v>
+        <v>363</v>
       </c>
       <c r="Q228">
-        <v>1837</v>
+        <v>2047</v>
       </c>
       <c r="R228" t="str">
         <v>[1,800]</v>

--- a/public/ArmyTable.xlsx
+++ b/public/ArmyTable.xlsx
@@ -797,7 +797,7 @@
         <v>10001</v>
       </c>
       <c r="C5" t="str">
-        <v>傅彤-步兵 T1</v>
+        <v>程普-步兵 T1</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -818,13 +818,13 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="M5" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -836,10 +836,10 @@
         <v>[]</v>
       </c>
       <c r="P5">
-        <v>523</v>
+        <v>206</v>
       </c>
       <c r="Q5">
-        <v>398</v>
+        <v>184</v>
       </c>
       <c r="R5" t="str">
         <v>[1,800]</v>
@@ -907,7 +907,7 @@
         <v>10002</v>
       </c>
       <c r="C6" t="str">
-        <v>朱桓-步兵 T1</v>
+        <v>王威-步兵 T1</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="M6" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -946,10 +946,10 @@
         <v>[]</v>
       </c>
       <c r="P6">
-        <v>522</v>
+        <v>210</v>
       </c>
       <c r="Q6">
-        <v>378</v>
+        <v>206</v>
       </c>
       <c r="R6" t="str">
         <v>[1,800]</v>
@@ -1017,7 +1017,7 @@
         <v>10003</v>
       </c>
       <c r="C7" t="str">
-        <v>蒋舒-步兵 T1</v>
+        <v>马忠-步兵 T1</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1038,13 +1038,13 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="M7" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1056,10 +1056,10 @@
         <v>[]</v>
       </c>
       <c r="P7">
-        <v>516</v>
+        <v>207</v>
       </c>
       <c r="Q7">
-        <v>415</v>
+        <v>197</v>
       </c>
       <c r="R7" t="str">
         <v>[1,800]</v>
@@ -1127,7 +1127,7 @@
         <v>10004</v>
       </c>
       <c r="C8" t="str">
-        <v>周泰-步兵 T1</v>
+        <v>文丑-步兵 T1</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1148,13 +1148,13 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="K8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="M8" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1166,10 +1166,10 @@
         <v>[]</v>
       </c>
       <c r="P8">
-        <v>539</v>
+        <v>209</v>
       </c>
       <c r="Q8">
-        <v>364</v>
+        <v>182</v>
       </c>
       <c r="R8" t="str">
         <v>[1,800]</v>
@@ -1237,7 +1237,7 @@
         <v>10005</v>
       </c>
       <c r="C9" t="str">
-        <v>程普-步兵 T1</v>
+        <v>麴义-步兵 T1</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -1258,13 +1258,13 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="K9">
         <v>10</v>
       </c>
       <c r="L9">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="M9" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1276,10 +1276,10 @@
         <v>[]</v>
       </c>
       <c r="P9">
-        <v>525</v>
+        <v>214</v>
       </c>
       <c r="Q9">
-        <v>418</v>
+        <v>198</v>
       </c>
       <c r="R9" t="str">
         <v>[1,800]</v>
@@ -1347,7 +1347,7 @@
         <v>10006</v>
       </c>
       <c r="C10" t="str">
-        <v>关兴-步兵 T1</v>
+        <v>高览-步兵 T1</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -1368,13 +1368,13 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="K10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="M10" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1386,10 +1386,10 @@
         <v>[]</v>
       </c>
       <c r="P10">
-        <v>538</v>
+        <v>208</v>
       </c>
       <c r="Q10">
-        <v>431</v>
+        <v>193</v>
       </c>
       <c r="R10" t="str">
         <v>[1,800]</v>
@@ -1457,7 +1457,7 @@
         <v>10007</v>
       </c>
       <c r="C11" t="str">
-        <v>乐进-步兵 T1</v>
+        <v>马延-步兵 T1</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>197</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -1478,13 +1478,13 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="K11">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="M11" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1496,10 +1496,10 @@
         <v>[]</v>
       </c>
       <c r="P11">
-        <v>522</v>
+        <v>209</v>
       </c>
       <c r="Q11">
-        <v>402</v>
+        <v>204</v>
       </c>
       <c r="R11" t="str">
         <v>[1,800]</v>
@@ -1567,7 +1567,7 @@
         <v>10008</v>
       </c>
       <c r="C12" t="str">
-        <v>苏由-步兵 T1</v>
+        <v>曹操-步兵 T1</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1576,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -1588,13 +1588,13 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="K12">
         <v>7</v>
       </c>
       <c r="L12">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="M12" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1606,10 +1606,10 @@
         <v>[]</v>
       </c>
       <c r="P12">
-        <v>539</v>
+        <v>214</v>
       </c>
       <c r="Q12">
-        <v>381</v>
+        <v>197</v>
       </c>
       <c r="R12" t="str">
         <v>[1,800]</v>
@@ -1677,7 +1677,7 @@
         <v>10009</v>
       </c>
       <c r="C13" t="str">
-        <v>高干-步兵 T1</v>
+        <v>周仓-步兵 T1</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -1698,13 +1698,13 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="M13" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1716,10 +1716,10 @@
         <v>[]</v>
       </c>
       <c r="P13">
-        <v>537</v>
+        <v>209</v>
       </c>
       <c r="Q13">
-        <v>398</v>
+        <v>186</v>
       </c>
       <c r="R13" t="str">
         <v>[1,800]</v>
@@ -1787,7 +1787,7 @@
         <v>10010</v>
       </c>
       <c r="C14" t="str">
-        <v>张翼-步兵 T1</v>
+        <v>廖化-步兵 T1</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -1808,13 +1808,13 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K14">
         <v>9</v>
       </c>
       <c r="L14">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="M14" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1826,10 +1826,10 @@
         <v>[]</v>
       </c>
       <c r="P14">
-        <v>536</v>
+        <v>204</v>
       </c>
       <c r="Q14">
-        <v>393</v>
+        <v>181</v>
       </c>
       <c r="R14" t="str">
         <v>[1,800]</v>
@@ -1897,7 +1897,7 @@
         <v>10011</v>
       </c>
       <c r="C15" t="str">
-        <v>高览-步兵 T2</v>
+        <v>韩当-步兵 T2</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>325</v>
+        <v>140</v>
       </c>
       <c r="G15">
         <v>4</v>
@@ -1918,13 +1918,13 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="K15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L15">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="M15" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -1936,10 +1936,10 @@
         <v>[]</v>
       </c>
       <c r="P15">
-        <v>514</v>
+        <v>206</v>
       </c>
       <c r="Q15">
-        <v>427</v>
+        <v>196</v>
       </c>
       <c r="R15" t="str">
         <v>[1,800]</v>
@@ -2007,7 +2007,7 @@
         <v>10012</v>
       </c>
       <c r="C16" t="str">
-        <v>丁奉-步兵 T2</v>
+        <v>吕旷-步兵 T2</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -2016,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>306</v>
+        <v>122</v>
       </c>
       <c r="G16">
         <v>4</v>
@@ -2028,13 +2028,13 @@
         <v>1</v>
       </c>
       <c r="J16">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="K16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L16">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="M16" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2046,10 +2046,10 @@
         <v>[]</v>
       </c>
       <c r="P16">
-        <v>538</v>
+        <v>206</v>
       </c>
       <c r="Q16">
-        <v>437</v>
+        <v>190</v>
       </c>
       <c r="R16" t="str">
         <v>[1,800]</v>
@@ -2117,7 +2117,7 @@
         <v>10013</v>
       </c>
       <c r="C17" t="str">
-        <v>华雄-步兵 T2</v>
+        <v>吕凯-步兵 T2</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2126,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>284</v>
+        <v>128</v>
       </c>
       <c r="G17">
         <v>4</v>
@@ -2138,13 +2138,13 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="K17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L17">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="M17" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2156,10 +2156,10 @@
         <v>[]</v>
       </c>
       <c r="P17">
-        <v>527</v>
+        <v>216</v>
       </c>
       <c r="Q17">
-        <v>412</v>
+        <v>204</v>
       </c>
       <c r="R17" t="str">
         <v>[1,800]</v>
@@ -2227,7 +2227,7 @@
         <v>10014</v>
       </c>
       <c r="C18" t="str">
-        <v>麴义-步兵 T2</v>
+        <v>关羽-步兵 T2</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="G18">
         <v>4</v>
@@ -2248,13 +2248,13 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="K18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L18">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="M18" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2266,10 +2266,10 @@
         <v>[]</v>
       </c>
       <c r="P18">
-        <v>523</v>
+        <v>205</v>
       </c>
       <c r="Q18">
-        <v>390</v>
+        <v>189</v>
       </c>
       <c r="R18" t="str">
         <v>[1,800]</v>
@@ -2337,7 +2337,7 @@
         <v>10015</v>
       </c>
       <c r="C19" t="str">
-        <v>管亥-步兵 T2</v>
+        <v>张允-步兵 T2</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -2346,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>337</v>
+        <v>148</v>
       </c>
       <c r="G19">
         <v>4</v>
@@ -2358,13 +2358,13 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="K19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L19">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
       <c r="M19" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2376,10 +2376,10 @@
         <v>[]</v>
       </c>
       <c r="P19">
-        <v>531</v>
+        <v>208</v>
       </c>
       <c r="Q19">
-        <v>413</v>
+        <v>188</v>
       </c>
       <c r="R19" t="str">
         <v>[1,800]</v>
@@ -2447,7 +2447,7 @@
         <v>10016</v>
       </c>
       <c r="C20" t="str">
-        <v>颜良-步兵 T2</v>
+        <v>甘宁-步兵 T2</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2456,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>354</v>
+        <v>120</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -2468,13 +2468,13 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>257</v>
+        <v>192</v>
       </c>
       <c r="K20">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L20">
-        <v>1.09</v>
+        <v>0.91</v>
       </c>
       <c r="M20" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2486,10 +2486,10 @@
         <v>[]</v>
       </c>
       <c r="P20">
-        <v>511</v>
+        <v>213</v>
       </c>
       <c r="Q20">
-        <v>438</v>
+        <v>209</v>
       </c>
       <c r="R20" t="str">
         <v>[1,800]</v>
@@ -2557,7 +2557,7 @@
         <v>10017</v>
       </c>
       <c r="C21" t="str">
-        <v>胡车儿-步兵 T2</v>
+        <v>乐进-步兵 T2</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>299</v>
+        <v>127</v>
       </c>
       <c r="G21">
         <v>4</v>
@@ -2578,13 +2578,13 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="K21">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L21">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2596,10 +2596,10 @@
         <v>[]</v>
       </c>
       <c r="P21">
-        <v>514</v>
+        <v>209</v>
       </c>
       <c r="Q21">
-        <v>415</v>
+        <v>218</v>
       </c>
       <c r="R21" t="str">
         <v>[1,800]</v>
@@ -2667,7 +2667,7 @@
         <v>10018</v>
       </c>
       <c r="C22" t="str">
-        <v>韩猛-步兵 T2</v>
+        <v>曹真-步兵 T2</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>298</v>
+        <v>141</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -2688,13 +2688,13 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="K22">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L22">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="M22" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2706,10 +2706,10 @@
         <v>[]</v>
       </c>
       <c r="P22">
-        <v>520</v>
+        <v>214</v>
       </c>
       <c r="Q22">
-        <v>365</v>
+        <v>207</v>
       </c>
       <c r="R22" t="str">
         <v>[1,800]</v>
@@ -2777,7 +2777,7 @@
         <v>10019</v>
       </c>
       <c r="C23" t="str">
-        <v>徐盛-步兵 T2</v>
+        <v>焦触-步兵 T2</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2786,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>262</v>
+        <v>121</v>
       </c>
       <c r="G23">
         <v>4</v>
@@ -2798,13 +2798,13 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="K23">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L23">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="M23" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2816,10 +2816,10 @@
         <v>[]</v>
       </c>
       <c r="P23">
-        <v>520</v>
+        <v>209</v>
       </c>
       <c r="Q23">
-        <v>373</v>
+        <v>182</v>
       </c>
       <c r="R23" t="str">
         <v>[1,800]</v>
@@ -2887,7 +2887,7 @@
         <v>10020</v>
       </c>
       <c r="C24" t="str">
-        <v>张南-步兵 T2</v>
+        <v>潘凤-步兵 T2</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>258</v>
+        <v>124</v>
       </c>
       <c r="G24">
         <v>4</v>
@@ -2908,13 +2908,13 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L24">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="M24" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -2926,10 +2926,10 @@
         <v>[]</v>
       </c>
       <c r="P24">
-        <v>529</v>
+        <v>211</v>
       </c>
       <c r="Q24">
-        <v>388</v>
+        <v>204</v>
       </c>
       <c r="R24" t="str">
         <v>[1,800]</v>
@@ -2997,7 +2997,7 @@
         <v>10021</v>
       </c>
       <c r="C25" t="str">
-        <v>严白虎-步兵 T3</v>
+        <v>王颀-步兵 T3</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>434</v>
+        <v>230</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -3018,13 +3018,13 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>279</v>
+        <v>340</v>
       </c>
       <c r="K25">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L25">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="M25" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3036,10 +3036,10 @@
         <v>[]</v>
       </c>
       <c r="P25">
-        <v>520</v>
+        <v>207</v>
       </c>
       <c r="Q25">
-        <v>411</v>
+        <v>206</v>
       </c>
       <c r="R25" t="str">
         <v>[1,800]</v>
@@ -3107,7 +3107,7 @@
         <v>10022</v>
       </c>
       <c r="C26" t="str">
-        <v>张允-步兵 T3</v>
+        <v>曹洪-步兵 T3</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -3116,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>494</v>
+        <v>188</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -3128,13 +3128,13 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="K26">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L26">
-        <v>0.98</v>
+        <v>1.09</v>
       </c>
       <c r="M26" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3146,10 +3146,10 @@
         <v>[]</v>
       </c>
       <c r="P26">
-        <v>520</v>
+        <v>212</v>
       </c>
       <c r="Q26">
-        <v>427</v>
+        <v>197</v>
       </c>
       <c r="R26" t="str">
         <v>[1,800]</v>
@@ -3217,7 +3217,7 @@
         <v>10023</v>
       </c>
       <c r="C27" t="str">
-        <v>臧霸-步兵 T3</v>
+        <v>吕翔-步兵 T3</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>454</v>
+        <v>198</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -3238,13 +3238,13 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="K27">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L27">
-        <v>0.92</v>
+        <v>1.05</v>
       </c>
       <c r="M27" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3256,10 +3256,10 @@
         <v>[]</v>
       </c>
       <c r="P27">
-        <v>529</v>
+        <v>204</v>
       </c>
       <c r="Q27">
-        <v>433</v>
+        <v>219</v>
       </c>
       <c r="R27" t="str">
         <v>[1,800]</v>
@@ -3327,7 +3327,7 @@
         <v>10024</v>
       </c>
       <c r="C28" t="str">
-        <v>刘封-步兵 T3</v>
+        <v>淳于琼-步兵 T3</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>457</v>
+        <v>208</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -3348,13 +3348,13 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="K28">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L28">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="M28" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3366,10 +3366,10 @@
         <v>[]</v>
       </c>
       <c r="P28">
-        <v>538</v>
+        <v>209</v>
       </c>
       <c r="Q28">
-        <v>409</v>
+        <v>214</v>
       </c>
       <c r="R28" t="str">
         <v>[1,800]</v>
@@ -3437,7 +3437,7 @@
         <v>10025</v>
       </c>
       <c r="C29" t="str">
-        <v>祖茂-步兵 T3</v>
+        <v>胡车儿-步兵 T3</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -3446,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>534</v>
+        <v>216</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -3458,10 +3458,10 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="K29">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L29">
         <v>0.91</v>
@@ -3476,10 +3476,10 @@
         <v>[]</v>
       </c>
       <c r="P29">
-        <v>539</v>
+        <v>208</v>
       </c>
       <c r="Q29">
-        <v>418</v>
+        <v>202</v>
       </c>
       <c r="R29" t="str">
         <v>[1,800]</v>
@@ -3547,7 +3547,7 @@
         <v>10026</v>
       </c>
       <c r="C30" t="str">
-        <v>焦触-步兵 T3</v>
+        <v>向宠-步兵 T3</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -3556,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>352</v>
+        <v>185</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3568,13 +3568,13 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="K30">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L30">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="M30" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3586,10 +3586,10 @@
         <v>[]</v>
       </c>
       <c r="P30">
-        <v>517</v>
+        <v>208</v>
       </c>
       <c r="Q30">
-        <v>382</v>
+        <v>202</v>
       </c>
       <c r="R30" t="str">
         <v>[1,800]</v>
@@ -3657,7 +3657,7 @@
         <v>10027</v>
       </c>
       <c r="C31" t="str">
-        <v>郭援-步兵 T3</v>
+        <v>丁奉-步兵 T3</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -3666,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>438</v>
+        <v>191</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -3678,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="J31">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="K31">
         <v>16</v>
@@ -3696,10 +3696,10 @@
         <v>[]</v>
       </c>
       <c r="P31">
-        <v>520</v>
+        <v>216</v>
       </c>
       <c r="Q31">
-        <v>435</v>
+        <v>187</v>
       </c>
       <c r="R31" t="str">
         <v>[1,800]</v>
@@ -3767,7 +3767,7 @@
         <v>10028</v>
       </c>
       <c r="C32" t="str">
-        <v>王威-步兵 T3</v>
+        <v>韩猛-步兵 T3</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>431</v>
+        <v>181</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -3788,7 +3788,7 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>357</v>
+        <v>272</v>
       </c>
       <c r="K32">
         <v>15</v>
@@ -3806,10 +3806,10 @@
         <v>[]</v>
       </c>
       <c r="P32">
-        <v>514</v>
+        <v>210</v>
       </c>
       <c r="Q32">
-        <v>387</v>
+        <v>211</v>
       </c>
       <c r="R32" t="str">
         <v>[1,800]</v>
@@ -3877,7 +3877,7 @@
         <v>10029</v>
       </c>
       <c r="C33" t="str">
-        <v>关平-步兵 T3</v>
+        <v>傅彤-步兵 T3</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -3886,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>499</v>
+        <v>206</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -3898,13 +3898,13 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>341</v>
+        <v>302</v>
       </c>
       <c r="K33">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L33">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="M33" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -3916,10 +3916,10 @@
         <v>[]</v>
       </c>
       <c r="P33">
-        <v>537</v>
+        <v>208</v>
       </c>
       <c r="Q33">
-        <v>370</v>
+        <v>201</v>
       </c>
       <c r="R33" t="str">
         <v>[1,800]</v>
@@ -3987,7 +3987,7 @@
         <v>10030</v>
       </c>
       <c r="C34" t="str">
-        <v>裴元绍-步兵 T3</v>
+        <v>苏由-步兵 T3</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -3996,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>476</v>
+        <v>199</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -4008,13 +4008,13 @@
         <v>1</v>
       </c>
       <c r="J34">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="K34">
         <v>17</v>
       </c>
       <c r="L34">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="M34" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4026,10 +4026,10 @@
         <v>[]</v>
       </c>
       <c r="P34">
-        <v>513</v>
+        <v>210</v>
       </c>
       <c r="Q34">
-        <v>411</v>
+        <v>181</v>
       </c>
       <c r="R34" t="str">
         <v>[1,800]</v>
@@ -4097,7 +4097,7 @@
         <v>10031</v>
       </c>
       <c r="C35" t="str">
-        <v>廖化-步兵 T4</v>
+        <v>徐晃-步兵 T4</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -4106,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>760</v>
+        <v>264</v>
       </c>
       <c r="G35">
         <v>6</v>
@@ -4118,13 +4118,13 @@
         <v>1</v>
       </c>
       <c r="J35">
-        <v>408</v>
+        <v>342</v>
       </c>
       <c r="K35">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L35">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="M35" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4136,10 +4136,10 @@
         <v>[]</v>
       </c>
       <c r="P35">
-        <v>518</v>
+        <v>209</v>
       </c>
       <c r="Q35">
-        <v>429</v>
+        <v>215</v>
       </c>
       <c r="R35" t="str">
         <v>[1,800]</v>
@@ -4207,7 +4207,7 @@
         <v>10032</v>
       </c>
       <c r="C36" t="str">
-        <v>马忠-步兵 T4</v>
+        <v>蒋舒-步兵 T4</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -4216,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>772</v>
+        <v>313</v>
       </c>
       <c r="G36">
         <v>6</v>
@@ -4228,13 +4228,13 @@
         <v>1</v>
       </c>
       <c r="J36">
-        <v>442</v>
+        <v>372</v>
       </c>
       <c r="K36">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L36">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="M36" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4246,10 +4246,10 @@
         <v>[]</v>
       </c>
       <c r="P36">
-        <v>535</v>
+        <v>212</v>
       </c>
       <c r="Q36">
-        <v>403</v>
+        <v>217</v>
       </c>
       <c r="R36" t="str">
         <v>[1,800]</v>
@@ -4317,7 +4317,7 @@
         <v>10033</v>
       </c>
       <c r="C37" t="str">
-        <v>关樾-步兵 T4</v>
+        <v>吴班-步兵 T4</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>772</v>
+        <v>254</v>
       </c>
       <c r="G37">
         <v>6</v>
@@ -4338,13 +4338,13 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>424</v>
+        <v>325</v>
       </c>
       <c r="K37">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L37">
-        <v>0.91</v>
+        <v>1.04</v>
       </c>
       <c r="M37" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4356,10 +4356,10 @@
         <v>[]</v>
       </c>
       <c r="P37">
-        <v>535</v>
+        <v>204</v>
       </c>
       <c r="Q37">
-        <v>428</v>
+        <v>182</v>
       </c>
       <c r="R37" t="str">
         <v>[1,800]</v>
@@ -4427,7 +4427,7 @@
         <v>10034</v>
       </c>
       <c r="C38" t="str">
-        <v>牵招-步兵 T4</v>
+        <v>曹仁-步兵 T4</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -4436,7 +4436,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>802</v>
+        <v>293</v>
       </c>
       <c r="G38">
         <v>6</v>
@@ -4448,13 +4448,13 @@
         <v>1</v>
       </c>
       <c r="J38">
-        <v>449</v>
+        <v>372</v>
       </c>
       <c r="K38">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L38">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
       <c r="M38" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4466,10 +4466,10 @@
         <v>[]</v>
       </c>
       <c r="P38">
-        <v>528</v>
+        <v>213</v>
       </c>
       <c r="Q38">
-        <v>412</v>
+        <v>202</v>
       </c>
       <c r="R38" t="str">
         <v>[1,800]</v>
@@ -4537,7 +4537,7 @@
         <v>10035</v>
       </c>
       <c r="C39" t="str">
-        <v>周仓-步兵 T4</v>
+        <v>张燕-步兵 T4</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -4546,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>718</v>
+        <v>274</v>
       </c>
       <c r="G39">
         <v>6</v>
@@ -4558,13 +4558,13 @@
         <v>1</v>
       </c>
       <c r="J39">
-        <v>433</v>
+        <v>377</v>
       </c>
       <c r="K39">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L39">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="M39" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4576,10 +4576,10 @@
         <v>[]</v>
       </c>
       <c r="P39">
-        <v>527</v>
+        <v>204</v>
       </c>
       <c r="Q39">
-        <v>423</v>
+        <v>213</v>
       </c>
       <c r="R39" t="str">
         <v>[1,800]</v>
@@ -4647,7 +4647,7 @@
         <v>10036</v>
       </c>
       <c r="C40" t="str">
-        <v>黄盖-步兵 T4</v>
+        <v>蒋义渠-步兵 T4</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -4656,7 +4656,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>612</v>
+        <v>325</v>
       </c>
       <c r="G40">
         <v>6</v>
@@ -4668,13 +4668,13 @@
         <v>1</v>
       </c>
       <c r="J40">
-        <v>321</v>
+        <v>429</v>
       </c>
       <c r="K40">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L40">
-        <v>0.91</v>
+        <v>1.1</v>
       </c>
       <c r="M40" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4686,10 +4686,10 @@
         <v>[]</v>
       </c>
       <c r="P40">
-        <v>527</v>
+        <v>213</v>
       </c>
       <c r="Q40">
-        <v>407</v>
+        <v>192</v>
       </c>
       <c r="R40" t="str">
         <v>[1,800]</v>
@@ -4757,7 +4757,7 @@
         <v>10037</v>
       </c>
       <c r="C41" t="str">
-        <v>马延-步兵 T4</v>
+        <v>李典-步兵 T4</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>660</v>
+        <v>300</v>
       </c>
       <c r="G41">
         <v>6</v>
@@ -4778,13 +4778,13 @@
         <v>1</v>
       </c>
       <c r="J41">
-        <v>357</v>
+        <v>418</v>
       </c>
       <c r="K41">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L41">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="M41" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4796,10 +4796,10 @@
         <v>[]</v>
       </c>
       <c r="P41">
-        <v>534</v>
+        <v>204</v>
       </c>
       <c r="Q41">
-        <v>437</v>
+        <v>213</v>
       </c>
       <c r="R41" t="str">
         <v>[1,800]</v>
@@ -4867,7 +4867,7 @@
         <v>10038</v>
       </c>
       <c r="C42" t="str">
-        <v>吴班-步兵 T4</v>
+        <v>裴元绍-步兵 T4</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>743</v>
+        <v>316</v>
       </c>
       <c r="G42">
         <v>6</v>
@@ -4888,13 +4888,13 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="K42">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L42">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="M42" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -4906,10 +4906,10 @@
         <v>[]</v>
       </c>
       <c r="P42">
-        <v>527</v>
+        <v>213</v>
       </c>
       <c r="Q42">
-        <v>420</v>
+        <v>195</v>
       </c>
       <c r="R42" t="str">
         <v>[1,800]</v>
@@ -4977,7 +4977,7 @@
         <v>10039</v>
       </c>
       <c r="C43" t="str">
-        <v>吕旷-步兵 T4</v>
+        <v>张郃-步兵 T4</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -4986,7 +4986,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>666</v>
+        <v>337</v>
       </c>
       <c r="G43">
         <v>6</v>
@@ -4998,13 +4998,13 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <v>369</v>
+        <v>436</v>
       </c>
       <c r="K43">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L43">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="M43" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5016,10 +5016,10 @@
         <v>[]</v>
       </c>
       <c r="P43">
-        <v>537</v>
+        <v>207</v>
       </c>
       <c r="Q43">
-        <v>431</v>
+        <v>207</v>
       </c>
       <c r="R43" t="str">
         <v>[1,800]</v>
@@ -5087,7 +5087,7 @@
         <v>10040</v>
       </c>
       <c r="C44" t="str">
-        <v>韩当-步兵 T4</v>
+        <v>田豫-步兵 T4</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>643</v>
+        <v>304</v>
       </c>
       <c r="G44">
         <v>6</v>
@@ -5108,13 +5108,13 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="K44">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L44">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="M44" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -5126,10 +5126,10 @@
         <v>[]</v>
       </c>
       <c r="P44">
-        <v>534</v>
+        <v>206</v>
       </c>
       <c r="Q44">
-        <v>372</v>
+        <v>204</v>
       </c>
       <c r="R44" t="str">
         <v>[1,800]</v>
@@ -6029,7 +6029,7 @@
         <v>20001</v>
       </c>
       <c r="C53" t="str">
-        <v>黄月英-弓箭手 T1</v>
+        <v>左慈-弓箭手 T1</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -6038,7 +6038,7 @@
         <v>1</v>
       </c>
       <c r="F53">
-        <v>247</v>
+        <v>124</v>
       </c>
       <c r="G53">
         <v>3</v>
@@ -6050,13 +6050,13 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="K53">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L53">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="M53" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6068,10 +6068,10 @@
         <v>[]</v>
       </c>
       <c r="P53">
-        <v>426</v>
+        <v>168</v>
       </c>
       <c r="Q53">
-        <v>2300</v>
+        <v>1983</v>
       </c>
       <c r="R53" t="str">
         <v>[1,800]</v>
@@ -6139,7 +6139,7 @@
         <v>20002</v>
       </c>
       <c r="C54" t="str">
-        <v>薛综-弓箭手 T1</v>
+        <v>甄姬-弓箭手 T1</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -6148,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="F54">
-        <v>253</v>
+        <v>160</v>
       </c>
       <c r="G54">
         <v>3</v>
@@ -6160,13 +6160,13 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="K54">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L54">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="M54" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6178,10 +6178,10 @@
         <v>[]</v>
       </c>
       <c r="P54">
-        <v>437</v>
+        <v>166</v>
       </c>
       <c r="Q54">
-        <v>2201</v>
+        <v>2008</v>
       </c>
       <c r="R54" t="str">
         <v>[1,800]</v>
@@ -6249,7 +6249,7 @@
         <v>20003</v>
       </c>
       <c r="C55" t="str">
-        <v>田丰-弓箭手 T1</v>
+        <v>黄月英-弓箭手 T1</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -6258,7 +6258,7 @@
         <v>1</v>
       </c>
       <c r="F55">
-        <v>292</v>
+        <v>152</v>
       </c>
       <c r="G55">
         <v>3</v>
@@ -6270,13 +6270,13 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K55">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L55">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="M55" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6288,10 +6288,10 @@
         <v>[]</v>
       </c>
       <c r="P55">
-        <v>430</v>
+        <v>173</v>
       </c>
       <c r="Q55">
-        <v>2230</v>
+        <v>2416</v>
       </c>
       <c r="R55" t="str">
         <v>[1,800]</v>
@@ -6359,7 +6359,7 @@
         <v>20004</v>
       </c>
       <c r="C56" t="str">
-        <v>王异-弓箭手 T1</v>
+        <v>荀彧-弓箭手 T1</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -6368,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="F56">
-        <v>253</v>
+        <v>103</v>
       </c>
       <c r="G56">
         <v>3</v>
@@ -6380,13 +6380,13 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K56">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L56">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="M56" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6398,10 +6398,10 @@
         <v>[]</v>
       </c>
       <c r="P56">
-        <v>439</v>
+        <v>166</v>
       </c>
       <c r="Q56">
-        <v>2398</v>
+        <v>1995</v>
       </c>
       <c r="R56" t="str">
         <v>[1,800]</v>
@@ -6469,7 +6469,7 @@
         <v>20005</v>
       </c>
       <c r="C57" t="str">
-        <v>陈群-弓箭手 T1</v>
+        <v>蒋琬-弓箭手 T1</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -6478,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="F57">
-        <v>231</v>
+        <v>115</v>
       </c>
       <c r="G57">
         <v>3</v>
@@ -6493,10 +6493,10 @@
         <v>53</v>
       </c>
       <c r="K57">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L57">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="M57" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6508,10 +6508,10 @@
         <v>[]</v>
       </c>
       <c r="P57">
-        <v>435</v>
+        <v>165</v>
       </c>
       <c r="Q57">
-        <v>2094</v>
+        <v>2214</v>
       </c>
       <c r="R57" t="str">
         <v>[1,800]</v>
@@ -6579,7 +6579,7 @@
         <v>20006</v>
       </c>
       <c r="C58" t="str">
-        <v>大乔-弓箭手 T1</v>
+        <v>顾雍-弓箭手 T1</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -6588,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="F58">
-        <v>331</v>
+        <v>130</v>
       </c>
       <c r="G58">
         <v>3</v>
@@ -6600,13 +6600,13 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K58">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L58">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="M58" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6618,10 +6618,10 @@
         <v>[]</v>
       </c>
       <c r="P58">
-        <v>430</v>
+        <v>169</v>
       </c>
       <c r="Q58">
-        <v>2164</v>
+        <v>2403</v>
       </c>
       <c r="R58" t="str">
         <v>[1,800]</v>
@@ -6689,7 +6689,7 @@
         <v>20007</v>
       </c>
       <c r="C59" t="str">
-        <v>沮授-弓箭手 T1</v>
+        <v>步练师-弓箭手 T1</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -6698,7 +6698,7 @@
         <v>1</v>
       </c>
       <c r="F59">
-        <v>314</v>
+        <v>122</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -6710,13 +6710,13 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="K59">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L59">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="M59" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6728,10 +6728,10 @@
         <v>[]</v>
       </c>
       <c r="P59">
-        <v>410</v>
+        <v>167</v>
       </c>
       <c r="Q59">
-        <v>2291</v>
+        <v>2001</v>
       </c>
       <c r="R59" t="str">
         <v>[1,800]</v>
@@ -6799,7 +6799,7 @@
         <v>20008</v>
       </c>
       <c r="C60" t="str">
-        <v>张昭-弓箭手 T1</v>
+        <v>蔡文姬-弓箭手 T1</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -6808,7 +6808,7 @@
         <v>1</v>
       </c>
       <c r="F60">
-        <v>329</v>
+        <v>106</v>
       </c>
       <c r="G60">
         <v>3</v>
@@ -6820,13 +6820,13 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="K60">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="L60">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="M60" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6838,10 +6838,10 @@
         <v>[]</v>
       </c>
       <c r="P60">
-        <v>427</v>
+        <v>170</v>
       </c>
       <c r="Q60">
-        <v>2354</v>
+        <v>2264</v>
       </c>
       <c r="R60" t="str">
         <v>[1,800]</v>
@@ -6909,7 +6909,7 @@
         <v>20009</v>
       </c>
       <c r="C61" t="str">
-        <v>王朗-弓箭手 T1</v>
+        <v>戏志才-弓箭手 T1</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -6918,7 +6918,7 @@
         <v>1</v>
       </c>
       <c r="F61">
-        <v>293</v>
+        <v>145</v>
       </c>
       <c r="G61">
         <v>3</v>
@@ -6930,13 +6930,13 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="K61">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L61">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="M61" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -6948,10 +6948,10 @@
         <v>[]</v>
       </c>
       <c r="P61">
-        <v>420</v>
+        <v>169</v>
       </c>
       <c r="Q61">
-        <v>2271</v>
+        <v>2349</v>
       </c>
       <c r="R61" t="str">
         <v>[1,800]</v>
@@ -7019,7 +7019,7 @@
         <v>20010</v>
       </c>
       <c r="C62" t="str">
-        <v>水镜先生-弓箭手 T1</v>
+        <v>辛宪英-弓箭手 T1</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -7028,7 +7028,7 @@
         <v>1</v>
       </c>
       <c r="F62">
-        <v>233</v>
+        <v>147</v>
       </c>
       <c r="G62">
         <v>3</v>
@@ -7040,13 +7040,13 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="K62">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L62">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="M62" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7058,10 +7058,10 @@
         <v>[]</v>
       </c>
       <c r="P62">
-        <v>439</v>
+        <v>165</v>
       </c>
       <c r="Q62">
-        <v>2301</v>
+        <v>2062</v>
       </c>
       <c r="R62" t="str">
         <v>[1,800]</v>
@@ -7129,7 +7129,7 @@
         <v>20011</v>
       </c>
       <c r="C63" t="str">
-        <v>姜维-弓箭手 T2</v>
+        <v>小乔-弓箭手 T2</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -7138,7 +7138,7 @@
         <v>1</v>
       </c>
       <c r="F63">
-        <v>442</v>
+        <v>244</v>
       </c>
       <c r="G63">
         <v>4</v>
@@ -7150,13 +7150,13 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="K63">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L63">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="M63" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7168,10 +7168,10 @@
         <v>[]</v>
       </c>
       <c r="P63">
-        <v>411</v>
+        <v>174</v>
       </c>
       <c r="Q63">
-        <v>2172</v>
+        <v>2041</v>
       </c>
       <c r="R63" t="str">
         <v>[1,800]</v>
@@ -7239,7 +7239,7 @@
         <v>20012</v>
       </c>
       <c r="C64" t="str">
-        <v>步练师-弓箭手 T2</v>
+        <v>姜维-弓箭手 T2</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -7248,7 +7248,7 @@
         <v>1</v>
       </c>
       <c r="F64">
-        <v>590</v>
+        <v>259</v>
       </c>
       <c r="G64">
         <v>4</v>
@@ -7260,13 +7260,13 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K64">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L64">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="M64" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7278,10 +7278,10 @@
         <v>[]</v>
       </c>
       <c r="P64">
-        <v>439</v>
+        <v>172</v>
       </c>
       <c r="Q64">
-        <v>2186</v>
+        <v>2123</v>
       </c>
       <c r="R64" t="str">
         <v>[1,800]</v>
@@ -7349,7 +7349,7 @@
         <v>20013</v>
       </c>
       <c r="C65" t="str">
-        <v>顾雍-弓箭手 T2</v>
+        <v>钟繇-弓箭手 T2</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -7358,7 +7358,7 @@
         <v>1</v>
       </c>
       <c r="F65">
-        <v>524</v>
+        <v>221</v>
       </c>
       <c r="G65">
         <v>4</v>
@@ -7373,10 +7373,10 @@
         <v>90</v>
       </c>
       <c r="K65">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L65">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="M65" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7388,10 +7388,10 @@
         <v>[]</v>
       </c>
       <c r="P65">
-        <v>414</v>
+        <v>170</v>
       </c>
       <c r="Q65">
-        <v>2162</v>
+        <v>2082</v>
       </c>
       <c r="R65" t="str">
         <v>[1,800]</v>
@@ -7459,7 +7459,7 @@
         <v>20014</v>
       </c>
       <c r="C66" t="str">
-        <v>刘晔-弓箭手 T2</v>
+        <v>陈震-弓箭手 T2</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -7468,7 +7468,7 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>566</v>
+        <v>222</v>
       </c>
       <c r="G66">
         <v>4</v>
@@ -7480,10 +7480,10 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K66">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L66">
         <v>1.93</v>
@@ -7498,10 +7498,10 @@
         <v>[]</v>
       </c>
       <c r="P66">
-        <v>430</v>
+        <v>176</v>
       </c>
       <c r="Q66">
-        <v>2071</v>
+        <v>2308</v>
       </c>
       <c r="R66" t="str">
         <v>[1,800]</v>
@@ -7569,7 +7569,7 @@
         <v>20015</v>
       </c>
       <c r="C67" t="str">
-        <v>逢纪-弓箭手 T2</v>
+        <v>张春华-弓箭手 T2</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -7578,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="F67">
-        <v>494</v>
+        <v>286</v>
       </c>
       <c r="G67">
         <v>4</v>
@@ -7590,13 +7590,13 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K67">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L67">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="M67" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7608,10 +7608,10 @@
         <v>[]</v>
       </c>
       <c r="P67">
-        <v>426</v>
+        <v>175</v>
       </c>
       <c r="Q67">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="R67" t="str">
         <v>[1,800]</v>
@@ -7679,7 +7679,7 @@
         <v>20016</v>
       </c>
       <c r="C68" t="str">
-        <v>庞统-弓箭手 T2</v>
+        <v>宗预-弓箭手 T2</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -7688,7 +7688,7 @@
         <v>1</v>
       </c>
       <c r="F68">
-        <v>344</v>
+        <v>252</v>
       </c>
       <c r="G68">
         <v>4</v>
@@ -7700,13 +7700,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K68">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L68">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="M68" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7718,10 +7718,10 @@
         <v>[]</v>
       </c>
       <c r="P68">
-        <v>423</v>
+        <v>164</v>
       </c>
       <c r="Q68">
-        <v>2156</v>
+        <v>2286</v>
       </c>
       <c r="R68" t="str">
         <v>[1,800]</v>
@@ -7789,7 +7789,7 @@
         <v>20017</v>
       </c>
       <c r="C69" t="str">
-        <v>宗预-弓箭手 T2</v>
+        <v>贾诩-弓箭手 T2</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -7798,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="F69">
-        <v>522</v>
+        <v>218</v>
       </c>
       <c r="G69">
         <v>4</v>
@@ -7810,13 +7810,13 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K69">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L69">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="M69" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7828,10 +7828,10 @@
         <v>[]</v>
       </c>
       <c r="P69">
-        <v>433</v>
+        <v>168</v>
       </c>
       <c r="Q69">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="R69" t="str">
         <v>[1,800]</v>
@@ -7899,7 +7899,7 @@
         <v>20018</v>
       </c>
       <c r="C70" t="str">
-        <v>司马懿-弓箭手 T2</v>
+        <v>徐庶-弓箭手 T2</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -7908,7 +7908,7 @@
         <v>1</v>
       </c>
       <c r="F70">
-        <v>463</v>
+        <v>267</v>
       </c>
       <c r="G70">
         <v>4</v>
@@ -7920,13 +7920,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K70">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L70">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="M70" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -7938,10 +7938,10 @@
         <v>[]</v>
       </c>
       <c r="P70">
-        <v>418</v>
+        <v>170</v>
       </c>
       <c r="Q70">
-        <v>2332</v>
+        <v>2275</v>
       </c>
       <c r="R70" t="str">
         <v>[1,800]</v>
@@ -8009,7 +8009,7 @@
         <v>20019</v>
       </c>
       <c r="C71" t="str">
-        <v>蒯越-弓箭手 T2</v>
+        <v>糜竺-弓箭手 T2</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -8018,7 +8018,7 @@
         <v>1</v>
       </c>
       <c r="F71">
-        <v>440</v>
+        <v>265</v>
       </c>
       <c r="G71">
         <v>4</v>
@@ -8030,13 +8030,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K71">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L71">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="M71" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8048,10 +8048,10 @@
         <v>[]</v>
       </c>
       <c r="P71">
-        <v>439</v>
+        <v>169</v>
       </c>
       <c r="Q71">
-        <v>2273</v>
+        <v>2123</v>
       </c>
       <c r="R71" t="str">
         <v>[1,800]</v>
@@ -8119,7 +8119,7 @@
         <v>20020</v>
       </c>
       <c r="C72" t="str">
-        <v>孙乾-弓箭手 T2</v>
+        <v>郑玄-弓箭手 T2</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -8128,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="F72">
-        <v>388</v>
+        <v>209</v>
       </c>
       <c r="G72">
         <v>4</v>
@@ -8140,13 +8140,13 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="K72">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L72">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="M72" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8158,10 +8158,10 @@
         <v>[]</v>
       </c>
       <c r="P72">
-        <v>420</v>
+        <v>176</v>
       </c>
       <c r="Q72">
-        <v>2275</v>
+        <v>2048</v>
       </c>
       <c r="R72" t="str">
         <v>[1,800]</v>
@@ -8229,7 +8229,7 @@
         <v>20021</v>
       </c>
       <c r="C73" t="str">
-        <v>钟繇-弓箭手 T3</v>
+        <v>审配-弓箭手 T3</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -8238,7 +8238,7 @@
         <v>1</v>
       </c>
       <c r="F73">
-        <v>764</v>
+        <v>394</v>
       </c>
       <c r="G73">
         <v>5</v>
@@ -8250,13 +8250,13 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="K73">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L73">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="M73" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8268,10 +8268,10 @@
         <v>[]</v>
       </c>
       <c r="P73">
-        <v>412</v>
+        <v>176</v>
       </c>
       <c r="Q73">
-        <v>2222</v>
+        <v>2157</v>
       </c>
       <c r="R73" t="str">
         <v>[1,800]</v>
@@ -8339,7 +8339,7 @@
         <v>20022</v>
       </c>
       <c r="C74" t="str">
-        <v>左慈-弓箭手 T3</v>
+        <v>诸葛瑾-弓箭手 T3</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -8348,7 +8348,7 @@
         <v>1</v>
       </c>
       <c r="F74">
-        <v>672</v>
+        <v>342</v>
       </c>
       <c r="G74">
         <v>5</v>
@@ -8360,13 +8360,13 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K74">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L74">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="M74" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8378,10 +8378,10 @@
         <v>[]</v>
       </c>
       <c r="P74">
-        <v>418</v>
+        <v>175</v>
       </c>
       <c r="Q74">
-        <v>1998</v>
+        <v>1989</v>
       </c>
       <c r="R74" t="str">
         <v>[1,800]</v>
@@ -8449,7 +8449,7 @@
         <v>20023</v>
       </c>
       <c r="C75" t="str">
-        <v>蒋琬-弓箭手 T3</v>
+        <v>蒯良-弓箭手 T3</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -8458,7 +8458,7 @@
         <v>1</v>
       </c>
       <c r="F75">
-        <v>673</v>
+        <v>346</v>
       </c>
       <c r="G75">
         <v>5</v>
@@ -8470,13 +8470,13 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="K75">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L75">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="M75" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8488,10 +8488,10 @@
         <v>[]</v>
       </c>
       <c r="P75">
-        <v>434</v>
+        <v>171</v>
       </c>
       <c r="Q75">
-        <v>2381</v>
+        <v>2029</v>
       </c>
       <c r="R75" t="str">
         <v>[1,800]</v>
@@ -8559,7 +8559,7 @@
         <v>20024</v>
       </c>
       <c r="C76" t="str">
-        <v>简雍-弓箭手 T3</v>
+        <v>华佗-弓箭手 T3</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -8568,7 +8568,7 @@
         <v>1</v>
       </c>
       <c r="F76">
-        <v>647</v>
+        <v>451</v>
       </c>
       <c r="G76">
         <v>5</v>
@@ -8580,13 +8580,13 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="K76">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L76">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="M76" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8598,10 +8598,10 @@
         <v>[]</v>
       </c>
       <c r="P76">
-        <v>439</v>
+        <v>168</v>
       </c>
       <c r="Q76">
-        <v>2165</v>
+        <v>2253</v>
       </c>
       <c r="R76" t="str">
         <v>[1,800]</v>
@@ -8678,7 +8678,7 @@
         <v>1</v>
       </c>
       <c r="F77">
-        <v>849</v>
+        <v>331</v>
       </c>
       <c r="G77">
         <v>5</v>
@@ -8690,13 +8690,13 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K77">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L77">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="M77" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8708,10 +8708,10 @@
         <v>[]</v>
       </c>
       <c r="P77">
-        <v>412</v>
+        <v>171</v>
       </c>
       <c r="Q77">
-        <v>2184</v>
+        <v>2157</v>
       </c>
       <c r="R77" t="str">
         <v>[1,800]</v>
@@ -8779,7 +8779,7 @@
         <v>20026</v>
       </c>
       <c r="C78" t="str">
-        <v>黄忠-弓箭手 T3</v>
+        <v>貂蝉-弓箭手 T3</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -8788,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>827</v>
+        <v>290</v>
       </c>
       <c r="G78">
         <v>5</v>
@@ -8800,13 +8800,13 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K78">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="L78">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="M78" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8818,10 +8818,10 @@
         <v>[]</v>
       </c>
       <c r="P78">
-        <v>413</v>
+        <v>174</v>
       </c>
       <c r="Q78">
-        <v>2068</v>
+        <v>2106</v>
       </c>
       <c r="R78" t="str">
         <v>[1,800]</v>
@@ -8889,7 +8889,7 @@
         <v>20027</v>
       </c>
       <c r="C79" t="str">
-        <v>郭嘉-弓箭手 T3</v>
+        <v>陈群-弓箭手 T3</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -8898,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>728</v>
+        <v>315</v>
       </c>
       <c r="G79">
         <v>5</v>
@@ -8910,13 +8910,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="K79">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L79">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="M79" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -8928,10 +8928,10 @@
         <v>[]</v>
       </c>
       <c r="P79">
-        <v>438</v>
+        <v>170</v>
       </c>
       <c r="Q79">
-        <v>2207</v>
+        <v>2164</v>
       </c>
       <c r="R79" t="str">
         <v>[1,800]</v>
@@ -8999,7 +8999,7 @@
         <v>20028</v>
       </c>
       <c r="C80" t="str">
-        <v>郑玄-弓箭手 T3</v>
+        <v>廖立-弓箭手 T3</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -9008,7 +9008,7 @@
         <v>1</v>
       </c>
       <c r="F80">
-        <v>713</v>
+        <v>352</v>
       </c>
       <c r="G80">
         <v>5</v>
@@ -9020,13 +9020,13 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="K80">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L80">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="M80" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9038,10 +9038,10 @@
         <v>[]</v>
       </c>
       <c r="P80">
-        <v>429</v>
+        <v>172</v>
       </c>
       <c r="Q80">
-        <v>2237</v>
+        <v>2326</v>
       </c>
       <c r="R80" t="str">
         <v>[1,800]</v>
@@ -9109,7 +9109,7 @@
         <v>20029</v>
       </c>
       <c r="C81" t="str">
-        <v>小乔-弓箭手 T3</v>
+        <v>水镜先生-弓箭手 T3</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -9118,7 +9118,7 @@
         <v>1</v>
       </c>
       <c r="F81">
-        <v>845</v>
+        <v>365</v>
       </c>
       <c r="G81">
         <v>5</v>
@@ -9130,13 +9130,13 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="K81">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L81">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="M81" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9148,10 +9148,10 @@
         <v>[]</v>
       </c>
       <c r="P81">
-        <v>411</v>
+        <v>171</v>
       </c>
       <c r="Q81">
-        <v>2201</v>
+        <v>2125</v>
       </c>
       <c r="R81" t="str">
         <v>[1,800]</v>
@@ -9219,7 +9219,7 @@
         <v>20030</v>
       </c>
       <c r="C82" t="str">
-        <v>阚泽-弓箭手 T3</v>
+        <v>黄忠-弓箭手 T3</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -9228,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="F82">
-        <v>660</v>
+        <v>371</v>
       </c>
       <c r="G82">
         <v>5</v>
@@ -9240,13 +9240,13 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K82">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L82">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="M82" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9258,10 +9258,10 @@
         <v>[]</v>
       </c>
       <c r="P82">
-        <v>414</v>
+        <v>171</v>
       </c>
       <c r="Q82">
-        <v>2375</v>
+        <v>2076</v>
       </c>
       <c r="R82" t="str">
         <v>[1,800]</v>
@@ -9329,7 +9329,7 @@
         <v>20031</v>
       </c>
       <c r="C83" t="str">
-        <v>华佗-弓箭手 T4</v>
+        <v>司马懿-弓箭手 T4</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -9338,7 +9338,7 @@
         <v>1</v>
       </c>
       <c r="F83">
-        <v>887</v>
+        <v>424</v>
       </c>
       <c r="G83">
         <v>6</v>
@@ -9350,13 +9350,13 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K83">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L83">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="M83" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9368,10 +9368,10 @@
         <v>[]</v>
       </c>
       <c r="P83">
-        <v>419</v>
+        <v>165</v>
       </c>
       <c r="Q83">
-        <v>2057</v>
+        <v>2175</v>
       </c>
       <c r="R83" t="str">
         <v>[1,800]</v>
@@ -9439,7 +9439,7 @@
         <v>20032</v>
       </c>
       <c r="C84" t="str">
-        <v>虞翻-弓箭手 T4</v>
+        <v>王异-弓箭手 T4</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -9448,7 +9448,7 @@
         <v>1</v>
       </c>
       <c r="F84">
-        <v>854</v>
+        <v>638</v>
       </c>
       <c r="G84">
         <v>6</v>
@@ -9460,13 +9460,13 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="K84">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L84">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="M84" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9478,10 +9478,10 @@
         <v>[]</v>
       </c>
       <c r="P84">
-        <v>432</v>
+        <v>167</v>
       </c>
       <c r="Q84">
-        <v>2323</v>
+        <v>2378</v>
       </c>
       <c r="R84" t="str">
         <v>[1,800]</v>
@@ -9549,7 +9549,7 @@
         <v>20033</v>
       </c>
       <c r="C85" t="str">
-        <v>蔡文姬-弓箭手 T4</v>
+        <v>张昭-弓箭手 T4</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -9558,7 +9558,7 @@
         <v>1</v>
       </c>
       <c r="F85">
-        <v>1268</v>
+        <v>501</v>
       </c>
       <c r="G85">
         <v>6</v>
@@ -9570,13 +9570,13 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="K85">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="L85">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="M85" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9588,10 +9588,10 @@
         <v>[]</v>
       </c>
       <c r="P85">
-        <v>425</v>
+        <v>173</v>
       </c>
       <c r="Q85">
-        <v>2116</v>
+        <v>2296</v>
       </c>
       <c r="R85" t="str">
         <v>[1,800]</v>
@@ -9659,7 +9659,7 @@
         <v>20034</v>
       </c>
       <c r="C86" t="str">
-        <v>管辂-弓箭手 T4</v>
+        <v>秦宓-弓箭手 T4</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -9668,7 +9668,7 @@
         <v>1</v>
       </c>
       <c r="F86">
-        <v>1048</v>
+        <v>506</v>
       </c>
       <c r="G86">
         <v>6</v>
@@ -9680,13 +9680,13 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="K86">
         <v>53</v>
       </c>
       <c r="L86">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="M86" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9698,10 +9698,10 @@
         <v>[]</v>
       </c>
       <c r="P86">
-        <v>433</v>
+        <v>171</v>
       </c>
       <c r="Q86">
-        <v>2081</v>
+        <v>2221</v>
       </c>
       <c r="R86" t="str">
         <v>[1,800]</v>
@@ -9769,7 +9769,7 @@
         <v>20035</v>
       </c>
       <c r="C87" t="str">
-        <v>貂蝉-弓箭手 T4</v>
+        <v>诸葛亮-弓箭手 T4</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -9778,7 +9778,7 @@
         <v>1</v>
       </c>
       <c r="F87">
-        <v>942</v>
+        <v>545</v>
       </c>
       <c r="G87">
         <v>6</v>
@@ -9790,13 +9790,13 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="K87">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L87">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="M87" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9808,10 +9808,10 @@
         <v>[]</v>
       </c>
       <c r="P87">
-        <v>435</v>
+        <v>166</v>
       </c>
       <c r="Q87">
-        <v>2006</v>
+        <v>2140</v>
       </c>
       <c r="R87" t="str">
         <v>[1,800]</v>
@@ -9879,7 +9879,7 @@
         <v>20036</v>
       </c>
       <c r="C88" t="str">
-        <v>廖立-弓箭手 T4</v>
+        <v>庞德公-弓箭手 T4</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -9888,7 +9888,7 @@
         <v>1</v>
       </c>
       <c r="F88">
-        <v>1167</v>
+        <v>437</v>
       </c>
       <c r="G88">
         <v>6</v>
@@ -9900,13 +9900,13 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="K88">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L88">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="M88" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -9918,10 +9918,10 @@
         <v>[]</v>
       </c>
       <c r="P88">
-        <v>426</v>
+        <v>168</v>
       </c>
       <c r="Q88">
-        <v>2153</v>
+        <v>2101</v>
       </c>
       <c r="R88" t="str">
         <v>[1,800]</v>
@@ -9989,7 +9989,7 @@
         <v>20037</v>
       </c>
       <c r="C89" t="str">
-        <v>荀彧-弓箭手 T4</v>
+        <v>田丰-弓箭手 T4</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -9998,7 +9998,7 @@
         <v>1</v>
       </c>
       <c r="F89">
-        <v>1021</v>
+        <v>497</v>
       </c>
       <c r="G89">
         <v>6</v>
@@ -10010,13 +10010,13 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="K89">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="L89">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="M89" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10028,10 +10028,10 @@
         <v>[]</v>
       </c>
       <c r="P89">
-        <v>415</v>
+        <v>170</v>
       </c>
       <c r="Q89">
-        <v>2017</v>
+        <v>2168</v>
       </c>
       <c r="R89" t="str">
         <v>[1,800]</v>
@@ -10099,7 +10099,7 @@
         <v>20038</v>
       </c>
       <c r="C90" t="str">
-        <v>程昱-弓箭手 T4</v>
+        <v>伊籍-弓箭手 T4</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -10108,7 +10108,7 @@
         <v>1</v>
       </c>
       <c r="F90">
-        <v>1099</v>
+        <v>499</v>
       </c>
       <c r="G90">
         <v>6</v>
@@ -10120,13 +10120,13 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="K90">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L90">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="M90" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10138,10 +10138,10 @@
         <v>[]</v>
       </c>
       <c r="P90">
-        <v>428</v>
+        <v>174</v>
       </c>
       <c r="Q90">
-        <v>2327</v>
+        <v>2154</v>
       </c>
       <c r="R90" t="str">
         <v>[1,800]</v>
@@ -10209,7 +10209,7 @@
         <v>20039</v>
       </c>
       <c r="C91" t="str">
-        <v>张春华-弓箭手 T4</v>
+        <v>逢纪-弓箭手 T4</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -10218,7 +10218,7 @@
         <v>1</v>
       </c>
       <c r="F91">
-        <v>914</v>
+        <v>550</v>
       </c>
       <c r="G91">
         <v>6</v>
@@ -10230,13 +10230,13 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="K91">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L91">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="M91" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10248,10 +10248,10 @@
         <v>[]</v>
       </c>
       <c r="P91">
-        <v>436</v>
+        <v>167</v>
       </c>
       <c r="Q91">
-        <v>2157</v>
+        <v>2203</v>
       </c>
       <c r="R91" t="str">
         <v>[1,800]</v>
@@ -10319,7 +10319,7 @@
         <v>20040</v>
       </c>
       <c r="C92" t="str">
-        <v>陆逊-弓箭手 T4</v>
+        <v>杨修-弓箭手 T4</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -10328,7 +10328,7 @@
         <v>1</v>
       </c>
       <c r="F92">
-        <v>907</v>
+        <v>499</v>
       </c>
       <c r="G92">
         <v>6</v>
@@ -10340,13 +10340,13 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="K92">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L92">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="M92" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -10358,10 +10358,10 @@
         <v>[]</v>
       </c>
       <c r="P92">
-        <v>412</v>
+        <v>165</v>
       </c>
       <c r="Q92">
-        <v>2328</v>
+        <v>2354</v>
       </c>
       <c r="R92" t="str">
         <v>[1,800]</v>
@@ -11257,11 +11257,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="str">
+        <v>s</v>
+      </c>
       <c r="B101" t="str">
         <v>30001</v>
       </c>
       <c r="C101" t="str">
-        <v>张绣-骑兵 T1</v>
+        <v>凌统-骑兵 T1</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -11270,7 +11273,7 @@
         <v>1</v>
       </c>
       <c r="F101">
-        <v>282</v>
+        <v>114</v>
       </c>
       <c r="G101">
         <v>3</v>
@@ -11282,13 +11285,13 @@
         <v>1</v>
       </c>
       <c r="J101">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K101">
         <v>18</v>
       </c>
       <c r="L101">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="M101" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11300,10 +11303,10 @@
         <v>[]</v>
       </c>
       <c r="P101">
-        <v>627</v>
+        <v>243</v>
       </c>
       <c r="Q101">
-        <v>460</v>
+        <v>237</v>
       </c>
       <c r="R101" t="str">
         <v>[1,800]</v>
@@ -11371,7 +11374,7 @@
         <v>30002</v>
       </c>
       <c r="C102" t="str">
-        <v>徐荣-骑兵 T1</v>
+        <v>骨进-骑兵 T1</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -11380,7 +11383,7 @@
         <v>1</v>
       </c>
       <c r="F102">
-        <v>231</v>
+        <v>107</v>
       </c>
       <c r="G102">
         <v>3</v>
@@ -11392,13 +11395,13 @@
         <v>1</v>
       </c>
       <c r="J102">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K102">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L102">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="M102" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11410,10 +11413,10 @@
         <v>[]</v>
       </c>
       <c r="P102">
-        <v>618</v>
+        <v>252</v>
       </c>
       <c r="Q102">
-        <v>437</v>
+        <v>236</v>
       </c>
       <c r="R102" t="str">
         <v>[1,800]</v>
@@ -11481,7 +11484,7 @@
         <v>30003</v>
       </c>
       <c r="C103" t="str">
-        <v>胡轸-骑兵 T1</v>
+        <v>曹纯-骑兵 T1</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -11490,7 +11493,7 @@
         <v>1</v>
       </c>
       <c r="F103">
-        <v>290</v>
+        <v>99</v>
       </c>
       <c r="G103">
         <v>3</v>
@@ -11502,13 +11505,13 @@
         <v>1</v>
       </c>
       <c r="J103">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="K103">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L103">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="M103" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11520,10 +11523,10 @@
         <v>[]</v>
       </c>
       <c r="P103">
-        <v>613</v>
+        <v>255</v>
       </c>
       <c r="Q103">
-        <v>401</v>
+        <v>240</v>
       </c>
       <c r="R103" t="str">
         <v>[1,800]</v>
@@ -11591,7 +11594,7 @@
         <v>30004</v>
       </c>
       <c r="C104" t="str">
-        <v>韩忠-骑兵 T1</v>
+        <v>马玩-骑兵 T1</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -11600,7 +11603,7 @@
         <v>1</v>
       </c>
       <c r="F104">
-        <v>257</v>
+        <v>111</v>
       </c>
       <c r="G104">
         <v>3</v>
@@ -11612,13 +11615,13 @@
         <v>1</v>
       </c>
       <c r="J104">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K104">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L104">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="M104" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11630,10 +11633,10 @@
         <v>[]</v>
       </c>
       <c r="P104">
-        <v>630</v>
+        <v>244</v>
       </c>
       <c r="Q104">
-        <v>388</v>
+        <v>239</v>
       </c>
       <c r="R104" t="str">
         <v>[1,800]</v>
@@ -11701,7 +11704,7 @@
         <v>30005</v>
       </c>
       <c r="C105" t="str">
-        <v>董卓-骑兵 T1</v>
+        <v>马超-骑兵 T1</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -11710,7 +11713,7 @@
         <v>1</v>
       </c>
       <c r="F105">
-        <v>288</v>
+        <v>112</v>
       </c>
       <c r="G105">
         <v>3</v>
@@ -11722,13 +11725,13 @@
         <v>1</v>
       </c>
       <c r="J105">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K105">
         <v>19</v>
       </c>
       <c r="L105">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="M105" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11740,10 +11743,10 @@
         <v>[]</v>
       </c>
       <c r="P105">
-        <v>633</v>
+        <v>246</v>
       </c>
       <c r="Q105">
-        <v>447</v>
+        <v>208</v>
       </c>
       <c r="R105" t="str">
         <v>[1,800]</v>
@@ -11811,7 +11814,7 @@
         <v>30006</v>
       </c>
       <c r="C106" t="str">
-        <v>邓茂-骑兵 T1</v>
+        <v>张曼成-骑兵 T1</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -11820,7 +11823,7 @@
         <v>1</v>
       </c>
       <c r="F106">
-        <v>246</v>
+        <v>124</v>
       </c>
       <c r="G106">
         <v>3</v>
@@ -11832,13 +11835,13 @@
         <v>1</v>
       </c>
       <c r="J106">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="K106">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L106">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="M106" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11850,10 +11853,10 @@
         <v>[]</v>
       </c>
       <c r="P106">
-        <v>636</v>
+        <v>241</v>
       </c>
       <c r="Q106">
-        <v>446</v>
+        <v>214</v>
       </c>
       <c r="R106" t="str">
         <v>[1,800]</v>
@@ -11921,7 +11924,7 @@
         <v>30007</v>
       </c>
       <c r="C107" t="str">
-        <v>楼班-骑兵 T1</v>
+        <v>马铁-骑兵 T1</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -11930,7 +11933,7 @@
         <v>1</v>
       </c>
       <c r="F107">
-        <v>216</v>
+        <v>113</v>
       </c>
       <c r="G107">
         <v>3</v>
@@ -11942,13 +11945,13 @@
         <v>1</v>
       </c>
       <c r="J107">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="K107">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L107">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="M107" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -11960,10 +11963,10 @@
         <v>[]</v>
       </c>
       <c r="P107">
-        <v>626</v>
+        <v>243</v>
       </c>
       <c r="Q107">
-        <v>390</v>
+        <v>240</v>
       </c>
       <c r="R107" t="str">
         <v>[1,800]</v>
@@ -12031,7 +12034,7 @@
         <v>30008</v>
       </c>
       <c r="C108" t="str">
-        <v>马玩-骑兵 T1</v>
+        <v>曹彰-骑兵 T1</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -12040,7 +12043,7 @@
         <v>1</v>
       </c>
       <c r="F108">
-        <v>247</v>
+        <v>108</v>
       </c>
       <c r="G108">
         <v>3</v>
@@ -12052,13 +12055,13 @@
         <v>1</v>
       </c>
       <c r="J108">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K108">
         <v>16</v>
       </c>
       <c r="L108">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M108" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12070,10 +12073,10 @@
         <v>[]</v>
       </c>
       <c r="P108">
-        <v>634</v>
+        <v>254</v>
       </c>
       <c r="Q108">
-        <v>436</v>
+        <v>231</v>
       </c>
       <c r="R108" t="str">
         <v>[1,800]</v>
@@ -12141,7 +12144,7 @@
         <v>30009</v>
       </c>
       <c r="C109" t="str">
-        <v>张曼成-骑兵 T2</v>
+        <v>程银-骑兵 T2</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -12150,7 +12153,7 @@
         <v>1</v>
       </c>
       <c r="F109">
-        <v>501</v>
+        <v>202</v>
       </c>
       <c r="G109">
         <v>4</v>
@@ -12162,13 +12165,13 @@
         <v>1</v>
       </c>
       <c r="J109">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="K109">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L109">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="M109" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12180,10 +12183,10 @@
         <v>[]</v>
       </c>
       <c r="P109">
-        <v>601</v>
+        <v>241</v>
       </c>
       <c r="Q109">
-        <v>416</v>
+        <v>242</v>
       </c>
       <c r="R109" t="str">
         <v>[1,800]</v>
@@ -12251,7 +12254,7 @@
         <v>30010</v>
       </c>
       <c r="C110" t="str">
-        <v>韩遂-骑兵 T2</v>
+        <v>张卫-骑兵 T2</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -12260,7 +12263,7 @@
         <v>1</v>
       </c>
       <c r="F110">
-        <v>412</v>
+        <v>208</v>
       </c>
       <c r="G110">
         <v>4</v>
@@ -12272,13 +12275,13 @@
         <v>1</v>
       </c>
       <c r="J110">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="K110">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L110">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="M110" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12290,10 +12293,10 @@
         <v>[]</v>
       </c>
       <c r="P110">
-        <v>626</v>
+        <v>252</v>
       </c>
       <c r="Q110">
-        <v>439</v>
+        <v>203</v>
       </c>
       <c r="R110" t="str">
         <v>[1,800]</v>
@@ -12361,7 +12364,7 @@
         <v>30011</v>
       </c>
       <c r="C111" t="str">
-        <v>孟获-骑兵 T2</v>
+        <v>李傕-骑兵 T2</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -12370,7 +12373,7 @@
         <v>1</v>
       </c>
       <c r="F111">
-        <v>438</v>
+        <v>211</v>
       </c>
       <c r="G111">
         <v>4</v>
@@ -12382,13 +12385,13 @@
         <v>1</v>
       </c>
       <c r="J111">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="K111">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L111">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="M111" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12400,10 +12403,10 @@
         <v>[]</v>
       </c>
       <c r="P111">
-        <v>621</v>
+        <v>251</v>
       </c>
       <c r="Q111">
-        <v>433</v>
+        <v>236</v>
       </c>
       <c r="R111" t="str">
         <v>[1,800]</v>
@@ -12471,7 +12474,7 @@
         <v>30012</v>
       </c>
       <c r="C112" t="str">
-        <v>牛辅-骑兵 T2</v>
+        <v>孙尚香-骑兵 T2</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -12480,7 +12483,7 @@
         <v>1</v>
       </c>
       <c r="F112">
-        <v>424</v>
+        <v>173</v>
       </c>
       <c r="G112">
         <v>4</v>
@@ -12492,13 +12495,13 @@
         <v>1</v>
       </c>
       <c r="J112">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="K112">
         <v>21</v>
       </c>
       <c r="L112">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="M112" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12510,10 +12513,10 @@
         <v>[]</v>
       </c>
       <c r="P112">
-        <v>638</v>
+        <v>251</v>
       </c>
       <c r="Q112">
-        <v>401</v>
+        <v>231</v>
       </c>
       <c r="R112" t="str">
         <v>[1,800]</v>
@@ -12581,7 +12584,7 @@
         <v>30013</v>
       </c>
       <c r="C113" t="str">
-        <v>张卫-骑兵 T2</v>
+        <v>吕玲绮-骑兵 T2</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -12590,7 +12593,7 @@
         <v>1</v>
       </c>
       <c r="F113">
-        <v>537</v>
+        <v>170</v>
       </c>
       <c r="G113">
         <v>4</v>
@@ -12602,13 +12605,13 @@
         <v>1</v>
       </c>
       <c r="J113">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="K113">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L113">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="M113" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12620,10 +12623,10 @@
         <v>[]</v>
       </c>
       <c r="P113">
-        <v>638</v>
+        <v>240</v>
       </c>
       <c r="Q113">
-        <v>449</v>
+        <v>241</v>
       </c>
       <c r="R113" t="str">
         <v>[1,800]</v>
@@ -12691,7 +12694,7 @@
         <v>30014</v>
       </c>
       <c r="C114" t="str">
-        <v>骨进-骑兵 T2</v>
+        <v>董卓-骑兵 T2</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -12700,7 +12703,7 @@
         <v>1</v>
       </c>
       <c r="F114">
-        <v>477</v>
+        <v>209</v>
       </c>
       <c r="G114">
         <v>4</v>
@@ -12712,13 +12715,13 @@
         <v>1</v>
       </c>
       <c r="J114">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="K114">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L114">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="M114" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12730,10 +12733,10 @@
         <v>[]</v>
       </c>
       <c r="P114">
-        <v>629</v>
+        <v>249</v>
       </c>
       <c r="Q114">
-        <v>426</v>
+        <v>228</v>
       </c>
       <c r="R114" t="str">
         <v>[1,800]</v>
@@ -12801,7 +12804,7 @@
         <v>30015</v>
       </c>
       <c r="C115" t="str">
-        <v>蹋顿-骑兵 T2</v>
+        <v>张横-骑兵 T2</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -12810,7 +12813,7 @@
         <v>1</v>
       </c>
       <c r="F115">
-        <v>442</v>
+        <v>184</v>
       </c>
       <c r="G115">
         <v>4</v>
@@ -12822,13 +12825,13 @@
         <v>1</v>
       </c>
       <c r="J115">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K115">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L115">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M115" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12840,10 +12843,10 @@
         <v>[]</v>
       </c>
       <c r="P115">
-        <v>609</v>
+        <v>242</v>
       </c>
       <c r="Q115">
-        <v>431</v>
+        <v>205</v>
       </c>
       <c r="R115" t="str">
         <v>[1,800]</v>
@@ -12911,7 +12914,7 @@
         <v>30016</v>
       </c>
       <c r="C116" t="str">
-        <v>程远志-骑兵 T2</v>
+        <v>夏侯渊-骑兵 T2</v>
       </c>
       <c r="D116">
         <v>2</v>
@@ -12920,7 +12923,7 @@
         <v>1</v>
       </c>
       <c r="F116">
-        <v>434</v>
+        <v>197</v>
       </c>
       <c r="G116">
         <v>4</v>
@@ -12932,13 +12935,13 @@
         <v>1</v>
       </c>
       <c r="J116">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="K116">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L116">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="M116" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -12950,10 +12953,10 @@
         <v>[]</v>
       </c>
       <c r="P116">
-        <v>614</v>
+        <v>252</v>
       </c>
       <c r="Q116">
-        <v>395</v>
+        <v>231</v>
       </c>
       <c r="R116" t="str">
         <v>[1,800]</v>
@@ -13021,7 +13024,7 @@
         <v>30017</v>
       </c>
       <c r="C117" t="str">
-        <v>韩暹-骑兵 T3</v>
+        <v>杨奉-骑兵 T3</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -13030,7 +13033,7 @@
         <v>1</v>
       </c>
       <c r="F117">
-        <v>831</v>
+        <v>305</v>
       </c>
       <c r="G117">
         <v>5</v>
@@ -13042,10 +13045,10 @@
         <v>1</v>
       </c>
       <c r="J117">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="K117">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L117">
         <v>1.16</v>
@@ -13060,10 +13063,10 @@
         <v>[]</v>
       </c>
       <c r="P117">
-        <v>620</v>
+        <v>255</v>
       </c>
       <c r="Q117">
-        <v>409</v>
+        <v>201</v>
       </c>
       <c r="R117" t="str">
         <v>[1,800]</v>
@@ -13131,7 +13134,7 @@
         <v>30018</v>
       </c>
       <c r="C118" t="str">
-        <v>杨奉-骑兵 T3</v>
+        <v>赵云-骑兵 T3</v>
       </c>
       <c r="D118">
         <v>2</v>
@@ -13140,7 +13143,7 @@
         <v>1</v>
       </c>
       <c r="F118">
-        <v>674</v>
+        <v>300</v>
       </c>
       <c r="G118">
         <v>5</v>
@@ -13152,13 +13155,13 @@
         <v>1</v>
       </c>
       <c r="J118">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="K118">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L118">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="M118" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13170,10 +13173,10 @@
         <v>[]</v>
       </c>
       <c r="P118">
-        <v>627</v>
+        <v>251</v>
       </c>
       <c r="Q118">
-        <v>415</v>
+        <v>237</v>
       </c>
       <c r="R118" t="str">
         <v>[1,800]</v>
@@ -13241,7 +13244,7 @@
         <v>30019</v>
       </c>
       <c r="C119" t="str">
-        <v>张横-骑兵 T3</v>
+        <v>马休-骑兵 T3</v>
       </c>
       <c r="D119">
         <v>2</v>
@@ -13250,7 +13253,7 @@
         <v>1</v>
       </c>
       <c r="F119">
-        <v>736</v>
+        <v>286</v>
       </c>
       <c r="G119">
         <v>5</v>
@@ -13262,13 +13265,13 @@
         <v>1</v>
       </c>
       <c r="J119">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="K119">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L119">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="M119" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13280,10 +13283,10 @@
         <v>[]</v>
       </c>
       <c r="P119">
-        <v>616</v>
+        <v>246</v>
       </c>
       <c r="Q119">
-        <v>448</v>
+        <v>228</v>
       </c>
       <c r="R119" t="str">
         <v>[1,800]</v>
@@ -13351,7 +13354,7 @@
         <v>30020</v>
       </c>
       <c r="C120" t="str">
-        <v>严政-骑兵 T3</v>
+        <v>牛辅-骑兵 T3</v>
       </c>
       <c r="D120">
         <v>2</v>
@@ -13360,7 +13363,7 @@
         <v>1</v>
       </c>
       <c r="F120">
-        <v>673</v>
+        <v>304</v>
       </c>
       <c r="G120">
         <v>5</v>
@@ -13372,13 +13375,13 @@
         <v>1</v>
       </c>
       <c r="J120">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="K120">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L120">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="M120" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13390,10 +13393,10 @@
         <v>[]</v>
       </c>
       <c r="P120">
-        <v>603</v>
+        <v>241</v>
       </c>
       <c r="Q120">
-        <v>400</v>
+        <v>209</v>
       </c>
       <c r="R120" t="str">
         <v>[1,800]</v>
@@ -13461,7 +13464,7 @@
         <v>30021</v>
       </c>
       <c r="C121" t="str">
-        <v>吕玲绮-骑兵 T3</v>
+        <v>李堪-骑兵 T3</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -13470,7 +13473,7 @@
         <v>1</v>
       </c>
       <c r="F121">
-        <v>595</v>
+        <v>330</v>
       </c>
       <c r="G121">
         <v>5</v>
@@ -13482,13 +13485,13 @@
         <v>1</v>
       </c>
       <c r="J121">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K121">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L121">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="M121" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13500,10 +13503,10 @@
         <v>[]</v>
       </c>
       <c r="P121">
-        <v>604</v>
+        <v>255</v>
       </c>
       <c r="Q121">
-        <v>448</v>
+        <v>240</v>
       </c>
       <c r="R121" t="str">
         <v>[1,800]</v>
@@ -13571,7 +13574,7 @@
         <v>30022</v>
       </c>
       <c r="C122" t="str">
-        <v>杨秋-骑兵 T3</v>
+        <v>成公英-骑兵 T3</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -13580,7 +13583,7 @@
         <v>1</v>
       </c>
       <c r="F122">
-        <v>691</v>
+        <v>297</v>
       </c>
       <c r="G122">
         <v>5</v>
@@ -13592,13 +13595,13 @@
         <v>1</v>
       </c>
       <c r="J122">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="K122">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L122">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="M122" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13610,10 +13613,10 @@
         <v>[]</v>
       </c>
       <c r="P122">
-        <v>629</v>
+        <v>254</v>
       </c>
       <c r="Q122">
-        <v>415</v>
+        <v>199</v>
       </c>
       <c r="R122" t="str">
         <v>[1,800]</v>
@@ -13681,7 +13684,7 @@
         <v>30023</v>
       </c>
       <c r="C123" t="str">
-        <v>花鬘-骑兵 T3</v>
+        <v>库察-骑兵 T3</v>
       </c>
       <c r="D123">
         <v>2</v>
@@ -13690,7 +13693,7 @@
         <v>1</v>
       </c>
       <c r="F123">
-        <v>895</v>
+        <v>306</v>
       </c>
       <c r="G123">
         <v>5</v>
@@ -13702,13 +13705,13 @@
         <v>1</v>
       </c>
       <c r="J123">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="K123">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L123">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M123" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13720,10 +13723,10 @@
         <v>[]</v>
       </c>
       <c r="P123">
-        <v>628</v>
+        <v>252</v>
       </c>
       <c r="Q123">
-        <v>412</v>
+        <v>220</v>
       </c>
       <c r="R123" t="str">
         <v>[1,800]</v>
@@ -13791,7 +13794,7 @@
         <v>30024</v>
       </c>
       <c r="C124" t="str">
-        <v>马超-骑兵 T3</v>
+        <v>郭淮-骑兵 T3</v>
       </c>
       <c r="D124">
         <v>2</v>
@@ -13800,7 +13803,7 @@
         <v>1</v>
       </c>
       <c r="F124">
-        <v>708</v>
+        <v>339</v>
       </c>
       <c r="G124">
         <v>5</v>
@@ -13812,13 +13815,13 @@
         <v>1</v>
       </c>
       <c r="J124">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="K124">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L124">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="M124" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13830,10 +13833,10 @@
         <v>[]</v>
       </c>
       <c r="P124">
-        <v>624</v>
+        <v>252</v>
       </c>
       <c r="Q124">
-        <v>400</v>
+        <v>227</v>
       </c>
       <c r="R124" t="str">
         <v>[1,800]</v>
@@ -13901,7 +13904,7 @@
         <v>30025</v>
       </c>
       <c r="C125" t="str">
-        <v>夏侯渊-骑兵 T4</v>
+        <v>吕布-骑兵 T4</v>
       </c>
       <c r="D125">
         <v>2</v>
@@ -13910,7 +13913,7 @@
         <v>1</v>
       </c>
       <c r="F125">
-        <v>873</v>
+        <v>466</v>
       </c>
       <c r="G125">
         <v>6</v>
@@ -13922,13 +13925,13 @@
         <v>1</v>
       </c>
       <c r="J125">
-        <v>244</v>
+        <v>299</v>
       </c>
       <c r="K125">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L125">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="M125" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -13940,10 +13943,10 @@
         <v>[]</v>
       </c>
       <c r="P125">
-        <v>618</v>
+        <v>254</v>
       </c>
       <c r="Q125">
-        <v>378</v>
+        <v>218</v>
       </c>
       <c r="R125" t="str">
         <v>[1,800]</v>
@@ -14011,7 +14014,7 @@
         <v>30026</v>
       </c>
       <c r="C126" t="str">
-        <v>兀突骨-骑兵 T4</v>
+        <v>楼班-骑兵 T4</v>
       </c>
       <c r="D126">
         <v>2</v>
@@ -14020,7 +14023,7 @@
         <v>1</v>
       </c>
       <c r="F126">
-        <v>1057</v>
+        <v>479</v>
       </c>
       <c r="G126">
         <v>6</v>
@@ -14032,13 +14035,13 @@
         <v>1</v>
       </c>
       <c r="J126">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="K126">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L126">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="M126" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14050,10 +14053,10 @@
         <v>[]</v>
       </c>
       <c r="P126">
-        <v>640</v>
+        <v>243</v>
       </c>
       <c r="Q126">
-        <v>416</v>
+        <v>241</v>
       </c>
       <c r="R126" t="str">
         <v>[1,800]</v>
@@ -14121,7 +14124,7 @@
         <v>30027</v>
       </c>
       <c r="C127" t="str">
-        <v>吕蒙-骑兵 T4</v>
+        <v>李儒-骑兵 T4</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -14130,7 +14133,7 @@
         <v>1</v>
       </c>
       <c r="F127">
-        <v>971</v>
+        <v>514</v>
       </c>
       <c r="G127">
         <v>6</v>
@@ -14142,13 +14145,13 @@
         <v>1</v>
       </c>
       <c r="J127">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="K127">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L127">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="M127" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14160,10 +14163,10 @@
         <v>[]</v>
       </c>
       <c r="P127">
-        <v>626</v>
+        <v>245</v>
       </c>
       <c r="Q127">
-        <v>384</v>
+        <v>216</v>
       </c>
       <c r="R127" t="str">
         <v>[1,800]</v>
@@ -14231,7 +14234,7 @@
         <v>30028</v>
       </c>
       <c r="C128" t="str">
-        <v>库察-骑兵 T4</v>
+        <v>蹋顿-骑兵 T4</v>
       </c>
       <c r="D128">
         <v>2</v>
@@ -14240,7 +14243,7 @@
         <v>1</v>
       </c>
       <c r="F128">
-        <v>1012</v>
+        <v>353</v>
       </c>
       <c r="G128">
         <v>6</v>
@@ -14252,13 +14255,13 @@
         <v>1</v>
       </c>
       <c r="J128">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="K128">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L128">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="M128" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14270,10 +14273,10 @@
         <v>[]</v>
       </c>
       <c r="P128">
-        <v>632</v>
+        <v>242</v>
       </c>
       <c r="Q128">
-        <v>441</v>
+        <v>205</v>
       </c>
       <c r="R128" t="str">
         <v>[1,800]</v>
@@ -14341,7 +14344,7 @@
         <v>30029</v>
       </c>
       <c r="C129" t="str">
-        <v>李傕-骑兵 T4</v>
+        <v>张辽-骑兵 T4</v>
       </c>
       <c r="D129">
         <v>2</v>
@@ -14350,7 +14353,7 @@
         <v>1</v>
       </c>
       <c r="F129">
-        <v>911</v>
+        <v>375</v>
       </c>
       <c r="G129">
         <v>6</v>
@@ -14362,13 +14365,13 @@
         <v>1</v>
       </c>
       <c r="J129">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="K129">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L129">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="M129" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14380,10 +14383,10 @@
         <v>[]</v>
       </c>
       <c r="P129">
-        <v>639</v>
+        <v>242</v>
       </c>
       <c r="Q129">
-        <v>388</v>
+        <v>216</v>
       </c>
       <c r="R129" t="str">
         <v>[1,800]</v>
@@ -14451,7 +14454,7 @@
         <v>30030</v>
       </c>
       <c r="C130" t="str">
-        <v>马云禄-骑兵 T4</v>
+        <v>程远志-骑兵 T4</v>
       </c>
       <c r="D130">
         <v>2</v>
@@ -14460,7 +14463,7 @@
         <v>1</v>
       </c>
       <c r="F130">
-        <v>1004</v>
+        <v>411</v>
       </c>
       <c r="G130">
         <v>6</v>
@@ -14472,13 +14475,13 @@
         <v>1</v>
       </c>
       <c r="J130">
-        <v>347</v>
+        <v>248</v>
       </c>
       <c r="K130">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L130">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="M130" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14490,10 +14493,10 @@
         <v>[]</v>
       </c>
       <c r="P130">
-        <v>623</v>
+        <v>248</v>
       </c>
       <c r="Q130">
-        <v>389</v>
+        <v>229</v>
       </c>
       <c r="R130" t="str">
         <v>[1,800]</v>
@@ -14561,7 +14564,7 @@
         <v>30031</v>
       </c>
       <c r="C131" t="str">
-        <v>公孙瓒-骑兵 T4</v>
+        <v>夏侯惇-骑兵 T4</v>
       </c>
       <c r="D131">
         <v>2</v>
@@ -14570,7 +14573,7 @@
         <v>1</v>
       </c>
       <c r="F131">
-        <v>906</v>
+        <v>506</v>
       </c>
       <c r="G131">
         <v>6</v>
@@ -14582,13 +14585,13 @@
         <v>1</v>
       </c>
       <c r="J131">
-        <v>243</v>
+        <v>354</v>
       </c>
       <c r="K131">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L131">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="M131" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14600,10 +14603,10 @@
         <v>[]</v>
       </c>
       <c r="P131">
-        <v>638</v>
+        <v>251</v>
       </c>
       <c r="Q131">
-        <v>397</v>
+        <v>211</v>
       </c>
       <c r="R131" t="str">
         <v>[1,800]</v>
@@ -14671,7 +14674,7 @@
         <v>30032</v>
       </c>
       <c r="C132" t="str">
-        <v>波才-骑兵 T4</v>
+        <v>韩暹-骑兵 T4</v>
       </c>
       <c r="D132">
         <v>2</v>
@@ -14680,7 +14683,7 @@
         <v>1</v>
       </c>
       <c r="F132">
-        <v>1023</v>
+        <v>434</v>
       </c>
       <c r="G132">
         <v>6</v>
@@ -14692,13 +14695,13 @@
         <v>1</v>
       </c>
       <c r="J132">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="K132">
         <v>39</v>
       </c>
       <c r="L132">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="M132" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14710,10 +14713,10 @@
         <v>[]</v>
       </c>
       <c r="P132">
-        <v>618</v>
+        <v>255</v>
       </c>
       <c r="Q132">
-        <v>408</v>
+        <v>204</v>
       </c>
       <c r="R132" t="str">
         <v>[1,800]</v>
@@ -14781,7 +14784,7 @@
         <v>40001</v>
       </c>
       <c r="C133" t="str">
-        <v>黄权-长枪兵 T1</v>
+        <v>郝昭-长枪兵 T1</v>
       </c>
       <c r="D133">
         <v>3</v>
@@ -14790,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="F133">
-        <v>287</v>
+        <v>125</v>
       </c>
       <c r="G133">
         <v>3</v>
@@ -14802,13 +14805,13 @@
         <v>1</v>
       </c>
       <c r="J133">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="K133">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L133">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="M133" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14820,10 +14823,10 @@
         <v>[]</v>
       </c>
       <c r="P133">
-        <v>470</v>
+        <v>191</v>
       </c>
       <c r="Q133">
-        <v>444</v>
+        <v>228</v>
       </c>
       <c r="R133" t="str">
         <v>[1,800]</v>
@@ -14891,7 +14894,7 @@
         <v>40002</v>
       </c>
       <c r="C134" t="str">
-        <v>郝萌-长枪兵 T1</v>
+        <v>吕据-长枪兵 T1</v>
       </c>
       <c r="D134">
         <v>3</v>
@@ -14900,7 +14903,7 @@
         <v>1</v>
       </c>
       <c r="F134">
-        <v>246</v>
+        <v>138</v>
       </c>
       <c r="G134">
         <v>3</v>
@@ -14912,13 +14915,13 @@
         <v>1</v>
       </c>
       <c r="J134">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="K134">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L134">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="M134" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -14930,10 +14933,10 @@
         <v>[]</v>
       </c>
       <c r="P134">
-        <v>467</v>
+        <v>192</v>
       </c>
       <c r="Q134">
-        <v>449</v>
+        <v>271</v>
       </c>
       <c r="R134" t="str">
         <v>[1,800]</v>
@@ -15001,7 +15004,7 @@
         <v>40003</v>
       </c>
       <c r="C135" t="str">
-        <v>孟达-长枪兵 T1</v>
+        <v>泠苞-长枪兵 T1</v>
       </c>
       <c r="D135">
         <v>3</v>
@@ -15010,7 +15013,7 @@
         <v>1</v>
       </c>
       <c r="F135">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="G135">
         <v>3</v>
@@ -15022,13 +15025,13 @@
         <v>1</v>
       </c>
       <c r="J135">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="K135">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L135">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="M135" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15040,10 +15043,10 @@
         <v>[]</v>
       </c>
       <c r="P135">
-        <v>473</v>
+        <v>188</v>
       </c>
       <c r="Q135">
-        <v>484</v>
+        <v>240</v>
       </c>
       <c r="R135" t="str">
         <v>[1,800]</v>
@@ -15111,7 +15114,7 @@
         <v>40004</v>
       </c>
       <c r="C136" t="str">
-        <v>宋宪-长枪兵 T1</v>
+        <v>纪灵-长枪兵 T1</v>
       </c>
       <c r="D136">
         <v>3</v>
@@ -15120,7 +15123,7 @@
         <v>1</v>
       </c>
       <c r="F136">
-        <v>264</v>
+        <v>131</v>
       </c>
       <c r="G136">
         <v>3</v>
@@ -15132,13 +15135,13 @@
         <v>1</v>
       </c>
       <c r="J136">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="K136">
         <v>16</v>
       </c>
       <c r="L136">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="M136" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15150,10 +15153,10 @@
         <v>[]</v>
       </c>
       <c r="P136">
-        <v>477</v>
+        <v>185</v>
       </c>
       <c r="Q136">
-        <v>425</v>
+        <v>240</v>
       </c>
       <c r="R136" t="str">
         <v>[1,800]</v>
@@ -15221,7 +15224,7 @@
         <v>40005</v>
       </c>
       <c r="C137" t="str">
-        <v>侯成-长枪兵 T1</v>
+        <v>文钦-长枪兵 T1</v>
       </c>
       <c r="D137">
         <v>3</v>
@@ -15230,7 +15233,7 @@
         <v>1</v>
       </c>
       <c r="F137">
-        <v>276</v>
+        <v>129</v>
       </c>
       <c r="G137">
         <v>3</v>
@@ -15242,13 +15245,13 @@
         <v>1</v>
       </c>
       <c r="J137">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="K137">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L137">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="M137" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15260,10 +15263,10 @@
         <v>[]</v>
       </c>
       <c r="P137">
-        <v>461</v>
+        <v>186</v>
       </c>
       <c r="Q137">
-        <v>417</v>
+        <v>258</v>
       </c>
       <c r="R137" t="str">
         <v>[1,800]</v>
@@ -15331,7 +15334,7 @@
         <v>40006</v>
       </c>
       <c r="C138" t="str">
-        <v>钟会-长枪兵 T1</v>
+        <v>吴懿-长枪兵 T1</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -15340,7 +15343,7 @@
         <v>1</v>
       </c>
       <c r="F138">
-        <v>234</v>
+        <v>114</v>
       </c>
       <c r="G138">
         <v>3</v>
@@ -15352,13 +15355,13 @@
         <v>1</v>
       </c>
       <c r="J138">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="K138">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L138">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="M138" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15370,10 +15373,10 @@
         <v>[]</v>
       </c>
       <c r="P138">
-        <v>474</v>
+        <v>191</v>
       </c>
       <c r="Q138">
-        <v>414</v>
+        <v>259</v>
       </c>
       <c r="R138" t="str">
         <v>[1,800]</v>
@@ -15441,7 +15444,7 @@
         <v>40007</v>
       </c>
       <c r="C139" t="str">
-        <v>纪灵-长枪兵 T2</v>
+        <v>魏续-长枪兵 T2</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -15450,7 +15453,7 @@
         <v>1</v>
       </c>
       <c r="F139">
-        <v>509</v>
+        <v>173</v>
       </c>
       <c r="G139">
         <v>4</v>
@@ -15462,13 +15465,13 @@
         <v>1</v>
       </c>
       <c r="J139">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="K139">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L139">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="M139" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15480,10 +15483,10 @@
         <v>[]</v>
       </c>
       <c r="P139">
-        <v>481</v>
+        <v>195</v>
       </c>
       <c r="Q139">
-        <v>473</v>
+        <v>248</v>
       </c>
       <c r="R139" t="str">
         <v>[1,800]</v>
@@ -15551,7 +15554,7 @@
         <v>40008</v>
       </c>
       <c r="C140" t="str">
-        <v>成廉-长枪兵 T2</v>
+        <v>严颜-长枪兵 T2</v>
       </c>
       <c r="D140">
         <v>3</v>
@@ -15560,7 +15563,7 @@
         <v>1</v>
       </c>
       <c r="F140">
-        <v>441</v>
+        <v>164</v>
       </c>
       <c r="G140">
         <v>4</v>
@@ -15572,13 +15575,13 @@
         <v>1</v>
       </c>
       <c r="J140">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="K140">
         <v>19</v>
       </c>
       <c r="L140">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="M140" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15590,10 +15593,10 @@
         <v>[]</v>
       </c>
       <c r="P140">
-        <v>483</v>
+        <v>185</v>
       </c>
       <c r="Q140">
-        <v>450</v>
+        <v>256</v>
       </c>
       <c r="R140" t="str">
         <v>[1,800]</v>
@@ -15661,7 +15664,7 @@
         <v>40009</v>
       </c>
       <c r="C141" t="str">
-        <v>张嶷-长枪兵 T2</v>
+        <v>邢道荣-长枪兵 T2</v>
       </c>
       <c r="D141">
         <v>3</v>
@@ -15670,7 +15673,7 @@
         <v>1</v>
       </c>
       <c r="F141">
-        <v>482</v>
+        <v>204</v>
       </c>
       <c r="G141">
         <v>4</v>
@@ -15682,13 +15685,13 @@
         <v>1</v>
       </c>
       <c r="J141">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="K141">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L141">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="M141" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15700,10 +15703,10 @@
         <v>[]</v>
       </c>
       <c r="P141">
-        <v>481</v>
+        <v>190</v>
       </c>
       <c r="Q141">
-        <v>410</v>
+        <v>226</v>
       </c>
       <c r="R141" t="str">
         <v>[1,800]</v>
@@ -15771,7 +15774,7 @@
         <v>40010</v>
       </c>
       <c r="C142" t="str">
-        <v>邢道荣-长枪兵 T2</v>
+        <v>陈泰-长枪兵 T2</v>
       </c>
       <c r="D142">
         <v>3</v>
@@ -15780,7 +15783,7 @@
         <v>1</v>
       </c>
       <c r="F142">
-        <v>438</v>
+        <v>237</v>
       </c>
       <c r="G142">
         <v>4</v>
@@ -15792,13 +15795,13 @@
         <v>1</v>
       </c>
       <c r="J142">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="K142">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L142">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="M142" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15810,10 +15813,10 @@
         <v>[]</v>
       </c>
       <c r="P142">
-        <v>461</v>
+        <v>195</v>
       </c>
       <c r="Q142">
-        <v>471</v>
+        <v>258</v>
       </c>
       <c r="R142" t="str">
         <v>[1,800]</v>
@@ -15881,7 +15884,7 @@
         <v>40011</v>
       </c>
       <c r="C143" t="str">
-        <v>陈应-长枪兵 T2</v>
+        <v>宋宪-长枪兵 T2</v>
       </c>
       <c r="D143">
         <v>3</v>
@@ -15890,7 +15893,7 @@
         <v>1</v>
       </c>
       <c r="F143">
-        <v>392</v>
+        <v>227</v>
       </c>
       <c r="G143">
         <v>4</v>
@@ -15902,13 +15905,13 @@
         <v>1</v>
       </c>
       <c r="J143">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="K143">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L143">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="M143" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -15920,10 +15923,10 @@
         <v>[]</v>
       </c>
       <c r="P143">
-        <v>464</v>
+        <v>193</v>
       </c>
       <c r="Q143">
-        <v>437</v>
+        <v>260</v>
       </c>
       <c r="R143" t="str">
         <v>[1,800]</v>
@@ -15991,7 +15994,7 @@
         <v>40012</v>
       </c>
       <c r="C144" t="str">
-        <v>陈到-长枪兵 T2</v>
+        <v>张嶷-长枪兵 T2</v>
       </c>
       <c r="D144">
         <v>3</v>
@@ -16000,7 +16003,7 @@
         <v>1</v>
       </c>
       <c r="F144">
-        <v>519</v>
+        <v>233</v>
       </c>
       <c r="G144">
         <v>4</v>
@@ -16012,13 +16015,13 @@
         <v>1</v>
       </c>
       <c r="J144">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="K144">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L144">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="M144" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16030,10 +16033,10 @@
         <v>[]</v>
       </c>
       <c r="P144">
-        <v>482</v>
+        <v>189</v>
       </c>
       <c r="Q144">
-        <v>417</v>
+        <v>265</v>
       </c>
       <c r="R144" t="str">
         <v>[1,800]</v>
@@ -16101,7 +16104,7 @@
         <v>40013</v>
       </c>
       <c r="C145" t="str">
-        <v>金旋-长枪兵 T3</v>
+        <v>李严-长枪兵 T3</v>
       </c>
       <c r="D145">
         <v>3</v>
@@ -16110,7 +16113,7 @@
         <v>1</v>
       </c>
       <c r="F145">
-        <v>813</v>
+        <v>309</v>
       </c>
       <c r="G145">
         <v>5</v>
@@ -16122,13 +16125,13 @@
         <v>1</v>
       </c>
       <c r="J145">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="K145">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L145">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="M145" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16140,10 +16143,10 @@
         <v>[]</v>
       </c>
       <c r="P145">
-        <v>470</v>
+        <v>186</v>
       </c>
       <c r="Q145">
-        <v>408</v>
+        <v>268</v>
       </c>
       <c r="R145" t="str">
         <v>[1,800]</v>
@@ -16211,7 +16214,7 @@
         <v>40014</v>
       </c>
       <c r="C146" t="str">
-        <v>王基-长枪兵 T3</v>
+        <v>沙摩柯-长枪兵 T3</v>
       </c>
       <c r="D146">
         <v>3</v>
@@ -16220,7 +16223,7 @@
         <v>1</v>
       </c>
       <c r="F146">
-        <v>701</v>
+        <v>356</v>
       </c>
       <c r="G146">
         <v>5</v>
@@ -16232,13 +16235,13 @@
         <v>1</v>
       </c>
       <c r="J146">
-        <v>160</v>
+        <v>234</v>
       </c>
       <c r="K146">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L146">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="M146" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16250,10 +16253,10 @@
         <v>[]</v>
       </c>
       <c r="P146">
-        <v>467</v>
+        <v>195</v>
       </c>
       <c r="Q146">
-        <v>459</v>
+        <v>257</v>
       </c>
       <c r="R146" t="str">
         <v>[1,800]</v>
@@ -16321,7 +16324,7 @@
         <v>40015</v>
       </c>
       <c r="C147" t="str">
-        <v>唐咨-长枪兵 T3</v>
+        <v>成廉-长枪兵 T3</v>
       </c>
       <c r="D147">
         <v>3</v>
@@ -16330,7 +16333,7 @@
         <v>1</v>
       </c>
       <c r="F147">
-        <v>723</v>
+        <v>324</v>
       </c>
       <c r="G147">
         <v>5</v>
@@ -16342,13 +16345,13 @@
         <v>1</v>
       </c>
       <c r="J147">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="K147">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L147">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M147" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16360,10 +16363,10 @@
         <v>[]</v>
       </c>
       <c r="P147">
-        <v>474</v>
+        <v>189</v>
       </c>
       <c r="Q147">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="R147" t="str">
         <v>[1,800]</v>
@@ -16431,7 +16434,7 @@
         <v>40016</v>
       </c>
       <c r="C148" t="str">
-        <v>吕据-长枪兵 T3</v>
+        <v>高翔-长枪兵 T3</v>
       </c>
       <c r="D148">
         <v>3</v>
@@ -16440,7 +16443,7 @@
         <v>1</v>
       </c>
       <c r="F148">
-        <v>789</v>
+        <v>278</v>
       </c>
       <c r="G148">
         <v>5</v>
@@ -16452,13 +16455,13 @@
         <v>1</v>
       </c>
       <c r="J148">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="K148">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L148">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="M148" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16470,10 +16473,10 @@
         <v>[]</v>
       </c>
       <c r="P148">
-        <v>475</v>
+        <v>188</v>
       </c>
       <c r="Q148">
-        <v>484</v>
+        <v>271</v>
       </c>
       <c r="R148" t="str">
         <v>[1,800]</v>
@@ -16541,7 +16544,7 @@
         <v>40017</v>
       </c>
       <c r="C149" t="str">
-        <v>李严-长枪兵 T3</v>
+        <v>郝萌-长枪兵 T3</v>
       </c>
       <c r="D149">
         <v>3</v>
@@ -16550,7 +16553,7 @@
         <v>1</v>
       </c>
       <c r="F149">
-        <v>806</v>
+        <v>300</v>
       </c>
       <c r="G149">
         <v>5</v>
@@ -16562,13 +16565,13 @@
         <v>1</v>
       </c>
       <c r="J149">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="K149">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L149">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="M149" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16580,10 +16583,10 @@
         <v>[]</v>
       </c>
       <c r="P149">
-        <v>475</v>
+        <v>193</v>
       </c>
       <c r="Q149">
-        <v>447</v>
+        <v>257</v>
       </c>
       <c r="R149" t="str">
         <v>[1,800]</v>
@@ -16651,7 +16654,7 @@
         <v>40018</v>
       </c>
       <c r="C150" t="str">
-        <v>诸葛诞-长枪兵 T3</v>
+        <v>朱然-长枪兵 T3</v>
       </c>
       <c r="D150">
         <v>3</v>
@@ -16660,7 +16663,7 @@
         <v>1</v>
       </c>
       <c r="F150">
-        <v>819</v>
+        <v>332</v>
       </c>
       <c r="G150">
         <v>5</v>
@@ -16672,13 +16675,13 @@
         <v>1</v>
       </c>
       <c r="J150">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="K150">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L150">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="M150" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16690,10 +16693,10 @@
         <v>[]</v>
       </c>
       <c r="P150">
-        <v>476</v>
+        <v>192</v>
       </c>
       <c r="Q150">
-        <v>445</v>
+        <v>228</v>
       </c>
       <c r="R150" t="str">
         <v>[1,800]</v>
@@ -16761,7 +16764,7 @@
         <v>40019</v>
       </c>
       <c r="C151" t="str">
-        <v>吴懿-长枪兵 T4</v>
+        <v>杨龄-长枪兵 T4</v>
       </c>
       <c r="D151">
         <v>3</v>
@@ -16770,7 +16773,7 @@
         <v>1</v>
       </c>
       <c r="F151">
-        <v>1130</v>
+        <v>423</v>
       </c>
       <c r="G151">
         <v>6</v>
@@ -16782,10 +16785,10 @@
         <v>1</v>
       </c>
       <c r="J151">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="K151">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L151">
         <v>1.07</v>
@@ -16800,10 +16803,10 @@
         <v>[]</v>
       </c>
       <c r="P151">
-        <v>471</v>
+        <v>188</v>
       </c>
       <c r="Q151">
-        <v>447</v>
+        <v>252</v>
       </c>
       <c r="R151" t="str">
         <v>[1,800]</v>
@@ -16871,7 +16874,7 @@
         <v>40020</v>
       </c>
       <c r="C152" t="str">
-        <v>孙礼-长枪兵 T4</v>
+        <v>卓膺-长枪兵 T4</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -16880,7 +16883,7 @@
         <v>1</v>
       </c>
       <c r="F152">
-        <v>935</v>
+        <v>459</v>
       </c>
       <c r="G152">
         <v>6</v>
@@ -16892,13 +16895,13 @@
         <v>1</v>
       </c>
       <c r="J152">
-        <v>228</v>
+        <v>276</v>
       </c>
       <c r="K152">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L152">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="M152" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -16910,10 +16913,10 @@
         <v>[]</v>
       </c>
       <c r="P152">
-        <v>486</v>
+        <v>188</v>
       </c>
       <c r="Q152">
-        <v>479</v>
+        <v>261</v>
       </c>
       <c r="R152" t="str">
         <v>[1,800]</v>
@@ -16981,7 +16984,7 @@
         <v>40021</v>
       </c>
       <c r="C153" t="str">
-        <v>泠苞-长枪兵 T4</v>
+        <v>邓贤-长枪兵 T4</v>
       </c>
       <c r="D153">
         <v>3</v>
@@ -16990,7 +16993,7 @@
         <v>1</v>
       </c>
       <c r="F153">
-        <v>1050</v>
+        <v>531</v>
       </c>
       <c r="G153">
         <v>6</v>
@@ -17002,13 +17005,13 @@
         <v>1</v>
       </c>
       <c r="J153">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="K153">
         <v>41</v>
       </c>
       <c r="L153">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="M153" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17020,10 +17023,10 @@
         <v>[]</v>
       </c>
       <c r="P153">
-        <v>475</v>
+        <v>188</v>
       </c>
       <c r="Q153">
-        <v>422</v>
+        <v>266</v>
       </c>
       <c r="R153" t="str">
         <v>[1,800]</v>
@@ -17091,7 +17094,7 @@
         <v>40022</v>
       </c>
       <c r="C154" t="str">
-        <v>彭羕-长枪兵 T4</v>
+        <v>张飞-长枪兵 T4</v>
       </c>
       <c r="D154">
         <v>3</v>
@@ -17100,7 +17103,7 @@
         <v>1</v>
       </c>
       <c r="F154">
-        <v>875</v>
+        <v>461</v>
       </c>
       <c r="G154">
         <v>6</v>
@@ -17112,13 +17115,13 @@
         <v>1</v>
       </c>
       <c r="J154">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="K154">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L154">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="M154" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17130,10 +17133,10 @@
         <v>[]</v>
       </c>
       <c r="P154">
-        <v>476</v>
+        <v>191</v>
       </c>
       <c r="Q154">
-        <v>475</v>
+        <v>260</v>
       </c>
       <c r="R154" t="str">
         <v>[1,800]</v>
@@ -17201,7 +17204,7 @@
         <v>40023</v>
       </c>
       <c r="C155" t="str">
-        <v>句扶-长枪兵 T4</v>
+        <v>黄权-长枪兵 T4</v>
       </c>
       <c r="D155">
         <v>3</v>
@@ -17210,7 +17213,7 @@
         <v>1</v>
       </c>
       <c r="F155">
-        <v>1028</v>
+        <v>504</v>
       </c>
       <c r="G155">
         <v>6</v>
@@ -17222,13 +17225,13 @@
         <v>1</v>
       </c>
       <c r="J155">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="K155">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L155">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="M155" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17240,10 +17243,10 @@
         <v>[]</v>
       </c>
       <c r="P155">
-        <v>471</v>
+        <v>194</v>
       </c>
       <c r="Q155">
-        <v>450</v>
+        <v>267</v>
       </c>
       <c r="R155" t="str">
         <v>[1,800]</v>
@@ -17320,7 +17323,7 @@
         <v>1</v>
       </c>
       <c r="F156">
-        <v>1037</v>
+        <v>423</v>
       </c>
       <c r="G156">
         <v>6</v>
@@ -17332,13 +17335,13 @@
         <v>1</v>
       </c>
       <c r="J156">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="K156">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="L156">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="M156" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -17350,10 +17353,10 @@
         <v>[]</v>
       </c>
       <c r="P156">
-        <v>483</v>
+        <v>185</v>
       </c>
       <c r="Q156">
-        <v>482</v>
+        <v>259</v>
       </c>
       <c r="R156" t="str">
         <v>[1,800]</v>
@@ -18253,7 +18256,7 @@
         <v>50001</v>
       </c>
       <c r="C165" t="str">
-        <v>诸葛亮-法师 T1</v>
+        <v>陆逊-法师 T1</v>
       </c>
       <c r="D165">
         <v>4</v>
@@ -18262,7 +18265,7 @@
         <v>1</v>
       </c>
       <c r="F165">
-        <v>227</v>
+        <v>132</v>
       </c>
       <c r="G165">
         <v>3</v>
@@ -18274,13 +18277,13 @@
         <v>15</v>
       </c>
       <c r="J165">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K165">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L165">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M165" t="str">
         <v>[[2,252],[20,378],[40,504],[60,630],[80,756],[100,882],[120,1008],[140,1134],[160,1260],[180,1386],[200,1512]]</v>
@@ -18292,10 +18295,10 @@
         <v>[]</v>
       </c>
       <c r="P165">
-        <v>365</v>
+        <v>147</v>
       </c>
       <c r="Q165">
-        <v>1909</v>
+        <v>1891</v>
       </c>
       <c r="R165" t="str">
         <v>[1,800]</v>
@@ -18363,7 +18366,7 @@
         <v>50002</v>
       </c>
       <c r="C166" t="str">
-        <v>糜芳-法师 T1</v>
+        <v>太史慈-法师 T1</v>
       </c>
       <c r="D166">
         <v>4</v>
@@ -18372,7 +18375,7 @@
         <v>1</v>
       </c>
       <c r="F166">
-        <v>251</v>
+        <v>109</v>
       </c>
       <c r="G166">
         <v>3</v>
@@ -18384,13 +18387,13 @@
         <v>20</v>
       </c>
       <c r="J166">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K166">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L166">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="M166" t="str">
         <v>[[2,239],[20,359],[40,478],[60,598],[80,718],[100,837],[120,957],[140,1076],[160,1196],[180,1316],[200,1435]]</v>
@@ -18402,10 +18405,10 @@
         <v>[]</v>
       </c>
       <c r="P166">
-        <v>367</v>
+        <v>141</v>
       </c>
       <c r="Q166">
-        <v>2054</v>
+        <v>1956</v>
       </c>
       <c r="R166" t="str">
         <v>[1,800]</v>
@@ -18473,7 +18476,7 @@
         <v>50003</v>
       </c>
       <c r="C167" t="str">
-        <v>周瑜-法师 T1</v>
+        <v>管辂-法师 T1</v>
       </c>
       <c r="D167">
         <v>4</v>
@@ -18482,7 +18485,7 @@
         <v>1</v>
       </c>
       <c r="F167">
-        <v>229</v>
+        <v>140</v>
       </c>
       <c r="G167">
         <v>3</v>
@@ -18494,10 +18497,10 @@
         <v>20</v>
       </c>
       <c r="J167">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="K167">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L167">
         <v>1.4</v>
@@ -18512,10 +18515,10 @@
         <v>[]</v>
       </c>
       <c r="P167">
-        <v>379</v>
+        <v>152</v>
       </c>
       <c r="Q167">
-        <v>2138</v>
+        <v>2114</v>
       </c>
       <c r="R167" t="str">
         <v>[1,800]</v>
@@ -18583,7 +18586,7 @@
         <v>50004</v>
       </c>
       <c r="C168" t="str">
-        <v>秦宓-法师 T1</v>
+        <v>孙乾-法师 T1</v>
       </c>
       <c r="D168">
         <v>4</v>
@@ -18592,7 +18595,7 @@
         <v>1</v>
       </c>
       <c r="F168">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="G168">
         <v>3</v>
@@ -18604,13 +18607,13 @@
         <v>20</v>
       </c>
       <c r="J168">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="K168">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L168">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="M168" t="str">
         <v>[[2,347],[20,520],[40,694],[60,867],[80,1041],[100,1214],[120,1387],[140,1561],[160,1734],[180,1908],[200,2081]]</v>
@@ -18622,10 +18625,10 @@
         <v>[]</v>
       </c>
       <c r="P168">
-        <v>352</v>
+        <v>146</v>
       </c>
       <c r="Q168">
-        <v>1989</v>
+        <v>2030</v>
       </c>
       <c r="R168" t="str">
         <v>[1,800]</v>
@@ -18693,7 +18696,7 @@
         <v>50005</v>
       </c>
       <c r="C169" t="str">
-        <v>糜竺-法师 T1</v>
+        <v>简雍-法师 T1</v>
       </c>
       <c r="D169">
         <v>4</v>
@@ -18702,7 +18705,7 @@
         <v>1</v>
       </c>
       <c r="F169">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="G169">
         <v>3</v>
@@ -18714,13 +18717,13 @@
         <v>20</v>
       </c>
       <c r="J169">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K169">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L169">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="M169" t="str">
         <v>[[2,150],[20,224],[40,299],[60,374],[80,449],[100,523],[120,598],[140,673],[160,748],[180,822],[200,897]]</v>
@@ -18732,10 +18735,10 @@
         <v>[]</v>
       </c>
       <c r="P169">
-        <v>345</v>
+        <v>138</v>
       </c>
       <c r="Q169">
-        <v>1801</v>
+        <v>1848</v>
       </c>
       <c r="R169" t="str">
         <v>[1,800]</v>
@@ -18803,7 +18806,7 @@
         <v>50006</v>
       </c>
       <c r="C170" t="str">
-        <v>陈震-法师 T1</v>
+        <v>周瑜-法师 T1</v>
       </c>
       <c r="D170">
         <v>4</v>
@@ -18812,7 +18815,7 @@
         <v>1</v>
       </c>
       <c r="F170">
-        <v>240</v>
+        <v>133</v>
       </c>
       <c r="G170">
         <v>3</v>
@@ -18824,13 +18827,13 @@
         <v>20</v>
       </c>
       <c r="J170">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K170">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L170">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="M170" t="str">
         <v>[[2,275],[20,413],[40,550],[60,688],[80,825],[100,963],[120,1100],[140,1238],[160,1375],[180,1513],[200,1650]]</v>
@@ -18842,10 +18845,10 @@
         <v>[]</v>
       </c>
       <c r="P170">
-        <v>355</v>
+        <v>151</v>
       </c>
       <c r="Q170">
-        <v>1905</v>
+        <v>2142</v>
       </c>
       <c r="R170" t="str">
         <v>[1,800]</v>
@@ -18913,7 +18916,7 @@
         <v>50007</v>
       </c>
       <c r="C171" t="str">
-        <v>步骘-法师 T2</v>
+        <v>董昭-法师 T2</v>
       </c>
       <c r="D171">
         <v>4</v>
@@ -18922,7 +18925,7 @@
         <v>1</v>
       </c>
       <c r="F171">
-        <v>432</v>
+        <v>233</v>
       </c>
       <c r="G171">
         <v>4</v>
@@ -18934,13 +18937,13 @@
         <v>20</v>
       </c>
       <c r="J171">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="K171">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L171">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="M171" t="str">
         <v>[[2,311],[20,466],[40,622],[60,777],[80,933],[100,1088],[120,1244],[140,1399],[160,1555],[180,1710],[200,1866]]</v>
@@ -18952,10 +18955,10 @@
         <v>[]</v>
       </c>
       <c r="P171">
-        <v>362</v>
+        <v>141</v>
       </c>
       <c r="Q171">
-        <v>1855</v>
+        <v>2119</v>
       </c>
       <c r="R171" t="str">
         <v>[1,800]</v>
@@ -19023,7 +19026,7 @@
         <v>50008</v>
       </c>
       <c r="C172" t="str">
-        <v>蒯良-法师 T2</v>
+        <v>王朗-法师 T2</v>
       </c>
       <c r="D172">
         <v>4</v>
@@ -19032,7 +19035,7 @@
         <v>1</v>
       </c>
       <c r="F172">
-        <v>358</v>
+        <v>237</v>
       </c>
       <c r="G172">
         <v>4</v>
@@ -19044,13 +19047,13 @@
         <v>25</v>
       </c>
       <c r="J172">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K172">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L172">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="M172" t="str">
         <v>[[2,594],[20,891],[40,1188],[60,1485],[80,1782],[100,2079],[120,2376],[140,2673],[160,2970],[180,3267],[200,3564]]</v>
@@ -19062,10 +19065,10 @@
         <v>[]</v>
       </c>
       <c r="P172">
-        <v>372</v>
+        <v>145</v>
       </c>
       <c r="Q172">
-        <v>1946</v>
+        <v>2119</v>
       </c>
       <c r="R172" t="str">
         <v>[1,800]</v>
@@ -19133,7 +19136,7 @@
         <v>50009</v>
       </c>
       <c r="C173" t="str">
-        <v>审配-法师 T2</v>
+        <v>阚泽-法师 T2</v>
       </c>
       <c r="D173">
         <v>4</v>
@@ -19142,7 +19145,7 @@
         <v>1</v>
       </c>
       <c r="F173">
-        <v>422</v>
+        <v>207</v>
       </c>
       <c r="G173">
         <v>4</v>
@@ -19154,13 +19157,13 @@
         <v>25</v>
       </c>
       <c r="J173">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K173">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L173">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="M173" t="str">
         <v>[[2,288],[20,432],[40,576],[60,720],[80,864],[100,1008],[120,1152],[140,1296],[160,1440],[180,1584],[200,1728]]</v>
@@ -19172,10 +19175,10 @@
         <v>[]</v>
       </c>
       <c r="P173">
-        <v>353</v>
+        <v>150</v>
       </c>
       <c r="Q173">
-        <v>2130</v>
+        <v>1803</v>
       </c>
       <c r="R173" t="str">
         <v>[1,800]</v>
@@ -19243,7 +19246,7 @@
         <v>50010</v>
       </c>
       <c r="C174" t="str">
-        <v>陈宫-法师 T2</v>
+        <v>张温-法师 T2</v>
       </c>
       <c r="D174">
         <v>4</v>
@@ -19252,7 +19255,7 @@
         <v>1</v>
       </c>
       <c r="F174">
-        <v>328</v>
+        <v>191</v>
       </c>
       <c r="G174">
         <v>4</v>
@@ -19264,13 +19267,13 @@
         <v>25</v>
       </c>
       <c r="J174">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="K174">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L174">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="M174" t="str">
         <v>[[2,585],[20,878],[40,1170],[60,1463],[80,1755],[100,2048],[120,2340],[140,2633],[160,2925],[180,3218],[200,3510]]</v>
@@ -19282,10 +19285,10 @@
         <v>[]</v>
       </c>
       <c r="P174">
-        <v>349</v>
+        <v>151</v>
       </c>
       <c r="Q174">
-        <v>2089</v>
+        <v>1969</v>
       </c>
       <c r="R174" t="str">
         <v>[1,800]</v>
@@ -19353,7 +19356,7 @@
         <v>50011</v>
       </c>
       <c r="C175" t="str">
-        <v>庞德公-法师 T2</v>
+        <v>鲁肃-法师 T2</v>
       </c>
       <c r="D175">
         <v>4</v>
@@ -19362,7 +19365,7 @@
         <v>1</v>
       </c>
       <c r="F175">
-        <v>400</v>
+        <v>210</v>
       </c>
       <c r="G175">
         <v>4</v>
@@ -19374,13 +19377,13 @@
         <v>25</v>
       </c>
       <c r="J175">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="K175">
         <v>25</v>
       </c>
       <c r="L175">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M175" t="str">
         <v>[[2,495],[20,743],[40,990],[60,1238],[80,1485],[100,1733],[120,1980],[140,2228],[160,2475],[180,2723],[200,2970]]</v>
@@ -19392,10 +19395,10 @@
         <v>[]</v>
       </c>
       <c r="P175">
-        <v>371</v>
+        <v>146</v>
       </c>
       <c r="Q175">
-        <v>1927</v>
+        <v>1932</v>
       </c>
       <c r="R175" t="str">
         <v>[1,800]</v>
@@ -19463,7 +19466,7 @@
         <v>50012</v>
       </c>
       <c r="C176" t="str">
-        <v>董昭-法师 T2</v>
+        <v>薛综-法师 T2</v>
       </c>
       <c r="D176">
         <v>4</v>
@@ -19472,7 +19475,7 @@
         <v>1</v>
       </c>
       <c r="F176">
-        <v>431</v>
+        <v>206</v>
       </c>
       <c r="G176">
         <v>4</v>
@@ -19484,13 +19487,13 @@
         <v>25</v>
       </c>
       <c r="J176">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="K176">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L176">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="M176" t="str">
         <v>[[2,257],[20,386],[40,515],[60,644],[80,772],[100,901],[120,1030],[140,1158],[160,1287],[180,1416],[200,1544]]</v>
@@ -19502,10 +19505,10 @@
         <v>[]</v>
       </c>
       <c r="P176">
-        <v>342</v>
+        <v>147</v>
       </c>
       <c r="Q176">
-        <v>2140</v>
+        <v>1953</v>
       </c>
       <c r="R176" t="str">
         <v>[1,800]</v>
@@ -19573,7 +19576,7 @@
         <v>50013</v>
       </c>
       <c r="C177" t="str">
-        <v>鲁肃-法师 T3</v>
+        <v>糜芳-法师 T3</v>
       </c>
       <c r="D177">
         <v>4</v>
@@ -19582,7 +19585,7 @@
         <v>1</v>
       </c>
       <c r="F177">
-        <v>520</v>
+        <v>337</v>
       </c>
       <c r="G177">
         <v>5</v>
@@ -19594,13 +19597,13 @@
         <v>25</v>
       </c>
       <c r="J177">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="K177">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L177">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M177" t="str">
         <v>[[2,441],[20,662],[40,882],[60,1103],[80,1323],[100,1544],[120,1764],[140,1985],[160,2205],[180,2426],[200,2646]]</v>
@@ -19612,10 +19615,10 @@
         <v>[]</v>
       </c>
       <c r="P177">
-        <v>351</v>
+        <v>149</v>
       </c>
       <c r="Q177">
-        <v>1842</v>
+        <v>1953</v>
       </c>
       <c r="R177" t="str">
         <v>[1,800]</v>
@@ -19683,7 +19686,7 @@
         <v>50014</v>
       </c>
       <c r="C178" t="str">
-        <v>徐庶-法师 T3</v>
+        <v>郭嘉-法师 T3</v>
       </c>
       <c r="D178">
         <v>4</v>
@@ -19692,7 +19695,7 @@
         <v>1</v>
       </c>
       <c r="F178">
-        <v>667</v>
+        <v>377</v>
       </c>
       <c r="G178">
         <v>5</v>
@@ -19704,13 +19707,13 @@
         <v>30</v>
       </c>
       <c r="J178">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="K178">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L178">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="M178" t="str">
         <v>[[2,770],[20,1155],[40,1540],[60,1925],[80,2310],[100,2695],[120,3080],[140,3465],[160,3850],[180,4235],[200,4620]]</v>
@@ -19722,10 +19725,10 @@
         <v>[]</v>
       </c>
       <c r="P178">
-        <v>379</v>
+        <v>146</v>
       </c>
       <c r="Q178">
-        <v>1923</v>
+        <v>2083</v>
       </c>
       <c r="R178" t="str">
         <v>[1,800]</v>
@@ -19793,7 +19796,7 @@
         <v>50015</v>
       </c>
       <c r="C179" t="str">
-        <v>程昱-2-法师 T3</v>
+        <v>水镜先生-2-法师 T3</v>
       </c>
       <c r="D179">
         <v>4</v>
@@ -19802,7 +19805,7 @@
         <v>1</v>
       </c>
       <c r="F179">
-        <v>650</v>
+        <v>332</v>
       </c>
       <c r="G179">
         <v>5</v>
@@ -19814,7 +19817,7 @@
         <v>30</v>
       </c>
       <c r="J179">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K179">
         <v>37</v>
@@ -19832,10 +19835,10 @@
         <v>[]</v>
       </c>
       <c r="P179">
-        <v>376</v>
+        <v>143</v>
       </c>
       <c r="Q179">
-        <v>1838</v>
+        <v>1926</v>
       </c>
       <c r="R179" t="str">
         <v>[1,800]</v>
@@ -19903,7 +19906,7 @@
         <v>50016</v>
       </c>
       <c r="C180" t="str">
-        <v>祝融-2-法师 T3</v>
+        <v>钟繇-2-法师 T3</v>
       </c>
       <c r="D180">
         <v>4</v>
@@ -19912,7 +19915,7 @@
         <v>1</v>
       </c>
       <c r="F180">
-        <v>508</v>
+        <v>352</v>
       </c>
       <c r="G180">
         <v>5</v>
@@ -19924,13 +19927,13 @@
         <v>30</v>
       </c>
       <c r="J180">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="K180">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L180">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="M180" t="str">
         <v>[[2,728],[20,1092],[40,1456],[60,1820],[80,2184],[100,2548],[120,2912],[140,3276],[160,3640],[180,4004],[200,4368]]</v>
@@ -19942,10 +19945,10 @@
         <v>[]</v>
       </c>
       <c r="P180">
-        <v>345</v>
+        <v>152</v>
       </c>
       <c r="Q180">
-        <v>1839</v>
+        <v>2197</v>
       </c>
       <c r="R180" t="str">
         <v>[1,800]</v>
@@ -20013,7 +20016,7 @@
         <v>50017</v>
       </c>
       <c r="C181" t="str">
-        <v>辛宪英-2-法师 T3</v>
+        <v>张昭-2-法师 T3</v>
       </c>
       <c r="D181">
         <v>4</v>
@@ -20022,7 +20025,7 @@
         <v>1</v>
       </c>
       <c r="F181">
-        <v>646</v>
+        <v>360</v>
       </c>
       <c r="G181">
         <v>5</v>
@@ -20034,13 +20037,13 @@
         <v>30</v>
       </c>
       <c r="J181">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="K181">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L181">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="M181" t="str">
         <v>[[2,854],[20,1281],[40,1708],[60,2135],[80,2562],[100,2989],[120,3416],[140,3843],[160,4270],[180,4697],[200,5124]]</v>
@@ -20052,10 +20055,10 @@
         <v>[]</v>
       </c>
       <c r="P181">
-        <v>360</v>
+        <v>152</v>
       </c>
       <c r="Q181">
-        <v>2000</v>
+        <v>1844</v>
       </c>
       <c r="R181" t="str">
         <v>[1,800]</v>
@@ -20123,7 +20126,7 @@
         <v>50018</v>
       </c>
       <c r="C182" t="str">
-        <v>蒯越-2-法师 T3</v>
+        <v>贾诩-2-法师 T3</v>
       </c>
       <c r="D182">
         <v>4</v>
@@ -20132,7 +20135,7 @@
         <v>1</v>
       </c>
       <c r="F182">
-        <v>608</v>
+        <v>338</v>
       </c>
       <c r="G182">
         <v>5</v>
@@ -20144,13 +20147,13 @@
         <v>30</v>
       </c>
       <c r="J182">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="K182">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L182">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="M182" t="str">
         <v>[[2,700],[20,1050],[40,1400],[60,1750],[80,2100],[100,2450],[120,2800],[140,3150],[160,3500],[180,3850],[200,4200]]</v>
@@ -20162,10 +20165,10 @@
         <v>[]</v>
       </c>
       <c r="P182">
-        <v>342</v>
+        <v>137</v>
       </c>
       <c r="Q182">
-        <v>1949</v>
+        <v>1841</v>
       </c>
       <c r="R182" t="str">
         <v>[1,800]</v>
@@ -20233,7 +20236,7 @@
         <v>50019</v>
       </c>
       <c r="C183" t="str">
-        <v>大乔-2-法师 T4</v>
+        <v>郑玄-2-法师 T4</v>
       </c>
       <c r="D183">
         <v>4</v>
@@ -20242,7 +20245,7 @@
         <v>1</v>
       </c>
       <c r="F183">
-        <v>881</v>
+        <v>368</v>
       </c>
       <c r="G183">
         <v>6</v>
@@ -20254,13 +20257,13 @@
         <v>30</v>
       </c>
       <c r="J183">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="K183">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L183">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="M183" t="str">
         <v>[[2,532],[20,798],[40,1064],[60,1330],[80,1596],[100,1862],[120,2128],[140,2394],[160,2660],[180,2926],[200,3192]]</v>
@@ -20272,10 +20275,10 @@
         <v>[]</v>
       </c>
       <c r="P183">
-        <v>348</v>
+        <v>147</v>
       </c>
       <c r="Q183">
-        <v>2033</v>
+        <v>2025</v>
       </c>
       <c r="R183" t="str">
         <v>[1,800]</v>
@@ -20343,7 +20346,7 @@
         <v>50020</v>
       </c>
       <c r="C184" t="str">
-        <v>贾诩-2-法师 T4</v>
+        <v>张昭-2-法师 T4</v>
       </c>
       <c r="D184">
         <v>4</v>
@@ -20352,7 +20355,7 @@
         <v>1</v>
       </c>
       <c r="F184">
-        <v>885</v>
+        <v>443</v>
       </c>
       <c r="G184">
         <v>6</v>
@@ -20364,13 +20367,13 @@
         <v>30</v>
       </c>
       <c r="J184">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="K184">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L184">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="M184" t="str">
         <v>[[2,672],[20,1008],[40,1344],[60,1680],[80,2016],[100,2352],[120,2688],[140,3024],[160,3360],[180,3696],[200,4032]]</v>
@@ -20382,10 +20385,10 @@
         <v>[]</v>
       </c>
       <c r="P184">
-        <v>377</v>
+        <v>147</v>
       </c>
       <c r="Q184">
-        <v>1936</v>
+        <v>1988</v>
       </c>
       <c r="R184" t="str">
         <v>[1,800]</v>
@@ -20453,7 +20456,7 @@
         <v>50021</v>
       </c>
       <c r="C185" t="str">
-        <v>徐庶-2-法师 T4</v>
+        <v>逢纪-2-法师 T4</v>
       </c>
       <c r="D185">
         <v>4</v>
@@ -20462,7 +20465,7 @@
         <v>1</v>
       </c>
       <c r="F185">
-        <v>839</v>
+        <v>475</v>
       </c>
       <c r="G185">
         <v>6</v>
@@ -20474,13 +20477,13 @@
         <v>30</v>
       </c>
       <c r="J185">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="K185">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="L185">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="M185" t="str">
         <v>[[2,504],[20,756],[40,1008],[60,1260],[80,1512],[100,1764],[120,2016],[140,2268],[160,2520],[180,2772],[200,3024]]</v>
@@ -20492,10 +20495,10 @@
         <v>[]</v>
       </c>
       <c r="P185">
-        <v>371</v>
+        <v>150</v>
       </c>
       <c r="Q185">
-        <v>1915</v>
+        <v>1866</v>
       </c>
       <c r="R185" t="str">
         <v>[1,800]</v>
@@ -20563,7 +20566,7 @@
         <v>50022</v>
       </c>
       <c r="C186" t="str">
-        <v>蒯良-2-法师 T4</v>
+        <v>祝融-2-法师 T4</v>
       </c>
       <c r="D186">
         <v>4</v>
@@ -20572,7 +20575,7 @@
         <v>1</v>
       </c>
       <c r="F186">
-        <v>998</v>
+        <v>488</v>
       </c>
       <c r="G186">
         <v>6</v>
@@ -20584,13 +20587,13 @@
         <v>30</v>
       </c>
       <c r="J186">
-        <v>208</v>
+        <v>155</v>
       </c>
       <c r="K186">
         <v>51</v>
       </c>
       <c r="L186">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M186" t="str">
         <v>[[2,532],[20,798],[40,1064],[60,1330],[80,1596],[100,1862],[120,2128],[140,2394],[160,2660],[180,2926],[200,3192]]</v>
@@ -20602,10 +20605,10 @@
         <v>[]</v>
       </c>
       <c r="P186">
-        <v>372</v>
+        <v>141</v>
       </c>
       <c r="Q186">
-        <v>2165</v>
+        <v>2075</v>
       </c>
       <c r="R186" t="str">
         <v>[1,800]</v>
@@ -20673,7 +20676,7 @@
         <v>50023</v>
       </c>
       <c r="C187" t="str">
-        <v>徐庶-3-法师 T4</v>
+        <v>王朗-2-法师 T4</v>
       </c>
       <c r="D187">
         <v>4</v>
@@ -20682,7 +20685,7 @@
         <v>1</v>
       </c>
       <c r="F187">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="G187">
         <v>6</v>
@@ -20694,10 +20697,10 @@
         <v>30</v>
       </c>
       <c r="J187">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K187">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="L187">
         <v>1.2</v>
@@ -20712,10 +20715,10 @@
         <v>[]</v>
       </c>
       <c r="P187">
-        <v>362</v>
+        <v>141</v>
       </c>
       <c r="Q187">
-        <v>2013</v>
+        <v>1803</v>
       </c>
       <c r="R187" t="str">
         <v>[1,800]</v>
@@ -20783,7 +20786,7 @@
         <v>50024</v>
       </c>
       <c r="C188" t="str">
-        <v>徐庶-4-法师 T4</v>
+        <v>邓芝-2-法师 T4</v>
       </c>
       <c r="D188">
         <v>4</v>
@@ -20792,7 +20795,7 @@
         <v>1</v>
       </c>
       <c r="F188">
-        <v>690</v>
+        <v>370</v>
       </c>
       <c r="G188">
         <v>6</v>
@@ -20804,13 +20807,13 @@
         <v>30</v>
       </c>
       <c r="J188">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="K188">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L188">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="M188" t="str">
         <v>[[2,532],[20,798],[40,1064],[60,1330],[80,1596],[100,1862],[120,2128],[140,2394],[160,2660],[180,2926],[200,3192]]</v>
@@ -20822,10 +20825,10 @@
         <v>[]</v>
       </c>
       <c r="P188">
-        <v>371</v>
+        <v>146</v>
       </c>
       <c r="Q188">
-        <v>1948</v>
+        <v>2056</v>
       </c>
       <c r="R188" t="str">
         <v>[1,800]</v>
@@ -20893,7 +20896,7 @@
         <v>90001</v>
       </c>
       <c r="C189" t="str">
-        <v>【虚空母体】淳于琼-步兵 T1</v>
+        <v>【极秘项目】霍峻-步兵 T1</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -20902,7 +20905,7 @@
         <v>20</v>
       </c>
       <c r="F189">
-        <v>679</v>
+        <v>307</v>
       </c>
       <c r="G189">
         <v>3</v>
@@ -20914,13 +20917,13 @@
         <v>1</v>
       </c>
       <c r="J189">
-        <v>592</v>
+        <v>532</v>
       </c>
       <c r="K189">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L189">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="M189" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -20932,10 +20935,10 @@
         <v>[]</v>
       </c>
       <c r="P189">
-        <v>527</v>
+        <v>209</v>
       </c>
       <c r="Q189">
-        <v>387</v>
+        <v>186</v>
       </c>
       <c r="R189" t="str">
         <v>[1,800]</v>
@@ -21003,7 +21006,7 @@
         <v>90002</v>
       </c>
       <c r="C190" t="str">
-        <v>【钢铁暴君】徐晃-步兵 T1</v>
+        <v>【虚空母体】严白虎-步兵 T1</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -21012,7 +21015,7 @@
         <v>20</v>
       </c>
       <c r="F190">
-        <v>696</v>
+        <v>381</v>
       </c>
       <c r="G190">
         <v>3</v>
@@ -21024,13 +21027,13 @@
         <v>1</v>
       </c>
       <c r="J190">
-        <v>499</v>
+        <v>717</v>
       </c>
       <c r="K190">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L190">
-        <v>1.07</v>
+        <v>0.95</v>
       </c>
       <c r="M190" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21042,10 +21045,10 @@
         <v>[]</v>
       </c>
       <c r="P190">
-        <v>532</v>
+        <v>209</v>
       </c>
       <c r="Q190">
-        <v>438</v>
+        <v>219</v>
       </c>
       <c r="R190" t="str">
         <v>[1,800]</v>
@@ -21113,7 +21116,7 @@
         <v>90003</v>
       </c>
       <c r="C191" t="str">
-        <v>【虚空母体】向宠-步兵 T2</v>
+        <v>【极秘项目】朱桓-步兵 T2</v>
       </c>
       <c r="D191">
         <v>0</v>
@@ -21122,7 +21125,7 @@
         <v>20</v>
       </c>
       <c r="F191">
-        <v>1190</v>
+        <v>600</v>
       </c>
       <c r="G191">
         <v>4</v>
@@ -21134,13 +21137,13 @@
         <v>1</v>
       </c>
       <c r="J191">
-        <v>763</v>
+        <v>887</v>
       </c>
       <c r="K191">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L191">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="M191" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21152,10 +21155,10 @@
         <v>[]</v>
       </c>
       <c r="P191">
-        <v>514</v>
+        <v>214</v>
       </c>
       <c r="Q191">
-        <v>418</v>
+        <v>209</v>
       </c>
       <c r="R191" t="str">
         <v>[1,800]</v>
@@ -21223,7 +21226,7 @@
         <v>90004</v>
       </c>
       <c r="C192" t="str">
-        <v>【变异主宰】张苞-步兵 T2</v>
+        <v>【极秘项目】典韦-步兵 T2</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -21232,7 +21235,7 @@
         <v>20</v>
       </c>
       <c r="F192">
-        <v>1498</v>
+        <v>498</v>
       </c>
       <c r="G192">
         <v>4</v>
@@ -21244,13 +21247,13 @@
         <v>1</v>
       </c>
       <c r="J192">
-        <v>1064</v>
+        <v>748</v>
       </c>
       <c r="K192">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L192">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="M192" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21262,10 +21265,10 @@
         <v>[]</v>
       </c>
       <c r="P192">
-        <v>522</v>
+        <v>210</v>
       </c>
       <c r="Q192">
-        <v>414</v>
+        <v>195</v>
       </c>
       <c r="R192" t="str">
         <v>[1,800]</v>
@@ -21333,7 +21336,7 @@
         <v>90005</v>
       </c>
       <c r="C193" t="str">
-        <v>【末日先兆】蔡瑁-步兵 T2</v>
+        <v>【钢铁暴君】孙权-步兵 T2</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -21342,7 +21345,7 @@
         <v>20</v>
       </c>
       <c r="F193">
-        <v>1336</v>
+        <v>495</v>
       </c>
       <c r="G193">
         <v>4</v>
@@ -21354,13 +21357,13 @@
         <v>1</v>
       </c>
       <c r="J193">
-        <v>1047</v>
+        <v>738</v>
       </c>
       <c r="K193">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L193">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="M193" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21372,10 +21375,10 @@
         <v>[]</v>
       </c>
       <c r="P193">
-        <v>520</v>
+        <v>215</v>
       </c>
       <c r="Q193">
-        <v>361</v>
+        <v>208</v>
       </c>
       <c r="R193" t="str">
         <v>[1,800]</v>
@@ -21443,7 +21446,7 @@
         <v>90006</v>
       </c>
       <c r="C194" t="str">
-        <v>【钢铁暴君】王颀-步兵 T3</v>
+        <v>【变异主宰】刘备-步兵 T3</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -21452,7 +21455,7 @@
         <v>20</v>
       </c>
       <c r="F194">
-        <v>2253</v>
+        <v>834</v>
       </c>
       <c r="G194">
         <v>5</v>
@@ -21464,13 +21467,13 @@
         <v>1</v>
       </c>
       <c r="J194">
-        <v>1322</v>
+        <v>1204</v>
       </c>
       <c r="K194">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L194">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="M194" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21482,10 +21485,10 @@
         <v>[]</v>
       </c>
       <c r="P194">
-        <v>530</v>
+        <v>204</v>
       </c>
       <c r="Q194">
-        <v>411</v>
+        <v>205</v>
       </c>
       <c r="R194" t="str">
         <v>[1,800]</v>
@@ -21553,7 +21556,7 @@
         <v>90007</v>
       </c>
       <c r="C195" t="str">
-        <v>【零号病毒】霍峻-步兵 T3</v>
+        <v>【零号病毒】周泰-步兵 T3</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -21562,7 +21565,7 @@
         <v>20</v>
       </c>
       <c r="F195">
-        <v>1754</v>
+        <v>910</v>
       </c>
       <c r="G195">
         <v>5</v>
@@ -21574,13 +21577,13 @@
         <v>1</v>
       </c>
       <c r="J195">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="K195">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L195">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="M195" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21592,10 +21595,10 @@
         <v>[]</v>
       </c>
       <c r="P195">
-        <v>516</v>
+        <v>211</v>
       </c>
       <c r="Q195">
-        <v>394</v>
+        <v>197</v>
       </c>
       <c r="R195" t="str">
         <v>[1,800]</v>
@@ -21663,7 +21666,7 @@
         <v>90008</v>
       </c>
       <c r="C196" t="str">
-        <v>【变异主宰】吕凯-步兵 T4</v>
+        <v>【零号病毒】黄盖-步兵 T4</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -21672,7 +21675,7 @@
         <v>20</v>
       </c>
       <c r="F196">
-        <v>2597</v>
+        <v>1281</v>
       </c>
       <c r="G196">
         <v>6</v>
@@ -21684,13 +21687,13 @@
         <v>1</v>
       </c>
       <c r="J196">
-        <v>1596</v>
+        <v>1724</v>
       </c>
       <c r="K196">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="L196">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="M196" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21702,10 +21705,10 @@
         <v>[]</v>
       </c>
       <c r="P196">
-        <v>532</v>
+        <v>207</v>
       </c>
       <c r="Q196">
-        <v>383</v>
+        <v>186</v>
       </c>
       <c r="R196" t="str">
         <v>[1,800]</v>
@@ -21773,7 +21776,7 @@
         <v>90009</v>
       </c>
       <c r="C197" t="str">
-        <v>【虚空母体】潘凤-步兵 T4</v>
+        <v>【末日先兆】臧霸-步兵 T4</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -21782,7 +21785,7 @@
         <v>20</v>
       </c>
       <c r="F197">
-        <v>2845</v>
+        <v>1183</v>
       </c>
       <c r="G197">
         <v>6</v>
@@ -21794,13 +21797,13 @@
         <v>1</v>
       </c>
       <c r="J197">
-        <v>1534</v>
+        <v>1489</v>
       </c>
       <c r="K197">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L197">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="M197" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21812,10 +21815,10 @@
         <v>[]</v>
       </c>
       <c r="P197">
-        <v>532</v>
+        <v>209</v>
       </c>
       <c r="Q197">
-        <v>429</v>
+        <v>183</v>
       </c>
       <c r="R197" t="str">
         <v>[1,800]</v>
@@ -21883,7 +21886,7 @@
         <v>90010</v>
       </c>
       <c r="C198" t="str">
-        <v>【零号病毒】吕翔-步兵 T4</v>
+        <v>【极秘项目】傅佥-步兵 T4</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -21892,7 +21895,7 @@
         <v>20</v>
       </c>
       <c r="F198">
-        <v>2730</v>
+        <v>1207</v>
       </c>
       <c r="G198">
         <v>6</v>
@@ -21904,13 +21907,13 @@
         <v>1</v>
       </c>
       <c r="J198">
-        <v>1679</v>
+        <v>1532</v>
       </c>
       <c r="K198">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L198">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="M198" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -21922,10 +21925,10 @@
         <v>[]</v>
       </c>
       <c r="P198">
-        <v>517</v>
+        <v>213</v>
       </c>
       <c r="Q198">
-        <v>398</v>
+        <v>190</v>
       </c>
       <c r="R198" t="str">
         <v>[1,800]</v>
@@ -21993,7 +21996,7 @@
         <v>90011</v>
       </c>
       <c r="C199" t="str">
-        <v>【末日先兆】诸葛瑾-弓箭手 T1</v>
+        <v>【末日先兆】邓芝-弓箭手 T1</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -22002,7 +22005,7 @@
         <v>20</v>
       </c>
       <c r="F199">
-        <v>706</v>
+        <v>327</v>
       </c>
       <c r="G199">
         <v>3</v>
@@ -22014,13 +22017,13 @@
         <v>1</v>
       </c>
       <c r="J199">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K199">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L199">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="M199" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22032,10 +22035,10 @@
         <v>[]</v>
       </c>
       <c r="P199">
-        <v>438</v>
+        <v>168</v>
       </c>
       <c r="Q199">
-        <v>2380</v>
+        <v>2347</v>
       </c>
       <c r="R199" t="str">
         <v>[1,800]</v>
@@ -22103,7 +22106,7 @@
         <v>90012</v>
       </c>
       <c r="C200" t="str">
-        <v>【零号病毒】戏志才-弓箭手 T1</v>
+        <v>【虚空母体】大乔-弓箭手 T1</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -22112,7 +22115,7 @@
         <v>20</v>
       </c>
       <c r="F200">
-        <v>750</v>
+        <v>448</v>
       </c>
       <c r="G200">
         <v>3</v>
@@ -22124,13 +22127,13 @@
         <v>1</v>
       </c>
       <c r="J200">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="K200">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L200">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="M200" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22142,10 +22145,10 @@
         <v>[]</v>
       </c>
       <c r="P200">
-        <v>430</v>
+        <v>172</v>
       </c>
       <c r="Q200">
-        <v>2174</v>
+        <v>2192</v>
       </c>
       <c r="R200" t="str">
         <v>[1,800]</v>
@@ -22213,7 +22216,7 @@
         <v>90013</v>
       </c>
       <c r="C201" t="str">
-        <v>【极秘项目】辛宪英-弓箭手 T2</v>
+        <v>【变异主宰】沮授-弓箭手 T2</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -22222,7 +22225,7 @@
         <v>20</v>
       </c>
       <c r="F201">
-        <v>1197</v>
+        <v>547</v>
       </c>
       <c r="G201">
         <v>4</v>
@@ -22234,13 +22237,13 @@
         <v>1</v>
       </c>
       <c r="J201">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K201">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L201">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="M201" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22252,10 +22255,10 @@
         <v>[]</v>
       </c>
       <c r="P201">
-        <v>437</v>
+        <v>170</v>
       </c>
       <c r="Q201">
-        <v>2363</v>
+        <v>1985</v>
       </c>
       <c r="R201" t="str">
         <v>[1,800]</v>
@@ -22323,7 +22326,7 @@
         <v>90014</v>
       </c>
       <c r="C202" t="str">
-        <v>【极秘项目】满宠-弓箭手 T2</v>
+        <v>【钢铁暴君】程昱-弓箭手 T2</v>
       </c>
       <c r="D202">
         <v>1</v>
@@ -22332,7 +22335,7 @@
         <v>20</v>
       </c>
       <c r="F202">
-        <v>1372</v>
+        <v>660</v>
       </c>
       <c r="G202">
         <v>4</v>
@@ -22344,13 +22347,13 @@
         <v>1</v>
       </c>
       <c r="J202">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="K202">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L202">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="M202" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22362,10 +22365,10 @@
         <v>[]</v>
       </c>
       <c r="P202">
-        <v>435</v>
+        <v>170</v>
       </c>
       <c r="Q202">
-        <v>2255</v>
+        <v>2216</v>
       </c>
       <c r="R202" t="str">
         <v>[1,800]</v>
@@ -22433,7 +22436,7 @@
         <v>90015</v>
       </c>
       <c r="C203" t="str">
-        <v>【末日先兆】祝融-弓箭手 T2</v>
+        <v>【极秘项目】祝融-弓箭手 T2</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -22442,7 +22445,7 @@
         <v>20</v>
       </c>
       <c r="F203">
-        <v>1249</v>
+        <v>584</v>
       </c>
       <c r="G203">
         <v>4</v>
@@ -22454,13 +22457,13 @@
         <v>1</v>
       </c>
       <c r="J203">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="K203">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L203">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="M203" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22472,10 +22475,10 @@
         <v>[]</v>
       </c>
       <c r="P203">
-        <v>428</v>
+        <v>169</v>
       </c>
       <c r="Q203">
-        <v>2394</v>
+        <v>2305</v>
       </c>
       <c r="R203" t="str">
         <v>[1,800]</v>
@@ -22543,7 +22546,7 @@
         <v>90016</v>
       </c>
       <c r="C204" t="str">
-        <v>【末日先兆】贾诩-弓箭手 T3</v>
+        <v>【变异主宰】华歆-弓箭手 T3</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -22552,7 +22555,7 @@
         <v>20</v>
       </c>
       <c r="F204">
-        <v>1480</v>
+        <v>986</v>
       </c>
       <c r="G204">
         <v>5</v>
@@ -22564,13 +22567,13 @@
         <v>1</v>
       </c>
       <c r="J204">
-        <v>406</v>
+        <v>466</v>
       </c>
       <c r="K204">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="L204">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="M204" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22582,10 +22585,10 @@
         <v>[]</v>
       </c>
       <c r="P204">
-        <v>412</v>
+        <v>165</v>
       </c>
       <c r="Q204">
-        <v>2091</v>
+        <v>2407</v>
       </c>
       <c r="R204" t="str">
         <v>[1,800]</v>
@@ -22653,7 +22656,7 @@
         <v>90017</v>
       </c>
       <c r="C205" t="str">
-        <v>【零号病毒】甄姬-弓箭手 T3</v>
+        <v>【钢铁暴君】庞统-弓箭手 T3</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -22662,7 +22665,7 @@
         <v>20</v>
       </c>
       <c r="F205">
-        <v>1630</v>
+        <v>1103</v>
       </c>
       <c r="G205">
         <v>5</v>
@@ -22674,13 +22677,13 @@
         <v>1</v>
       </c>
       <c r="J205">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="K205">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="L205">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="M205" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22692,10 +22695,10 @@
         <v>[]</v>
       </c>
       <c r="P205">
-        <v>411</v>
+        <v>171</v>
       </c>
       <c r="Q205">
-        <v>2106</v>
+        <v>2222</v>
       </c>
       <c r="R205" t="str">
         <v>[1,800]</v>
@@ -22763,7 +22766,7 @@
         <v>90018</v>
       </c>
       <c r="C206" t="str">
-        <v>【虚空母体】太史慈-弓箭手 T4</v>
+        <v>【极秘项目】步骘-弓箭手 T4</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -22772,7 +22775,7 @@
         <v>20</v>
       </c>
       <c r="F206">
-        <v>2228</v>
+        <v>1275</v>
       </c>
       <c r="G206">
         <v>6</v>
@@ -22784,13 +22787,13 @@
         <v>1</v>
       </c>
       <c r="J206">
-        <v>629</v>
+        <v>599</v>
       </c>
       <c r="K206">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L206">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="M206" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22802,10 +22805,10 @@
         <v>[]</v>
       </c>
       <c r="P206">
-        <v>436</v>
+        <v>165</v>
       </c>
       <c r="Q206">
-        <v>2212</v>
+        <v>2403</v>
       </c>
       <c r="R206" t="str">
         <v>[1,800]</v>
@@ -22873,7 +22876,7 @@
         <v>90019</v>
       </c>
       <c r="C207" t="str">
-        <v>【末日先兆】华歆-弓箭手 T4</v>
+        <v>【钢铁暴君】蒯越-弓箭手 T4</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -22882,7 +22885,7 @@
         <v>20</v>
       </c>
       <c r="F207">
-        <v>2826</v>
+        <v>1333</v>
       </c>
       <c r="G207">
         <v>6</v>
@@ -22894,13 +22897,13 @@
         <v>1</v>
       </c>
       <c r="J207">
-        <v>590</v>
+        <v>678</v>
       </c>
       <c r="K207">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="L207">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="M207" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -22912,10 +22915,10 @@
         <v>[]</v>
       </c>
       <c r="P207">
-        <v>436</v>
+        <v>172</v>
       </c>
       <c r="Q207">
-        <v>1999</v>
+        <v>2318</v>
       </c>
       <c r="R207" t="str">
         <v>[1,800]</v>
@@ -22983,7 +22986,7 @@
         <v>90020</v>
       </c>
       <c r="C208" t="str">
-        <v>【零号病毒】杨修-弓箭手 T4</v>
+        <v>【末日先兆】陈宫-弓箭手 T4</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -22992,7 +22995,7 @@
         <v>20</v>
       </c>
       <c r="F208">
-        <v>2586</v>
+        <v>1204</v>
       </c>
       <c r="G208">
         <v>6</v>
@@ -23004,13 +23007,13 @@
         <v>1</v>
       </c>
       <c r="J208">
-        <v>700</v>
+        <v>667</v>
       </c>
       <c r="K208">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="L208">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="M208" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23022,10 +23025,10 @@
         <v>[]</v>
       </c>
       <c r="P208">
-        <v>425</v>
+        <v>165</v>
       </c>
       <c r="Q208">
-        <v>2368</v>
+        <v>2148</v>
       </c>
       <c r="R208" t="str">
         <v>[1,800]</v>
@@ -23093,7 +23096,7 @@
         <v>90021</v>
       </c>
       <c r="C209" t="str">
-        <v>【极秘项目】张辽-骑兵 T1</v>
+        <v>【钢铁暴君】公孙瓒-骑兵 T1</v>
       </c>
       <c r="D209">
         <v>2</v>
@@ -23102,7 +23105,7 @@
         <v>20</v>
       </c>
       <c r="F209">
-        <v>954</v>
+        <v>400</v>
       </c>
       <c r="G209">
         <v>3</v>
@@ -23114,13 +23117,13 @@
         <v>1</v>
       </c>
       <c r="J209">
-        <v>524</v>
+        <v>413</v>
       </c>
       <c r="K209">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L209">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M209" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23132,10 +23135,10 @@
         <v>[]</v>
       </c>
       <c r="P209">
-        <v>607</v>
+        <v>254</v>
       </c>
       <c r="Q209">
-        <v>451</v>
+        <v>223</v>
       </c>
       <c r="R209" t="str">
         <v>[1,800]</v>
@@ -23203,7 +23206,7 @@
         <v>90022</v>
       </c>
       <c r="C210" t="str">
-        <v>【变异主宰】张济-骑兵 T1</v>
+        <v>【极秘项目】高升-骑兵 T1</v>
       </c>
       <c r="D210">
         <v>2</v>
@@ -23212,7 +23215,7 @@
         <v>20</v>
       </c>
       <c r="F210">
-        <v>911</v>
+        <v>446</v>
       </c>
       <c r="G210">
         <v>3</v>
@@ -23224,13 +23227,13 @@
         <v>1</v>
       </c>
       <c r="J210">
-        <v>576</v>
+        <v>532</v>
       </c>
       <c r="K210">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L210">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="M210" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23242,10 +23245,10 @@
         <v>[]</v>
       </c>
       <c r="P210">
-        <v>633</v>
+        <v>256</v>
       </c>
       <c r="Q210">
-        <v>397</v>
+        <v>220</v>
       </c>
       <c r="R210" t="str">
         <v>[1,800]</v>
@@ -23313,7 +23316,7 @@
         <v>90023</v>
       </c>
       <c r="C211" t="str">
-        <v>【零号病毒】侯选-骑兵 T2</v>
+        <v>【末日先兆】庞德-骑兵 T2</v>
       </c>
       <c r="D211">
         <v>2</v>
@@ -23322,7 +23325,7 @@
         <v>20</v>
       </c>
       <c r="F211">
-        <v>1554</v>
+        <v>595</v>
       </c>
       <c r="G211">
         <v>4</v>
@@ -23334,13 +23337,13 @@
         <v>1</v>
       </c>
       <c r="J211">
-        <v>671</v>
+        <v>609</v>
       </c>
       <c r="K211">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L211">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="M211" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23352,10 +23355,10 @@
         <v>[]</v>
       </c>
       <c r="P211">
-        <v>610</v>
+        <v>251</v>
       </c>
       <c r="Q211">
-        <v>437</v>
+        <v>207</v>
       </c>
       <c r="R211" t="str">
         <v>[1,800]</v>
@@ -23423,7 +23426,7 @@
         <v>90024</v>
       </c>
       <c r="C212" t="str">
-        <v>【末日先兆】张宝-骑兵 T2</v>
+        <v>【极秘项目】邓茂-骑兵 T2</v>
       </c>
       <c r="D212">
         <v>2</v>
@@ -23432,7 +23435,7 @@
         <v>20</v>
       </c>
       <c r="F212">
-        <v>1472</v>
+        <v>640</v>
       </c>
       <c r="G212">
         <v>4</v>
@@ -23444,13 +23447,13 @@
         <v>1</v>
       </c>
       <c r="J212">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="K212">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L212">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="M212" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23462,10 +23465,10 @@
         <v>[]</v>
       </c>
       <c r="P212">
-        <v>607</v>
+        <v>248</v>
       </c>
       <c r="Q212">
-        <v>410</v>
+        <v>220</v>
       </c>
       <c r="R212" t="str">
         <v>[1,800]</v>
@@ -23533,7 +23536,7 @@
         <v>90025</v>
       </c>
       <c r="C213" t="str">
-        <v>【虚空母体】孙尚香-骑兵 T3</v>
+        <v>【变异主宰】吕蒙-骑兵 T3</v>
       </c>
       <c r="D213">
         <v>2</v>
@@ -23542,7 +23545,7 @@
         <v>20</v>
       </c>
       <c r="F213">
-        <v>2356</v>
+        <v>1060</v>
       </c>
       <c r="G213">
         <v>5</v>
@@ -23554,13 +23557,13 @@
         <v>1</v>
       </c>
       <c r="J213">
-        <v>1021</v>
+        <v>1010</v>
       </c>
       <c r="K213">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L213">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="M213" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23572,10 +23575,10 @@
         <v>[]</v>
       </c>
       <c r="P213">
-        <v>607</v>
+        <v>254</v>
       </c>
       <c r="Q213">
-        <v>417</v>
+        <v>227</v>
       </c>
       <c r="R213" t="str">
         <v>[1,800]</v>
@@ -23643,7 +23646,7 @@
         <v>90026</v>
       </c>
       <c r="C214" t="str">
-        <v>【末日先兆】高升-骑兵 T3</v>
+        <v>【末日先兆】马腾-骑兵 T3</v>
       </c>
       <c r="D214">
         <v>2</v>
@@ -23652,7 +23655,7 @@
         <v>20</v>
       </c>
       <c r="F214">
-        <v>2597</v>
+        <v>1019</v>
       </c>
       <c r="G214">
         <v>5</v>
@@ -23664,13 +23667,13 @@
         <v>1</v>
       </c>
       <c r="J214">
-        <v>1071</v>
+        <v>952</v>
       </c>
       <c r="K214">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="L214">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="M214" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23682,10 +23685,10 @@
         <v>[]</v>
       </c>
       <c r="P214">
-        <v>602</v>
+        <v>252</v>
       </c>
       <c r="Q214">
-        <v>452</v>
+        <v>236</v>
       </c>
       <c r="R214" t="str">
         <v>[1,800]</v>
@@ -23753,7 +23756,7 @@
         <v>90027</v>
       </c>
       <c r="C215" t="str">
-        <v>【零号病毒】张角-骑兵 T4</v>
+        <v>【变异主宰】徐荣-骑兵 T4</v>
       </c>
       <c r="D215">
         <v>2</v>
@@ -23762,7 +23765,7 @@
         <v>20</v>
       </c>
       <c r="F215">
-        <v>3380</v>
+        <v>1372</v>
       </c>
       <c r="G215">
         <v>6</v>
@@ -23774,13 +23777,13 @@
         <v>1</v>
       </c>
       <c r="J215">
-        <v>1390</v>
+        <v>1030</v>
       </c>
       <c r="K215">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="L215">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="M215" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23792,10 +23795,10 @@
         <v>[]</v>
       </c>
       <c r="P215">
-        <v>605</v>
+        <v>252</v>
       </c>
       <c r="Q215">
-        <v>417</v>
+        <v>225</v>
       </c>
       <c r="R215" t="str">
         <v>[1,800]</v>
@@ -23863,7 +23866,7 @@
         <v>90028</v>
       </c>
       <c r="C216" t="str">
-        <v>【末日先兆】赵弘-骑兵 T4</v>
+        <v>【末日先兆】张角-骑兵 T4</v>
       </c>
       <c r="D216">
         <v>2</v>
@@ -23872,7 +23875,7 @@
         <v>20</v>
       </c>
       <c r="F216">
-        <v>3149</v>
+        <v>1334</v>
       </c>
       <c r="G216">
         <v>6</v>
@@ -23884,13 +23887,13 @@
         <v>1</v>
       </c>
       <c r="J216">
-        <v>1023</v>
+        <v>1092</v>
       </c>
       <c r="K216">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L216">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="M216" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -23902,10 +23905,10 @@
         <v>[]</v>
       </c>
       <c r="P216">
-        <v>603</v>
+        <v>244</v>
       </c>
       <c r="Q216">
-        <v>415</v>
+        <v>226</v>
       </c>
       <c r="R216" t="str">
         <v>[1,800]</v>
@@ -23973,7 +23976,7 @@
         <v>90029</v>
       </c>
       <c r="C217" t="str">
-        <v>【虚空母体】胡遵-长枪兵 T1</v>
+        <v>【零号病毒】赵范-长枪兵 T1</v>
       </c>
       <c r="D217">
         <v>3</v>
@@ -23982,7 +23985,7 @@
         <v>20</v>
       </c>
       <c r="F217">
-        <v>974</v>
+        <v>437</v>
       </c>
       <c r="G217">
         <v>3</v>
@@ -23994,13 +23997,13 @@
         <v>1</v>
       </c>
       <c r="J217">
-        <v>437</v>
+        <v>359</v>
       </c>
       <c r="K217">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L217">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="M217" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24012,10 +24015,10 @@
         <v>[]</v>
       </c>
       <c r="P217">
-        <v>484</v>
+        <v>196</v>
       </c>
       <c r="Q217">
-        <v>449</v>
+        <v>247</v>
       </c>
       <c r="R217" t="str">
         <v>[1,800]</v>
@@ -24083,7 +24086,7 @@
         <v>90030</v>
       </c>
       <c r="C218" t="str">
-        <v>【变异主宰】朱然-长枪兵 T2</v>
+        <v>【虚空母体】吴兰-长枪兵 T2</v>
       </c>
       <c r="D218">
         <v>3</v>
@@ -24092,7 +24095,7 @@
         <v>20</v>
       </c>
       <c r="F218">
-        <v>1583</v>
+        <v>657</v>
       </c>
       <c r="G218">
         <v>4</v>
@@ -24104,13 +24107,13 @@
         <v>1</v>
       </c>
       <c r="J218">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="K218">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L218">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="M218" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24122,10 +24125,10 @@
         <v>[]</v>
       </c>
       <c r="P218">
-        <v>460</v>
+        <v>185</v>
       </c>
       <c r="Q218">
-        <v>412</v>
+        <v>265</v>
       </c>
       <c r="R218" t="str">
         <v>[1,800]</v>
@@ -24193,7 +24196,7 @@
         <v>90031</v>
       </c>
       <c r="C219" t="str">
-        <v>【钢铁暴君】潘璋-长枪兵 T2</v>
+        <v>【极秘项目】刘璝-长枪兵 T2</v>
       </c>
       <c r="D219">
         <v>3</v>
@@ -24202,7 +24205,7 @@
         <v>20</v>
       </c>
       <c r="F219">
-        <v>1901</v>
+        <v>735</v>
       </c>
       <c r="G219">
         <v>4</v>
@@ -24214,13 +24217,13 @@
         <v>1</v>
       </c>
       <c r="J219">
-        <v>696</v>
+        <v>522</v>
       </c>
       <c r="K219">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L219">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="M219" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24232,10 +24235,10 @@
         <v>[]</v>
       </c>
       <c r="P219">
-        <v>488</v>
+        <v>192</v>
       </c>
       <c r="Q219">
-        <v>468</v>
+        <v>265</v>
       </c>
       <c r="R219" t="str">
         <v>[1,800]</v>
@@ -24303,7 +24306,7 @@
         <v>90032</v>
       </c>
       <c r="C220" t="str">
-        <v>【虚空母体】邓贤-长枪兵 T3</v>
+        <v>【零号病毒】刘贤-长枪兵 T3</v>
       </c>
       <c r="D220">
         <v>3</v>
@@ -24312,7 +24315,7 @@
         <v>20</v>
       </c>
       <c r="F220">
-        <v>2538</v>
+        <v>1149</v>
       </c>
       <c r="G220">
         <v>5</v>
@@ -24324,13 +24327,13 @@
         <v>1</v>
       </c>
       <c r="J220">
-        <v>942</v>
+        <v>776</v>
       </c>
       <c r="K220">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L220">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="M220" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24342,10 +24345,10 @@
         <v>[]</v>
       </c>
       <c r="P220">
-        <v>468</v>
+        <v>195</v>
       </c>
       <c r="Q220">
-        <v>494</v>
+        <v>258</v>
       </c>
       <c r="R220" t="str">
         <v>[1,800]</v>
@@ -24413,7 +24416,7 @@
         <v>90033</v>
       </c>
       <c r="C221" t="str">
-        <v>【变异主宰】费诗-长枪兵 T4</v>
+        <v>【零号病毒】盛曼-长枪兵 T4</v>
       </c>
       <c r="D221">
         <v>3</v>
@@ -24422,7 +24425,7 @@
         <v>20</v>
       </c>
       <c r="F221">
-        <v>3425</v>
+        <v>1479</v>
       </c>
       <c r="G221">
         <v>6</v>
@@ -24434,13 +24437,13 @@
         <v>1</v>
       </c>
       <c r="J221">
-        <v>930</v>
+        <v>1022</v>
       </c>
       <c r="K221">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L221">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="M221" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24452,10 +24455,10 @@
         <v>[]</v>
       </c>
       <c r="P221">
-        <v>477</v>
+        <v>190</v>
       </c>
       <c r="Q221">
-        <v>419</v>
+        <v>244</v>
       </c>
       <c r="R221" t="str">
         <v>[1,800]</v>
@@ -24523,7 +24526,7 @@
         <v>90034</v>
       </c>
       <c r="C222" t="str">
-        <v>【钢铁暴君】盛曼-长枪兵 T4</v>
+        <v>【零号病毒】张任-长枪兵 T4</v>
       </c>
       <c r="D222">
         <v>3</v>
@@ -24532,7 +24535,7 @@
         <v>20</v>
       </c>
       <c r="F222">
-        <v>3803</v>
+        <v>1634</v>
       </c>
       <c r="G222">
         <v>6</v>
@@ -24544,13 +24547,13 @@
         <v>1</v>
       </c>
       <c r="J222">
-        <v>1182</v>
+        <v>1173</v>
       </c>
       <c r="K222">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L222">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="M222" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24562,10 +24565,10 @@
         <v>[]</v>
       </c>
       <c r="P222">
-        <v>477</v>
+        <v>192</v>
       </c>
       <c r="Q222">
-        <v>447</v>
+        <v>228</v>
       </c>
       <c r="R222" t="str">
         <v>[1,800]</v>
@@ -24633,7 +24636,7 @@
         <v>90035</v>
       </c>
       <c r="C223" t="str">
-        <v>【零号病毒】邓芝-法师 T1</v>
+        <v>【末日先兆】刘晔-法师 T1</v>
       </c>
       <c r="D223">
         <v>4</v>
@@ -24642,7 +24645,7 @@
         <v>20</v>
       </c>
       <c r="F223">
-        <v>654</v>
+        <v>317</v>
       </c>
       <c r="G223">
         <v>3</v>
@@ -24654,13 +24657,13 @@
         <v>1</v>
       </c>
       <c r="J223">
-        <v>281</v>
+        <v>240</v>
       </c>
       <c r="K223">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L223">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="M223" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24672,10 +24675,10 @@
         <v>[]</v>
       </c>
       <c r="P223">
-        <v>379</v>
+        <v>152</v>
       </c>
       <c r="Q223">
-        <v>2188</v>
+        <v>1857</v>
       </c>
       <c r="R223" t="str">
         <v>[1,800]</v>
@@ -24743,7 +24746,7 @@
         <v>90036</v>
       </c>
       <c r="C224" t="str">
-        <v>【虚空母体】伊籍-法师 T2</v>
+        <v>【变异主宰】满宠-法师 T2</v>
       </c>
       <c r="D224">
         <v>4</v>
@@ -24752,7 +24755,7 @@
         <v>20</v>
       </c>
       <c r="F224">
-        <v>1081</v>
+        <v>677</v>
       </c>
       <c r="G224">
         <v>4</v>
@@ -24764,13 +24767,13 @@
         <v>1</v>
       </c>
       <c r="J224">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="K224">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="L224">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M224" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24782,10 +24785,10 @@
         <v>[]</v>
       </c>
       <c r="P224">
-        <v>373</v>
+        <v>137</v>
       </c>
       <c r="Q224">
-        <v>2096</v>
+        <v>2051</v>
       </c>
       <c r="R224" t="str">
         <v>[1,800]</v>
@@ -24853,7 +24856,7 @@
         <v>90037</v>
       </c>
       <c r="C225" t="str">
-        <v>【零号病毒】张温-法师 T2</v>
+        <v>【钢铁暴君】虞翻-法师 T2</v>
       </c>
       <c r="D225">
         <v>4</v>
@@ -24862,7 +24865,7 @@
         <v>20</v>
       </c>
       <c r="F225">
-        <v>1010</v>
+        <v>520</v>
       </c>
       <c r="G225">
         <v>4</v>
@@ -24874,13 +24877,13 @@
         <v>1</v>
       </c>
       <c r="J225">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="K225">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L225">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M225" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -24892,10 +24895,10 @@
         <v>[]</v>
       </c>
       <c r="P225">
-        <v>356</v>
+        <v>147</v>
       </c>
       <c r="Q225">
-        <v>1873</v>
+        <v>1852</v>
       </c>
       <c r="R225" t="str">
         <v>[1,800]</v>
@@ -24963,7 +24966,7 @@
         <v>90038</v>
       </c>
       <c r="C226" t="str">
-        <v>【极秘项目】郭嘉-2-法师 T3</v>
+        <v>【钢铁暴君】简雍-2-法师 T3</v>
       </c>
       <c r="D226">
         <v>4</v>
@@ -24972,7 +24975,7 @@
         <v>20</v>
       </c>
       <c r="F226">
-        <v>1608</v>
+        <v>996</v>
       </c>
       <c r="G226">
         <v>5</v>
@@ -24987,10 +24990,10 @@
         <v>622</v>
       </c>
       <c r="K226">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="L226">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M226" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25002,10 +25005,10 @@
         <v>[]</v>
       </c>
       <c r="P226">
-        <v>364</v>
+        <v>139</v>
       </c>
       <c r="Q226">
-        <v>2061</v>
+        <v>1948</v>
       </c>
       <c r="R226" t="str">
         <v>[1,800]</v>
@@ -25073,7 +25076,7 @@
         <v>90039</v>
       </c>
       <c r="C227" t="str">
-        <v>【极秘项目】郑玄-2-法师 T4</v>
+        <v>【零号病毒】杨修-2-法师 T4</v>
       </c>
       <c r="D227">
         <v>4</v>
@@ -25082,7 +25085,7 @@
         <v>20</v>
       </c>
       <c r="F227">
-        <v>1964</v>
+        <v>1333</v>
       </c>
       <c r="G227">
         <v>6</v>
@@ -25094,13 +25097,13 @@
         <v>1</v>
       </c>
       <c r="J227">
-        <v>671</v>
+        <v>827</v>
       </c>
       <c r="K227">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="L227">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="M227" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25112,10 +25115,10 @@
         <v>[]</v>
       </c>
       <c r="P227">
-        <v>371</v>
+        <v>143</v>
       </c>
       <c r="Q227">
-        <v>2101</v>
+        <v>1997</v>
       </c>
       <c r="R227" t="str">
         <v>[1,800]</v>
@@ -25183,7 +25186,7 @@
         <v>90040</v>
       </c>
       <c r="C228" t="str">
-        <v>【末日先兆】田丰-2-法师 T4</v>
+        <v>【极秘项目】糜竺-2-法师 T4</v>
       </c>
       <c r="D228">
         <v>4</v>
@@ -25192,7 +25195,7 @@
         <v>20</v>
       </c>
       <c r="F228">
-        <v>2000</v>
+        <v>1174</v>
       </c>
       <c r="G228">
         <v>6</v>
@@ -25204,13 +25207,13 @@
         <v>1</v>
       </c>
       <c r="J228">
-        <v>666</v>
+        <v>797</v>
       </c>
       <c r="K228">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L228">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M228" t="str">
         <v>[[2,10],[20,15],[40,20],[60,25],[80,30],[100,35],[120,40],[140,45],[160,50],[180,55],[200,60]]</v>
@@ -25222,10 +25225,10 @@
         <v>[]</v>
       </c>
       <c r="P228">
-        <v>363</v>
+        <v>151</v>
       </c>
       <c r="Q228">
-        <v>2047</v>
+        <v>1861</v>
       </c>
       <c r="R228" t="str">
         <v>[1,800]</v>
